--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 44.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 44.xlsx
@@ -526,8 +526,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -570,7 +568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,8 +672,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -705,6 +701,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-337.229</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.31074e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-85.693</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1891677672469068</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7369276951108555</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.646059691506951</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.274137981231705</v>
+      </c>
+      <c r="J2" t="n">
+        <v>43.23998836931862</v>
+      </c>
+      <c r="K2" t="n">
+        <v>88.04074021856752</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 29.232x + -17353.575</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>410.1391862482902</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>12630.45900436312</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.093273558950987e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9999116059118714</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-307.612</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.31092e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-85.965</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1238418258838945</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8256399147447308</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.969801875323515</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.437909316127456</v>
+      </c>
+      <c r="J3" t="n">
+        <v>46.60818918490256</v>
+      </c>
+      <c r="K3" t="n">
+        <v>88.22567557649077</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 32.281x + -18131.169</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>493.9139008458086</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>273699440.7054271</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.666724291889467e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9628264413360366</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-290.1850000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.30923e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-86.087</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2144136583031686</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.124017338721299</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.182837451482748</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.65248513987442</v>
+      </c>
+      <c r="J4" t="n">
+        <v>49.20482039651593</v>
+      </c>
+      <c r="K4" t="n">
+        <v>88.35940401177758</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 34.914x + -19324.755</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>487.9730295432886</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>565722063.336921</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.645372564140362e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9646060326260341</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-279.684</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.30831e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-86.172</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2476273661163117</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.154570546728067</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.053075183255546</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.636362038593727</v>
+      </c>
+      <c r="J5" t="n">
+        <v>51.18873802409495</v>
+      </c>
+      <c r="K5" t="n">
+        <v>88.40748480580964</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 35.969x + -19669.064</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>483.5685848812222</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>34807032.39252497</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.629435086995487e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.965989828461488</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-272.276</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.30732e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-86.23999999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1252804013569031</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.9704399411066609</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.061181387223711</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.636420322434469</v>
+      </c>
+      <c r="J6" t="n">
+        <v>52.94814378168517</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88.4142134505725</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 36.122x + -19500.700</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>479.2088034241564</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>131330757.6997159</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.620041392643991e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9667632488015196</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-267.3969999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.30672e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-86.295</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.09404670860756448</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7812088270480014</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.867572637364046</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.22129298974005</v>
+      </c>
+      <c r="J7" t="n">
+        <v>53.52551061649774</v>
+      </c>
+      <c r="K7" t="n">
+        <v>88.42772692480922</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 36.432x + -19445.721</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>474.9458182087178</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>531346021.4324536</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.611908377862559e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9674692400662943</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-264.516</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.30625e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-86.34</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1228003521305071</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.746298260802548</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.859051873793806</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.695443427447941</v>
+      </c>
+      <c r="J8" t="n">
+        <v>55.01521405872123</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.44136907204947</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 36.751x + -19403.558</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>452.6693174013192</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>19540.95346841798</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.651426516536248e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9999407474072944</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-256.321</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.30557e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-86.38800000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3173440132565482</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.215377711469345</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.049935329264336</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.833846285352921</v>
+      </c>
+      <c r="J9" t="n">
+        <v>56.28781123008387</v>
+      </c>
+      <c r="K9" t="n">
+        <v>88.53736308504917</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 39.164x + -20583.000</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>444.4654801102821</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>19373.55504270451</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.619434150107878e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9999971707143199</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-252.991</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.30502e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-86.435</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1473610650084578</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8975412581101935</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.994539157616666</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.334364118080773</v>
+      </c>
+      <c r="J10" t="n">
+        <v>56.98661826206741</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.51207522436367</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 38.499x + -19986.557</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>463.3826782451251</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>505037849.5341532</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.590784952882569e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9692961082749496</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-250.708</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.30461e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-86.471</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2008111106454332</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.936753940896295</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.022717128860716</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.708103625232501</v>
+      </c>
+      <c r="J11" t="n">
+        <v>58.23754521918063</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.51733126350859</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 38.635x + -19865.090</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>459.8460698803496</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>125205771.326377</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.585200962990779e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9697854849437182</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-247.0309999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.30396e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-86.502</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2182071178662087</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.238854444106783</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.126442471263416</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.769790194419202</v>
+      </c>
+      <c r="J12" t="n">
+        <v>58.78268433913383</v>
+      </c>
+      <c r="K12" t="n">
+        <v>88.56720331537667</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 39.980x + -20438.610</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>456.535593862355</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>30261567.83792722</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.578304503495486e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9703828459429824</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-243.6439999999999</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.30336e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-86.551</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.057203935471222</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.7423998963592601</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.825349951805483</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.749675994406678</v>
+      </c>
+      <c r="J13" t="n">
+        <v>60.55232095585726</v>
+      </c>
+      <c r="K13" t="n">
+        <v>88.52835104804589</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 38.924x + -19658.857</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>453.3252433312804</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>24406528.33733271</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.571142709843805e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9710070636950802</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-239.736</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.30318e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-86.578</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3355118006090689</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.0546286162963</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.963915187534201</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.653681702395809</v>
+      </c>
+      <c r="J14" t="n">
+        <v>60.39003210395629</v>
+      </c>
+      <c r="K14" t="n">
+        <v>88.59559147359067</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 40.789x + -20518.750</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>450.1756658591516</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>368403734.9110797</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.570387008638566e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9710668020018245</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-239.864</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.30283e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-86.607</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.08381697072254403</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.6622663164524278</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.821702201168221</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.598462456042973</v>
+      </c>
+      <c r="J15" t="n">
+        <v>60.93329143749861</v>
+      </c>
+      <c r="K15" t="n">
+        <v>88.54799173466215</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 39.451x + -19610.255</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>390.4033625687773</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>14812.44420648461</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.810943691312676e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9999376930343222</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-234.0529999999999</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.3024e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-86.645</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.208993761671171</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.9838515005265427</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.276315517275626</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.036776084535712</v>
+      </c>
+      <c r="J16" t="n">
+        <v>62.76000087932445</v>
+      </c>
+      <c r="K16" t="n">
+        <v>88.61491352476993</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 41.358x + -20467.670</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>389.6324228856581</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>14696.0377982667</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.92395061491683e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9999099209967212</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-235.574</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.30212e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-86.661</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.05504091268241985</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.813299975779324</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.808545190727474</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.598157774250983</v>
+      </c>
+      <c r="J17" t="n">
+        <v>62.23119011215179</v>
+      </c>
+      <c r="K17" t="n">
+        <v>88.58032367455016</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 40.350x + -19765.597</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>391.6664340667907</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>14606.99948540395</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.821039805761228e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9999809804529132</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-232.062</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.302e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-86.70099999999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.01006198454032868</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.6724467444565766</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.913784081724455</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.619853803284911</v>
+      </c>
+      <c r="J18" t="n">
+        <v>63.74488861182004</v>
+      </c>
+      <c r="K18" t="n">
+        <v>88.56936219810409</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 40.041x + -19426.789</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>437.7563510322282</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>238340325.8260486</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.553730672204273e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9725661161631419</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-226.016</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.30153e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-86.73099999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.3489491391578226</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.14543414556674</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.094766878576161</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.895603469208018</v>
+      </c>
+      <c r="J19" t="n">
+        <v>64.49380423097003</v>
+      </c>
+      <c r="K19" t="n">
+        <v>88.68260999075152</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 43.484x + -21074.705</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>434.6282572127394</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>43203306.43225927</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.548358501799225e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9730434320345782</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-224.78</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.30162e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-86.751</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.4592932571369939</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.262518948695205</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.138603999650732</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.093030726535285</v>
+      </c>
+      <c r="J20" t="n">
+        <v>64.75111926901496</v>
+      </c>
+      <c r="K20" t="n">
+        <v>88.70555660327932</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 44.255x + -21298.445</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>431.5496335866495</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>240533985.6582939</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.547163012132256e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9731733912713522</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-221.1290000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.30124e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-86.788</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.5784393798319761</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.199006056664344</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.584353767217681</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.09893110001336</v>
+      </c>
+      <c r="J21" t="n">
+        <v>66.00820900158939</v>
+      </c>
+      <c r="K21" t="n">
+        <v>88.72506501427763</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 44.933x + -21457.989</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>428.4961588415422</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>118815944.0394076</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.542253843597307e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9736206015581541</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-223.675</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.30106e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-86.80500000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1841589197346305</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.8254539618597847</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.79962785055217</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.64399304451693</v>
+      </c>
+      <c r="J22" t="n">
+        <v>65.09843453295856</v>
+      </c>
+      <c r="K22" t="n">
+        <v>88.64646175454304</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 42.322x + -19936.898</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>425.4542816572644</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>347583200.8772737</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.540041125874781e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9738210209580928</v>
       </c>
     </row>
   </sheetData>
@@ -822,8 +1910,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -866,7 +1952,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,8 +2056,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1001,6 +2085,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-986.109</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.32747e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-82.62</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1361674486368757</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.6951387111463744</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.570732828739516</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.689883408787427</v>
+      </c>
+      <c r="J2" t="n">
+        <v>12.53857835234174</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.15893059983844</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 11.807x + -6573.882</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>384.3381527024216</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>11775.32105460459</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.374093315062157e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9751735203580616</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-722.866</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.30919e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-84.18300000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.532150272004141</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.210418908681541</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.338021988684739</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.062052903139473</v>
+      </c>
+      <c r="J3" t="n">
+        <v>17.44851834549598</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.52053831888745</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 16.447x + -8455.455</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>453.5502752916325</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>744707921.196215</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.905968989159095e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9424682329928887</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-600.921</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.29034e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-84.90900000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2469856326385768</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.055304848843566</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.101027334430435</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.120585401615591</v>
+      </c>
+      <c r="J4" t="n">
+        <v>21.6456801803703</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.11978400360309</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 19.876x + -9966.590</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>446.9128653674636</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>122348596.6650685</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.773423667132198e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9511392247189556</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-524.385</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.27686e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-85.346</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3863131525657775</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.179541527615291</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.289245961809367</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.288325019824794</v>
+      </c>
+      <c r="J5" t="n">
+        <v>25.26169656842603</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.50438817739025</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 22.944x + -11379.843</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>442.1150697035575</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>483107236.94912</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.696845536368017e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9562245000466196</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-476.685</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.26802e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-85.64</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.179374713438361</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8884067456263414</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.078081249393724</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.161591249876211</v>
+      </c>
+      <c r="J6" t="n">
+        <v>28.37953158425153</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.71142443502828</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 25.022x + -12212.472</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>437.4918011690357</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>716242726.0374465</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.646980008581899e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9596925259217173</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-440.562</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.26186e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-85.848</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4169030028191914</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.175918185659689</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.310833883318672</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.230985236751725</v>
+      </c>
+      <c r="J7" t="n">
+        <v>30.95396112776657</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.89546152366736</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 27.213x + -13152.682</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>375.2179786613265</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>14362.51599599425</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.011577568869954e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9991934526489029</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-413.5529999999999</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.25762e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-86.011</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.32157645890788</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.14066606777911</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.150468722718487</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.337236574369384</v>
+      </c>
+      <c r="J8" t="n">
+        <v>33.18990029491716</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.02257435294243</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 28.963x + -13825.471</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>376.1330110265083</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>14197.74840955629</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.860080093500697e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9997302702765594</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-394.6850000000001</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.25455e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-86.15000000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.02551731958397743</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.6761551914902059</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.880578455709672</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.8867058155056</v>
+      </c>
+      <c r="J9" t="n">
+        <v>35.21594600656827</v>
+      </c>
+      <c r="K9" t="n">
+        <v>88.07443435814942</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 29.744x + -13944.872</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>423.2257346382985</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>232460446.9736118</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.565866153131764e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9657299414965271</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-375.1689999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.25236e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-86.256</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4566571384644836</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.223104794895522</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.439441831590814</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.561734848174533</v>
+      </c>
+      <c r="J10" t="n">
+        <v>37.00941068948779</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.2036612326601</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 31.885x + -14845.972</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>418.5699821633839</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>114807163.3957939</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.549818680972762e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9670550345576974</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-359.9040000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.2505e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-86.35599999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4441617951607826</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.303725084715581</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.47961051565611</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.853929146596404</v>
+      </c>
+      <c r="J11" t="n">
+        <v>38.77297714531522</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.28161213153919</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 33.333x + -15346.097</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>414.1299460976634</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>451825689.7642848</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.536131569002642e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9681813411110219</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +2618,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,8 +2722,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1149,6 +2751,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-635.5000000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.30706e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-84.178</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.34997300561733</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.068307750939603</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.107521643482996</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.855595614588376</v>
+      </c>
+      <c r="J2" t="n">
+        <v>20.61445383534398</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.86144946380473</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 18.237x + -11143.104</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>417.5068185752541</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>12977.65313528089</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.038867498814914e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9998583928630428</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-490.831</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.28327e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-85.096</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3480201929434792</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.122418004165132</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.332426035980133</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.025322765063958</v>
+      </c>
+      <c r="J3" t="n">
+        <v>27.64414288353401</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.58003764361428</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 23.662x + -13751.002</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>508.0667941279152</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>451461944.1884012</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.750376676224168e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.952159472204091</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-425.772</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.27039e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-85.479</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4797119460741948</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.393004009766325</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.665058076893076</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.374769836106637</v>
+      </c>
+      <c r="J4" t="n">
+        <v>32.46834711581667</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.91385601540614</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 27.453x + -15747.414</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>502.6456510843087</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>206166154.7535846</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.678223889175268e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9570167642475148</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-387.563</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.26238e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-85.726</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1509853362372944</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.028815228672975</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.953242640510532</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.623318961829938</v>
+      </c>
+      <c r="J5" t="n">
+        <v>36.19187331902096</v>
+      </c>
+      <c r="K5" t="n">
+        <v>88.05373631179418</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 29.428x + -16627.169</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>498.4396734279157</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>204393482.0758557</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.634445930390748e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.960071266487176</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-360.293</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.25732e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-85.892</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.33539212366313</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.086720055367662</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.923474992936034</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.597600772268267</v>
+      </c>
+      <c r="J6" t="n">
+        <v>39.386628487237</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88.17432383016353</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 31.373x + -17551.889</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>494.0234310620984</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>438625635.8532071</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.606462367255953e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9620840071446448</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-344.453</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.25378e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-86.005</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2050212053430038</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.098739483456608</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.995448201650674</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.628447982528026</v>
+      </c>
+      <c r="J7" t="n">
+        <v>41.5542873515418</v>
+      </c>
+      <c r="K7" t="n">
+        <v>88.25540629771258</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 32.832x + -18173.351</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>489.4728570395134</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>32380417.54701016</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.584815734986672e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9637287600108656</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-332.53</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.25107e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-86.09399999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1863026194483362</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.198981194939213</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.28739097338252</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.37752713498274</v>
+      </c>
+      <c r="J8" t="n">
+        <v>43.72072980697462</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.30606317303224</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 33.814x + -18510.386</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>485.0689837616429</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>531345991.4080034</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.571962671235971e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9646456513848748</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-319.693</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.2493e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-86.17700000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3698680663038392</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.207732489257296</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.357290938704292</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.160520434592018</v>
+      </c>
+      <c r="J9" t="n">
+        <v>45.43859926446282</v>
+      </c>
+      <c r="K9" t="n">
+        <v>88.38564068815192</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 35.482x + -19274.904</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>461.6395463025264</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>19981.87027291454</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.561293990758285e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9999662812709396</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-313.4730000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.2475e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-86.23399999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3186650638850966</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.183238834098437</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.285978271572241</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.84111882406275</v>
+      </c>
+      <c r="J10" t="n">
+        <v>46.26871929486438</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.40788830141688</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 35.978x + -19354.113</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>456.4975233873164</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>19821.06600705465</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.608007004954683e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9997107040280762</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-308.6129999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.24627e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-86.288</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1000187332045756</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9334257235927691</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.178012065861433</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.403926230720264</v>
+      </c>
+      <c r="J11" t="n">
+        <v>47.7987471254273</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.39919616265577</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 35.783x + -19036.106</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>454.1545828518642</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>19700.56225115172</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.618344503575198e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9996017073697221</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-297.4870000000001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.24514e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-86.354</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1979704984502514</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.9459101128129158</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.069024636101454</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.745052116782441</v>
+      </c>
+      <c r="J12" t="n">
+        <v>49.15079237132448</v>
+      </c>
+      <c r="K12" t="n">
+        <v>88.4476791384474</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 36.901x + -19497.407</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>471.1205816293415</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>257051752.1430815</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.531553734385983e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.967899915299149</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-295.8099999999999</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.24428e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-86.38800000000001</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1465717306350811</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.8235232392790938</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.91135430950407</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.788301351993532</v>
+      </c>
+      <c r="J13" t="n">
+        <v>49.90071484780559</v>
+      </c>
+      <c r="K13" t="n">
+        <v>88.44513591150732</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 36.840x + -19293.011</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>468.0741620206001</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>196796592.6595076</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.526117669715226e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9683422125716753</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-294.326</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.24404e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-86.423</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.4575688148383557</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.749847401600178</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.788845591553747</v>
+      </c>
+      <c r="J14" t="n">
+        <v>50.69654843323498</v>
+      </c>
+      <c r="K14" t="n">
+        <v>88.40789809003768</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 35.978x + -18633.703</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>465.1827305649302</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>24933884.25577632</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.518962477579243e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9690302537693788</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-284.7909999999999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.24345e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-86.467</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.2989020923816637</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9949061126661013</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.230222417198598</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4.260751953319771</v>
+      </c>
+      <c r="J15" t="n">
+        <v>52.20507813638782</v>
+      </c>
+      <c r="K15" t="n">
+        <v>88.5112146069895</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 38.476x + -19901.549</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>462.256513666429</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>508127762.911929</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.515884585214217e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9692657220254105</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-281.174</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.24315e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-86.499</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1717064825833105</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.078459478462247</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.222011098371834</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.436703981218254</v>
+      </c>
+      <c r="J16" t="n">
+        <v>52.91428360131394</v>
+      </c>
+      <c r="K16" t="n">
+        <v>88.52840792470087</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 38.926x + -20000.507</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>459.4788567106507</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>29889948.63197297</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.509417738307164e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9698839922952155</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-277.816</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.2423e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-86.52800000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.3425369347413282</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.109439532511245</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.321838790590484</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.13101221015685</v>
+      </c>
+      <c r="J17" t="n">
+        <v>53.06704557050637</v>
+      </c>
+      <c r="K17" t="n">
+        <v>88.56260943717959</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 39.853x + -20360.781</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>456.5584869726523</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>24405148.00093558</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.504166853825801e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9703192114877017</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-274.038</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.24185e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-86.566</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.3901634095448928</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.019409482490878</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.258237197299817</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.486474963116302</v>
+      </c>
+      <c r="J18" t="n">
+        <v>54.36689369533922</v>
+      </c>
+      <c r="K18" t="n">
+        <v>88.56753740361231</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 39.990x + -20263.061</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>453.6618683443547</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>372428787.2463068</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.501992025221879e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9704868570277222</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-268.314</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.24146e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-86.60599999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.4607338224862711</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.061792391589784</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.31994462243097</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.943979187191733</v>
+      </c>
+      <c r="J19" t="n">
+        <v>55.10218724730932</v>
+      </c>
+      <c r="K19" t="n">
+        <v>88.59895201626152</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 40.887x + -20591.792</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>450.8250450737046</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>123559401.376678</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.49664764293655e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9709854369999015</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-266.547</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.24131e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-86.634</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.2308113243613014</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.9916132066949297</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.134387622570785</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.107375136290581</v>
+      </c>
+      <c r="J20" t="n">
+        <v>55.86309720888527</v>
+      </c>
+      <c r="K20" t="n">
+        <v>88.59557787635029</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 40.789x + -20371.843</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>447.9321946077594</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>39584486.3827277</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.491831414766263e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.971460780650405</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-265.449</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.24162e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-86.652</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.3199519294809126</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.008254574876492</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.266414422292578</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.2604254969553</v>
+      </c>
+      <c r="J21" t="n">
+        <v>56.04949379710914</v>
+      </c>
+      <c r="K21" t="n">
+        <v>88.61092415293518</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 41.239x + -20458.402</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>444.9643080183889</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>486018027.4957576</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.491712496362159e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9715150856058709</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-260.703</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.24093e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-86.69499999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1624381050349279</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.952099154792975</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.166182340570337</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.806378148365617</v>
+      </c>
+      <c r="J22" t="n">
+        <v>57.05982317227738</v>
+      </c>
+      <c r="K22" t="n">
+        <v>88.62558245532303</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 41.679x + -20509.685</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>387.491590786557</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>14647.29090377409</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.931470320474982e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9994536368452093</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +3856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,8 +3960,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1297,6 +3989,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-1056.626</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.35515e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-81.949</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1170783647342188</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5059949187078068</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.244073675354597</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.505660756385728</v>
+      </c>
+      <c r="J2" t="n">
+        <v>11.58510910988858</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.62960094989177</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 10.638x + -6318.601</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>401.3409320117067</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>12266.62804113551</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.885917557203309e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9998607934151046</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-811.0740000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.3576e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.504</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1770143049183889</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7288909806375486</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.743827917031706</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.238376637589871</v>
+      </c>
+      <c r="J3" t="n">
+        <v>14.98251882609012</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.91547373847337</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 14.004x + -7267.109</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>461.9684892189916</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>189176154.32179</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.071882196427054e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9354349541119821</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-670.4369999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.33892e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-84.34999999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3774864855725109</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.222253321778176</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.153717627897348</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.949111041390478</v>
+      </c>
+      <c r="J4" t="n">
+        <v>18.53797784322582</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.67284613602878</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 17.201x + -8697.314</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>452.8946722373672</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>247333581.1174081</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.910211725883793e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9455506425615341</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-587.011</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.32242e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-84.872</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2207267044645005</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7850253600324124</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.927979268195397</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.594281116519263</v>
+      </c>
+      <c r="J5" t="n">
+        <v>21.70898147114228</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.07813236585309</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 19.592x + -9727.400</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>448.0721764289243</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>489651655.3091006</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.811749780587644e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9516550946126729</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-529.675</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.31062e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-85.23</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7682043116565506</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.856546614266416</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.507778122344825</v>
+      </c>
+      <c r="J6" t="n">
+        <v>24.55633013016182</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.35690331565235</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 21.662x + -10613.006</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>387.8907264242617</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>14722.57483900916</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.78467925192736e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.999954871514722</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-481.646</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.3019e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-85.489</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6938688356963437</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.535191137175546</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.373345303758873</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.187859866391999</v>
+      </c>
+      <c r="J7" t="n">
+        <v>27.15753613198025</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.6524006523772</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 24.392x + -11939.005</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>387.4882096521496</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>14565.33249140431</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.858273155035598e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9999302783926767</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-449.7590000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.29518e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-85.70099999999999</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4273147365462783</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.164794258278842</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.110231392073239</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.69012131262431</v>
+      </c>
+      <c r="J8" t="n">
+        <v>29.50944106745597</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.77488195674073</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 25.737x + -12399.005</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>435.3280852846409</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1067083309.103381</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.66515963430215e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9612697947300535</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-428.611</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.28996e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-85.848</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0996481150750038</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8816638290681411</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.159627993282163</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.81846214288689</v>
+      </c>
+      <c r="J9" t="n">
+        <v>31.32364688653896</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.86689840153443</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 26.848x + -12770.771</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>431.080079089411</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>236711912.7382494</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.639521466366806e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9630171867253494</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-406.5040000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.28643e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-85.988</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2098674807550704</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8915616150853767</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.883437041723484</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.496889128610654</v>
+      </c>
+      <c r="J10" t="n">
+        <v>33.1771868432983</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.96552851428962</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 28.151x + -13239.069</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>426.9455822466085</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>232797051.4751672</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.617918238474145e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9646142846243742</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-390.01</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.28332e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-86.09699999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2707419140622818</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8057784469185791</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.969836104905034</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.531162463444806</v>
+      </c>
+      <c r="J11" t="n">
+        <v>34.79719312026643</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.04529689164828</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 29.300x + -13642.323</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>422.9713898025815</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>460142131.6411566</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.600997412236512e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9658481183341294</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +4522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,8 +4626,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1445,6 +4655,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-605.5409999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.3174e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-84.312</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1466560106074055</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7909223270948768</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.834458300235291</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.378101104123332</v>
+      </c>
+      <c r="J2" t="n">
+        <v>21.64528522293118</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.93415724150684</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 18.671x + -11267.543</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>413.6397995909341</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>12855.27665633393</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.063059043963831e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9998594507856552</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-477.905</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.29904e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-85.123</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.005538227187246246</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8767578020637388</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.056940813997742</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.48077490730674</v>
+      </c>
+      <c r="J3" t="n">
+        <v>28.07064347318826</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.57886299883263</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 23.651x + -13623.491</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>504.1080482705274</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>212004258.9676698</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.76960210774205e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.952351491373408</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-418.8009999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.28818e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-85.491</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1084492126329171</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6216246200157268</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.787129843763723</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.417993202758161</v>
+      </c>
+      <c r="J4" t="n">
+        <v>32.79156716416851</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.83651041555267</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 26.470x + -14977.867</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>498.9625108066003</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>205971976.4805169</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.701795515197108e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9570047195353525</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-379.134</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.28102e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-85.702</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5128371948061642</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.270905694763022</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.320494709531284</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.145127283348575</v>
+      </c>
+      <c r="J5" t="n">
+        <v>36.66467659377618</v>
+      </c>
+      <c r="K5" t="n">
+        <v>88.08318252701439</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 29.880x + -16860.743</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>494.8279817347797</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>204276944.4449124</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.662980667773361e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9596698304204523</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-358.9870000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.27721e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-85.84699999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1422573560457784</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.072839873372846</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.155257463792059</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.689192494796274</v>
+      </c>
+      <c r="J6" t="n">
+        <v>39.15116107258653</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88.146135370062</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 30.895x + -17204.992</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>491.1009426238819</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>268276508.0949699</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.638297250791552e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9614932281963975</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-343.6850000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.27421e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-85.94799999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3380801083358004</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.101765365166823</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.186822727042977</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.972537064581535</v>
+      </c>
+      <c r="J7" t="n">
+        <v>41.36042981173465</v>
+      </c>
+      <c r="K7" t="n">
+        <v>88.22461016538058</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 32.262x + -17826.127</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>487.5097976123487</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>266696322.562239</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.620722230722741e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9627793078413682</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-334.998</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.27209e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-86.026</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.07073546241606062</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7628891307913273</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.919110813184661</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.625164154394543</v>
+      </c>
+      <c r="J8" t="n">
+        <v>42.61115366685323</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.22980484370761</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 32.357x + -17662.878</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>483.9257299017522</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>32436991.70759945</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.605428083959634e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9639753032259454</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-323.74</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.27064e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-86.09999999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.10520214565025</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8956999781879786</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.053744069667137</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.642056169251668</v>
+      </c>
+      <c r="J9" t="n">
+        <v>44.38049495350964</v>
+      </c>
+      <c r="K9" t="n">
+        <v>88.28871311541049</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 33.471x + -18142.008</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>480.5746890858928</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>265881309.4744598</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.595987671116799e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.964701457858171</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-316.516</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.26921e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-86.16500000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1293459264094534</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6908941506051539</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.825486447114681</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.554737399297384</v>
+      </c>
+      <c r="J10" t="n">
+        <v>45.70796032381075</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.29553731921057</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 33.605x + -18028.235</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>477.3957378957134</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>39976177.00676858</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.584275984886347e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9656534236131127</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-307.014</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.26801e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-86.223</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1071733257497104</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.794890130587134</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.867954467227979</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.483286109589747</v>
+      </c>
+      <c r="J11" t="n">
+        <v>46.86128319522583</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.35670680541432</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 34.857x + -18594.160</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>474.2632636704056</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>277771317.5458045</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.57690799887126e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9662239069635387</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-299.1220000000001</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.26742e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-86.271</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2706083490681295</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.091031177201525</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.234953854333868</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.763714525688878</v>
+      </c>
+      <c r="J12" t="n">
+        <v>48.18520150771418</v>
+      </c>
+      <c r="K12" t="n">
+        <v>88.42310230508649</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 36.325x + -19294.282</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>452.1065659361487</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>19558.83710782218</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.616303913931211e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9997301300802032</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-294.813</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.26635e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-86.316</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3267298175510797</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.014292689819402</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.134192927024096</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.937175823566062</v>
+      </c>
+      <c r="J13" t="n">
+        <v>49.60921218783606</v>
+      </c>
+      <c r="K13" t="n">
+        <v>88.4329419493239</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 36.554x + -19260.959</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>449.1944204792102</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>19425.52933163869</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.639577318564796e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.999619091970365</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-290.412</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.26562e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-86.355</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3094855945849919</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.068789551178543</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.338753151420487</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4.243791745242246</v>
+      </c>
+      <c r="J14" t="n">
+        <v>50.42886630235844</v>
+      </c>
+      <c r="K14" t="n">
+        <v>88.45874035630399</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 37.166x + -19448.230</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>460.2325273481125</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>38683.00340727783</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.351863288882294e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9999853736984827</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-288.622</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.26515e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-86.39</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.7983451849352146</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.740528127336466</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.255942271477679</v>
+      </c>
+      <c r="J15" t="n">
+        <v>50.34829654686414</v>
+      </c>
+      <c r="K15" t="n">
+        <v>88.41744094016497</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 36.195x + -18725.898</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>462.4229830846041</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>144479826.0997836</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.552128336099687e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9683037781995539</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-284.066</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.2646e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-86.42700000000001</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1279106318375822</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.5754525880817078</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.784440624225103</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.448260582828453</v>
+      </c>
+      <c r="J16" t="n">
+        <v>51.22309445809199</v>
+      </c>
+      <c r="K16" t="n">
+        <v>88.44132740436413</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 36.750x + -18886.941</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>459.5585606628492</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>41238169.75850678</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.545466003043468e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9688979033961977</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-279.795</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.26394e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-86.45699999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.253654714929808</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.022723335436528</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.224548951030416</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.765334561674507</v>
+      </c>
+      <c r="J17" t="n">
+        <v>52.19987647105145</v>
+      </c>
+      <c r="K17" t="n">
+        <v>88.50440518869166</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 38.301x + -19615.421</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>456.6859799976505</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>43460215.46930999</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.540925058369769e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9692702804163457</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-275.567</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.26374e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-86.492</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.2159049786653465</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.9761446982641432</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.940968751994782</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.722405636825479</v>
+      </c>
+      <c r="J18" t="n">
+        <v>52.83708057919942</v>
+      </c>
+      <c r="K18" t="n">
+        <v>88.51765224689362</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 38.643x + -19647.010</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>453.8411188632443</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>38460242.22836501</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.536211345540183e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9697153380012947</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-270.004</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.2638e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-86.536</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.2534787236025289</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.9834675489087685</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.268755383824328</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.316719300911866</v>
+      </c>
+      <c r="J19" t="n">
+        <v>54.80611539971656</v>
+      </c>
+      <c r="K19" t="n">
+        <v>88.53705771774206</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 39.156x + -19761.716</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>451.0108621774502</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>21259478.69612383</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.529559385986428e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9703830507537771</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-266.783</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.26328e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-86.56100000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3066626449590391</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.18561329762216</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.338480945484351</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.341233181403069</v>
+      </c>
+      <c r="J20" t="n">
+        <v>55.10881030534473</v>
+      </c>
+      <c r="K20" t="n">
+        <v>88.58152449431284</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 40.384x + -20289.570</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>448.1262092295214</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>490198934.9228548</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.52920920227185e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9703624252895054</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-262.7550000000001</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.2629e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-86.595</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.3668393158147265</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.127873434860789</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.474121194570248</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.076683365692913</v>
+      </c>
+      <c r="J21" t="n">
+        <v>55.83818631662398</v>
+      </c>
+      <c r="K21" t="n">
+        <v>88.59181697158111</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 40.680x + -20282.438</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>445.2077970737978</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>32351444.4834045</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.522644306313298e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9709733423175045</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-262.084</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.26279e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-86.629</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1438473665939159</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.7442005041494888</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.933264284410188</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.81839016743388</v>
+      </c>
+      <c r="J22" t="n">
+        <v>56.5397844351407</v>
+      </c>
+      <c r="K22" t="n">
+        <v>88.54693039657742</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 39.422x + -19417.872</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>387.6326706436827</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>14650.15744522106</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.770970618415128e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9999999992224516</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +5760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,8 +5864,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1593,6 +5893,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-1116.007</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.3844e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-81.483</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.3382322657692987</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.157843625984063</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.422606508382946</v>
+      </c>
+      <c r="J2" t="n">
+        <v>10.68008110400516</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.19640999586274</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 9.839x + -5797.629</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>401.2684479302368</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>12277.19927807831</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.936443436839519e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9999570629799829</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-844.4739999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.37784e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-83.21899999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2654812877297626</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9215643634608963</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.669345070026846</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.068149414999698</v>
+      </c>
+      <c r="J3" t="n">
+        <v>14.11268588153117</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.68961848328014</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 13.267x + -6922.351</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>462.997499506849</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>127063480.6720969</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.152318743749638e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9319402511427759</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-691.444</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.35504e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-84.16500000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4100689592596045</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.298320342097948</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.284799040593863</v>
+      </c>
+      <c r="I4" t="n">
+        <v>4.042781692325867</v>
+      </c>
+      <c r="J4" t="n">
+        <v>17.73830282654147</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.52767524266713</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 16.480x + -8366.976</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>453.5408611539115</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>866894126.9619812</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.963171007952433e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9432320972927444</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-596.24</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.33706e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-84.77800000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.4899967867846697</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.735179536800184</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.193156145591488</v>
+      </c>
+      <c r="J5" t="n">
+        <v>21.1798942205214</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.97704545282109</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 18.936x + -9391.428</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>447.951195547946</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>244803525.546838</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.84725242443577e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.950380062239808</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-527.187</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.32416e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-85.18600000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.141345512817076</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8190931707101601</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.756938166500427</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.386988568805672</v>
+      </c>
+      <c r="J6" t="n">
+        <v>24.36108710288901</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.33710315743693</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 21.501x + -10553.162</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>442.9257617222612</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>856282864.8633318</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.772644914782185e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9551420399356122</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-479.942</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.31483e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-85.47499999999999</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3439401604466351</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8657656126410932</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.875856121602542</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.537895632568991</v>
+      </c>
+      <c r="J7" t="n">
+        <v>27.13202657744137</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.59032332998324</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 23.763x + -11536.429</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>437.7637461364064</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>268724466.0924232</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.720905355363748e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9585553476596684</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-435.574</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.30793e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-85.732</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4604850833243131</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.109914848374851</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.308342263894427</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.920045801734132</v>
+      </c>
+      <c r="J8" t="n">
+        <v>30.35279066342608</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.8143050160608</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 26.201x + -12587.045</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>432.8112250283656</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>480685736.6744587</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.678937175833626e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9615026410472478</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-411.447</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.30247e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-85.902</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2999307877428217</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9800893598861788</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.119079371528126</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.908558183588118</v>
+      </c>
+      <c r="J9" t="n">
+        <v>32.53982992533621</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.9145297638772</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 27.462x + -12987.065</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>427.7116423138801</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>466906241.2131789</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.650264029140633e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9634826176562891</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-388.778</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.29801e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-86.053</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.411238113829507</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9952827532781753</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.028326472117302</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.894566949310097</v>
+      </c>
+      <c r="J10" t="n">
+        <v>34.76397741326362</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.02824320657038</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 29.047x + -13563.960</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>422.8134724267125</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>115514300.6546874</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.624899104186133e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9653207405812123</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-368.522</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.29497e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-86.179</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5134694490528923</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.109108059572474</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.039385633766229</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.713173305765208</v>
+      </c>
+      <c r="J11" t="n">
+        <v>36.67342717835749</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.1294758376914</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 30.620x + -14140.524</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>418.1694107433777</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>228006258.8307897</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.606098128282009e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9667348603860002</v>
       </c>
     </row>
   </sheetData>
@@ -1606,7 +6426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,8 +6530,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1741,6 +6559,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-589.119</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.33147e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-84.33799999999999</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3258577084993483</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9520017987766776</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.855944644003308</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.316435731796127</v>
+      </c>
+      <c r="J2" t="n">
+        <v>21.96761367783734</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.99143406142086</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 19.027x + -11445.014</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>411.4847566371973</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>12805.52047976563</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.019861976126505e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9992221911964151</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-449.7940000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.30999e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-85.217</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3293039216451865</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.033546965194124</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.002769489833849</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.413611935319827</v>
+      </c>
+      <c r="J3" t="n">
+        <v>29.733003271023</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.69798119081817</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 24.876x + -14334.554</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>406.6230085257923</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>12499.71566678819</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.958769300755683e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9998564064757421</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-392.052</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.29836e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-85.58499999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.04455474984218243</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7565947237361847</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.866204306430255</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.614826827480504</v>
+      </c>
+      <c r="J4" t="n">
+        <v>35.2788430528721</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.93297297251844</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 27.707x + -15655.220</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>496.8019119526533</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>38329289.77467448</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.702237719215283e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9581560383515961</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-350.797</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.29139e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-85.819</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4013141461522192</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.107291610322234</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.302745424725117</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.608208940133158</v>
+      </c>
+      <c r="J5" t="n">
+        <v>39.78538437699773</v>
+      </c>
+      <c r="K5" t="n">
+        <v>88.1673149802655</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 31.253x + -17552.902</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>492.5871603537111</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>206150332.7870738</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.66218556101196e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.96095755194495</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-331.1610000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.28691e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-85.967</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.03479645903504334</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8812153160969424</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.872818297105591</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.67302559839973</v>
+      </c>
+      <c r="J6" t="n">
+        <v>42.98167512642116</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88.20694045728443</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 31.944x + -17665.173</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>488.1433242255991</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>533020840.2533325</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.636272364173152e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9628296080854974</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-313.47</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.2844e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-86.069</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3528049734544864</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.165020149584014</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.21839936886128</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.66548990642041</v>
+      </c>
+      <c r="J7" t="n">
+        <v>45.31578484970868</v>
+      </c>
+      <c r="K7" t="n">
+        <v>88.34535717654239</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 34.618x + -19045.017</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>483.708953156379</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>528397900.0558928</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.619029547129035e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9641508311391753</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-306.149</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.28249e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-86.137</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.272422507264124</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.309936203944573</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.236105257702661</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.210769440082148</v>
+      </c>
+      <c r="J8" t="n">
+        <v>46.91691415303764</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.36962109374078</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 35.133x + -19086.189</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>479.120900958271</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>27815257.0629561</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.604447601736841e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9653078051009671</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-298.102</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.28111e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-86.21899999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1506620635191318</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8463571645583284</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.967692609759312</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.596630110209516</v>
+      </c>
+      <c r="J9" t="n">
+        <v>48.36515225953097</v>
+      </c>
+      <c r="K9" t="n">
+        <v>88.36376478389015</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 35.007x + -18740.190</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>474.6818010733176</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>209061758.1705164</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.594313289769467e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9661143745270701</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-288.6429999999999</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.2803e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-86.28700000000001</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2225815255348992</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9682392106775048</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.990809095765928</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.619191134727895</v>
+      </c>
+      <c r="J10" t="n">
+        <v>50.35375143179193</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.41430249651171</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 36.124x + -19162.233</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>470.4776566608213</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>376317361.8949968</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.584780816567173e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9669291287786758</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-278.92</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.27948e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-86.35899999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2162050347754862</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.165015622510612</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.012037859329955</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.825982988594146</v>
+      </c>
+      <c r="J11" t="n">
+        <v>52.35326364388573</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.46027909897302</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 37.203x + -19537.476</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>466.3157580589374</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>184502702.3353789</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.574328816867003e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9678495856498377</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-276.6859999999999</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.27892e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-86.398</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.2130842364610746</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.9223338840492973</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.020537080491285</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.87030527589662</v>
+      </c>
+      <c r="J12" t="n">
+        <v>53.17769611302881</v>
+      </c>
+      <c r="K12" t="n">
+        <v>88.45790751371491</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 37.146x + -19293.522</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>462.4596568639181</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>252268722.3131012</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.568592973788237e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9683443735731847</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-270.665</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.27846e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-86.446</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.8189507774767394</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.082851587733845</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.859974788990074</v>
+      </c>
+      <c r="J13" t="n">
+        <v>54.20515290736561</v>
+      </c>
+      <c r="K13" t="n">
+        <v>88.48120916935508</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 37.716x + -19418.176</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>459.0536672754662</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>500444557.5419207</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.56204689521897e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9689315162202172</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-266.7959999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.27794e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-86.485</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1562899414167817</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.9193115289736362</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.038768073066207</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.858321619859296</v>
+      </c>
+      <c r="J14" t="n">
+        <v>55.19783926016496</v>
+      </c>
+      <c r="K14" t="n">
+        <v>88.50555168438382</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 38.330x + -19580.677</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>455.9005693837224</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>20455725.14820769</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.552862953913366e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9697708494781503</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-261.222</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.27743e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-86.523</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3537218889199849</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9495326202037344</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.085128330697852</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.908830738010967</v>
+      </c>
+      <c r="J15" t="n">
+        <v>56.12994823689989</v>
+      </c>
+      <c r="K15" t="n">
+        <v>88.56203744312006</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 39.837x + -20255.006</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>452.9030260230035</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>31005403.79109703</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.548692116930682e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9701243141686168</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-254.509</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.27717e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-86.559</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.7574180232765471</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.407892515069325</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.52556589879231</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4.475928413108665</v>
+      </c>
+      <c r="J16" t="n">
+        <v>57.49036305754034</v>
+      </c>
+      <c r="K16" t="n">
+        <v>88.63150128014676</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 41.860x + -21207.900</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>449.9864692495883</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>63631055.82727703</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.545176062880895e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9704422031000955</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-251.8969999999999</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.27683e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-86.58799999999999</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.5542309681581681</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.422936979236153</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.525252422402946</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.539571968238964</v>
+      </c>
+      <c r="J17" t="n">
+        <v>58.07758416564766</v>
+      </c>
+      <c r="K17" t="n">
+        <v>88.64734493622599</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 42.350x + -21310.610</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>447.16368423153</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>29137634.58581872</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.53973230184615e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9709433624001308</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-248.052</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.27651e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-86.629</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.5209003317724171</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.283280774650653</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.399450948407695</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4.314842577668829</v>
+      </c>
+      <c r="J18" t="n">
+        <v>59.44820497917339</v>
+      </c>
+      <c r="K18" t="n">
+        <v>88.64176660387149</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 42.176x + -21027.092</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>444.3426586010088</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>243619641.034614</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.53662878373613e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9712147003152898</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-247.234</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.27623e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-86.649</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.4068267615120338</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.237068690615623</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.266937673015637</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.345863648322625</v>
+      </c>
+      <c r="J19" t="n">
+        <v>59.41282454077522</v>
+      </c>
+      <c r="K19" t="n">
+        <v>88.6415447618203</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 42.169x + -20863.324</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>382.5665925025276</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>14640.61363609664</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.840020828968935e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9999916004944329</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-247.227</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.27607e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-86.673</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3695311121514252</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.038505783191453</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.271131201469705</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.40071741080645</v>
+      </c>
+      <c r="J20" t="n">
+        <v>59.78483602410884</v>
+      </c>
+      <c r="K20" t="n">
+        <v>88.62503337343971</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 41.663x + -20423.788</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>384.0746943260944</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>14528.86542580894</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.807623170057344e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9999939742079252</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-242.819</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.27591e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-86.708</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2545535526063741</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.120415397779185</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.193693232619549</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.778796737428401</v>
+      </c>
+      <c r="J21" t="n">
+        <v>60.36278398469429</v>
+      </c>
+      <c r="K21" t="n">
+        <v>88.65168799164165</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 42.487x + -20697.076</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>383.3399647353281</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>14444.32641952303</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.830018224121077e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9999761710090245</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-240.8340000000001</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.27573e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-86.736</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.1190667162621253</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.8753615421750344</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.953911778508747</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.734256223231199</v>
+      </c>
+      <c r="J22" t="n">
+        <v>61.13808275216898</v>
+      </c>
+      <c r="K22" t="n">
+        <v>88.63309405342189</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 41.908x + -20228.362</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>384.3909374771277</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>14340.04024074499</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.828160608103209e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9994260817750297</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +7664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,8 +7768,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1889,6 +7797,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-985.4110000000001</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.40223e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-82.286</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.06162012762814157</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.439228780333837</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.195203042418833</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.32066092744001</v>
+      </c>
+      <c r="J2" t="n">
+        <v>12.01798818002055</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.8139623061827</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 11.018x + -6003.296</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>464.9724588880945</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>220306949.1122401</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.374492149744388e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9199419207352918</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-656.3070000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.37618e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-84.377</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1849950104960643</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8423112625826841</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.833908928148588</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.162219921272718</v>
+      </c>
+      <c r="J3" t="n">
+        <v>18.50798644541923</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.62458325486665</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 16.955x + -8212.592</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>434.490743922799</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>237105640.0677775</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.954888243984967e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9462547863971524</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-510.7180000000001</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.35242e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-85.26000000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3405918299855741</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.073089468789402</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.042218242309757</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.574660683794903</v>
+      </c>
+      <c r="J4" t="n">
+        <v>24.60534947919054</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.3890273612713</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 21.929x + -10330.032</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>425.7608775569464</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>348104184.3594183</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.794161866603849e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9565540520001856</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-430.376</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.33778e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-85.744</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.2967348996549194</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.851350060147066</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.893777366735887</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.419631047145218</v>
+      </c>
+      <c r="J5" t="n">
+        <v>30.0053737842962</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.77139012119497</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 25.696x + -11897.868</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>420.4304966360089</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>458055224.3765739</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.710629628121894e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9621202160241172</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-379.626</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.32853e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-86.042</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6226230013620048</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.121965273119605</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.254890971691287</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.926950469623697</v>
+      </c>
+      <c r="J6" t="n">
+        <v>34.62174111700075</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88.03533260284908</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 29.152x + -13355.927</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>397.8913973704734</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>3397.831774943771</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.571162943572849e-06</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.6752791414455797</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-351.289</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.32323e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-86.236</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1877202104371021</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.818183521928777</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.940188897509272</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.589569572338323</v>
+      </c>
+      <c r="J7" t="n">
+        <v>38.06080787104456</v>
+      </c>
+      <c r="K7" t="n">
+        <v>88.13283198947201</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 30.675x + -13800.841</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>410.1174022247833</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>334276082.5770438</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.630213256622675e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9677724451568417</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-326.248</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.31977e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-86.39</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4209796303226168</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.192217601717408</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.251904411361157</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.924028481412031</v>
+      </c>
+      <c r="J8" t="n">
+        <v>41.41661017260304</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.27693489298296</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 33.242x + -14793.300</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>396.2959188826026</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>6346.574506333167</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.356028611338022e-06</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.7879806849877327</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-310.277</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.31771e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-86.495</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.6791812691234488</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.466788809007914</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.400432718480625</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.196222456706882</v>
+      </c>
+      <c r="J9" t="n">
+        <v>43.57931849112421</v>
+      </c>
+      <c r="K9" t="n">
+        <v>88.37610270270885</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 35.273x + -15514.394</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>392.3626232627054</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>5996.277670237979</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>8.64233392790516e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.8106817111585489</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-296.297</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.31646e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-86.59999999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.4905549652338899</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9134199675749795</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.298762745894673</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.896246123998786</v>
+      </c>
+      <c r="J10" t="n">
+        <v>46.25133121667332</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.40072588932526</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 35.817x + -15488.914</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>395.169689835852</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>858168112.426217</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.578396045130931e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9719144384489259</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-284.457</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.31534e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-86.676</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.6496682845579123</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.380142625163894</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.323237249056527</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.385269091674787</v>
+      </c>
+      <c r="J11" t="n">
+        <v>48.12029825382421</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.48310651177644</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 37.763x + -16175.818</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>390.8990093260031</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>106492834.8877234</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.56732814570492e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9728603115912168</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 44.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 44.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -555,6 +555,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-553.0369999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.20671e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-85.027</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2592409025321324</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9470958424594437</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.083809444969338</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.885659123435903</v>
+      </c>
+      <c r="J2" t="n">
+        <v>25.87851946020051</v>
+      </c>
+      <c r="K2" t="n">
+        <v>87.4424278048556</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 22.388x + -13482.989</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-13482.98883291923</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>411.7593169325443</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>553.0369999999999</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.126325610808854e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9935780019390091</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-497.374</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.19954e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-85.34</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2288959382093803</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.059651900100525</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.30958613787316</v>
+      </c>
+      <c r="I3" t="n">
+        <v>4.267012574421083</v>
+      </c>
+      <c r="J3" t="n">
+        <v>29.24786619718802</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.6983490486076</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 24.880x + -14754.478</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-14754.47805260957</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>408.4420714575168</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>497.374</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.70928386553016e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9531955260823682</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-459.6539999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.19583e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-85.55200000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2820303004677656</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.127764399325045</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.561763980526628</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.914912258458589</v>
+      </c>
+      <c r="J4" t="n">
+        <v>31.78288735280085</v>
+      </c>
+      <c r="K4" t="n">
+        <v>87.8781563271466</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 26.990x + -15805.612</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-15805.6122655137</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>508.2532943336094</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>459.6539999999999</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.587258504028678e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9562218307784481</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-431.9299999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.19433e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-85.705</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.617726263216971</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.466357826862079</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.43325503512701</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.723863567195568</v>
+      </c>
+      <c r="J5" t="n">
+        <v>34.05395567057716</v>
+      </c>
+      <c r="K5" t="n">
+        <v>88.01088500171414</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 28.793x + -16662.248</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-16662.24750039758</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>502.7470326817317</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>431.9299999999999</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.564040085131281e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9582697792751641</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-419.816</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.19324e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-85.821</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.08341713720714644</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6927304569214585</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.719033824937099</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.390682883751945</v>
+      </c>
+      <c r="J6" t="n">
+        <v>35.25600591313493</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88.00346802386724</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 28.686x + -16250.757</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-16250.75718620393</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>497.3203805432613</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>419.816</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.546538643246325e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9598706068651358</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-397.246</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.19321e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-85.932</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4477101144131692</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.21157984861598</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.488766060222591</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4.528723460939269</v>
+      </c>
+      <c r="J7" t="n">
+        <v>37.47266828665983</v>
+      </c>
+      <c r="K7" t="n">
+        <v>88.14003333900527</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 30.794x + -17312.657</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-17312.65688873198</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>492.1355905401169</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>397.246</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.531511706728881e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9613525716706356</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-384.735</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.19347e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-86.023</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2192703842532396</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8899690075623548</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.33330608949918</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.352120064226918</v>
+      </c>
+      <c r="J8" t="n">
+        <v>38.91708004599719</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.17364051126479</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 31.361x + -17370.873</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-17370.87342789974</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>487.1860973437121</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>384.735</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.519242541262174e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9626157026254559</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-378.247</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.19379e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-86.107</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.293677663963487</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.295911837183952</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.970807334557848</v>
+      </c>
+      <c r="J9" t="n">
+        <v>39.61543225940728</v>
+      </c>
+      <c r="K9" t="n">
+        <v>88.10651301461166</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 30.248x + -16398.229</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-16398.22928104388</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>482.430855581866</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>378.247</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.506891132876705e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9639062228131657</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-359.98</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.19423e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-86.176</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2999328747787245</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.175056750453406</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.238146360464952</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.557186703779543</v>
+      </c>
+      <c r="J10" t="n">
+        <v>41.70704608956122</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.28540654790196</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 33.407x + -18104.561</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-18104.56078389052</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>455.381417439908</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>359.98</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.520922072394433e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9999371831637335</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-353.0020000000001</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.19487e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-86.23</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.211663794161916</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.000507544959648</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.352497966147505</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.335805436043651</v>
+      </c>
+      <c r="J11" t="n">
+        <v>42.49744099667571</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.31519116606668</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 33.997x + -18220.442</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-18220.44189905057</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>450.053664539966</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>353.0020000000001</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.562523329086697e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9997907550928897</v>
       </c>
     </row>
   </sheetData>
@@ -674,12 +1194,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -689,7 +1209,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -734,19 +1254,19 @@
       <c r="K2" t="n">
         <v>88.04074021856752</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 29.232x + -17353.575</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-17353.57524213114</v>
       </c>
       <c r="Y2" t="n">
         <v>410.1391862482902</v>
       </c>
       <c r="Z2" t="n">
-        <v>12630.45900436312</v>
+        <v>337.229</v>
       </c>
       <c r="AA2" t="n">
         <v>2.093273558950987e-07</v>
@@ -786,19 +1306,19 @@
       <c r="K3" t="n">
         <v>88.22567557649077</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 32.281x + -18131.169</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-18131.16864417374</v>
       </c>
       <c r="Y3" t="n">
         <v>493.9139008458086</v>
       </c>
       <c r="Z3" t="n">
-        <v>273699440.7054271</v>
+        <v>307.612</v>
       </c>
       <c r="AA3" t="n">
         <v>1.666724291889467e-07</v>
@@ -838,19 +1358,19 @@
       <c r="K4" t="n">
         <v>88.35940401177758</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 34.914x + -19324.755</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-19324.75488081173</v>
       </c>
       <c r="Y4" t="n">
         <v>487.9730295432886</v>
       </c>
       <c r="Z4" t="n">
-        <v>565722063.336921</v>
+        <v>290.1850000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>1.645372564140362e-07</v>
@@ -890,19 +1410,19 @@
       <c r="K5" t="n">
         <v>88.40748480580964</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 35.969x + -19669.064</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-19669.0640710365</v>
       </c>
       <c r="Y5" t="n">
         <v>483.5685848812222</v>
       </c>
       <c r="Z5" t="n">
-        <v>34807032.39252497</v>
+        <v>279.684</v>
       </c>
       <c r="AA5" t="n">
         <v>1.629435086995487e-07</v>
@@ -942,19 +1462,19 @@
       <c r="K6" t="n">
         <v>88.4142134505725</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 36.122x + -19500.700</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-19500.70018840255</v>
       </c>
       <c r="Y6" t="n">
         <v>479.2088034241564</v>
       </c>
       <c r="Z6" t="n">
-        <v>131330757.6997159</v>
+        <v>272.276</v>
       </c>
       <c r="AA6" t="n">
         <v>1.620041392643991e-07</v>
@@ -994,19 +1514,19 @@
       <c r="K7" t="n">
         <v>88.42772692480922</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 36.432x + -19445.721</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-19445.72062952601</v>
       </c>
       <c r="Y7" t="n">
         <v>474.9458182087178</v>
       </c>
       <c r="Z7" t="n">
-        <v>531346021.4324536</v>
+        <v>267.3969999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>1.611908377862559e-07</v>
@@ -1046,19 +1566,19 @@
       <c r="K8" t="n">
         <v>88.44136907204947</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 36.751x + -19403.558</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-19403.55810838039</v>
       </c>
       <c r="Y8" t="n">
         <v>452.6693174013192</v>
       </c>
       <c r="Z8" t="n">
-        <v>19540.95346841798</v>
+        <v>264.516</v>
       </c>
       <c r="AA8" t="n">
         <v>1.651426516536248e-07</v>
@@ -1098,19 +1618,19 @@
       <c r="K9" t="n">
         <v>88.53736308504917</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 39.164x + -20583.000</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-20583.00029529128</v>
       </c>
       <c r="Y9" t="n">
         <v>444.4654801102821</v>
       </c>
       <c r="Z9" t="n">
-        <v>19373.55504270451</v>
+        <v>256.321</v>
       </c>
       <c r="AA9" t="n">
         <v>1.619434150107878e-07</v>
@@ -1150,19 +1670,19 @@
       <c r="K10" t="n">
         <v>88.51207522436367</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 38.499x + -19986.557</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-19986.55733397512</v>
       </c>
       <c r="Y10" t="n">
         <v>463.3826782451251</v>
       </c>
       <c r="Z10" t="n">
-        <v>505037849.5341532</v>
+        <v>252.991</v>
       </c>
       <c r="AA10" t="n">
         <v>1.590784952882569e-07</v>
@@ -1202,19 +1722,19 @@
       <c r="K11" t="n">
         <v>88.51733126350859</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 38.635x + -19865.090</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-19865.0899368243</v>
       </c>
       <c r="Y11" t="n">
         <v>459.8460698803496</v>
       </c>
       <c r="Z11" t="n">
-        <v>125205771.326377</v>
+        <v>250.708</v>
       </c>
       <c r="AA11" t="n">
         <v>1.585200962990779e-07</v>
@@ -1254,19 +1774,19 @@
       <c r="K12" t="n">
         <v>88.56720331537667</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 39.980x + -20438.610</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-20438.61023290347</v>
       </c>
       <c r="Y12" t="n">
         <v>456.535593862355</v>
       </c>
       <c r="Z12" t="n">
-        <v>30261567.83792722</v>
+        <v>247.0309999999999</v>
       </c>
       <c r="AA12" t="n">
         <v>1.578304503495486e-07</v>
@@ -1306,19 +1826,19 @@
       <c r="K13" t="n">
         <v>88.52835104804589</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 38.924x + -19658.857</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-19658.85723440928</v>
       </c>
       <c r="Y13" t="n">
         <v>453.3252433312804</v>
       </c>
       <c r="Z13" t="n">
-        <v>24406528.33733271</v>
+        <v>243.6439999999999</v>
       </c>
       <c r="AA13" t="n">
         <v>1.571142709843805e-07</v>
@@ -1358,19 +1878,19 @@
       <c r="K14" t="n">
         <v>88.59559147359067</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 40.789x + -20518.750</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-20518.7504317746</v>
       </c>
       <c r="Y14" t="n">
         <v>450.1756658591516</v>
       </c>
       <c r="Z14" t="n">
-        <v>368403734.9110797</v>
+        <v>239.736</v>
       </c>
       <c r="AA14" t="n">
         <v>1.570387008638566e-07</v>
@@ -1410,19 +1930,19 @@
       <c r="K15" t="n">
         <v>88.54799173466215</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 39.451x + -19610.255</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-19610.25467803122</v>
       </c>
       <c r="Y15" t="n">
         <v>390.4033625687773</v>
       </c>
       <c r="Z15" t="n">
-        <v>14812.44420648461</v>
+        <v>239.864</v>
       </c>
       <c r="AA15" t="n">
         <v>1.810943691312676e-07</v>
@@ -1462,19 +1982,19 @@
       <c r="K16" t="n">
         <v>88.61491352476993</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 41.358x + -20467.670</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-20467.66969357239</v>
       </c>
       <c r="Y16" t="n">
         <v>389.6324228856581</v>
       </c>
       <c r="Z16" t="n">
-        <v>14696.0377982667</v>
+        <v>234.0529999999999</v>
       </c>
       <c r="AA16" t="n">
         <v>1.92395061491683e-07</v>
@@ -1514,19 +2034,19 @@
       <c r="K17" t="n">
         <v>88.58032367455016</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 40.350x + -19765.597</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-19765.59665077637</v>
       </c>
       <c r="Y17" t="n">
         <v>391.6664340667907</v>
       </c>
       <c r="Z17" t="n">
-        <v>14606.99948540395</v>
+        <v>235.574</v>
       </c>
       <c r="AA17" t="n">
         <v>1.821039805761228e-07</v>
@@ -1566,19 +2086,19 @@
       <c r="K18" t="n">
         <v>88.56936219810409</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 40.041x + -19426.789</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-19426.78853111032</v>
       </c>
       <c r="Y18" t="n">
         <v>437.7563510322282</v>
       </c>
       <c r="Z18" t="n">
-        <v>238340325.8260486</v>
+        <v>232.062</v>
       </c>
       <c r="AA18" t="n">
         <v>1.553730672204273e-07</v>
@@ -1618,19 +2138,19 @@
       <c r="K19" t="n">
         <v>88.68260999075152</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 43.484x + -21074.705</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-21074.70458151443</v>
       </c>
       <c r="Y19" t="n">
         <v>434.6282572127394</v>
       </c>
       <c r="Z19" t="n">
-        <v>43203306.43225927</v>
+        <v>226.016</v>
       </c>
       <c r="AA19" t="n">
         <v>1.548358501799225e-07</v>
@@ -1670,19 +2190,19 @@
       <c r="K20" t="n">
         <v>88.70555660327932</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 44.255x + -21298.445</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-21298.44450886489</v>
       </c>
       <c r="Y20" t="n">
         <v>431.5496335866495</v>
       </c>
       <c r="Z20" t="n">
-        <v>240533985.6582939</v>
+        <v>224.78</v>
       </c>
       <c r="AA20" t="n">
         <v>1.547163012132256e-07</v>
@@ -1722,19 +2242,19 @@
       <c r="K21" t="n">
         <v>88.72506501427763</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 44.933x + -21457.989</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-21457.98938338228</v>
       </c>
       <c r="Y21" t="n">
         <v>428.4961588415422</v>
       </c>
       <c r="Z21" t="n">
-        <v>118815944.0394076</v>
+        <v>221.1290000000001</v>
       </c>
       <c r="AA21" t="n">
         <v>1.542253843597307e-07</v>
@@ -1774,19 +2294,19 @@
       <c r="K22" t="n">
         <v>88.64646175454304</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 42.322x + -19936.898</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-19936.89837474209</v>
       </c>
       <c r="Y22" t="n">
         <v>425.4542816572644</v>
       </c>
       <c r="Z22" t="n">
-        <v>347583200.8772737</v>
+        <v>223.675</v>
       </c>
       <c r="AA22" t="n">
         <v>1.540041125874781e-07</v>
@@ -1806,7 +2326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1912,12 +2432,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1927,7 +2447,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1939,6 +2459,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-592.948</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1.25063e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-84.61</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3000083943625262</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.9158886657891948</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.051297540249093</v>
+      </c>
+      <c r="I2" t="n">
+        <v>3.327041424851076</v>
+      </c>
+      <c r="J2" t="n">
+        <v>23.34614256899606</v>
+      </c>
+      <c r="K2" t="n">
+        <v>87.15764732125336</v>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>y = 20.141x + -12416.248</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-12416.24824919289</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>416.7629595657864</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>592.948</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>2.027534594319083e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.9998456956762208</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-461.2750000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1.23272e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-85.401</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3718031353244102</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.150446463190796</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.105665931539575</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.666482707452562</v>
+      </c>
+      <c r="J3" t="n">
+        <v>30.72085962664737</v>
+      </c>
+      <c r="K3" t="n">
+        <v>87.78532861792188</v>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>y = 25.858x + -15186.358</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-15186.3575794681</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>511.2152587891023</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>461.2750000000001</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.65047606081878e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.9549259975515666</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-409.583</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1.22369e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-85.697</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5130646141852944</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.164007022900213</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.356902026301368</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.812946807856191</v>
+      </c>
+      <c r="J4" t="n">
+        <v>35.20072304081879</v>
+      </c>
+      <c r="K4" t="n">
+        <v>88.03366245045362</v>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>y = 29.127x + -16863.785</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-16863.78495476274</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>505.9367732007904</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>409.583</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.5975165127509e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9587661132799178</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-379.999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1.21862e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-85.873</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5440481711753026</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.300054607860941</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.442327180136729</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4.373229128399669</v>
+      </c>
+      <c r="J5" t="n">
+        <v>38.52866075119788</v>
+      </c>
+      <c r="K5" t="n">
+        <v>88.17218214797073</v>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>y = 31.336x + -17961.247</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-17961.24743845963</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>501.6073645736557</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>379.999</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.567713072065792e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9609994784080305</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-364.242</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.21539e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-85.994</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1618090581572138</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.036940590453794</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.273496132321186</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4.30493880081522</v>
+      </c>
+      <c r="J6" t="n">
+        <v>40.92424233450262</v>
+      </c>
+      <c r="K6" t="n">
+        <v>88.20328996725124</v>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>y = 31.879x + -17997.618</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-17997.61842269876</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>497.2754351093973</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>364.242</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1.547601861903376e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9625708344887036</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-347.5880000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>1.21327e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-86.095</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2322641009039744</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.186193344601766</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.310006168819295</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.900509452169649</v>
+      </c>
+      <c r="J7" t="n">
+        <v>42.73237899993157</v>
+      </c>
+      <c r="K7" t="n">
+        <v>88.28718814438813</v>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>y = 33.441x + -18713.218</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-18713.21818627753</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>492.8619727179022</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>347.5880000000001</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.530852102112056e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9639646642554476</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-338.093</v>
+      </c>
+      <c r="D8" t="n">
+        <v>1.21216e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-86.167</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.3722272200796527</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.064072962050821</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.209219656306761</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4.435566180927724</v>
+      </c>
+      <c r="J8" t="n">
+        <v>44.38599647293455</v>
+      </c>
+      <c r="K8" t="n">
+        <v>88.32363446272743</v>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>y = 34.169x + -18898.645</t>
+        </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-18898.64523204229</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>488.3942272544898</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>338.093</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.521024047703086e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.964807304604266</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-330.276</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.21129e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-86.23</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4087745846202038</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.055070454831164</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.195061888764573</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.911996225899578</v>
+      </c>
+      <c r="J9" t="n">
+        <v>45.1429322308387</v>
+      </c>
+      <c r="K9" t="n">
+        <v>88.36763392993825</v>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>y = 35.090x + -19225.256</t>
+        </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-19225.25622158501</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>484.120822323998</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>330.276</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.511903614561794e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9656207271375492</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-326.2660000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.21079e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-86.28</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1400350886607939</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7379697854399586</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.997536108911883</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.745755240794018</v>
+      </c>
+      <c r="J10" t="n">
+        <v>46.09280040956353</v>
+      </c>
+      <c r="K10" t="n">
+        <v>88.34160963739218</v>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>y = 34.539x + -18659.025</t>
+        </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-18659.02516410564</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>463.1183379140412</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>326.2660000000001</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.514960415288417e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9999999910375739</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-317.47</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.21056e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-86.343</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7206889141056847</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.125091127095456</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.895131803872445</v>
+      </c>
+      <c r="J11" t="n">
+        <v>47.57521652007836</v>
+      </c>
+      <c r="K11" t="n">
+        <v>88.38430872173819</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>y = 35.453x + -18979.199</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-18979.19883645495</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>447.4710340674641</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>317.47</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.544921834051245e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9998720592015995</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-314.12</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1.21028e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-86.38800000000001</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.4152602782483014</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.639276292922631</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.319077867050486</v>
+      </c>
+      <c r="J12" t="n">
+        <v>47.9705969226253</v>
+      </c>
+      <c r="K12" t="n">
+        <v>88.35971792468607</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>y = 34.921x + -18468.812</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-18468.81200397372</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>450.809896135095</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>314.12</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.53486678242163e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9999784495102679</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-306.949</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1.21043e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-86.422</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1987081434781723</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.8072135140727715</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.169363442069613</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.727183872848466</v>
+      </c>
+      <c r="J13" t="n">
+        <v>48.93086825827017</v>
+      </c>
+      <c r="K13" t="n">
+        <v>88.45574418417671</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>y = 37.094x + -19566.448</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-19566.44751812772</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>469.4180430424947</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>306.949</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.486442747547208e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9681241025185824</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-303.97</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.21058e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-86.45</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.4021529186021932</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.021582353028955</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.074545426710853</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4.092368856186695</v>
+      </c>
+      <c r="J14" t="n">
+        <v>49.48891371898634</v>
+      </c>
+      <c r="K14" t="n">
+        <v>88.4792489974719</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>y = 37.667x + -19723.256</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-19723.2558422374</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>466.1555757796788</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>303.97</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.481236604844619e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9686812738645403</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-298.276</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1.21044e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-86.494</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.2486247768178571</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.033305322371733</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.163700048807765</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.826135880936663</v>
+      </c>
+      <c r="J15" t="n">
+        <v>50.40206552789888</v>
+      </c>
+      <c r="K15" t="n">
+        <v>88.49929168139049</v>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>y = 38.170x + -19826.422</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-19826.4224640925</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>463.0021897313908</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>298.276</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.47557375829487e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9692500426275285</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-296.371</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1.21072e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-86.518</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.3275684081618971</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.021644997469853</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.288826933864577</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.913387317242083</v>
+      </c>
+      <c r="J16" t="n">
+        <v>50.66712618557644</v>
+      </c>
+      <c r="K16" t="n">
+        <v>88.51103564188456</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>y = 38.472x + -19831.291</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-19831.29149342823</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>459.8739648972207</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>296.371</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.475107914481014e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9693403502596317</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-289.057</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1.21078e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-86.562</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.2219867409237588</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.169840118159426</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.466983994616491</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4.457823184390808</v>
+      </c>
+      <c r="J17" t="n">
+        <v>52.24965849362908</v>
+      </c>
+      <c r="K17" t="n">
+        <v>88.55553570648043</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>y = 39.657x + -20320.008</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-20320.00828788663</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>456.860752762009</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>289.057</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.469994822494576e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9698792964890748</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-291.61</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1.21099e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-86.58199999999999</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.05189449339734914</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.5526090158011652</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.725850722246733</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.36217087547942</v>
+      </c>
+      <c r="J18" t="n">
+        <v>51.66254020830205</v>
+      </c>
+      <c r="K18" t="n">
+        <v>88.48590104804566</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>y = 37.833x + -19124.797</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-19124.79737006264</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>453.9074739756753</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>291.61</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1.465458601378154e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.970382403861018</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-282.7089999999999</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1.21126e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-86.619</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.345839797616567</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.263085181407936</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.348656458485426</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4.501850808431209</v>
+      </c>
+      <c r="J19" t="n">
+        <v>53.38551896821182</v>
+      </c>
+      <c r="K19" t="n">
+        <v>88.58755038149658</v>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>y = 40.557x + -20487.725</t>
+        </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-20487.72512551313</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>450.9131413153963</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>282.7089999999999</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.463834274094101e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9705832143502697</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-282.302</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1.21159e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-86.63800000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.4923295745828308</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.26394536192847</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.536477595217099</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4.177107884469164</v>
+      </c>
+      <c r="J20" t="n">
+        <v>53.31935458482945</v>
+      </c>
+      <c r="K20" t="n">
+        <v>88.59251266954739</v>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>y = 40.700x + -20400.881</t>
+        </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-20400.88055875661</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>447.9520199798416</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>282.302</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.461839679337601e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9708403020313032</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-275.712</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1.21189e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-86.685</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2881277376624667</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.178764676032695</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.422534925743671</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4.68560362374344</v>
+      </c>
+      <c r="J21" t="n">
+        <v>55.24004642700121</v>
+      </c>
+      <c r="K21" t="n">
+        <v>88.60755895712755</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>y = 41.140x + -20450.972</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-20450.9722368486</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>445.0454203031626</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>275.712</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.454227153458093e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9716732193384044</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-282.243</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1.21212e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-86.68000000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.08822780322679714</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.66186518467809</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.813005322637104</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.616948192704309</v>
+      </c>
+      <c r="J22" t="n">
+        <v>53.31111285670836</v>
+      </c>
+      <c r="K22" t="n">
+        <v>88.54159149224458</v>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>y = 39.278x + -19296.229</t>
+        </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-19296.228715192</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>442.0774439788123</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>282.243</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.45726388151133e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9713941597797097</v>
       </c>
     </row>
   </sheetData>
@@ -2058,12 +3670,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2073,7 +3685,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2118,19 +3730,19 @@
       <c r="K2" t="n">
         <v>85.15893059983844</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 11.807x + -6573.882</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-6573.881938216876</v>
       </c>
       <c r="Y2" t="n">
         <v>384.3381527024216</v>
       </c>
       <c r="Z2" t="n">
-        <v>11775.32105460459</v>
+        <v>986.109</v>
       </c>
       <c r="AA2" t="n">
         <v>2.374093315062157e-07</v>
@@ -2170,19 +3782,19 @@
       <c r="K3" t="n">
         <v>86.52053831888745</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 16.447x + -8455.455</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-8455.454687471025</v>
       </c>
       <c r="Y3" t="n">
         <v>453.5502752916325</v>
       </c>
       <c r="Z3" t="n">
-        <v>744707921.196215</v>
+        <v>722.866</v>
       </c>
       <c r="AA3" t="n">
         <v>1.905968989159095e-07</v>
@@ -2222,19 +3834,19 @@
       <c r="K4" t="n">
         <v>87.11978400360309</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 19.876x + -9966.590</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-9966.589926908709</v>
       </c>
       <c r="Y4" t="n">
         <v>446.9128653674636</v>
       </c>
       <c r="Z4" t="n">
-        <v>122348596.6650685</v>
+        <v>600.921</v>
       </c>
       <c r="AA4" t="n">
         <v>1.773423667132198e-07</v>
@@ -2274,19 +3886,19 @@
       <c r="K5" t="n">
         <v>87.50438817739025</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 22.944x + -11379.843</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-11379.84288682476</v>
       </c>
       <c r="Y5" t="n">
         <v>442.1150697035575</v>
       </c>
       <c r="Z5" t="n">
-        <v>483107236.94912</v>
+        <v>524.385</v>
       </c>
       <c r="AA5" t="n">
         <v>1.696845536368017e-07</v>
@@ -2326,19 +3938,19 @@
       <c r="K6" t="n">
         <v>87.71142443502828</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 25.022x + -12212.472</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-12212.47173573682</v>
       </c>
       <c r="Y6" t="n">
         <v>437.4918011690357</v>
       </c>
       <c r="Z6" t="n">
-        <v>716242726.0374465</v>
+        <v>476.685</v>
       </c>
       <c r="AA6" t="n">
         <v>1.646980008581899e-07</v>
@@ -2378,19 +3990,19 @@
       <c r="K7" t="n">
         <v>87.89546152366736</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 27.213x + -13152.682</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-13152.68204207807</v>
       </c>
       <c r="Y7" t="n">
         <v>375.2179786613265</v>
       </c>
       <c r="Z7" t="n">
-        <v>14362.51599599425</v>
+        <v>440.562</v>
       </c>
       <c r="AA7" t="n">
         <v>2.011577568869954e-07</v>
@@ -2430,19 +4042,19 @@
       <c r="K8" t="n">
         <v>88.02257435294243</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 28.963x + -13825.471</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-13825.47071609503</v>
       </c>
       <c r="Y8" t="n">
         <v>376.1330110265083</v>
       </c>
       <c r="Z8" t="n">
-        <v>14197.74840955629</v>
+        <v>413.5529999999999</v>
       </c>
       <c r="AA8" t="n">
         <v>1.860080093500697e-07</v>
@@ -2482,19 +4094,19 @@
       <c r="K9" t="n">
         <v>88.07443435814942</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 29.744x + -13944.872</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-13944.87180468092</v>
       </c>
       <c r="Y9" t="n">
         <v>423.2257346382985</v>
       </c>
       <c r="Z9" t="n">
-        <v>232460446.9736118</v>
+        <v>394.6850000000001</v>
       </c>
       <c r="AA9" t="n">
         <v>1.565866153131764e-07</v>
@@ -2534,19 +4146,19 @@
       <c r="K10" t="n">
         <v>88.2036612326601</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 31.885x + -14845.972</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-14845.97249191081</v>
       </c>
       <c r="Y10" t="n">
         <v>418.5699821633839</v>
       </c>
       <c r="Z10" t="n">
-        <v>114807163.3957939</v>
+        <v>375.1689999999999</v>
       </c>
       <c r="AA10" t="n">
         <v>1.549818680972762e-07</v>
@@ -2586,19 +4198,19 @@
       <c r="K11" t="n">
         <v>88.28161213153919</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 33.333x + -15346.097</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-15346.09664441817</v>
       </c>
       <c r="Y11" t="n">
         <v>414.1299460976634</v>
       </c>
       <c r="Z11" t="n">
-        <v>451825689.7642848</v>
+        <v>359.9040000000001</v>
       </c>
       <c r="AA11" t="n">
         <v>1.536131569002642e-07</v>
@@ -2724,12 +4336,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2739,7 +4351,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2784,19 +4396,19 @@
       <c r="K2" t="n">
         <v>86.86144946380473</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 18.237x + -11143.104</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-11143.10422310316</v>
       </c>
       <c r="Y2" t="n">
         <v>417.5068185752541</v>
       </c>
       <c r="Z2" t="n">
-        <v>12977.65313528089</v>
+        <v>635.5000000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>2.038867498814914e-07</v>
@@ -2836,19 +4448,19 @@
       <c r="K3" t="n">
         <v>87.58003764361428</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 23.662x + -13751.002</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-13751.00150610183</v>
       </c>
       <c r="Y3" t="n">
         <v>508.0667941279152</v>
       </c>
       <c r="Z3" t="n">
-        <v>451461944.1884012</v>
+        <v>490.831</v>
       </c>
       <c r="AA3" t="n">
         <v>1.750376676224168e-07</v>
@@ -2888,19 +4500,19 @@
       <c r="K4" t="n">
         <v>87.91385601540614</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 27.453x + -15747.414</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-15747.41414918185</v>
       </c>
       <c r="Y4" t="n">
         <v>502.6456510843087</v>
       </c>
       <c r="Z4" t="n">
-        <v>206166154.7535846</v>
+        <v>425.772</v>
       </c>
       <c r="AA4" t="n">
         <v>1.678223889175268e-07</v>
@@ -2940,19 +4552,19 @@
       <c r="K5" t="n">
         <v>88.05373631179418</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 29.428x + -16627.169</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-16627.16855542043</v>
       </c>
       <c r="Y5" t="n">
         <v>498.4396734279157</v>
       </c>
       <c r="Z5" t="n">
-        <v>204393482.0758557</v>
+        <v>387.563</v>
       </c>
       <c r="AA5" t="n">
         <v>1.634445930390748e-07</v>
@@ -2992,19 +4604,19 @@
       <c r="K6" t="n">
         <v>88.17432383016353</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 31.373x + -17551.889</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-17551.88878711573</v>
       </c>
       <c r="Y6" t="n">
         <v>494.0234310620984</v>
       </c>
       <c r="Z6" t="n">
-        <v>438625635.8532071</v>
+        <v>360.293</v>
       </c>
       <c r="AA6" t="n">
         <v>1.606462367255953e-07</v>
@@ -3044,19 +4656,19 @@
       <c r="K7" t="n">
         <v>88.25540629771258</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 32.832x + -18173.351</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-18173.35050536688</v>
       </c>
       <c r="Y7" t="n">
         <v>489.4728570395134</v>
       </c>
       <c r="Z7" t="n">
-        <v>32380417.54701016</v>
+        <v>344.453</v>
       </c>
       <c r="AA7" t="n">
         <v>1.584815734986672e-07</v>
@@ -3096,19 +4708,19 @@
       <c r="K8" t="n">
         <v>88.30606317303224</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 33.814x + -18510.386</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-18510.38553921237</v>
       </c>
       <c r="Y8" t="n">
         <v>485.0689837616429</v>
       </c>
       <c r="Z8" t="n">
-        <v>531345991.4080034</v>
+        <v>332.53</v>
       </c>
       <c r="AA8" t="n">
         <v>1.571962671235971e-07</v>
@@ -3148,19 +4760,19 @@
       <c r="K9" t="n">
         <v>88.38564068815192</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 35.482x + -19274.904</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-19274.90352499807</v>
       </c>
       <c r="Y9" t="n">
         <v>461.6395463025264</v>
       </c>
       <c r="Z9" t="n">
-        <v>19981.87027291454</v>
+        <v>319.693</v>
       </c>
       <c r="AA9" t="n">
         <v>1.561293990758285e-07</v>
@@ -3200,19 +4812,19 @@
       <c r="K10" t="n">
         <v>88.40788830141688</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 35.978x + -19354.113</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-19354.11255195818</v>
       </c>
       <c r="Y10" t="n">
         <v>456.4975233873164</v>
       </c>
       <c r="Z10" t="n">
-        <v>19821.06600705465</v>
+        <v>313.4730000000001</v>
       </c>
       <c r="AA10" t="n">
         <v>1.608007004954683e-07</v>
@@ -3252,19 +4864,19 @@
       <c r="K11" t="n">
         <v>88.39919616265577</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 35.783x + -19036.106</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-19036.10569833713</v>
       </c>
       <c r="Y11" t="n">
         <v>454.1545828518642</v>
       </c>
       <c r="Z11" t="n">
-        <v>19700.56225115172</v>
+        <v>308.6129999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>1.618344503575198e-07</v>
@@ -3304,19 +4916,19 @@
       <c r="K12" t="n">
         <v>88.4476791384474</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 36.901x + -19497.407</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-19497.40703510112</v>
       </c>
       <c r="Y12" t="n">
         <v>471.1205816293415</v>
       </c>
       <c r="Z12" t="n">
-        <v>257051752.1430815</v>
+        <v>297.4870000000001</v>
       </c>
       <c r="AA12" t="n">
         <v>1.531553734385983e-07</v>
@@ -3356,19 +4968,19 @@
       <c r="K13" t="n">
         <v>88.44513591150732</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 36.840x + -19293.011</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-19293.01124821303</v>
       </c>
       <c r="Y13" t="n">
         <v>468.0741620206001</v>
       </c>
       <c r="Z13" t="n">
-        <v>196796592.6595076</v>
+        <v>295.8099999999999</v>
       </c>
       <c r="AA13" t="n">
         <v>1.526117669715226e-07</v>
@@ -3408,19 +5020,19 @@
       <c r="K14" t="n">
         <v>88.40789809003768</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 35.978x + -18633.703</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-18633.70275949086</v>
       </c>
       <c r="Y14" t="n">
         <v>465.1827305649302</v>
       </c>
       <c r="Z14" t="n">
-        <v>24933884.25577632</v>
+        <v>294.326</v>
       </c>
       <c r="AA14" t="n">
         <v>1.518962477579243e-07</v>
@@ -3460,19 +5072,19 @@
       <c r="K15" t="n">
         <v>88.5112146069895</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 38.476x + -19901.549</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-19901.54851131805</v>
       </c>
       <c r="Y15" t="n">
         <v>462.256513666429</v>
       </c>
       <c r="Z15" t="n">
-        <v>508127762.911929</v>
+        <v>284.7909999999999</v>
       </c>
       <c r="AA15" t="n">
         <v>1.515884585214217e-07</v>
@@ -3512,19 +5124,19 @@
       <c r="K16" t="n">
         <v>88.52840792470087</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 38.926x + -20000.507</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-20000.50700315995</v>
       </c>
       <c r="Y16" t="n">
         <v>459.4788567106507</v>
       </c>
       <c r="Z16" t="n">
-        <v>29889948.63197297</v>
+        <v>281.174</v>
       </c>
       <c r="AA16" t="n">
         <v>1.509417738307164e-07</v>
@@ -3564,19 +5176,19 @@
       <c r="K17" t="n">
         <v>88.56260943717959</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 39.853x + -20360.781</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-20360.78126008563</v>
       </c>
       <c r="Y17" t="n">
         <v>456.5584869726523</v>
       </c>
       <c r="Z17" t="n">
-        <v>24405148.00093558</v>
+        <v>277.816</v>
       </c>
       <c r="AA17" t="n">
         <v>1.504166853825801e-07</v>
@@ -3616,19 +5228,19 @@
       <c r="K18" t="n">
         <v>88.56753740361231</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 39.990x + -20263.061</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-20263.0610343937</v>
       </c>
       <c r="Y18" t="n">
         <v>453.6618683443547</v>
       </c>
       <c r="Z18" t="n">
-        <v>372428787.2463068</v>
+        <v>274.038</v>
       </c>
       <c r="AA18" t="n">
         <v>1.501992025221879e-07</v>
@@ -3668,19 +5280,19 @@
       <c r="K19" t="n">
         <v>88.59895201626152</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 40.887x + -20591.792</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-20591.79155524877</v>
       </c>
       <c r="Y19" t="n">
         <v>450.8250450737046</v>
       </c>
       <c r="Z19" t="n">
-        <v>123559401.376678</v>
+        <v>268.314</v>
       </c>
       <c r="AA19" t="n">
         <v>1.49664764293655e-07</v>
@@ -3720,19 +5332,19 @@
       <c r="K20" t="n">
         <v>88.59557787635029</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 40.789x + -20371.843</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-20371.84324781778</v>
       </c>
       <c r="Y20" t="n">
         <v>447.9321946077594</v>
       </c>
       <c r="Z20" t="n">
-        <v>39584486.3827277</v>
+        <v>266.547</v>
       </c>
       <c r="AA20" t="n">
         <v>1.491831414766263e-07</v>
@@ -3772,19 +5384,19 @@
       <c r="K21" t="n">
         <v>88.61092415293518</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 41.239x + -20458.402</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-20458.4021150452</v>
       </c>
       <c r="Y21" t="n">
         <v>444.9643080183889</v>
       </c>
       <c r="Z21" t="n">
-        <v>486018027.4957576</v>
+        <v>265.449</v>
       </c>
       <c r="AA21" t="n">
         <v>1.491712496362159e-07</v>
@@ -3824,19 +5436,19 @@
       <c r="K22" t="n">
         <v>88.62558245532303</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 41.679x + -20509.685</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-20509.68482550468</v>
       </c>
       <c r="Y22" t="n">
         <v>387.491590786557</v>
       </c>
       <c r="Z22" t="n">
-        <v>14647.29090377409</v>
+        <v>260.703</v>
       </c>
       <c r="AA22" t="n">
         <v>1.931470320474982e-07</v>
@@ -3962,12 +5574,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3977,7 +5589,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4022,19 +5634,19 @@
       <c r="K2" t="n">
         <v>84.62960094989177</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 10.638x + -6318.601</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-6318.601230315276</v>
       </c>
       <c r="Y2" t="n">
         <v>401.3409320117067</v>
       </c>
       <c r="Z2" t="n">
-        <v>12266.62804113551</v>
+        <v>1056.626</v>
       </c>
       <c r="AA2" t="n">
         <v>1.885917557203309e-07</v>
@@ -4074,19 +5686,19 @@
       <c r="K3" t="n">
         <v>85.91547373847337</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 14.004x + -7267.109</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-7267.108957893212</v>
       </c>
       <c r="Y3" t="n">
         <v>461.9684892189916</v>
       </c>
       <c r="Z3" t="n">
-        <v>189176154.32179</v>
+        <v>811.0740000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>2.071882196427054e-07</v>
@@ -4126,19 +5738,19 @@
       <c r="K4" t="n">
         <v>86.67284613602878</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 17.201x + -8697.314</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-8697.313979497821</v>
       </c>
       <c r="Y4" t="n">
         <v>452.8946722373672</v>
       </c>
       <c r="Z4" t="n">
-        <v>247333581.1174081</v>
+        <v>670.4369999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>1.910211725883793e-07</v>
@@ -4178,19 +5790,19 @@
       <c r="K5" t="n">
         <v>87.07813236585309</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 19.592x + -9727.400</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-9727.399628183486</v>
       </c>
       <c r="Y5" t="n">
         <v>448.0721764289243</v>
       </c>
       <c r="Z5" t="n">
-        <v>489651655.3091006</v>
+        <v>587.011</v>
       </c>
       <c r="AA5" t="n">
         <v>1.811749780587644e-07</v>
@@ -4230,19 +5842,19 @@
       <c r="K6" t="n">
         <v>87.35690331565235</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 21.662x + -10613.006</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-10613.00555506835</v>
       </c>
       <c r="Y6" t="n">
         <v>387.8907264242617</v>
       </c>
       <c r="Z6" t="n">
-        <v>14722.57483900916</v>
+        <v>529.675</v>
       </c>
       <c r="AA6" t="n">
         <v>1.78467925192736e-07</v>
@@ -4282,19 +5894,19 @@
       <c r="K7" t="n">
         <v>87.6524006523772</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 24.392x + -11939.005</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-11939.00536769757</v>
       </c>
       <c r="Y7" t="n">
         <v>387.4882096521496</v>
       </c>
       <c r="Z7" t="n">
-        <v>14565.33249140431</v>
+        <v>481.646</v>
       </c>
       <c r="AA7" t="n">
         <v>1.858273155035598e-07</v>
@@ -4334,19 +5946,19 @@
       <c r="K8" t="n">
         <v>87.77488195674073</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 25.737x + -12399.005</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-12399.00526128336</v>
       </c>
       <c r="Y8" t="n">
         <v>435.3280852846409</v>
       </c>
       <c r="Z8" t="n">
-        <v>1067083309.103381</v>
+        <v>449.7590000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>1.66515963430215e-07</v>
@@ -4386,19 +5998,19 @@
       <c r="K9" t="n">
         <v>87.86689840153443</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 26.848x + -12770.771</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-12770.77070569713</v>
       </c>
       <c r="Y9" t="n">
         <v>431.080079089411</v>
       </c>
       <c r="Z9" t="n">
-        <v>236711912.7382494</v>
+        <v>428.611</v>
       </c>
       <c r="AA9" t="n">
         <v>1.639521466366806e-07</v>
@@ -4438,19 +6050,19 @@
       <c r="K10" t="n">
         <v>87.96552851428962</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 28.151x + -13239.069</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-13239.06867644153</v>
       </c>
       <c r="Y10" t="n">
         <v>426.9455822466085</v>
       </c>
       <c r="Z10" t="n">
-        <v>232797051.4751672</v>
+        <v>406.5040000000001</v>
       </c>
       <c r="AA10" t="n">
         <v>1.617918238474145e-07</v>
@@ -4490,19 +6102,19 @@
       <c r="K11" t="n">
         <v>88.04529689164828</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 29.300x + -13642.323</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-13642.32268949657</v>
       </c>
       <c r="Y11" t="n">
         <v>422.9713898025815</v>
       </c>
       <c r="Z11" t="n">
-        <v>460142131.6411566</v>
+        <v>390.01</v>
       </c>
       <c r="AA11" t="n">
         <v>1.600997412236512e-07</v>
@@ -4628,12 +6240,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4643,7 +6255,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4688,19 +6300,19 @@
       <c r="K2" t="n">
         <v>86.93415724150684</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 18.671x + -11267.543</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-11267.54250541104</v>
       </c>
       <c r="Y2" t="n">
         <v>413.6397995909341</v>
       </c>
       <c r="Z2" t="n">
-        <v>12855.27665633393</v>
+        <v>605.5409999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>2.063059043963831e-07</v>
@@ -4740,19 +6352,19 @@
       <c r="K3" t="n">
         <v>87.57886299883263</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 23.651x + -13623.491</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-13623.49116949148</v>
       </c>
       <c r="Y3" t="n">
         <v>504.1080482705274</v>
       </c>
       <c r="Z3" t="n">
-        <v>212004258.9676698</v>
+        <v>477.905</v>
       </c>
       <c r="AA3" t="n">
         <v>1.76960210774205e-07</v>
@@ -4792,19 +6404,19 @@
       <c r="K4" t="n">
         <v>87.83651041555267</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 26.470x + -14977.867</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-14977.867423515</v>
       </c>
       <c r="Y4" t="n">
         <v>498.9625108066003</v>
       </c>
       <c r="Z4" t="n">
-        <v>205971976.4805169</v>
+        <v>418.8009999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>1.701795515197108e-07</v>
@@ -4844,19 +6456,19 @@
       <c r="K5" t="n">
         <v>88.08318252701439</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 29.880x + -16860.743</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-16860.74281362224</v>
       </c>
       <c r="Y5" t="n">
         <v>494.8279817347797</v>
       </c>
       <c r="Z5" t="n">
-        <v>204276944.4449124</v>
+        <v>379.134</v>
       </c>
       <c r="AA5" t="n">
         <v>1.662980667773361e-07</v>
@@ -4896,19 +6508,19 @@
       <c r="K6" t="n">
         <v>88.146135370062</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 30.895x + -17204.992</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-17204.99234994837</v>
       </c>
       <c r="Y6" t="n">
         <v>491.1009426238819</v>
       </c>
       <c r="Z6" t="n">
-        <v>268276508.0949699</v>
+        <v>358.9870000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>1.638297250791552e-07</v>
@@ -4948,19 +6560,19 @@
       <c r="K7" t="n">
         <v>88.22461016538058</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 32.262x + -17826.127</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-17826.12717549497</v>
       </c>
       <c r="Y7" t="n">
         <v>487.5097976123487</v>
       </c>
       <c r="Z7" t="n">
-        <v>266696322.562239</v>
+        <v>343.6850000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>1.620722230722741e-07</v>
@@ -5000,19 +6612,19 @@
       <c r="K8" t="n">
         <v>88.22980484370761</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 32.357x + -17662.878</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-17662.87811060166</v>
       </c>
       <c r="Y8" t="n">
         <v>483.9257299017522</v>
       </c>
       <c r="Z8" t="n">
-        <v>32436991.70759945</v>
+        <v>334.998</v>
       </c>
       <c r="AA8" t="n">
         <v>1.605428083959634e-07</v>
@@ -5052,19 +6664,19 @@
       <c r="K9" t="n">
         <v>88.28871311541049</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 33.471x + -18142.008</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-18142.0077608619</v>
       </c>
       <c r="Y9" t="n">
         <v>480.5746890858928</v>
       </c>
       <c r="Z9" t="n">
-        <v>265881309.4744598</v>
+        <v>323.74</v>
       </c>
       <c r="AA9" t="n">
         <v>1.595987671116799e-07</v>
@@ -5104,19 +6716,19 @@
       <c r="K10" t="n">
         <v>88.29553731921057</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 33.605x + -18028.235</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-18028.23479334352</v>
       </c>
       <c r="Y10" t="n">
         <v>477.3957378957134</v>
       </c>
       <c r="Z10" t="n">
-        <v>39976177.00676858</v>
+        <v>316.516</v>
       </c>
       <c r="AA10" t="n">
         <v>1.584275984886347e-07</v>
@@ -5156,19 +6768,19 @@
       <c r="K11" t="n">
         <v>88.35670680541432</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 34.857x + -18594.160</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-18594.15966303758</v>
       </c>
       <c r="Y11" t="n">
         <v>474.2632636704056</v>
       </c>
       <c r="Z11" t="n">
-        <v>277771317.5458045</v>
+        <v>307.014</v>
       </c>
       <c r="AA11" t="n">
         <v>1.57690799887126e-07</v>
@@ -5208,19 +6820,19 @@
       <c r="K12" t="n">
         <v>88.42310230508649</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 36.325x + -19294.282</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-19294.28177003079</v>
       </c>
       <c r="Y12" t="n">
         <v>452.1065659361487</v>
       </c>
       <c r="Z12" t="n">
-        <v>19558.83710782218</v>
+        <v>299.1220000000001</v>
       </c>
       <c r="AA12" t="n">
         <v>1.616303913931211e-07</v>
@@ -5260,19 +6872,19 @@
       <c r="K13" t="n">
         <v>88.4329419493239</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 36.554x + -19260.959</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-19260.95894229419</v>
       </c>
       <c r="Y13" t="n">
         <v>449.1944204792102</v>
       </c>
       <c r="Z13" t="n">
-        <v>19425.52933163869</v>
+        <v>294.813</v>
       </c>
       <c r="AA13" t="n">
         <v>1.639577318564796e-07</v>
@@ -5312,19 +6924,19 @@
       <c r="K14" t="n">
         <v>88.45874035630399</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 37.166x + -19448.230</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-19448.23039167188</v>
       </c>
       <c r="Y14" t="n">
         <v>460.2325273481125</v>
       </c>
       <c r="Z14" t="n">
-        <v>38683.00340727783</v>
+        <v>290.412</v>
       </c>
       <c r="AA14" t="n">
         <v>1.351863288882294e-07</v>
@@ -5364,19 +6976,19 @@
       <c r="K15" t="n">
         <v>88.41744094016497</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 36.195x + -18725.898</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-18725.89809953444</v>
       </c>
       <c r="Y15" t="n">
         <v>462.4229830846041</v>
       </c>
       <c r="Z15" t="n">
-        <v>144479826.0997836</v>
+        <v>288.622</v>
       </c>
       <c r="AA15" t="n">
         <v>1.552128336099687e-07</v>
@@ -5416,19 +7028,19 @@
       <c r="K16" t="n">
         <v>88.44132740436413</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 36.750x + -18886.941</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-18886.9408467312</v>
       </c>
       <c r="Y16" t="n">
         <v>459.5585606628492</v>
       </c>
       <c r="Z16" t="n">
-        <v>41238169.75850678</v>
+        <v>284.066</v>
       </c>
       <c r="AA16" t="n">
         <v>1.545466003043468e-07</v>
@@ -5468,19 +7080,19 @@
       <c r="K17" t="n">
         <v>88.50440518869166</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 38.301x + -19615.421</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-19615.42122235966</v>
       </c>
       <c r="Y17" t="n">
         <v>456.6859799976505</v>
       </c>
       <c r="Z17" t="n">
-        <v>43460215.46930999</v>
+        <v>279.795</v>
       </c>
       <c r="AA17" t="n">
         <v>1.540925058369769e-07</v>
@@ -5520,19 +7132,19 @@
       <c r="K18" t="n">
         <v>88.51765224689362</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 38.643x + -19647.010</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-19647.01006491083</v>
       </c>
       <c r="Y18" t="n">
         <v>453.8411188632443</v>
       </c>
       <c r="Z18" t="n">
-        <v>38460242.22836501</v>
+        <v>275.567</v>
       </c>
       <c r="AA18" t="n">
         <v>1.536211345540183e-07</v>
@@ -5572,19 +7184,19 @@
       <c r="K19" t="n">
         <v>88.53705771774206</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 39.156x + -19761.716</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-19761.71601802037</v>
       </c>
       <c r="Y19" t="n">
         <v>451.0108621774502</v>
       </c>
       <c r="Z19" t="n">
-        <v>21259478.69612383</v>
+        <v>270.004</v>
       </c>
       <c r="AA19" t="n">
         <v>1.529559385986428e-07</v>
@@ -5624,19 +7236,19 @@
       <c r="K20" t="n">
         <v>88.58152449431284</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 40.384x + -20289.570</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-20289.56991448857</v>
       </c>
       <c r="Y20" t="n">
         <v>448.1262092295214</v>
       </c>
       <c r="Z20" t="n">
-        <v>490198934.9228548</v>
+        <v>266.783</v>
       </c>
       <c r="AA20" t="n">
         <v>1.52920920227185e-07</v>
@@ -5676,19 +7288,19 @@
       <c r="K21" t="n">
         <v>88.59181697158111</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 40.680x + -20282.438</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-20282.43814255865</v>
       </c>
       <c r="Y21" t="n">
         <v>445.2077970737978</v>
       </c>
       <c r="Z21" t="n">
-        <v>32351444.4834045</v>
+        <v>262.7550000000001</v>
       </c>
       <c r="AA21" t="n">
         <v>1.522644306313298e-07</v>
@@ -5728,19 +7340,19 @@
       <c r="K22" t="n">
         <v>88.54693039657742</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 39.422x + -19417.872</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-19417.87201350284</v>
       </c>
       <c r="Y22" t="n">
         <v>387.6326706436827</v>
       </c>
       <c r="Z22" t="n">
-        <v>14650.15744522106</v>
+        <v>262.084</v>
       </c>
       <c r="AA22" t="n">
         <v>1.770970618415128e-07</v>
@@ -5866,12 +7478,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5881,7 +7493,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -5926,19 +7538,19 @@
       <c r="K2" t="n">
         <v>84.19640999586274</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 9.839x + -5797.629</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5797.629448077008</v>
       </c>
       <c r="Y2" t="n">
         <v>401.2684479302368</v>
       </c>
       <c r="Z2" t="n">
-        <v>12277.19927807831</v>
+        <v>1116.007</v>
       </c>
       <c r="AA2" t="n">
         <v>1.936443436839519e-07</v>
@@ -5978,19 +7590,19 @@
       <c r="K3" t="n">
         <v>85.68961848328014</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 13.267x + -6922.351</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-6922.350553473259</v>
       </c>
       <c r="Y3" t="n">
         <v>462.997499506849</v>
       </c>
       <c r="Z3" t="n">
-        <v>127063480.6720969</v>
+        <v>844.4739999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>2.152318743749638e-07</v>
@@ -6030,19 +7642,19 @@
       <c r="K4" t="n">
         <v>86.52767524266713</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 16.480x + -8366.976</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-8366.976392895383</v>
       </c>
       <c r="Y4" t="n">
         <v>453.5408611539115</v>
       </c>
       <c r="Z4" t="n">
-        <v>866894126.9619812</v>
+        <v>691.444</v>
       </c>
       <c r="AA4" t="n">
         <v>1.963171007952433e-07</v>
@@ -6082,19 +7694,19 @@
       <c r="K5" t="n">
         <v>86.97704545282109</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 18.936x + -9391.428</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-9391.427589237817</v>
       </c>
       <c r="Y5" t="n">
         <v>447.951195547946</v>
       </c>
       <c r="Z5" t="n">
-        <v>244803525.546838</v>
+        <v>596.24</v>
       </c>
       <c r="AA5" t="n">
         <v>1.84725242443577e-07</v>
@@ -6134,19 +7746,19 @@
       <c r="K6" t="n">
         <v>87.33710315743693</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 21.501x + -10553.162</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-10553.16174262014</v>
       </c>
       <c r="Y6" t="n">
         <v>442.9257617222612</v>
       </c>
       <c r="Z6" t="n">
-        <v>856282864.8633318</v>
+        <v>527.187</v>
       </c>
       <c r="AA6" t="n">
         <v>1.772644914782185e-07</v>
@@ -6186,19 +7798,19 @@
       <c r="K7" t="n">
         <v>87.59032332998324</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 23.763x + -11536.429</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-11536.42873129448</v>
       </c>
       <c r="Y7" t="n">
         <v>437.7637461364064</v>
       </c>
       <c r="Z7" t="n">
-        <v>268724466.0924232</v>
+        <v>479.942</v>
       </c>
       <c r="AA7" t="n">
         <v>1.720905355363748e-07</v>
@@ -6238,19 +7850,19 @@
       <c r="K8" t="n">
         <v>87.8143050160608</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 26.201x + -12587.045</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-12587.04489751725</v>
       </c>
       <c r="Y8" t="n">
         <v>432.8112250283656</v>
       </c>
       <c r="Z8" t="n">
-        <v>480685736.6744587</v>
+        <v>435.574</v>
       </c>
       <c r="AA8" t="n">
         <v>1.678937175833626e-07</v>
@@ -6290,19 +7902,19 @@
       <c r="K9" t="n">
         <v>87.9145297638772</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 27.462x + -12987.065</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-12987.06484830528</v>
       </c>
       <c r="Y9" t="n">
         <v>427.7116423138801</v>
       </c>
       <c r="Z9" t="n">
-        <v>466906241.2131789</v>
+        <v>411.447</v>
       </c>
       <c r="AA9" t="n">
         <v>1.650264029140633e-07</v>
@@ -6342,19 +7954,19 @@
       <c r="K10" t="n">
         <v>88.02824320657038</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 29.047x + -13563.960</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-13563.95959294808</v>
       </c>
       <c r="Y10" t="n">
         <v>422.8134724267125</v>
       </c>
       <c r="Z10" t="n">
-        <v>115514300.6546874</v>
+        <v>388.778</v>
       </c>
       <c r="AA10" t="n">
         <v>1.624899104186133e-07</v>
@@ -6394,19 +8006,19 @@
       <c r="K11" t="n">
         <v>88.1294758376914</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 30.620x + -14140.524</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-14140.52357055255</v>
       </c>
       <c r="Y11" t="n">
         <v>418.1694107433777</v>
       </c>
       <c r="Z11" t="n">
-        <v>228006258.8307897</v>
+        <v>368.522</v>
       </c>
       <c r="AA11" t="n">
         <v>1.606098128282009e-07</v>
@@ -6532,12 +8144,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6547,7 +8159,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -6592,19 +8204,19 @@
       <c r="K2" t="n">
         <v>86.99143406142086</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 19.027x + -11445.014</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-11445.01442247303</v>
       </c>
       <c r="Y2" t="n">
         <v>411.4847566371973</v>
       </c>
       <c r="Z2" t="n">
-        <v>12805.52047976563</v>
+        <v>589.119</v>
       </c>
       <c r="AA2" t="n">
         <v>2.019861976126505e-07</v>
@@ -6644,19 +8256,19 @@
       <c r="K3" t="n">
         <v>87.69798119081817</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 24.876x + -14334.554</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-14334.55366853595</v>
       </c>
       <c r="Y3" t="n">
         <v>406.6230085257923</v>
       </c>
       <c r="Z3" t="n">
-        <v>12499.71566678819</v>
+        <v>449.7940000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>1.958769300755683e-07</v>
@@ -6696,19 +8308,19 @@
       <c r="K4" t="n">
         <v>87.93297297251844</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 27.707x + -15655.220</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-15655.2204556749</v>
       </c>
       <c r="Y4" t="n">
         <v>496.8019119526533</v>
       </c>
       <c r="Z4" t="n">
-        <v>38329289.77467448</v>
+        <v>392.052</v>
       </c>
       <c r="AA4" t="n">
         <v>1.702237719215283e-07</v>
@@ -6748,19 +8360,19 @@
       <c r="K5" t="n">
         <v>88.1673149802655</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 31.253x + -17552.902</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-17552.9021772235</v>
       </c>
       <c r="Y5" t="n">
         <v>492.5871603537111</v>
       </c>
       <c r="Z5" t="n">
-        <v>206150332.7870738</v>
+        <v>350.797</v>
       </c>
       <c r="AA5" t="n">
         <v>1.66218556101196e-07</v>
@@ -6800,19 +8412,19 @@
       <c r="K6" t="n">
         <v>88.20694045728443</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 31.944x + -17665.173</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-17665.17301877854</v>
       </c>
       <c r="Y6" t="n">
         <v>488.1433242255991</v>
       </c>
       <c r="Z6" t="n">
-        <v>533020840.2533325</v>
+        <v>331.1610000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>1.636272364173152e-07</v>
@@ -6852,19 +8464,19 @@
       <c r="K7" t="n">
         <v>88.34535717654239</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 34.618x + -19045.017</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-19045.01738430858</v>
       </c>
       <c r="Y7" t="n">
         <v>483.708953156379</v>
       </c>
       <c r="Z7" t="n">
-        <v>528397900.0558928</v>
+        <v>313.47</v>
       </c>
       <c r="AA7" t="n">
         <v>1.619029547129035e-07</v>
@@ -6904,19 +8516,19 @@
       <c r="K8" t="n">
         <v>88.36962109374078</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 35.133x + -19086.189</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-19086.18945467061</v>
       </c>
       <c r="Y8" t="n">
         <v>479.120900958271</v>
       </c>
       <c r="Z8" t="n">
-        <v>27815257.0629561</v>
+        <v>306.149</v>
       </c>
       <c r="AA8" t="n">
         <v>1.604447601736841e-07</v>
@@ -6956,19 +8568,19 @@
       <c r="K9" t="n">
         <v>88.36376478389015</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 35.007x + -18740.190</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-18740.19042748851</v>
       </c>
       <c r="Y9" t="n">
         <v>474.6818010733176</v>
       </c>
       <c r="Z9" t="n">
-        <v>209061758.1705164</v>
+        <v>298.102</v>
       </c>
       <c r="AA9" t="n">
         <v>1.594313289769467e-07</v>
@@ -7008,19 +8620,19 @@
       <c r="K10" t="n">
         <v>88.41430249651171</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 36.124x + -19162.233</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-19162.2325878878</v>
       </c>
       <c r="Y10" t="n">
         <v>470.4776566608213</v>
       </c>
       <c r="Z10" t="n">
-        <v>376317361.8949968</v>
+        <v>288.6429999999999</v>
       </c>
       <c r="AA10" t="n">
         <v>1.584780816567173e-07</v>
@@ -7060,19 +8672,19 @@
       <c r="K11" t="n">
         <v>88.46027909897302</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 37.203x + -19537.476</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-19537.47587190667</v>
       </c>
       <c r="Y11" t="n">
         <v>466.3157580589374</v>
       </c>
       <c r="Z11" t="n">
-        <v>184502702.3353789</v>
+        <v>278.92</v>
       </c>
       <c r="AA11" t="n">
         <v>1.574328816867003e-07</v>
@@ -7112,19 +8724,19 @@
       <c r="K12" t="n">
         <v>88.45790751371491</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 37.146x + -19293.522</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-19293.52170483638</v>
       </c>
       <c r="Y12" t="n">
         <v>462.4596568639181</v>
       </c>
       <c r="Z12" t="n">
-        <v>252268722.3131012</v>
+        <v>276.6859999999999</v>
       </c>
       <c r="AA12" t="n">
         <v>1.568592973788237e-07</v>
@@ -7164,19 +8776,19 @@
       <c r="K13" t="n">
         <v>88.48120916935508</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 37.716x + -19418.176</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-19418.17589975747</v>
       </c>
       <c r="Y13" t="n">
         <v>459.0536672754662</v>
       </c>
       <c r="Z13" t="n">
-        <v>500444557.5419207</v>
+        <v>270.665</v>
       </c>
       <c r="AA13" t="n">
         <v>1.56204689521897e-07</v>
@@ -7216,19 +8828,19 @@
       <c r="K14" t="n">
         <v>88.50555168438382</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 38.330x + -19580.677</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-19580.67726198515</v>
       </c>
       <c r="Y14" t="n">
         <v>455.9005693837224</v>
       </c>
       <c r="Z14" t="n">
-        <v>20455725.14820769</v>
+        <v>266.7959999999999</v>
       </c>
       <c r="AA14" t="n">
         <v>1.552862953913366e-07</v>
@@ -7268,19 +8880,19 @@
       <c r="K15" t="n">
         <v>88.56203744312006</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 39.837x + -20255.006</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-20255.00593051117</v>
       </c>
       <c r="Y15" t="n">
         <v>452.9030260230035</v>
       </c>
       <c r="Z15" t="n">
-        <v>31005403.79109703</v>
+        <v>261.222</v>
       </c>
       <c r="AA15" t="n">
         <v>1.548692116930682e-07</v>
@@ -7320,19 +8932,19 @@
       <c r="K16" t="n">
         <v>88.63150128014676</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 41.860x + -21207.900</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-21207.89974175621</v>
       </c>
       <c r="Y16" t="n">
         <v>449.9864692495883</v>
       </c>
       <c r="Z16" t="n">
-        <v>63631055.82727703</v>
+        <v>254.509</v>
       </c>
       <c r="AA16" t="n">
         <v>1.545176062880895e-07</v>
@@ -7372,19 +8984,19 @@
       <c r="K17" t="n">
         <v>88.64734493622599</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 42.350x + -21310.610</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-21310.61041361716</v>
       </c>
       <c r="Y17" t="n">
         <v>447.16368423153</v>
       </c>
       <c r="Z17" t="n">
-        <v>29137634.58581872</v>
+        <v>251.8969999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>1.53973230184615e-07</v>
@@ -7424,19 +9036,19 @@
       <c r="K18" t="n">
         <v>88.64176660387149</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 42.176x + -21027.092</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-21027.09218341374</v>
       </c>
       <c r="Y18" t="n">
         <v>444.3426586010088</v>
       </c>
       <c r="Z18" t="n">
-        <v>243619641.034614</v>
+        <v>248.052</v>
       </c>
       <c r="AA18" t="n">
         <v>1.53662878373613e-07</v>
@@ -7476,19 +9088,19 @@
       <c r="K19" t="n">
         <v>88.6415447618203</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 42.169x + -20863.324</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-20863.32448287797</v>
       </c>
       <c r="Y19" t="n">
         <v>382.5665925025276</v>
       </c>
       <c r="Z19" t="n">
-        <v>14640.61363609664</v>
+        <v>247.234</v>
       </c>
       <c r="AA19" t="n">
         <v>1.840020828968935e-07</v>
@@ -7528,19 +9140,19 @@
       <c r="K20" t="n">
         <v>88.62503337343971</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 41.663x + -20423.788</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-20423.78777180623</v>
       </c>
       <c r="Y20" t="n">
         <v>384.0746943260944</v>
       </c>
       <c r="Z20" t="n">
-        <v>14528.86542580894</v>
+        <v>247.227</v>
       </c>
       <c r="AA20" t="n">
         <v>1.807623170057344e-07</v>
@@ -7580,19 +9192,19 @@
       <c r="K21" t="n">
         <v>88.65168799164165</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 42.487x + -20697.076</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-20697.07563756706</v>
       </c>
       <c r="Y21" t="n">
         <v>383.3399647353281</v>
       </c>
       <c r="Z21" t="n">
-        <v>14444.32641952303</v>
+        <v>242.819</v>
       </c>
       <c r="AA21" t="n">
         <v>1.830018224121077e-07</v>
@@ -7632,19 +9244,19 @@
       <c r="K22" t="n">
         <v>88.63309405342189</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 41.908x + -20228.362</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-20228.36187724904</v>
       </c>
       <c r="Y22" t="n">
         <v>384.3909374771277</v>
       </c>
       <c r="Z22" t="n">
-        <v>14340.04024074499</v>
+        <v>240.8340000000001</v>
       </c>
       <c r="AA22" t="n">
         <v>1.828160608103209e-07</v>
@@ -7770,12 +9382,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7785,7 +9397,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -7830,19 +9442,19 @@
       <c r="K2" t="n">
         <v>84.8139623061827</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 11.018x + -6003.296</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-6003.296112035475</v>
       </c>
       <c r="Y2" t="n">
         <v>464.9724588880945</v>
       </c>
       <c r="Z2" t="n">
-        <v>220306949.1122401</v>
+        <v>985.4110000000001</v>
       </c>
       <c r="AA2" t="n">
         <v>2.374492149744388e-07</v>
@@ -7882,19 +9494,19 @@
       <c r="K3" t="n">
         <v>86.62458325486665</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 16.955x + -8212.592</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-8212.592004588181</v>
       </c>
       <c r="Y3" t="n">
         <v>434.490743922799</v>
       </c>
       <c r="Z3" t="n">
-        <v>237105640.0677775</v>
+        <v>656.3070000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>1.954888243984967e-07</v>
@@ -7934,19 +9546,19 @@
       <c r="K4" t="n">
         <v>87.3890273612713</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 21.929x + -10330.032</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-10330.03164878563</v>
       </c>
       <c r="Y4" t="n">
         <v>425.7608775569464</v>
       </c>
       <c r="Z4" t="n">
-        <v>348104184.3594183</v>
+        <v>510.7180000000001</v>
       </c>
       <c r="AA4" t="n">
         <v>1.794161866603849e-07</v>
@@ -7986,19 +9598,19 @@
       <c r="K5" t="n">
         <v>87.77139012119497</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 25.696x + -11897.868</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-11897.86760157973</v>
       </c>
       <c r="Y5" t="n">
         <v>420.4304966360089</v>
       </c>
       <c r="Z5" t="n">
-        <v>458055224.3765739</v>
+        <v>430.376</v>
       </c>
       <c r="AA5" t="n">
         <v>1.710629628121894e-07</v>
@@ -8038,19 +9650,19 @@
       <c r="K6" t="n">
         <v>88.03533260284908</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 29.152x + -13355.927</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-13355.92669654902</v>
       </c>
       <c r="Y6" t="n">
         <v>397.8913973704734</v>
       </c>
       <c r="Z6" t="n">
-        <v>3397.831774943771</v>
+        <v>379.626</v>
       </c>
       <c r="AA6" t="n">
         <v>3.571162943572849e-06</v>
@@ -8090,19 +9702,19 @@
       <c r="K7" t="n">
         <v>88.13283198947201</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 30.675x + -13800.841</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-13800.84145847396</v>
       </c>
       <c r="Y7" t="n">
         <v>410.1174022247833</v>
       </c>
       <c r="Z7" t="n">
-        <v>334276082.5770438</v>
+        <v>351.289</v>
       </c>
       <c r="AA7" t="n">
         <v>1.630213256622675e-07</v>
@@ -8142,19 +9754,19 @@
       <c r="K8" t="n">
         <v>88.27693489298296</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 33.242x + -14793.300</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-14793.3004948806</v>
       </c>
       <c r="Y8" t="n">
         <v>396.2959188826026</v>
       </c>
       <c r="Z8" t="n">
-        <v>6346.574506333167</v>
+        <v>326.248</v>
       </c>
       <c r="AA8" t="n">
         <v>1.356028611338022e-06</v>
@@ -8194,19 +9806,19 @@
       <c r="K9" t="n">
         <v>88.37610270270885</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 35.273x + -15514.394</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-15514.39383203477</v>
       </c>
       <c r="Y9" t="n">
         <v>392.3626232627054</v>
       </c>
       <c r="Z9" t="n">
-        <v>5996.277670237979</v>
+        <v>310.277</v>
       </c>
       <c r="AA9" t="n">
         <v>8.64233392790516e-07</v>
@@ -8246,19 +9858,19 @@
       <c r="K10" t="n">
         <v>88.40072588932526</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 35.817x + -15488.914</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-15488.91399378103</v>
       </c>
       <c r="Y10" t="n">
         <v>395.169689835852</v>
       </c>
       <c r="Z10" t="n">
-        <v>858168112.426217</v>
+        <v>296.297</v>
       </c>
       <c r="AA10" t="n">
         <v>1.578396045130931e-07</v>
@@ -8298,19 +9910,19 @@
       <c r="K11" t="n">
         <v>88.48310651177644</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 37.763x + -16175.818</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-16175.81827169919</v>
       </c>
       <c r="Y11" t="n">
         <v>390.8990093260031</v>
       </c>
       <c r="Z11" t="n">
-        <v>106492834.8877234</v>
+        <v>284.457</v>
       </c>
       <c r="AA11" t="n">
         <v>1.56732814570492e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 44.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 44.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -588,10 +588,8 @@
       <c r="K2" t="n">
         <v>87.4424278048556</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 22.388x + -13482.989</t>
-        </is>
+      <c r="W2" t="n">
+        <v>22.38752812102091</v>
       </c>
       <c r="X2" t="n">
         <v>-13482.98883291923</v>
@@ -600,7 +598,7 @@
         <v>411.7593169325443</v>
       </c>
       <c r="Z2" t="n">
-        <v>553.0369999999999</v>
+        <v>12996.38220382945</v>
       </c>
       <c r="AA2" t="n">
         <v>2.126325610808854e-07</v>
@@ -640,10 +638,8 @@
       <c r="K3" t="n">
         <v>87.6983490486076</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 24.880x + -14754.478</t>
-        </is>
+      <c r="W3" t="n">
+        <v>24.87994801800321</v>
       </c>
       <c r="X3" t="n">
         <v>-14754.47805260957</v>
@@ -652,7 +648,7 @@
         <v>408.4420714575168</v>
       </c>
       <c r="Z3" t="n">
-        <v>497.374</v>
+        <v>12831.97957776769</v>
       </c>
       <c r="AA3" t="n">
         <v>2.70928386553016e-07</v>
@@ -692,10 +688,8 @@
       <c r="K4" t="n">
         <v>87.8781563271466</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 26.990x + -15805.612</t>
-        </is>
+      <c r="W4" t="n">
+        <v>26.9904823777094</v>
       </c>
       <c r="X4" t="n">
         <v>-15805.6122655137</v>
@@ -704,7 +698,7 @@
         <v>508.2532943336094</v>
       </c>
       <c r="Z4" t="n">
-        <v>459.6539999999999</v>
+        <v>417896320.6781315</v>
       </c>
       <c r="AA4" t="n">
         <v>1.587258504028678e-07</v>
@@ -744,10 +738,8 @@
       <c r="K5" t="n">
         <v>88.01088500171414</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 28.793x + -16662.248</t>
-        </is>
+      <c r="W5" t="n">
+        <v>28.7930860066893</v>
       </c>
       <c r="X5" t="n">
         <v>-16662.24750039758</v>
@@ -756,7 +748,7 @@
         <v>502.7470326817317</v>
       </c>
       <c r="Z5" t="n">
-        <v>431.9299999999999</v>
+        <v>275812126.4245548</v>
       </c>
       <c r="AA5" t="n">
         <v>1.564040085131281e-07</v>
@@ -796,10 +788,8 @@
       <c r="K6" t="n">
         <v>88.00346802386724</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 28.686x + -16250.757</t>
-        </is>
+      <c r="W6" t="n">
+        <v>28.68603553470534</v>
       </c>
       <c r="X6" t="n">
         <v>-16250.75718620393</v>
@@ -808,7 +798,7 @@
         <v>497.3203805432613</v>
       </c>
       <c r="Z6" t="n">
-        <v>419.816</v>
+        <v>440524805.7179161</v>
       </c>
       <c r="AA6" t="n">
         <v>1.546538643246325e-07</v>
@@ -848,10 +838,8 @@
       <c r="K7" t="n">
         <v>88.14003333900527</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 30.794x + -17312.657</t>
-        </is>
+      <c r="W7" t="n">
+        <v>30.79391307633621</v>
       </c>
       <c r="X7" t="n">
         <v>-17312.65688873198</v>
@@ -860,7 +848,7 @@
         <v>492.1355905401169</v>
       </c>
       <c r="Z7" t="n">
-        <v>397.246</v>
+        <v>268873143.2274749</v>
       </c>
       <c r="AA7" t="n">
         <v>1.531511706728881e-07</v>
@@ -900,10 +888,8 @@
       <c r="K8" t="n">
         <v>88.17364051126479</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 31.361x + -17370.873</t>
-        </is>
+      <c r="W8" t="n">
+        <v>31.36095214640958</v>
       </c>
       <c r="X8" t="n">
         <v>-17370.87342789974</v>
@@ -912,7 +898,7 @@
         <v>487.1860973437121</v>
       </c>
       <c r="Z8" t="n">
-        <v>384.735</v>
+        <v>136545608.480812</v>
       </c>
       <c r="AA8" t="n">
         <v>1.519242541262174e-07</v>
@@ -952,10 +938,8 @@
       <c r="K9" t="n">
         <v>88.10651301461166</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 30.248x + -16398.229</t>
-        </is>
+      <c r="W9" t="n">
+        <v>30.24838303471771</v>
       </c>
       <c r="X9" t="n">
         <v>-16398.22928104388</v>
@@ -964,7 +948,7 @@
         <v>482.430855581866</v>
       </c>
       <c r="Z9" t="n">
-        <v>378.247</v>
+        <v>31925202.95289881</v>
       </c>
       <c r="AA9" t="n">
         <v>1.506891132876705e-07</v>
@@ -1004,10 +988,8 @@
       <c r="K10" t="n">
         <v>88.28540654790196</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 33.407x + -18104.561</t>
-        </is>
+      <c r="W10" t="n">
+        <v>33.40656362594859</v>
       </c>
       <c r="X10" t="n">
         <v>-18104.56078389052</v>
@@ -1016,7 +998,7 @@
         <v>455.381417439908</v>
       </c>
       <c r="Z10" t="n">
-        <v>359.98</v>
+        <v>19846.0964544713</v>
       </c>
       <c r="AA10" t="n">
         <v>1.520922072394433e-07</v>
@@ -1056,10 +1038,8 @@
       <c r="K11" t="n">
         <v>88.31519116606668</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 33.997x + -18220.442</t>
-        </is>
+      <c r="W11" t="n">
+        <v>33.99748577623005</v>
       </c>
       <c r="X11" t="n">
         <v>-18220.44189905057</v>
@@ -1068,7 +1048,7 @@
         <v>450.053664539966</v>
       </c>
       <c r="Z11" t="n">
-        <v>353.0020000000001</v>
+        <v>19670.14489609735</v>
       </c>
       <c r="AA11" t="n">
         <v>1.562523329086697e-07</v>
@@ -1194,12 +1174,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1254,10 +1234,8 @@
       <c r="K2" t="n">
         <v>88.04074021856752</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 29.232x + -17353.575</t>
-        </is>
+      <c r="W2" t="n">
+        <v>29.2321853742016</v>
       </c>
       <c r="X2" t="n">
         <v>-17353.57524213114</v>
@@ -1266,7 +1244,7 @@
         <v>410.1391862482902</v>
       </c>
       <c r="Z2" t="n">
-        <v>337.229</v>
+        <v>12630.45900436312</v>
       </c>
       <c r="AA2" t="n">
         <v>2.093273558950987e-07</v>
@@ -1306,10 +1284,8 @@
       <c r="K3" t="n">
         <v>88.22567557649077</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 32.281x + -18131.169</t>
-        </is>
+      <c r="W3" t="n">
+        <v>32.28127953372072</v>
       </c>
       <c r="X3" t="n">
         <v>-18131.16864417374</v>
@@ -1318,7 +1294,7 @@
         <v>493.9139008458086</v>
       </c>
       <c r="Z3" t="n">
-        <v>307.612</v>
+        <v>273699440.7054271</v>
       </c>
       <c r="AA3" t="n">
         <v>1.666724291889467e-07</v>
@@ -1358,10 +1334,8 @@
       <c r="K4" t="n">
         <v>88.35940401177758</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 34.914x + -19324.755</t>
-        </is>
+      <c r="W4" t="n">
+        <v>34.91421424587239</v>
       </c>
       <c r="X4" t="n">
         <v>-19324.75488081173</v>
@@ -1370,7 +1344,7 @@
         <v>487.9730295432886</v>
       </c>
       <c r="Z4" t="n">
-        <v>290.1850000000001</v>
+        <v>565722063.336921</v>
       </c>
       <c r="AA4" t="n">
         <v>1.645372564140362e-07</v>
@@ -1410,10 +1384,8 @@
       <c r="K5" t="n">
         <v>88.40748480580964</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 35.969x + -19669.064</t>
-        </is>
+      <c r="W5" t="n">
+        <v>35.96890284209613</v>
       </c>
       <c r="X5" t="n">
         <v>-19669.0640710365</v>
@@ -1422,7 +1394,7 @@
         <v>483.5685848812222</v>
       </c>
       <c r="Z5" t="n">
-        <v>279.684</v>
+        <v>34807032.39252497</v>
       </c>
       <c r="AA5" t="n">
         <v>1.629435086995487e-07</v>
@@ -1462,10 +1434,8 @@
       <c r="K6" t="n">
         <v>88.4142134505725</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 36.122x + -19500.700</t>
-        </is>
+      <c r="W6" t="n">
+        <v>36.12160081984797</v>
       </c>
       <c r="X6" t="n">
         <v>-19500.70018840255</v>
@@ -1474,7 +1444,7 @@
         <v>479.2088034241564</v>
       </c>
       <c r="Z6" t="n">
-        <v>272.276</v>
+        <v>131330757.6997159</v>
       </c>
       <c r="AA6" t="n">
         <v>1.620041392643991e-07</v>
@@ -1514,10 +1484,8 @@
       <c r="K7" t="n">
         <v>88.42772692480922</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 36.432x + -19445.721</t>
-        </is>
+      <c r="W7" t="n">
+        <v>36.43221901709584</v>
       </c>
       <c r="X7" t="n">
         <v>-19445.72062952601</v>
@@ -1526,7 +1494,7 @@
         <v>474.9458182087178</v>
       </c>
       <c r="Z7" t="n">
-        <v>267.3969999999999</v>
+        <v>531346021.4324536</v>
       </c>
       <c r="AA7" t="n">
         <v>1.611908377862559e-07</v>
@@ -1566,10 +1534,8 @@
       <c r="K8" t="n">
         <v>88.44136907204947</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 36.751x + -19403.558</t>
-        </is>
+      <c r="W8" t="n">
+        <v>36.7512568353227</v>
       </c>
       <c r="X8" t="n">
         <v>-19403.55810838039</v>
@@ -1578,7 +1544,7 @@
         <v>452.6693174013192</v>
       </c>
       <c r="Z8" t="n">
-        <v>264.516</v>
+        <v>19540.95346841798</v>
       </c>
       <c r="AA8" t="n">
         <v>1.651426516536248e-07</v>
@@ -1618,10 +1584,8 @@
       <c r="K9" t="n">
         <v>88.53736308504917</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 39.164x + -20583.000</t>
-        </is>
+      <c r="W9" t="n">
+        <v>39.16442447517871</v>
       </c>
       <c r="X9" t="n">
         <v>-20583.00029529128</v>
@@ -1630,7 +1594,7 @@
         <v>444.4654801102821</v>
       </c>
       <c r="Z9" t="n">
-        <v>256.321</v>
+        <v>19373.55504270451</v>
       </c>
       <c r="AA9" t="n">
         <v>1.619434150107878e-07</v>
@@ -1670,10 +1634,8 @@
       <c r="K10" t="n">
         <v>88.51207522436367</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 38.499x + -19986.557</t>
-        </is>
+      <c r="W10" t="n">
+        <v>38.49851807474564</v>
       </c>
       <c r="X10" t="n">
         <v>-19986.55733397512</v>
@@ -1682,7 +1644,7 @@
         <v>463.3826782451251</v>
       </c>
       <c r="Z10" t="n">
-        <v>252.991</v>
+        <v>505037849.5341532</v>
       </c>
       <c r="AA10" t="n">
         <v>1.590784952882569e-07</v>
@@ -1722,10 +1684,8 @@
       <c r="K11" t="n">
         <v>88.51733126350859</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 38.635x + -19865.090</t>
-        </is>
+      <c r="W11" t="n">
+        <v>38.63505603306751</v>
       </c>
       <c r="X11" t="n">
         <v>-19865.0899368243</v>
@@ -1734,7 +1694,7 @@
         <v>459.8460698803496</v>
       </c>
       <c r="Z11" t="n">
-        <v>250.708</v>
+        <v>125205771.326377</v>
       </c>
       <c r="AA11" t="n">
         <v>1.585200962990779e-07</v>
@@ -1774,10 +1734,8 @@
       <c r="K12" t="n">
         <v>88.56720331537667</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 39.980x + -20438.610</t>
-        </is>
+      <c r="W12" t="n">
+        <v>39.98043567866102</v>
       </c>
       <c r="X12" t="n">
         <v>-20438.61023290347</v>
@@ -1786,7 +1744,7 @@
         <v>456.535593862355</v>
       </c>
       <c r="Z12" t="n">
-        <v>247.0309999999999</v>
+        <v>30261567.83792722</v>
       </c>
       <c r="AA12" t="n">
         <v>1.578304503495486e-07</v>
@@ -1826,10 +1784,8 @@
       <c r="K13" t="n">
         <v>88.52835104804589</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 38.924x + -19658.857</t>
-        </is>
+      <c r="W13" t="n">
+        <v>38.92448607146015</v>
       </c>
       <c r="X13" t="n">
         <v>-19658.85723440928</v>
@@ -1838,7 +1794,7 @@
         <v>453.3252433312804</v>
       </c>
       <c r="Z13" t="n">
-        <v>243.6439999999999</v>
+        <v>24406528.33733271</v>
       </c>
       <c r="AA13" t="n">
         <v>1.571142709843805e-07</v>
@@ -1878,10 +1834,8 @@
       <c r="K14" t="n">
         <v>88.59559147359067</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 40.789x + -20518.750</t>
-        </is>
+      <c r="W14" t="n">
+        <v>40.78891806168746</v>
       </c>
       <c r="X14" t="n">
         <v>-20518.7504317746</v>
@@ -1890,7 +1844,7 @@
         <v>450.1756658591516</v>
       </c>
       <c r="Z14" t="n">
-        <v>239.736</v>
+        <v>368403734.9110797</v>
       </c>
       <c r="AA14" t="n">
         <v>1.570387008638566e-07</v>
@@ -1930,10 +1884,8 @@
       <c r="K15" t="n">
         <v>88.54799173466215</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 39.451x + -19610.255</t>
-        </is>
+      <c r="W15" t="n">
+        <v>39.45123082301276</v>
       </c>
       <c r="X15" t="n">
         <v>-19610.25467803122</v>
@@ -1942,7 +1894,7 @@
         <v>390.4033625687773</v>
       </c>
       <c r="Z15" t="n">
-        <v>239.864</v>
+        <v>14812.44420648461</v>
       </c>
       <c r="AA15" t="n">
         <v>1.810943691312676e-07</v>
@@ -1982,10 +1934,8 @@
       <c r="K16" t="n">
         <v>88.61491352476993</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 41.358x + -20467.670</t>
-        </is>
+      <c r="W16" t="n">
+        <v>41.35815267015276</v>
       </c>
       <c r="X16" t="n">
         <v>-20467.66969357239</v>
@@ -1994,7 +1944,7 @@
         <v>389.6324228856581</v>
       </c>
       <c r="Z16" t="n">
-        <v>234.0529999999999</v>
+        <v>14696.0377982667</v>
       </c>
       <c r="AA16" t="n">
         <v>1.92395061491683e-07</v>
@@ -2034,10 +1984,8 @@
       <c r="K17" t="n">
         <v>88.58032367455016</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 40.350x + -19765.597</t>
-        </is>
+      <c r="W17" t="n">
+        <v>40.35008009489908</v>
       </c>
       <c r="X17" t="n">
         <v>-19765.59665077637</v>
@@ -2046,7 +1994,7 @@
         <v>391.6664340667907</v>
       </c>
       <c r="Z17" t="n">
-        <v>235.574</v>
+        <v>14606.99948540395</v>
       </c>
       <c r="AA17" t="n">
         <v>1.821039805761228e-07</v>
@@ -2086,10 +2034,8 @@
       <c r="K18" t="n">
         <v>88.56936219810409</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 40.041x + -19426.789</t>
-        </is>
+      <c r="W18" t="n">
+        <v>40.04079270212811</v>
       </c>
       <c r="X18" t="n">
         <v>-19426.78853111032</v>
@@ -2098,7 +2044,7 @@
         <v>437.7563510322282</v>
       </c>
       <c r="Z18" t="n">
-        <v>232.062</v>
+        <v>238340325.8260486</v>
       </c>
       <c r="AA18" t="n">
         <v>1.553730672204273e-07</v>
@@ -2138,10 +2084,8 @@
       <c r="K19" t="n">
         <v>88.68260999075152</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 43.484x + -21074.705</t>
-        </is>
+      <c r="W19" t="n">
+        <v>43.48422405642729</v>
       </c>
       <c r="X19" t="n">
         <v>-21074.70458151443</v>
@@ -2150,7 +2094,7 @@
         <v>434.6282572127394</v>
       </c>
       <c r="Z19" t="n">
-        <v>226.016</v>
+        <v>43203306.43225927</v>
       </c>
       <c r="AA19" t="n">
         <v>1.548358501799225e-07</v>
@@ -2190,10 +2134,8 @@
       <c r="K20" t="n">
         <v>88.70555660327932</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 44.255x + -21298.445</t>
-        </is>
+      <c r="W20" t="n">
+        <v>44.25533876230251</v>
       </c>
       <c r="X20" t="n">
         <v>-21298.44450886489</v>
@@ -2202,7 +2144,7 @@
         <v>431.5496335866495</v>
       </c>
       <c r="Z20" t="n">
-        <v>224.78</v>
+        <v>240533985.6582939</v>
       </c>
       <c r="AA20" t="n">
         <v>1.547163012132256e-07</v>
@@ -2242,10 +2184,8 @@
       <c r="K21" t="n">
         <v>88.72506501427763</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 44.933x + -21457.989</t>
-        </is>
+      <c r="W21" t="n">
+        <v>44.93274033895188</v>
       </c>
       <c r="X21" t="n">
         <v>-21457.98938338228</v>
@@ -2254,7 +2194,7 @@
         <v>428.4961588415422</v>
       </c>
       <c r="Z21" t="n">
-        <v>221.1290000000001</v>
+        <v>118815944.0394076</v>
       </c>
       <c r="AA21" t="n">
         <v>1.542253843597307e-07</v>
@@ -2294,10 +2234,8 @@
       <c r="K22" t="n">
         <v>88.64646175454304</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 42.322x + -19936.898</t>
-        </is>
+      <c r="W22" t="n">
+        <v>42.32249866755602</v>
       </c>
       <c r="X22" t="n">
         <v>-19936.89837474209</v>
@@ -2306,7 +2244,7 @@
         <v>425.4542816572644</v>
       </c>
       <c r="Z22" t="n">
-        <v>223.675</v>
+        <v>347583200.8772737</v>
       </c>
       <c r="AA22" t="n">
         <v>1.540041125874781e-07</v>
@@ -2432,12 +2370,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2492,10 +2430,8 @@
       <c r="K2" t="n">
         <v>87.15764732125336</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 20.141x + -12416.248</t>
-        </is>
+      <c r="W2" t="n">
+        <v>20.14133245779954</v>
       </c>
       <c r="X2" t="n">
         <v>-12416.24824919289</v>
@@ -2504,7 +2440,7 @@
         <v>416.7629595657864</v>
       </c>
       <c r="Z2" t="n">
-        <v>592.948</v>
+        <v>13043.37358641603</v>
       </c>
       <c r="AA2" t="n">
         <v>2.027534594319083e-07</v>
@@ -2544,10 +2480,8 @@
       <c r="K3" t="n">
         <v>87.78532861792188</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 25.858x + -15186.358</t>
-        </is>
+      <c r="W3" t="n">
+        <v>25.85812158977623</v>
       </c>
       <c r="X3" t="n">
         <v>-15186.3575794681</v>
@@ -2556,7 +2490,7 @@
         <v>511.2152587891023</v>
       </c>
       <c r="Z3" t="n">
-        <v>461.2750000000001</v>
+        <v>1153050632.107476</v>
       </c>
       <c r="AA3" t="n">
         <v>1.65047606081878e-07</v>
@@ -2596,10 +2530,8 @@
       <c r="K4" t="n">
         <v>88.03366245045362</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 29.127x + -16863.785</t>
-        </is>
+      <c r="W4" t="n">
+        <v>29.12688285461806</v>
       </c>
       <c r="X4" t="n">
         <v>-16863.78495476274</v>
@@ -2608,7 +2540,7 @@
         <v>505.9367732007904</v>
       </c>
       <c r="Z4" t="n">
-        <v>409.583</v>
+        <v>276973980.2023099</v>
       </c>
       <c r="AA4" t="n">
         <v>1.5975165127509e-07</v>
@@ -2648,10 +2580,8 @@
       <c r="K5" t="n">
         <v>88.17218214797073</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 31.336x + -17961.247</t>
-        </is>
+      <c r="W5" t="n">
+        <v>31.33591318030961</v>
       </c>
       <c r="X5" t="n">
         <v>-17961.24743845963</v>
@@ -2660,7 +2590,7 @@
         <v>501.6073645736557</v>
       </c>
       <c r="Z5" t="n">
-        <v>379.999</v>
+        <v>274198527.786215</v>
       </c>
       <c r="AA5" t="n">
         <v>1.567713072065792e-07</v>
@@ -2700,10 +2630,8 @@
       <c r="K6" t="n">
         <v>88.20328996725124</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 31.879x + -17997.618</t>
-        </is>
+      <c r="W6" t="n">
+        <v>31.87882102497744</v>
       </c>
       <c r="X6" t="n">
         <v>-17997.61842269876</v>
@@ -2712,7 +2640,7 @@
         <v>497.2754351093973</v>
       </c>
       <c r="Z6" t="n">
-        <v>364.242</v>
+        <v>339643224.7489861</v>
       </c>
       <c r="AA6" t="n">
         <v>1.547601861903376e-07</v>
@@ -2752,10 +2680,8 @@
       <c r="K7" t="n">
         <v>88.28718814438813</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 33.441x + -18713.218</t>
-        </is>
+      <c r="W7" t="n">
+        <v>33.44133250330943</v>
       </c>
       <c r="X7" t="n">
         <v>-18713.21818627753</v>
@@ -2764,7 +2690,7 @@
         <v>492.8619727179022</v>
       </c>
       <c r="Z7" t="n">
-        <v>347.5880000000001</v>
+        <v>48122411.69188027</v>
       </c>
       <c r="AA7" t="n">
         <v>1.530852102112056e-07</v>
@@ -2804,10 +2730,8 @@
       <c r="K8" t="n">
         <v>88.32363446272743</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 34.169x + -18898.645</t>
-        </is>
+      <c r="W8" t="n">
+        <v>34.16881832590185</v>
       </c>
       <c r="X8" t="n">
         <v>-18898.64523204229</v>
@@ -2816,7 +2740,7 @@
         <v>488.3942272544898</v>
       </c>
       <c r="Z8" t="n">
-        <v>338.093</v>
+        <v>139167288.1738239</v>
       </c>
       <c r="AA8" t="n">
         <v>1.521024047703086e-07</v>
@@ -2856,10 +2780,8 @@
       <c r="K9" t="n">
         <v>88.36763392993825</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 35.090x + -19225.256</t>
-        </is>
+      <c r="W9" t="n">
+        <v>35.09033763922436</v>
       </c>
       <c r="X9" t="n">
         <v>-19225.25622158501</v>
@@ -2868,7 +2790,7 @@
         <v>484.120822323998</v>
       </c>
       <c r="Z9" t="n">
-        <v>330.276</v>
+        <v>132677314.3519183</v>
       </c>
       <c r="AA9" t="n">
         <v>1.511903614561794e-07</v>
@@ -2908,10 +2830,8 @@
       <c r="K10" t="n">
         <v>88.34160963739218</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 34.539x + -18659.025</t>
-        </is>
+      <c r="W10" t="n">
+        <v>34.53938201459988</v>
       </c>
       <c r="X10" t="n">
         <v>-18659.02516410564</v>
@@ -2920,7 +2840,7 @@
         <v>463.1183379140412</v>
       </c>
       <c r="Z10" t="n">
-        <v>326.2660000000001</v>
+        <v>19931.75710437477</v>
       </c>
       <c r="AA10" t="n">
         <v>1.514960415288417e-07</v>
@@ -2960,10 +2880,8 @@
       <c r="K11" t="n">
         <v>88.38430872173819</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 35.453x + -18979.199</t>
-        </is>
+      <c r="W11" t="n">
+        <v>35.45268359604334</v>
       </c>
       <c r="X11" t="n">
         <v>-18979.19883645495</v>
@@ -2972,7 +2890,7 @@
         <v>447.4710340674641</v>
       </c>
       <c r="Z11" t="n">
-        <v>317.47</v>
+        <v>19780.44097911213</v>
       </c>
       <c r="AA11" t="n">
         <v>1.544921834051245e-07</v>
@@ -3012,10 +2930,8 @@
       <c r="K12" t="n">
         <v>88.35971792468607</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 34.921x + -18468.812</t>
-        </is>
+      <c r="W12" t="n">
+        <v>34.9208996904884</v>
       </c>
       <c r="X12" t="n">
         <v>-18468.81200397372</v>
@@ -3024,7 +2940,7 @@
         <v>450.809896135095</v>
       </c>
       <c r="Z12" t="n">
-        <v>314.12</v>
+        <v>19636.48241462802</v>
       </c>
       <c r="AA12" t="n">
         <v>1.53486678242163e-07</v>
@@ -3064,10 +2980,8 @@
       <c r="K13" t="n">
         <v>88.45574418417671</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 37.094x + -19566.448</t>
-        </is>
+      <c r="W13" t="n">
+        <v>37.09353364939714</v>
       </c>
       <c r="X13" t="n">
         <v>-19566.44751812772</v>
@@ -3076,7 +2990,7 @@
         <v>469.4180430424947</v>
       </c>
       <c r="Z13" t="n">
-        <v>306.949</v>
+        <v>195687052.8469674</v>
       </c>
       <c r="AA13" t="n">
         <v>1.486442747547208e-07</v>
@@ -3116,10 +3030,8 @@
       <c r="K14" t="n">
         <v>88.4792489974719</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 37.667x + -19723.256</t>
-        </is>
+      <c r="W14" t="n">
+        <v>37.6671290290443</v>
       </c>
       <c r="X14" t="n">
         <v>-19723.2558422374</v>
@@ -3128,7 +3040,7 @@
         <v>466.1555757796788</v>
       </c>
       <c r="Z14" t="n">
-        <v>303.97</v>
+        <v>33889271.05198988</v>
       </c>
       <c r="AA14" t="n">
         <v>1.481236604844619e-07</v>
@@ -3168,10 +3080,8 @@
       <c r="K15" t="n">
         <v>88.49929168139049</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 38.170x + -19826.422</t>
-        </is>
+      <c r="W15" t="n">
+        <v>38.17042650371392</v>
       </c>
       <c r="X15" t="n">
         <v>-19826.4224640925</v>
@@ -3180,7 +3090,7 @@
         <v>463.0021897313908</v>
       </c>
       <c r="Z15" t="n">
-        <v>298.276</v>
+        <v>30610608.87774355</v>
       </c>
       <c r="AA15" t="n">
         <v>1.47557375829487e-07</v>
@@ -3220,10 +3130,8 @@
       <c r="K16" t="n">
         <v>88.51103564188456</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 38.472x + -19831.291</t>
-        </is>
+      <c r="W16" t="n">
+        <v>38.47162663800614</v>
       </c>
       <c r="X16" t="n">
         <v>-19831.29149342823</v>
@@ -3232,7 +3140,7 @@
         <v>459.8739648972207</v>
       </c>
       <c r="Z16" t="n">
-        <v>296.371</v>
+        <v>1017990087.164893</v>
       </c>
       <c r="AA16" t="n">
         <v>1.475107914481014e-07</v>
@@ -3272,10 +3180,8 @@
       <c r="K17" t="n">
         <v>88.55553570648043</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 39.657x + -20320.008</t>
-        </is>
+      <c r="W17" t="n">
+        <v>39.657359911227</v>
       </c>
       <c r="X17" t="n">
         <v>-20320.00828788663</v>
@@ -3284,7 +3190,7 @@
         <v>456.860752762009</v>
       </c>
       <c r="Z17" t="n">
-        <v>289.057</v>
+        <v>501709512.345993</v>
       </c>
       <c r="AA17" t="n">
         <v>1.469994822494576e-07</v>
@@ -3324,10 +3230,8 @@
       <c r="K18" t="n">
         <v>88.48590104804566</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 37.833x + -19124.797</t>
-        </is>
+      <c r="W18" t="n">
+        <v>37.83269357607153</v>
       </c>
       <c r="X18" t="n">
         <v>-19124.79737006264</v>
@@ -3336,7 +3240,7 @@
         <v>453.9074739756753</v>
       </c>
       <c r="Z18" t="n">
-        <v>291.61</v>
+        <v>32599065.49987507</v>
       </c>
       <c r="AA18" t="n">
         <v>1.465458601378154e-07</v>
@@ -3376,10 +3280,8 @@
       <c r="K19" t="n">
         <v>88.58755038149658</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 40.557x + -20487.725</t>
-        </is>
+      <c r="W19" t="n">
+        <v>40.5566129735538</v>
       </c>
       <c r="X19" t="n">
         <v>-20487.72512551313</v>
@@ -3388,7 +3290,7 @@
         <v>450.9131413153963</v>
       </c>
       <c r="Z19" t="n">
-        <v>282.7089999999999</v>
+        <v>371115134.107501</v>
       </c>
       <c r="AA19" t="n">
         <v>1.463834274094101e-07</v>
@@ -3428,10 +3330,8 @@
       <c r="K20" t="n">
         <v>88.59251266954739</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 40.700x + -20400.881</t>
-        </is>
+      <c r="W20" t="n">
+        <v>40.69965867500078</v>
       </c>
       <c r="X20" t="n">
         <v>-20400.88055875661</v>
@@ -3440,7 +3340,7 @@
         <v>447.9520199798416</v>
       </c>
       <c r="Z20" t="n">
-        <v>282.302</v>
+        <v>488609989.4587379</v>
       </c>
       <c r="AA20" t="n">
         <v>1.461839679337601e-07</v>
@@ -3480,10 +3380,8 @@
       <c r="K21" t="n">
         <v>88.60755895712755</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 41.140x + -20450.972</t>
-        </is>
+      <c r="W21" t="n">
+        <v>41.13962263995629</v>
       </c>
       <c r="X21" t="n">
         <v>-20450.9722368486</v>
@@ -3492,7 +3390,7 @@
         <v>445.0454203031626</v>
       </c>
       <c r="Z21" t="n">
-        <v>275.712</v>
+        <v>24252836.08707369</v>
       </c>
       <c r="AA21" t="n">
         <v>1.454227153458093e-07</v>
@@ -3532,10 +3430,8 @@
       <c r="K22" t="n">
         <v>88.54159149224458</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 39.278x + -19296.229</t>
-        </is>
+      <c r="W22" t="n">
+        <v>39.27802433211544</v>
       </c>
       <c r="X22" t="n">
         <v>-19296.228715192</v>
@@ -3544,7 +3440,7 @@
         <v>442.0774439788123</v>
       </c>
       <c r="Z22" t="n">
-        <v>282.243</v>
+        <v>254351094.1608738</v>
       </c>
       <c r="AA22" t="n">
         <v>1.45726388151133e-07</v>
@@ -3670,12 +3566,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3730,10 +3626,8 @@
       <c r="K2" t="n">
         <v>85.15893059983844</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 11.807x + -6573.882</t>
-        </is>
+      <c r="W2" t="n">
+        <v>11.80717833307756</v>
       </c>
       <c r="X2" t="n">
         <v>-6573.881938216876</v>
@@ -3742,7 +3636,7 @@
         <v>384.3381527024216</v>
       </c>
       <c r="Z2" t="n">
-        <v>986.109</v>
+        <v>11775.32105460459</v>
       </c>
       <c r="AA2" t="n">
         <v>2.374093315062157e-07</v>
@@ -3782,10 +3676,8 @@
       <c r="K3" t="n">
         <v>86.52053831888745</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 16.447x + -8455.455</t>
-        </is>
+      <c r="W3" t="n">
+        <v>16.44660403800632</v>
       </c>
       <c r="X3" t="n">
         <v>-8455.454687471025</v>
@@ -3794,7 +3686,7 @@
         <v>453.5502752916325</v>
       </c>
       <c r="Z3" t="n">
-        <v>722.866</v>
+        <v>744707921.196215</v>
       </c>
       <c r="AA3" t="n">
         <v>1.905968989159095e-07</v>
@@ -3834,10 +3726,8 @@
       <c r="K4" t="n">
         <v>87.11978400360309</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 19.876x + -9966.590</t>
-        </is>
+      <c r="W4" t="n">
+        <v>19.87611670466828</v>
       </c>
       <c r="X4" t="n">
         <v>-9966.589926908709</v>
@@ -3846,7 +3736,7 @@
         <v>446.9128653674636</v>
       </c>
       <c r="Z4" t="n">
-        <v>600.921</v>
+        <v>122348596.6650685</v>
       </c>
       <c r="AA4" t="n">
         <v>1.773423667132198e-07</v>
@@ -3886,10 +3776,8 @@
       <c r="K5" t="n">
         <v>87.50438817739025</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 22.944x + -11379.843</t>
-        </is>
+      <c r="W5" t="n">
+        <v>22.94408966952435</v>
       </c>
       <c r="X5" t="n">
         <v>-11379.84288682476</v>
@@ -3898,7 +3786,7 @@
         <v>442.1150697035575</v>
       </c>
       <c r="Z5" t="n">
-        <v>524.385</v>
+        <v>483107236.94912</v>
       </c>
       <c r="AA5" t="n">
         <v>1.696845536368017e-07</v>
@@ -3938,10 +3826,8 @@
       <c r="K6" t="n">
         <v>87.71142443502828</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 25.022x + -12212.472</t>
-        </is>
+      <c r="W6" t="n">
+        <v>25.02224796670136</v>
       </c>
       <c r="X6" t="n">
         <v>-12212.47173573682</v>
@@ -3950,7 +3836,7 @@
         <v>437.4918011690357</v>
       </c>
       <c r="Z6" t="n">
-        <v>476.685</v>
+        <v>716242726.0374465</v>
       </c>
       <c r="AA6" t="n">
         <v>1.646980008581899e-07</v>
@@ -3990,10 +3876,8 @@
       <c r="K7" t="n">
         <v>87.89546152366736</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 27.213x + -13152.682</t>
-        </is>
+      <c r="W7" t="n">
+        <v>27.21262190425853</v>
       </c>
       <c r="X7" t="n">
         <v>-13152.68204207807</v>
@@ -4002,7 +3886,7 @@
         <v>375.2179786613265</v>
       </c>
       <c r="Z7" t="n">
-        <v>440.562</v>
+        <v>14362.51599599425</v>
       </c>
       <c r="AA7" t="n">
         <v>2.011577568869954e-07</v>
@@ -4042,10 +3926,8 @@
       <c r="K8" t="n">
         <v>88.02257435294243</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 28.963x + -13825.471</t>
-        </is>
+      <c r="W8" t="n">
+        <v>28.96342985097152</v>
       </c>
       <c r="X8" t="n">
         <v>-13825.47071609503</v>
@@ -4054,7 +3936,7 @@
         <v>376.1330110265083</v>
       </c>
       <c r="Z8" t="n">
-        <v>413.5529999999999</v>
+        <v>14197.74840955629</v>
       </c>
       <c r="AA8" t="n">
         <v>1.860080093500697e-07</v>
@@ -4094,10 +3976,8 @@
       <c r="K9" t="n">
         <v>88.07443435814942</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 29.744x + -13944.872</t>
-        </is>
+      <c r="W9" t="n">
+        <v>29.74409468062561</v>
       </c>
       <c r="X9" t="n">
         <v>-13944.87180468092</v>
@@ -4106,7 +3986,7 @@
         <v>423.2257346382985</v>
       </c>
       <c r="Z9" t="n">
-        <v>394.6850000000001</v>
+        <v>232460446.9736118</v>
       </c>
       <c r="AA9" t="n">
         <v>1.565866153131764e-07</v>
@@ -4146,10 +4026,8 @@
       <c r="K10" t="n">
         <v>88.2036612326601</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 31.885x + -14845.972</t>
-        </is>
+      <c r="W10" t="n">
+        <v>31.88541402709111</v>
       </c>
       <c r="X10" t="n">
         <v>-14845.97249191081</v>
@@ -4158,7 +4036,7 @@
         <v>418.5699821633839</v>
       </c>
       <c r="Z10" t="n">
-        <v>375.1689999999999</v>
+        <v>114807163.3957939</v>
       </c>
       <c r="AA10" t="n">
         <v>1.549818680972762e-07</v>
@@ -4198,10 +4076,8 @@
       <c r="K11" t="n">
         <v>88.28161213153919</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 33.333x + -15346.097</t>
-        </is>
+      <c r="W11" t="n">
+        <v>33.33275362869809</v>
       </c>
       <c r="X11" t="n">
         <v>-15346.09664441817</v>
@@ -4210,7 +4086,7 @@
         <v>414.1299460976634</v>
       </c>
       <c r="Z11" t="n">
-        <v>359.9040000000001</v>
+        <v>451825689.7642848</v>
       </c>
       <c r="AA11" t="n">
         <v>1.536131569002642e-07</v>
@@ -4336,12 +4212,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4396,10 +4272,8 @@
       <c r="K2" t="n">
         <v>86.86144946380473</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 18.237x + -11143.104</t>
-        </is>
+      <c r="W2" t="n">
+        <v>18.23722750448354</v>
       </c>
       <c r="X2" t="n">
         <v>-11143.10422310316</v>
@@ -4408,7 +4282,7 @@
         <v>417.5068185752541</v>
       </c>
       <c r="Z2" t="n">
-        <v>635.5000000000001</v>
+        <v>12977.65313528089</v>
       </c>
       <c r="AA2" t="n">
         <v>2.038867498814914e-07</v>
@@ -4448,10 +4322,8 @@
       <c r="K3" t="n">
         <v>87.58003764361428</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 23.662x + -13751.002</t>
-        </is>
+      <c r="W3" t="n">
+        <v>23.66222979266279</v>
       </c>
       <c r="X3" t="n">
         <v>-13751.00150610183</v>
@@ -4460,7 +4332,7 @@
         <v>508.0667941279152</v>
       </c>
       <c r="Z3" t="n">
-        <v>490.831</v>
+        <v>451461944.1884012</v>
       </c>
       <c r="AA3" t="n">
         <v>1.750376676224168e-07</v>
@@ -4500,10 +4372,8 @@
       <c r="K4" t="n">
         <v>87.91385601540614</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 27.453x + -15747.414</t>
-        </is>
+      <c r="W4" t="n">
+        <v>27.4527831287973</v>
       </c>
       <c r="X4" t="n">
         <v>-15747.41414918185</v>
@@ -4512,7 +4382,7 @@
         <v>502.6456510843087</v>
       </c>
       <c r="Z4" t="n">
-        <v>425.772</v>
+        <v>206166154.7535846</v>
       </c>
       <c r="AA4" t="n">
         <v>1.678223889175268e-07</v>
@@ -4552,10 +4422,8 @@
       <c r="K5" t="n">
         <v>88.05373631179418</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 29.428x + -16627.169</t>
-        </is>
+      <c r="W5" t="n">
+        <v>29.42753379693054</v>
       </c>
       <c r="X5" t="n">
         <v>-16627.16855542043</v>
@@ -4564,7 +4432,7 @@
         <v>498.4396734279157</v>
       </c>
       <c r="Z5" t="n">
-        <v>387.563</v>
+        <v>204393482.0758557</v>
       </c>
       <c r="AA5" t="n">
         <v>1.634445930390748e-07</v>
@@ -4604,10 +4472,8 @@
       <c r="K6" t="n">
         <v>88.17432383016353</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 31.373x + -17551.889</t>
-        </is>
+      <c r="W6" t="n">
+        <v>31.37269795974946</v>
       </c>
       <c r="X6" t="n">
         <v>-17551.88878711573</v>
@@ -4616,7 +4482,7 @@
         <v>494.0234310620984</v>
       </c>
       <c r="Z6" t="n">
-        <v>360.293</v>
+        <v>438625635.8532071</v>
       </c>
       <c r="AA6" t="n">
         <v>1.606462367255953e-07</v>
@@ -4656,10 +4522,8 @@
       <c r="K7" t="n">
         <v>88.25540629771258</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 32.832x + -18173.351</t>
-        </is>
+      <c r="W7" t="n">
+        <v>32.8317540952881</v>
       </c>
       <c r="X7" t="n">
         <v>-18173.35050536688</v>
@@ -4668,7 +4532,7 @@
         <v>489.4728570395134</v>
       </c>
       <c r="Z7" t="n">
-        <v>344.453</v>
+        <v>32380417.54701016</v>
       </c>
       <c r="AA7" t="n">
         <v>1.584815734986672e-07</v>
@@ -4708,10 +4572,8 @@
       <c r="K8" t="n">
         <v>88.30606317303224</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 33.814x + -18510.386</t>
-        </is>
+      <c r="W8" t="n">
+        <v>33.81418008510435</v>
       </c>
       <c r="X8" t="n">
         <v>-18510.38553921237</v>
@@ -4720,7 +4582,7 @@
         <v>485.0689837616429</v>
       </c>
       <c r="Z8" t="n">
-        <v>332.53</v>
+        <v>531345991.4080034</v>
       </c>
       <c r="AA8" t="n">
         <v>1.571962671235971e-07</v>
@@ -4760,10 +4622,8 @@
       <c r="K9" t="n">
         <v>88.38564068815192</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 35.482x + -19274.904</t>
-        </is>
+      <c r="W9" t="n">
+        <v>35.48195020107263</v>
       </c>
       <c r="X9" t="n">
         <v>-19274.90352499807</v>
@@ -4772,7 +4632,7 @@
         <v>461.6395463025264</v>
       </c>
       <c r="Z9" t="n">
-        <v>319.693</v>
+        <v>19981.87027291454</v>
       </c>
       <c r="AA9" t="n">
         <v>1.561293990758285e-07</v>
@@ -4812,10 +4672,8 @@
       <c r="K10" t="n">
         <v>88.40788830141688</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 35.978x + -19354.113</t>
-        </is>
+      <c r="W10" t="n">
+        <v>35.97802328936388</v>
       </c>
       <c r="X10" t="n">
         <v>-19354.11255195818</v>
@@ -4824,7 +4682,7 @@
         <v>456.4975233873164</v>
       </c>
       <c r="Z10" t="n">
-        <v>313.4730000000001</v>
+        <v>19821.06600705465</v>
       </c>
       <c r="AA10" t="n">
         <v>1.608007004954683e-07</v>
@@ -4864,10 +4722,8 @@
       <c r="K11" t="n">
         <v>88.39919616265577</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 35.783x + -19036.106</t>
-        </is>
+      <c r="W11" t="n">
+        <v>35.78256683045963</v>
       </c>
       <c r="X11" t="n">
         <v>-19036.10569833713</v>
@@ -4876,7 +4732,7 @@
         <v>454.1545828518642</v>
       </c>
       <c r="Z11" t="n">
-        <v>308.6129999999999</v>
+        <v>19700.56225115172</v>
       </c>
       <c r="AA11" t="n">
         <v>1.618344503575198e-07</v>
@@ -4916,10 +4772,8 @@
       <c r="K12" t="n">
         <v>88.4476791384474</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 36.901x + -19497.407</t>
-        </is>
+      <c r="W12" t="n">
+        <v>36.90072148038194</v>
       </c>
       <c r="X12" t="n">
         <v>-19497.40703510112</v>
@@ -4928,7 +4782,7 @@
         <v>471.1205816293415</v>
       </c>
       <c r="Z12" t="n">
-        <v>297.4870000000001</v>
+        <v>257051752.1430815</v>
       </c>
       <c r="AA12" t="n">
         <v>1.531553734385983e-07</v>
@@ -4968,10 +4822,8 @@
       <c r="K13" t="n">
         <v>88.44513591150732</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 36.840x + -19293.011</t>
-        </is>
+      <c r="W13" t="n">
+        <v>36.84033492456643</v>
       </c>
       <c r="X13" t="n">
         <v>-19293.01124821303</v>
@@ -4980,7 +4832,7 @@
         <v>468.0741620206001</v>
       </c>
       <c r="Z13" t="n">
-        <v>295.8099999999999</v>
+        <v>196796592.6595076</v>
       </c>
       <c r="AA13" t="n">
         <v>1.526117669715226e-07</v>
@@ -5020,10 +4872,8 @@
       <c r="K14" t="n">
         <v>88.40789809003768</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 35.978x + -18633.703</t>
-        </is>
+      <c r="W14" t="n">
+        <v>35.9782446047068</v>
       </c>
       <c r="X14" t="n">
         <v>-18633.70275949086</v>
@@ -5032,7 +4882,7 @@
         <v>465.1827305649302</v>
       </c>
       <c r="Z14" t="n">
-        <v>294.326</v>
+        <v>24933884.25577632</v>
       </c>
       <c r="AA14" t="n">
         <v>1.518962477579243e-07</v>
@@ -5072,10 +4922,8 @@
       <c r="K15" t="n">
         <v>88.5112146069895</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 38.476x + -19901.549</t>
-        </is>
+      <c r="W15" t="n">
+        <v>38.4762533487286</v>
       </c>
       <c r="X15" t="n">
         <v>-19901.54851131805</v>
@@ -5084,7 +4932,7 @@
         <v>462.256513666429</v>
       </c>
       <c r="Z15" t="n">
-        <v>284.7909999999999</v>
+        <v>508127762.911929</v>
       </c>
       <c r="AA15" t="n">
         <v>1.515884585214217e-07</v>
@@ -5124,10 +4972,8 @@
       <c r="K16" t="n">
         <v>88.52840792470087</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 38.926x + -20000.507</t>
-        </is>
+      <c r="W16" t="n">
+        <v>38.92599115469031</v>
       </c>
       <c r="X16" t="n">
         <v>-20000.50700315995</v>
@@ -5136,7 +4982,7 @@
         <v>459.4788567106507</v>
       </c>
       <c r="Z16" t="n">
-        <v>281.174</v>
+        <v>29889948.63197297</v>
       </c>
       <c r="AA16" t="n">
         <v>1.509417738307164e-07</v>
@@ -5176,10 +5022,8 @@
       <c r="K17" t="n">
         <v>88.56260943717959</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 39.853x + -20360.781</t>
-        </is>
+      <c r="W17" t="n">
+        <v>39.85260544806466</v>
       </c>
       <c r="X17" t="n">
         <v>-20360.78126008563</v>
@@ -5188,7 +5032,7 @@
         <v>456.5584869726523</v>
       </c>
       <c r="Z17" t="n">
-        <v>277.816</v>
+        <v>24405148.00093558</v>
       </c>
       <c r="AA17" t="n">
         <v>1.504166853825801e-07</v>
@@ -5228,10 +5072,8 @@
       <c r="K18" t="n">
         <v>88.56753740361231</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 39.990x + -20263.061</t>
-        </is>
+      <c r="W18" t="n">
+        <v>39.98976406375478</v>
       </c>
       <c r="X18" t="n">
         <v>-20263.0610343937</v>
@@ -5240,7 +5082,7 @@
         <v>453.6618683443547</v>
       </c>
       <c r="Z18" t="n">
-        <v>274.038</v>
+        <v>372428787.2463068</v>
       </c>
       <c r="AA18" t="n">
         <v>1.501992025221879e-07</v>
@@ -5280,10 +5122,8 @@
       <c r="K19" t="n">
         <v>88.59895201626152</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 40.887x + -20591.792</t>
-        </is>
+      <c r="W19" t="n">
+        <v>40.88679319135042</v>
       </c>
       <c r="X19" t="n">
         <v>-20591.79155524877</v>
@@ -5292,7 +5132,7 @@
         <v>450.8250450737046</v>
       </c>
       <c r="Z19" t="n">
-        <v>268.314</v>
+        <v>123559401.376678</v>
       </c>
       <c r="AA19" t="n">
         <v>1.49664764293655e-07</v>
@@ -5332,10 +5172,8 @@
       <c r="K20" t="n">
         <v>88.59557787635029</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 40.789x + -20371.843</t>
-        </is>
+      <c r="W20" t="n">
+        <v>40.78852299604019</v>
       </c>
       <c r="X20" t="n">
         <v>-20371.84324781778</v>
@@ -5344,7 +5182,7 @@
         <v>447.9321946077594</v>
       </c>
       <c r="Z20" t="n">
-        <v>266.547</v>
+        <v>39584486.3827277</v>
       </c>
       <c r="AA20" t="n">
         <v>1.491831414766263e-07</v>
@@ -5384,10 +5222,8 @@
       <c r="K21" t="n">
         <v>88.61092415293518</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 41.239x + -20458.402</t>
-        </is>
+      <c r="W21" t="n">
+        <v>41.23932730799857</v>
       </c>
       <c r="X21" t="n">
         <v>-20458.4021150452</v>
@@ -5396,7 +5232,7 @@
         <v>444.9643080183889</v>
       </c>
       <c r="Z21" t="n">
-        <v>265.449</v>
+        <v>486018027.4957576</v>
       </c>
       <c r="AA21" t="n">
         <v>1.491712496362159e-07</v>
@@ -5436,10 +5272,8 @@
       <c r="K22" t="n">
         <v>88.62558245532303</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 41.679x + -20509.685</t>
-        </is>
+      <c r="W22" t="n">
+        <v>41.6793203925384</v>
       </c>
       <c r="X22" t="n">
         <v>-20509.68482550468</v>
@@ -5448,7 +5282,7 @@
         <v>387.491590786557</v>
       </c>
       <c r="Z22" t="n">
-        <v>260.703</v>
+        <v>14647.29090377409</v>
       </c>
       <c r="AA22" t="n">
         <v>1.931470320474982e-07</v>
@@ -5574,12 +5408,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5634,10 +5468,8 @@
       <c r="K2" t="n">
         <v>84.62960094989177</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 10.638x + -6318.601</t>
-        </is>
+      <c r="W2" t="n">
+        <v>10.63755028327457</v>
       </c>
       <c r="X2" t="n">
         <v>-6318.601230315276</v>
@@ -5646,7 +5478,7 @@
         <v>401.3409320117067</v>
       </c>
       <c r="Z2" t="n">
-        <v>1056.626</v>
+        <v>12266.62804113551</v>
       </c>
       <c r="AA2" t="n">
         <v>1.885917557203309e-07</v>
@@ -5686,10 +5518,8 @@
       <c r="K3" t="n">
         <v>85.91547373847337</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 14.004x + -7267.109</t>
-        </is>
+      <c r="W3" t="n">
+        <v>14.00375052746339</v>
       </c>
       <c r="X3" t="n">
         <v>-7267.108957893212</v>
@@ -5698,7 +5528,7 @@
         <v>461.9684892189916</v>
       </c>
       <c r="Z3" t="n">
-        <v>811.0740000000001</v>
+        <v>189176154.32179</v>
       </c>
       <c r="AA3" t="n">
         <v>2.071882196427054e-07</v>
@@ -5738,10 +5568,8 @@
       <c r="K4" t="n">
         <v>86.67284613602878</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 17.201x + -8697.314</t>
-        </is>
+      <c r="W4" t="n">
+        <v>17.20129726343182</v>
       </c>
       <c r="X4" t="n">
         <v>-8697.313979497821</v>
@@ -5750,7 +5578,7 @@
         <v>452.8946722373672</v>
       </c>
       <c r="Z4" t="n">
-        <v>670.4369999999999</v>
+        <v>247333581.1174081</v>
       </c>
       <c r="AA4" t="n">
         <v>1.910211725883793e-07</v>
@@ -5790,10 +5618,8 @@
       <c r="K5" t="n">
         <v>87.07813236585309</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 19.592x + -9727.400</t>
-        </is>
+      <c r="W5" t="n">
+        <v>19.59229849147633</v>
       </c>
       <c r="X5" t="n">
         <v>-9727.399628183486</v>
@@ -5802,7 +5628,7 @@
         <v>448.0721764289243</v>
       </c>
       <c r="Z5" t="n">
-        <v>587.011</v>
+        <v>489651655.3091006</v>
       </c>
       <c r="AA5" t="n">
         <v>1.811749780587644e-07</v>
@@ -5842,10 +5668,8 @@
       <c r="K6" t="n">
         <v>87.35690331565235</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 21.662x + -10613.006</t>
-        </is>
+      <c r="W6" t="n">
+        <v>21.66214025265463</v>
       </c>
       <c r="X6" t="n">
         <v>-10613.00555506835</v>
@@ -5854,7 +5678,7 @@
         <v>387.8907264242617</v>
       </c>
       <c r="Z6" t="n">
-        <v>529.675</v>
+        <v>14722.57483900916</v>
       </c>
       <c r="AA6" t="n">
         <v>1.78467925192736e-07</v>
@@ -5894,10 +5718,8 @@
       <c r="K7" t="n">
         <v>87.6524006523772</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 24.392x + -11939.005</t>
-        </is>
+      <c r="W7" t="n">
+        <v>24.39245563260854</v>
       </c>
       <c r="X7" t="n">
         <v>-11939.00536769757</v>
@@ -5906,7 +5728,7 @@
         <v>387.4882096521496</v>
       </c>
       <c r="Z7" t="n">
-        <v>481.646</v>
+        <v>14565.33249140431</v>
       </c>
       <c r="AA7" t="n">
         <v>1.858273155035598e-07</v>
@@ -5946,10 +5768,8 @@
       <c r="K8" t="n">
         <v>87.77488195674073</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 25.737x + -12399.005</t>
-        </is>
+      <c r="W8" t="n">
+        <v>25.73659953235223</v>
       </c>
       <c r="X8" t="n">
         <v>-12399.00526128336</v>
@@ -5958,7 +5778,7 @@
         <v>435.3280852846409</v>
       </c>
       <c r="Z8" t="n">
-        <v>449.7590000000001</v>
+        <v>1067083309.103381</v>
       </c>
       <c r="AA8" t="n">
         <v>1.66515963430215e-07</v>
@@ -5998,10 +5818,8 @@
       <c r="K9" t="n">
         <v>87.86689840153443</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 26.848x + -12770.771</t>
-        </is>
+      <c r="W9" t="n">
+        <v>26.84790333880436</v>
       </c>
       <c r="X9" t="n">
         <v>-12770.77070569713</v>
@@ -6010,7 +5828,7 @@
         <v>431.080079089411</v>
       </c>
       <c r="Z9" t="n">
-        <v>428.611</v>
+        <v>236711912.7382494</v>
       </c>
       <c r="AA9" t="n">
         <v>1.639521466366806e-07</v>
@@ -6050,10 +5868,8 @@
       <c r="K10" t="n">
         <v>87.96552851428962</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 28.151x + -13239.069</t>
-        </is>
+      <c r="W10" t="n">
+        <v>28.15065127886286</v>
       </c>
       <c r="X10" t="n">
         <v>-13239.06867644153</v>
@@ -6062,7 +5878,7 @@
         <v>426.9455822466085</v>
       </c>
       <c r="Z10" t="n">
-        <v>406.5040000000001</v>
+        <v>232797051.4751672</v>
       </c>
       <c r="AA10" t="n">
         <v>1.617918238474145e-07</v>
@@ -6102,10 +5918,8 @@
       <c r="K11" t="n">
         <v>88.04529689164828</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 29.300x + -13642.323</t>
-        </is>
+      <c r="W11" t="n">
+        <v>29.30038257793186</v>
       </c>
       <c r="X11" t="n">
         <v>-13642.32268949657</v>
@@ -6114,7 +5928,7 @@
         <v>422.9713898025815</v>
       </c>
       <c r="Z11" t="n">
-        <v>390.01</v>
+        <v>460142131.6411566</v>
       </c>
       <c r="AA11" t="n">
         <v>1.600997412236512e-07</v>
@@ -6240,12 +6054,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6300,10 +6114,8 @@
       <c r="K2" t="n">
         <v>86.93415724150684</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 18.671x + -11267.543</t>
-        </is>
+      <c r="W2" t="n">
+        <v>18.67058754681381</v>
       </c>
       <c r="X2" t="n">
         <v>-11267.54250541104</v>
@@ -6312,7 +6124,7 @@
         <v>413.6397995909341</v>
       </c>
       <c r="Z2" t="n">
-        <v>605.5409999999999</v>
+        <v>12855.27665633393</v>
       </c>
       <c r="AA2" t="n">
         <v>2.063059043963831e-07</v>
@@ -6352,10 +6164,8 @@
       <c r="K3" t="n">
         <v>87.57886299883263</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 23.651x + -13623.491</t>
-        </is>
+      <c r="W3" t="n">
+        <v>23.65073609951575</v>
       </c>
       <c r="X3" t="n">
         <v>-13623.49116949148</v>
@@ -6364,7 +6174,7 @@
         <v>504.1080482705274</v>
       </c>
       <c r="Z3" t="n">
-        <v>477.905</v>
+        <v>212004258.9676698</v>
       </c>
       <c r="AA3" t="n">
         <v>1.76960210774205e-07</v>
@@ -6404,10 +6214,8 @@
       <c r="K4" t="n">
         <v>87.83651041555267</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 26.470x + -14977.867</t>
-        </is>
+      <c r="W4" t="n">
+        <v>26.47045134942096</v>
       </c>
       <c r="X4" t="n">
         <v>-14977.867423515</v>
@@ -6416,7 +6224,7 @@
         <v>498.9625108066003</v>
       </c>
       <c r="Z4" t="n">
-        <v>418.8009999999999</v>
+        <v>205971976.4805169</v>
       </c>
       <c r="AA4" t="n">
         <v>1.701795515197108e-07</v>
@@ -6456,10 +6264,8 @@
       <c r="K5" t="n">
         <v>88.08318252701439</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 29.880x + -16860.743</t>
-        </is>
+      <c r="W5" t="n">
+        <v>29.8799458783788</v>
       </c>
       <c r="X5" t="n">
         <v>-16860.74281362224</v>
@@ -6468,7 +6274,7 @@
         <v>494.8279817347797</v>
       </c>
       <c r="Z5" t="n">
-        <v>379.134</v>
+        <v>204276944.4449124</v>
       </c>
       <c r="AA5" t="n">
         <v>1.662980667773361e-07</v>
@@ -6508,10 +6314,8 @@
       <c r="K6" t="n">
         <v>88.146135370062</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 30.895x + -17204.992</t>
-        </is>
+      <c r="W6" t="n">
+        <v>30.89534296018612</v>
       </c>
       <c r="X6" t="n">
         <v>-17204.99234994837</v>
@@ -6520,7 +6324,7 @@
         <v>491.1009426238819</v>
       </c>
       <c r="Z6" t="n">
-        <v>358.9870000000001</v>
+        <v>268276508.0949699</v>
       </c>
       <c r="AA6" t="n">
         <v>1.638297250791552e-07</v>
@@ -6560,10 +6364,8 @@
       <c r="K7" t="n">
         <v>88.22461016538058</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 32.262x + -17826.127</t>
-        </is>
+      <c r="W7" t="n">
+        <v>32.26189514937747</v>
       </c>
       <c r="X7" t="n">
         <v>-17826.12717549497</v>
@@ -6572,7 +6374,7 @@
         <v>487.5097976123487</v>
       </c>
       <c r="Z7" t="n">
-        <v>343.6850000000001</v>
+        <v>266696322.562239</v>
       </c>
       <c r="AA7" t="n">
         <v>1.620722230722741e-07</v>
@@ -6612,10 +6414,8 @@
       <c r="K8" t="n">
         <v>88.22980484370761</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 32.357x + -17662.878</t>
-        </is>
+      <c r="W8" t="n">
+        <v>32.35662896061542</v>
       </c>
       <c r="X8" t="n">
         <v>-17662.87811060166</v>
@@ -6624,7 +6424,7 @@
         <v>483.9257299017522</v>
       </c>
       <c r="Z8" t="n">
-        <v>334.998</v>
+        <v>32436991.70759945</v>
       </c>
       <c r="AA8" t="n">
         <v>1.605428083959634e-07</v>
@@ -6664,10 +6464,8 @@
       <c r="K9" t="n">
         <v>88.28871311541049</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 33.471x + -18142.008</t>
-        </is>
+      <c r="W9" t="n">
+        <v>33.4711506743183</v>
       </c>
       <c r="X9" t="n">
         <v>-18142.0077608619</v>
@@ -6676,7 +6474,7 @@
         <v>480.5746890858928</v>
       </c>
       <c r="Z9" t="n">
-        <v>323.74</v>
+        <v>265881309.4744598</v>
       </c>
       <c r="AA9" t="n">
         <v>1.595987671116799e-07</v>
@@ -6716,10 +6514,8 @@
       <c r="K10" t="n">
         <v>88.29553731921057</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 33.605x + -18028.235</t>
-        </is>
+      <c r="W10" t="n">
+        <v>33.60523960628514</v>
       </c>
       <c r="X10" t="n">
         <v>-18028.23479334352</v>
@@ -6728,7 +6524,7 @@
         <v>477.3957378957134</v>
       </c>
       <c r="Z10" t="n">
-        <v>316.516</v>
+        <v>39976177.00676858</v>
       </c>
       <c r="AA10" t="n">
         <v>1.584275984886347e-07</v>
@@ -6768,10 +6564,8 @@
       <c r="K11" t="n">
         <v>88.35670680541432</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 34.857x + -18594.160</t>
-        </is>
+      <c r="W11" t="n">
+        <v>34.85687671376026</v>
       </c>
       <c r="X11" t="n">
         <v>-18594.15966303758</v>
@@ -6780,7 +6574,7 @@
         <v>474.2632636704056</v>
       </c>
       <c r="Z11" t="n">
-        <v>307.014</v>
+        <v>277771317.5458045</v>
       </c>
       <c r="AA11" t="n">
         <v>1.57690799887126e-07</v>
@@ -6820,10 +6614,8 @@
       <c r="K12" t="n">
         <v>88.42310230508649</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 36.325x + -19294.282</t>
-        </is>
+      <c r="W12" t="n">
+        <v>36.32531931398978</v>
       </c>
       <c r="X12" t="n">
         <v>-19294.28177003079</v>
@@ -6832,7 +6624,7 @@
         <v>452.1065659361487</v>
       </c>
       <c r="Z12" t="n">
-        <v>299.1220000000001</v>
+        <v>19558.83710782218</v>
       </c>
       <c r="AA12" t="n">
         <v>1.616303913931211e-07</v>
@@ -6872,10 +6664,8 @@
       <c r="K13" t="n">
         <v>88.4329419493239</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 36.554x + -19260.959</t>
-        </is>
+      <c r="W13" t="n">
+        <v>36.55352286501222</v>
       </c>
       <c r="X13" t="n">
         <v>-19260.95894229419</v>
@@ -6884,7 +6674,7 @@
         <v>449.1944204792102</v>
       </c>
       <c r="Z13" t="n">
-        <v>294.813</v>
+        <v>19425.52933163869</v>
       </c>
       <c r="AA13" t="n">
         <v>1.639577318564796e-07</v>
@@ -6924,10 +6714,8 @@
       <c r="K14" t="n">
         <v>88.45874035630399</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 37.166x + -19448.230</t>
-        </is>
+      <c r="W14" t="n">
+        <v>37.16567749678064</v>
       </c>
       <c r="X14" t="n">
         <v>-19448.23039167188</v>
@@ -6936,7 +6724,7 @@
         <v>460.2325273481125</v>
       </c>
       <c r="Z14" t="n">
-        <v>290.412</v>
+        <v>38683.00340727783</v>
       </c>
       <c r="AA14" t="n">
         <v>1.351863288882294e-07</v>
@@ -6976,10 +6764,8 @@
       <c r="K15" t="n">
         <v>88.41744094016497</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 36.195x + -18725.898</t>
-        </is>
+      <c r="W15" t="n">
+        <v>36.19530523381967</v>
       </c>
       <c r="X15" t="n">
         <v>-18725.89809953444</v>
@@ -6988,7 +6774,7 @@
         <v>462.4229830846041</v>
       </c>
       <c r="Z15" t="n">
-        <v>288.622</v>
+        <v>144479826.0997836</v>
       </c>
       <c r="AA15" t="n">
         <v>1.552128336099687e-07</v>
@@ -7028,10 +6814,8 @@
       <c r="K16" t="n">
         <v>88.44132740436413</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 36.750x + -18886.941</t>
-        </is>
+      <c r="W16" t="n">
+        <v>36.75027388639614</v>
       </c>
       <c r="X16" t="n">
         <v>-18886.9408467312</v>
@@ -7040,7 +6824,7 @@
         <v>459.5585606628492</v>
       </c>
       <c r="Z16" t="n">
-        <v>284.066</v>
+        <v>41238169.75850678</v>
       </c>
       <c r="AA16" t="n">
         <v>1.545466003043468e-07</v>
@@ -7080,10 +6864,8 @@
       <c r="K17" t="n">
         <v>88.50440518869166</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 38.301x + -19615.421</t>
-        </is>
+      <c r="W17" t="n">
+        <v>38.30099254929406</v>
       </c>
       <c r="X17" t="n">
         <v>-19615.42122235966</v>
@@ -7092,7 +6874,7 @@
         <v>456.6859799976505</v>
       </c>
       <c r="Z17" t="n">
-        <v>279.795</v>
+        <v>43460215.46930999</v>
       </c>
       <c r="AA17" t="n">
         <v>1.540925058369769e-07</v>
@@ -7132,10 +6914,8 @@
       <c r="K18" t="n">
         <v>88.51765224689362</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 38.643x + -19647.010</t>
-        </is>
+      <c r="W18" t="n">
+        <v>38.64342569425023</v>
       </c>
       <c r="X18" t="n">
         <v>-19647.01006491083</v>
@@ -7144,7 +6924,7 @@
         <v>453.8411188632443</v>
       </c>
       <c r="Z18" t="n">
-        <v>275.567</v>
+        <v>38460242.22836501</v>
       </c>
       <c r="AA18" t="n">
         <v>1.536211345540183e-07</v>
@@ -7184,10 +6964,8 @@
       <c r="K19" t="n">
         <v>88.53705771774206</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 39.156x + -19761.716</t>
-        </is>
+      <c r="W19" t="n">
+        <v>39.15624593465425</v>
       </c>
       <c r="X19" t="n">
         <v>-19761.71601802037</v>
@@ -7196,7 +6974,7 @@
         <v>451.0108621774502</v>
       </c>
       <c r="Z19" t="n">
-        <v>270.004</v>
+        <v>21259478.69612383</v>
       </c>
       <c r="AA19" t="n">
         <v>1.529559385986428e-07</v>
@@ -7236,10 +7014,8 @@
       <c r="K20" t="n">
         <v>88.58152449431284</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 40.384x + -20289.570</t>
-        </is>
+      <c r="W20" t="n">
+        <v>40.38425269964616</v>
       </c>
       <c r="X20" t="n">
         <v>-20289.56991448857</v>
@@ -7248,7 +7024,7 @@
         <v>448.1262092295214</v>
       </c>
       <c r="Z20" t="n">
-        <v>266.783</v>
+        <v>490198934.9228548</v>
       </c>
       <c r="AA20" t="n">
         <v>1.52920920227185e-07</v>
@@ -7288,10 +7064,8 @@
       <c r="K21" t="n">
         <v>88.59181697158111</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 40.680x + -20282.438</t>
-        </is>
+      <c r="W21" t="n">
+        <v>40.67954334462346</v>
       </c>
       <c r="X21" t="n">
         <v>-20282.43814255865</v>
@@ -7300,7 +7074,7 @@
         <v>445.2077970737978</v>
       </c>
       <c r="Z21" t="n">
-        <v>262.7550000000001</v>
+        <v>32351444.4834045</v>
       </c>
       <c r="AA21" t="n">
         <v>1.522644306313298e-07</v>
@@ -7340,10 +7114,8 @@
       <c r="K22" t="n">
         <v>88.54693039657742</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 39.422x + -19417.872</t>
-        </is>
+      <c r="W22" t="n">
+        <v>39.42240286257832</v>
       </c>
       <c r="X22" t="n">
         <v>-19417.87201350284</v>
@@ -7352,7 +7124,7 @@
         <v>387.6326706436827</v>
       </c>
       <c r="Z22" t="n">
-        <v>262.084</v>
+        <v>14650.15744522106</v>
       </c>
       <c r="AA22" t="n">
         <v>1.770970618415128e-07</v>
@@ -7478,12 +7250,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7538,10 +7310,8 @@
       <c r="K2" t="n">
         <v>84.19640999586274</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.839x + -5797.629</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.838684912765187</v>
       </c>
       <c r="X2" t="n">
         <v>-5797.629448077008</v>
@@ -7550,7 +7320,7 @@
         <v>401.2684479302368</v>
       </c>
       <c r="Z2" t="n">
-        <v>1116.007</v>
+        <v>12277.19927807831</v>
       </c>
       <c r="AA2" t="n">
         <v>1.936443436839519e-07</v>
@@ -7590,10 +7360,8 @@
       <c r="K3" t="n">
         <v>85.68961848328014</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 13.267x + -6922.351</t>
-        </is>
+      <c r="W3" t="n">
+        <v>13.26742145290707</v>
       </c>
       <c r="X3" t="n">
         <v>-6922.350553473259</v>
@@ -7602,7 +7370,7 @@
         <v>462.997499506849</v>
       </c>
       <c r="Z3" t="n">
-        <v>844.4739999999999</v>
+        <v>127063480.6720969</v>
       </c>
       <c r="AA3" t="n">
         <v>2.152318743749638e-07</v>
@@ -7642,10 +7410,8 @@
       <c r="K4" t="n">
         <v>86.52767524266713</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 16.480x + -8366.976</t>
-        </is>
+      <c r="W4" t="n">
+        <v>16.48049111772875</v>
       </c>
       <c r="X4" t="n">
         <v>-8366.976392895383</v>
@@ -7654,7 +7420,7 @@
         <v>453.5408611539115</v>
       </c>
       <c r="Z4" t="n">
-        <v>691.444</v>
+        <v>866894126.9619812</v>
       </c>
       <c r="AA4" t="n">
         <v>1.963171007952433e-07</v>
@@ -7694,10 +7460,8 @@
       <c r="K5" t="n">
         <v>86.97704545282109</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 18.936x + -9391.428</t>
-        </is>
+      <c r="W5" t="n">
+        <v>18.93597953363713</v>
       </c>
       <c r="X5" t="n">
         <v>-9391.427589237817</v>
@@ -7706,7 +7470,7 @@
         <v>447.951195547946</v>
       </c>
       <c r="Z5" t="n">
-        <v>596.24</v>
+        <v>244803525.546838</v>
       </c>
       <c r="AA5" t="n">
         <v>1.84725242443577e-07</v>
@@ -7746,10 +7510,8 @@
       <c r="K6" t="n">
         <v>87.33710315743693</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 21.501x + -10553.162</t>
-        </is>
+      <c r="W6" t="n">
+        <v>21.50084027900747</v>
       </c>
       <c r="X6" t="n">
         <v>-10553.16174262014</v>
@@ -7758,7 +7520,7 @@
         <v>442.9257617222612</v>
       </c>
       <c r="Z6" t="n">
-        <v>527.187</v>
+        <v>856282864.8633318</v>
       </c>
       <c r="AA6" t="n">
         <v>1.772644914782185e-07</v>
@@ -7798,10 +7560,8 @@
       <c r="K7" t="n">
         <v>87.59032332998324</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 23.763x + -11536.429</t>
-        </is>
+      <c r="W7" t="n">
+        <v>23.76335180213213</v>
       </c>
       <c r="X7" t="n">
         <v>-11536.42873129448</v>
@@ -7810,7 +7570,7 @@
         <v>437.7637461364064</v>
       </c>
       <c r="Z7" t="n">
-        <v>479.942</v>
+        <v>268724466.0924232</v>
       </c>
       <c r="AA7" t="n">
         <v>1.720905355363748e-07</v>
@@ -7850,10 +7610,8 @@
       <c r="K8" t="n">
         <v>87.8143050160608</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 26.201x + -12587.045</t>
-        </is>
+      <c r="W8" t="n">
+        <v>26.2012697335072</v>
       </c>
       <c r="X8" t="n">
         <v>-12587.04489751725</v>
@@ -7862,7 +7620,7 @@
         <v>432.8112250283656</v>
       </c>
       <c r="Z8" t="n">
-        <v>435.574</v>
+        <v>480685736.6744587</v>
       </c>
       <c r="AA8" t="n">
         <v>1.678937175833626e-07</v>
@@ -7902,10 +7660,8 @@
       <c r="K9" t="n">
         <v>87.9145297638772</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 27.462x + -12987.065</t>
-        </is>
+      <c r="W9" t="n">
+        <v>27.46166008361796</v>
       </c>
       <c r="X9" t="n">
         <v>-12987.06484830528</v>
@@ -7914,7 +7670,7 @@
         <v>427.7116423138801</v>
       </c>
       <c r="Z9" t="n">
-        <v>411.447</v>
+        <v>466906241.2131789</v>
       </c>
       <c r="AA9" t="n">
         <v>1.650264029140633e-07</v>
@@ -7954,10 +7710,8 @@
       <c r="K10" t="n">
         <v>88.02824320657038</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 29.047x + -13563.960</t>
-        </is>
+      <c r="W10" t="n">
+        <v>29.04676655345619</v>
       </c>
       <c r="X10" t="n">
         <v>-13563.95959294808</v>
@@ -7966,7 +7720,7 @@
         <v>422.8134724267125</v>
       </c>
       <c r="Z10" t="n">
-        <v>388.778</v>
+        <v>115514300.6546874</v>
       </c>
       <c r="AA10" t="n">
         <v>1.624899104186133e-07</v>
@@ -8006,10 +7760,8 @@
       <c r="K11" t="n">
         <v>88.1294758376914</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 30.620x + -14140.524</t>
-        </is>
+      <c r="W11" t="n">
+        <v>30.61998538944753</v>
       </c>
       <c r="X11" t="n">
         <v>-14140.52357055255</v>
@@ -8018,7 +7770,7 @@
         <v>418.1694107433777</v>
       </c>
       <c r="Z11" t="n">
-        <v>368.522</v>
+        <v>228006258.8307897</v>
       </c>
       <c r="AA11" t="n">
         <v>1.606098128282009e-07</v>
@@ -8144,12 +7896,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8204,10 +7956,8 @@
       <c r="K2" t="n">
         <v>86.99143406142086</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 19.027x + -11445.014</t>
-        </is>
+      <c r="W2" t="n">
+        <v>19.02670963092257</v>
       </c>
       <c r="X2" t="n">
         <v>-11445.01442247303</v>
@@ -8216,7 +7966,7 @@
         <v>411.4847566371973</v>
       </c>
       <c r="Z2" t="n">
-        <v>589.119</v>
+        <v>12805.52047976563</v>
       </c>
       <c r="AA2" t="n">
         <v>2.019861976126505e-07</v>
@@ -8256,10 +8006,8 @@
       <c r="K3" t="n">
         <v>87.69798119081817</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 24.876x + -14334.554</t>
-        </is>
+      <c r="W3" t="n">
+        <v>24.87596797356468</v>
       </c>
       <c r="X3" t="n">
         <v>-14334.55366853595</v>
@@ -8268,7 +8016,7 @@
         <v>406.6230085257923</v>
       </c>
       <c r="Z3" t="n">
-        <v>449.7940000000001</v>
+        <v>12499.71566678819</v>
       </c>
       <c r="AA3" t="n">
         <v>1.958769300755683e-07</v>
@@ -8308,10 +8056,8 @@
       <c r="K4" t="n">
         <v>87.93297297251844</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 27.707x + -15655.220</t>
-        </is>
+      <c r="W4" t="n">
+        <v>27.70690446285733</v>
       </c>
       <c r="X4" t="n">
         <v>-15655.2204556749</v>
@@ -8320,7 +8066,7 @@
         <v>496.8019119526533</v>
       </c>
       <c r="Z4" t="n">
-        <v>392.052</v>
+        <v>38329289.77467448</v>
       </c>
       <c r="AA4" t="n">
         <v>1.702237719215283e-07</v>
@@ -8360,10 +8106,8 @@
       <c r="K5" t="n">
         <v>88.1673149802655</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 31.253x + -17552.902</t>
-        </is>
+      <c r="W5" t="n">
+        <v>31.2526360170059</v>
       </c>
       <c r="X5" t="n">
         <v>-17552.9021772235</v>
@@ -8372,7 +8116,7 @@
         <v>492.5871603537111</v>
       </c>
       <c r="Z5" t="n">
-        <v>350.797</v>
+        <v>206150332.7870738</v>
       </c>
       <c r="AA5" t="n">
         <v>1.66218556101196e-07</v>
@@ -8412,10 +8156,8 @@
       <c r="K6" t="n">
         <v>88.20694045728443</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 31.944x + -17665.173</t>
-        </is>
+      <c r="W6" t="n">
+        <v>31.94376564284343</v>
       </c>
       <c r="X6" t="n">
         <v>-17665.17301877854</v>
@@ -8424,7 +8166,7 @@
         <v>488.1433242255991</v>
       </c>
       <c r="Z6" t="n">
-        <v>331.1610000000001</v>
+        <v>533020840.2533325</v>
       </c>
       <c r="AA6" t="n">
         <v>1.636272364173152e-07</v>
@@ -8464,10 +8206,8 @@
       <c r="K7" t="n">
         <v>88.34535717654239</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 34.618x + -19045.017</t>
-        </is>
+      <c r="W7" t="n">
+        <v>34.61765263849517</v>
       </c>
       <c r="X7" t="n">
         <v>-19045.01738430858</v>
@@ -8476,7 +8216,7 @@
         <v>483.708953156379</v>
       </c>
       <c r="Z7" t="n">
-        <v>313.47</v>
+        <v>528397900.0558928</v>
       </c>
       <c r="AA7" t="n">
         <v>1.619029547129035e-07</v>
@@ -8516,10 +8256,8 @@
       <c r="K8" t="n">
         <v>88.36962109374078</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 35.133x + -19086.189</t>
-        </is>
+      <c r="W8" t="n">
+        <v>35.13313012917322</v>
       </c>
       <c r="X8" t="n">
         <v>-19086.18945467061</v>
@@ -8528,7 +8266,7 @@
         <v>479.120900958271</v>
       </c>
       <c r="Z8" t="n">
-        <v>306.149</v>
+        <v>27815257.0629561</v>
       </c>
       <c r="AA8" t="n">
         <v>1.604447601736841e-07</v>
@@ -8568,10 +8306,8 @@
       <c r="K9" t="n">
         <v>88.36376478389015</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 35.007x + -18740.190</t>
-        </is>
+      <c r="W9" t="n">
+        <v>35.00731581978029</v>
       </c>
       <c r="X9" t="n">
         <v>-18740.19042748851</v>
@@ -8580,7 +8316,7 @@
         <v>474.6818010733176</v>
       </c>
       <c r="Z9" t="n">
-        <v>298.102</v>
+        <v>209061758.1705164</v>
       </c>
       <c r="AA9" t="n">
         <v>1.594313289769467e-07</v>
@@ -8620,10 +8356,8 @@
       <c r="K10" t="n">
         <v>88.41430249651171</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 36.124x + -19162.233</t>
-        </is>
+      <c r="W10" t="n">
+        <v>36.12363028953727</v>
       </c>
       <c r="X10" t="n">
         <v>-19162.2325878878</v>
@@ -8632,7 +8366,7 @@
         <v>470.4776566608213</v>
       </c>
       <c r="Z10" t="n">
-        <v>288.6429999999999</v>
+        <v>376317361.8949968</v>
       </c>
       <c r="AA10" t="n">
         <v>1.584780816567173e-07</v>
@@ -8672,10 +8406,8 @@
       <c r="K11" t="n">
         <v>88.46027909897302</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 37.203x + -19537.476</t>
-        </is>
+      <c r="W11" t="n">
+        <v>37.20283747653777</v>
       </c>
       <c r="X11" t="n">
         <v>-19537.47587190667</v>
@@ -8684,7 +8416,7 @@
         <v>466.3157580589374</v>
       </c>
       <c r="Z11" t="n">
-        <v>278.92</v>
+        <v>184502702.3353789</v>
       </c>
       <c r="AA11" t="n">
         <v>1.574328816867003e-07</v>
@@ -8724,10 +8456,8 @@
       <c r="K12" t="n">
         <v>88.45790751371491</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 37.146x + -19293.522</t>
-        </is>
+      <c r="W12" t="n">
+        <v>37.14559562717868</v>
       </c>
       <c r="X12" t="n">
         <v>-19293.52170483638</v>
@@ -8736,7 +8466,7 @@
         <v>462.4596568639181</v>
       </c>
       <c r="Z12" t="n">
-        <v>276.6859999999999</v>
+        <v>252268722.3131012</v>
       </c>
       <c r="AA12" t="n">
         <v>1.568592973788237e-07</v>
@@ -8776,10 +8506,8 @@
       <c r="K13" t="n">
         <v>88.48120916935508</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 37.716x + -19418.176</t>
-        </is>
+      <c r="W13" t="n">
+        <v>37.71576555712016</v>
       </c>
       <c r="X13" t="n">
         <v>-19418.17589975747</v>
@@ -8788,7 +8516,7 @@
         <v>459.0536672754662</v>
       </c>
       <c r="Z13" t="n">
-        <v>270.665</v>
+        <v>500444557.5419207</v>
       </c>
       <c r="AA13" t="n">
         <v>1.56204689521897e-07</v>
@@ -8828,10 +8556,8 @@
       <c r="K14" t="n">
         <v>88.50555168438382</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 38.330x + -19580.677</t>
-        </is>
+      <c r="W14" t="n">
+        <v>38.33038926246649</v>
       </c>
       <c r="X14" t="n">
         <v>-19580.67726198515</v>
@@ -8840,7 +8566,7 @@
         <v>455.9005693837224</v>
       </c>
       <c r="Z14" t="n">
-        <v>266.7959999999999</v>
+        <v>20455725.14820769</v>
       </c>
       <c r="AA14" t="n">
         <v>1.552862953913366e-07</v>
@@ -8880,10 +8606,8 @@
       <c r="K15" t="n">
         <v>88.56203744312006</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 39.837x + -20255.006</t>
-        </is>
+      <c r="W15" t="n">
+        <v>39.83674618757358</v>
       </c>
       <c r="X15" t="n">
         <v>-20255.00593051117</v>
@@ -8892,7 +8616,7 @@
         <v>452.9030260230035</v>
       </c>
       <c r="Z15" t="n">
-        <v>261.222</v>
+        <v>31005403.79109703</v>
       </c>
       <c r="AA15" t="n">
         <v>1.548692116930682e-07</v>
@@ -8932,10 +8656,8 @@
       <c r="K16" t="n">
         <v>88.63150128014676</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 41.860x + -21207.900</t>
-        </is>
+      <c r="W16" t="n">
+        <v>41.85965454286513</v>
       </c>
       <c r="X16" t="n">
         <v>-21207.89974175621</v>
@@ -8944,7 +8666,7 @@
         <v>449.9864692495883</v>
       </c>
       <c r="Z16" t="n">
-        <v>254.509</v>
+        <v>63631055.82727703</v>
       </c>
       <c r="AA16" t="n">
         <v>1.545176062880895e-07</v>
@@ -8984,10 +8706,8 @@
       <c r="K17" t="n">
         <v>88.64734493622599</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 42.350x + -21310.610</t>
-        </is>
+      <c r="W17" t="n">
+        <v>42.35014234586185</v>
       </c>
       <c r="X17" t="n">
         <v>-21310.61041361716</v>
@@ -8996,7 +8716,7 @@
         <v>447.16368423153</v>
       </c>
       <c r="Z17" t="n">
-        <v>251.8969999999999</v>
+        <v>29137634.58581872</v>
       </c>
       <c r="AA17" t="n">
         <v>1.53973230184615e-07</v>
@@ -9036,10 +8756,8 @@
       <c r="K18" t="n">
         <v>88.64176660387149</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 42.176x + -21027.092</t>
-        </is>
+      <c r="W18" t="n">
+        <v>42.17614341893815</v>
       </c>
       <c r="X18" t="n">
         <v>-21027.09218341374</v>
@@ -9048,7 +8766,7 @@
         <v>444.3426586010088</v>
       </c>
       <c r="Z18" t="n">
-        <v>248.052</v>
+        <v>243619641.034614</v>
       </c>
       <c r="AA18" t="n">
         <v>1.53662878373613e-07</v>
@@ -9088,10 +8806,8 @@
       <c r="K19" t="n">
         <v>88.6415447618203</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 42.169x + -20863.324</t>
-        </is>
+      <c r="W19" t="n">
+        <v>42.16925327755298</v>
       </c>
       <c r="X19" t="n">
         <v>-20863.32448287797</v>
@@ -9100,7 +8816,7 @@
         <v>382.5665925025276</v>
       </c>
       <c r="Z19" t="n">
-        <v>247.234</v>
+        <v>14640.61363609664</v>
       </c>
       <c r="AA19" t="n">
         <v>1.840020828968935e-07</v>
@@ -9140,10 +8856,8 @@
       <c r="K20" t="n">
         <v>88.62503337343971</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 41.663x + -20423.788</t>
-        </is>
+      <c r="W20" t="n">
+        <v>41.66266970249227</v>
       </c>
       <c r="X20" t="n">
         <v>-20423.78777180623</v>
@@ -9152,7 +8866,7 @@
         <v>384.0746943260944</v>
       </c>
       <c r="Z20" t="n">
-        <v>247.227</v>
+        <v>14528.86542580894</v>
       </c>
       <c r="AA20" t="n">
         <v>1.807623170057344e-07</v>
@@ -9192,10 +8906,8 @@
       <c r="K21" t="n">
         <v>88.65168799164165</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 42.487x + -20697.076</t>
-        </is>
+      <c r="W21" t="n">
+        <v>42.48660724714126</v>
       </c>
       <c r="X21" t="n">
         <v>-20697.07563756706</v>
@@ -9204,7 +8916,7 @@
         <v>383.3399647353281</v>
       </c>
       <c r="Z21" t="n">
-        <v>242.819</v>
+        <v>14444.32641952303</v>
       </c>
       <c r="AA21" t="n">
         <v>1.830018224121077e-07</v>
@@ -9244,10 +8956,8 @@
       <c r="K22" t="n">
         <v>88.63309405342189</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 41.908x + -20228.362</t>
-        </is>
+      <c r="W22" t="n">
+        <v>41.90844962525627</v>
       </c>
       <c r="X22" t="n">
         <v>-20228.36187724904</v>
@@ -9256,7 +8966,7 @@
         <v>384.3909374771277</v>
       </c>
       <c r="Z22" t="n">
-        <v>240.8340000000001</v>
+        <v>14340.04024074499</v>
       </c>
       <c r="AA22" t="n">
         <v>1.828160608103209e-07</v>
@@ -9382,12 +9092,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9442,10 +9152,8 @@
       <c r="K2" t="n">
         <v>84.8139623061827</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 11.018x + -6003.296</t>
-        </is>
+      <c r="W2" t="n">
+        <v>11.01789625690584</v>
       </c>
       <c r="X2" t="n">
         <v>-6003.296112035475</v>
@@ -9454,7 +9162,7 @@
         <v>464.9724588880945</v>
       </c>
       <c r="Z2" t="n">
-        <v>985.4110000000001</v>
+        <v>220306949.1122401</v>
       </c>
       <c r="AA2" t="n">
         <v>2.374492149744388e-07</v>
@@ -9494,10 +9202,8 @@
       <c r="K3" t="n">
         <v>86.62458325486665</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 16.955x + -8212.592</t>
-        </is>
+      <c r="W3" t="n">
+        <v>16.9547893359629</v>
       </c>
       <c r="X3" t="n">
         <v>-8212.592004588181</v>
@@ -9506,7 +9212,7 @@
         <v>434.490743922799</v>
       </c>
       <c r="Z3" t="n">
-        <v>656.3070000000001</v>
+        <v>237105640.0677775</v>
       </c>
       <c r="AA3" t="n">
         <v>1.954888243984967e-07</v>
@@ -9546,10 +9252,8 @@
       <c r="K4" t="n">
         <v>87.3890273612713</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 21.929x + -10330.032</t>
-        </is>
+      <c r="W4" t="n">
+        <v>21.92903611373315</v>
       </c>
       <c r="X4" t="n">
         <v>-10330.03164878563</v>
@@ -9558,7 +9262,7 @@
         <v>425.7608775569464</v>
       </c>
       <c r="Z4" t="n">
-        <v>510.7180000000001</v>
+        <v>348104184.3594183</v>
       </c>
       <c r="AA4" t="n">
         <v>1.794161866603849e-07</v>
@@ -9598,10 +9302,8 @@
       <c r="K5" t="n">
         <v>87.77139012119497</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 25.696x + -11897.868</t>
-        </is>
+      <c r="W5" t="n">
+        <v>25.6962342498526</v>
       </c>
       <c r="X5" t="n">
         <v>-11897.86760157973</v>
@@ -9610,7 +9312,7 @@
         <v>420.4304966360089</v>
       </c>
       <c r="Z5" t="n">
-        <v>430.376</v>
+        <v>458055224.3765739</v>
       </c>
       <c r="AA5" t="n">
         <v>1.710629628121894e-07</v>
@@ -9650,10 +9352,8 @@
       <c r="K6" t="n">
         <v>88.03533260284908</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 29.152x + -13355.927</t>
-        </is>
+      <c r="W6" t="n">
+        <v>29.15166289375034</v>
       </c>
       <c r="X6" t="n">
         <v>-13355.92669654902</v>
@@ -9662,7 +9362,7 @@
         <v>397.8913973704734</v>
       </c>
       <c r="Z6" t="n">
-        <v>379.626</v>
+        <v>3397.831774943771</v>
       </c>
       <c r="AA6" t="n">
         <v>3.571162943572849e-06</v>
@@ -9702,10 +9402,8 @@
       <c r="K7" t="n">
         <v>88.13283198947201</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 30.675x + -13800.841</t>
-        </is>
+      <c r="W7" t="n">
+        <v>30.67506254791456</v>
       </c>
       <c r="X7" t="n">
         <v>-13800.84145847396</v>
@@ -9714,7 +9412,7 @@
         <v>410.1174022247833</v>
       </c>
       <c r="Z7" t="n">
-        <v>351.289</v>
+        <v>334276082.5770438</v>
       </c>
       <c r="AA7" t="n">
         <v>1.630213256622675e-07</v>
@@ -9754,10 +9452,8 @@
       <c r="K8" t="n">
         <v>88.27693489298296</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 33.242x + -14793.300</t>
-        </is>
+      <c r="W8" t="n">
+        <v>33.24221793349674</v>
       </c>
       <c r="X8" t="n">
         <v>-14793.3004948806</v>
@@ -9766,7 +9462,7 @@
         <v>396.2959188826026</v>
       </c>
       <c r="Z8" t="n">
-        <v>326.248</v>
+        <v>6346.574506333167</v>
       </c>
       <c r="AA8" t="n">
         <v>1.356028611338022e-06</v>
@@ -9806,10 +9502,8 @@
       <c r="K9" t="n">
         <v>88.37610270270885</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 35.273x + -15514.394</t>
-        </is>
+      <c r="W9" t="n">
+        <v>35.2734357622226</v>
       </c>
       <c r="X9" t="n">
         <v>-15514.39383203477</v>
@@ -9818,7 +9512,7 @@
         <v>392.3626232627054</v>
       </c>
       <c r="Z9" t="n">
-        <v>310.277</v>
+        <v>5996.277670237979</v>
       </c>
       <c r="AA9" t="n">
         <v>8.64233392790516e-07</v>
@@ -9858,10 +9552,8 @@
       <c r="K10" t="n">
         <v>88.40072588932526</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 35.817x + -15488.914</t>
-        </is>
+      <c r="W10" t="n">
+        <v>35.81681113464622</v>
       </c>
       <c r="X10" t="n">
         <v>-15488.91399378103</v>
@@ -9870,7 +9562,7 @@
         <v>395.169689835852</v>
       </c>
       <c r="Z10" t="n">
-        <v>296.297</v>
+        <v>858168112.426217</v>
       </c>
       <c r="AA10" t="n">
         <v>1.578396045130931e-07</v>
@@ -9910,10 +9602,8 @@
       <c r="K11" t="n">
         <v>88.48310651177644</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 37.763x + -16175.818</t>
-        </is>
+      <c r="W11" t="n">
+        <v>37.76296282865111</v>
       </c>
       <c r="X11" t="n">
         <v>-16175.81827169919</v>
@@ -9922,7 +9612,7 @@
         <v>390.8990093260031</v>
       </c>
       <c r="Z11" t="n">
-        <v>284.457</v>
+        <v>106492834.8877234</v>
       </c>
       <c r="AA11" t="n">
         <v>1.56732814570492e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 44.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 44.xlsx
@@ -428,7 +428,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -559,7 +559,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-553.0369999999999</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-497.374</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-459.6539999999999</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-431.9299999999999</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-419.816</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-397.246</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-384.735</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-378.247</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-359.98</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-353.0020000000001</v>
@@ -1074,7 +1074,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2270,7 +2270,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3597,7 +3597,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-986.109</v>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-722.866</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-600.921</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-524.385</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-476.685</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-440.562</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-413.5529999999999</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-394.6850000000001</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-375.1689999999999</v>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-359.9040000000001</v>
@@ -4112,7 +4112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5439,7 +5439,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-1056.626</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-811.0740000000001</v>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-670.4369999999999</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-587.011</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-529.675</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-481.646</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-449.7590000000001</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-428.611</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-406.5040000000001</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-390.01</v>
@@ -5954,7 +5954,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7281,7 +7281,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-1116.007</v>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-844.4739999999999</v>
@@ -7381,7 +7381,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-691.444</v>
@@ -7431,7 +7431,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-596.24</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-527.187</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-479.942</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-435.574</v>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-411.447</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-388.778</v>
@@ -7731,7 +7731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-368.522</v>
@@ -7796,7 +7796,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -8992,7 +8992,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -9123,7 +9123,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-985.4110000000001</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-656.3070000000001</v>
@@ -9223,7 +9223,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-510.7180000000001</v>
@@ -9273,7 +9273,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-430.376</v>
@@ -9323,7 +9323,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-379.626</v>
@@ -9373,7 +9373,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-351.289</v>
@@ -9423,7 +9423,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-326.248</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-310.277</v>
@@ -9523,7 +9523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-296.297</v>
@@ -9573,7 +9573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-284.457</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 44.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 44.xlsx
@@ -562,7 +562,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-553.0369999999999</v>
+        <v>165.3560000000001</v>
       </c>
       <c r="D2" t="n">
         <v>1.20671e-07</v>
@@ -612,7 +612,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-497.374</v>
+        <v>159.085</v>
       </c>
       <c r="D3" t="n">
         <v>1.19954e-07</v>
@@ -662,7 +662,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-459.6539999999999</v>
+        <v>153.983</v>
       </c>
       <c r="D4" t="n">
         <v>1.19583e-07</v>
@@ -712,7 +712,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-431.9299999999999</v>
+        <v>151.135</v>
       </c>
       <c r="D5" t="n">
         <v>1.19433e-07</v>
@@ -762,7 +762,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-419.816</v>
+        <v>139.909</v>
       </c>
       <c r="D6" t="n">
         <v>1.19324e-07</v>
@@ -812,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-397.246</v>
+        <v>139.419</v>
       </c>
       <c r="D7" t="n">
         <v>1.19321e-07</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-384.735</v>
+        <v>133.6900000000001</v>
       </c>
       <c r="D8" t="n">
         <v>1.19347e-07</v>
@@ -912,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-378.247</v>
+        <v>123.512</v>
       </c>
       <c r="D9" t="n">
         <v>1.19379e-07</v>
@@ -962,7 +962,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-359.98</v>
+        <v>128.252</v>
       </c>
       <c r="D10" t="n">
         <v>1.19423e-07</v>
@@ -1012,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-353.0020000000001</v>
+        <v>124.595</v>
       </c>
       <c r="D11" t="n">
         <v>1.19487e-07</v>
@@ -1208,7 +1208,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-337.229</v>
+        <v>156.985</v>
       </c>
       <c r="D2" t="n">
         <v>1.31074e-07</v>
@@ -1258,7 +1258,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-307.612</v>
+        <v>133.288</v>
       </c>
       <c r="D3" t="n">
         <v>1.31092e-07</v>
@@ -1308,7 +1308,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-290.1850000000001</v>
+        <v>128.7099999999999</v>
       </c>
       <c r="D4" t="n">
         <v>1.30923e-07</v>
@@ -1358,7 +1358,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-279.684</v>
+        <v>124.245</v>
       </c>
       <c r="D5" t="n">
         <v>1.30831e-07</v>
@@ -1408,7 +1408,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-272.276</v>
+        <v>120.6560000000001</v>
       </c>
       <c r="D6" t="n">
         <v>1.30732e-07</v>
@@ -1458,7 +1458,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-267.3969999999999</v>
+        <v>116.7300000000001</v>
       </c>
       <c r="D7" t="n">
         <v>1.30672e-07</v>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-264.516</v>
+        <v>113.102</v>
       </c>
       <c r="D8" t="n">
         <v>1.30625e-07</v>
@@ -1558,7 +1558,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-256.321</v>
+        <v>113.992</v>
       </c>
       <c r="D9" t="n">
         <v>1.30557e-07</v>
@@ -1608,7 +1608,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-252.991</v>
+        <v>109.841</v>
       </c>
       <c r="D10" t="n">
         <v>1.30502e-07</v>
@@ -1658,7 +1658,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-250.708</v>
+        <v>107.521</v>
       </c>
       <c r="D11" t="n">
         <v>1.30461e-07</v>
@@ -1708,7 +1708,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-247.0309999999999</v>
+        <v>107.365</v>
       </c>
       <c r="D12" t="n">
         <v>1.30396e-07</v>
@@ -1758,7 +1758,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-243.6439999999999</v>
+        <v>102.9</v>
       </c>
       <c r="D13" t="n">
         <v>1.30336e-07</v>
@@ -1808,7 +1808,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-239.736</v>
+        <v>103.528</v>
       </c>
       <c r="D14" t="n">
         <v>1.30318e-07</v>
@@ -1858,7 +1858,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-239.864</v>
+        <v>99.56200000000001</v>
       </c>
       <c r="D15" t="n">
         <v>1.30283e-07</v>
@@ -1908,7 +1908,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-234.0529999999999</v>
+        <v>99.94499999999999</v>
       </c>
       <c r="D16" t="n">
         <v>1.3024e-07</v>
@@ -1958,7 +1958,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-235.574</v>
+        <v>97.38499999999999</v>
       </c>
       <c r="D17" t="n">
         <v>1.30212e-07</v>
@@ -2008,7 +2008,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-232.062</v>
+        <v>94.57000000000005</v>
       </c>
       <c r="D18" t="n">
         <v>1.302e-07</v>
@@ -2058,7 +2058,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-226.016</v>
+        <v>97.08100000000002</v>
       </c>
       <c r="D19" t="n">
         <v>1.30153e-07</v>
@@ -2108,7 +2108,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-224.78</v>
+        <v>96.137</v>
       </c>
       <c r="D20" t="n">
         <v>1.30162e-07</v>
@@ -2158,7 +2158,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-221.1290000000001</v>
+        <v>94.35799999999995</v>
       </c>
       <c r="D21" t="n">
         <v>1.30124e-07</v>
@@ -2208,7 +2208,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-223.675</v>
+        <v>90.22499999999997</v>
       </c>
       <c r="D22" t="n">
         <v>1.30106e-07</v>
@@ -2404,7 +2404,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-592.948</v>
+        <v>173.051</v>
       </c>
       <c r="D2" t="n">
         <v>1.25063e-07</v>
@@ -2454,7 +2454,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-461.2750000000001</v>
+        <v>149.7909999999999</v>
       </c>
       <c r="D3" t="n">
         <v>1.23272e-07</v>
@@ -2504,7 +2504,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-409.583</v>
+        <v>144.8030000000001</v>
       </c>
       <c r="D4" t="n">
         <v>1.22369e-07</v>
@@ -2554,7 +2554,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-379.999</v>
+        <v>141.254</v>
       </c>
       <c r="D5" t="n">
         <v>1.21862e-07</v>
@@ -2604,7 +2604,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-364.242</v>
+        <v>134.606</v>
       </c>
       <c r="D6" t="n">
         <v>1.21539e-07</v>
@@ -2654,7 +2654,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-347.5880000000001</v>
+        <v>132.833</v>
       </c>
       <c r="D7" t="n">
         <v>1.21327e-07</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-338.093</v>
+        <v>129.3650000000001</v>
       </c>
       <c r="D8" t="n">
         <v>1.21216e-07</v>
@@ -2754,7 +2754,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-330.276</v>
+        <v>126.149</v>
       </c>
       <c r="D9" t="n">
         <v>1.21129e-07</v>
@@ -2804,7 +2804,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-326.2660000000001</v>
+        <v>121.513</v>
       </c>
       <c r="D10" t="n">
         <v>1.21079e-07</v>
@@ -2854,7 +2854,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-317.47</v>
+        <v>118.6129999999999</v>
       </c>
       <c r="D11" t="n">
         <v>1.21056e-07</v>
@@ -2904,7 +2904,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-314.12</v>
+        <v>113.862</v>
       </c>
       <c r="D12" t="n">
         <v>1.21028e-07</v>
@@ -2954,7 +2954,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-306.949</v>
+        <v>115.446</v>
       </c>
       <c r="D13" t="n">
         <v>1.21043e-07</v>
@@ -3004,7 +3004,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-303.97</v>
+        <v>113.891</v>
       </c>
       <c r="D14" t="n">
         <v>1.21058e-07</v>
@@ -3054,7 +3054,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-298.276</v>
+        <v>111.984</v>
       </c>
       <c r="D15" t="n">
         <v>1.21044e-07</v>
@@ -3104,7 +3104,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-296.371</v>
+        <v>110.748</v>
       </c>
       <c r="D16" t="n">
         <v>1.21072e-07</v>
@@ -3154,7 +3154,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-289.057</v>
+        <v>109.53</v>
       </c>
       <c r="D17" t="n">
         <v>1.21078e-07</v>
@@ -3204,7 +3204,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-291.61</v>
+        <v>104.501</v>
       </c>
       <c r="D18" t="n">
         <v>1.21099e-07</v>
@@ -3254,7 +3254,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-282.7089999999999</v>
+        <v>106.825</v>
       </c>
       <c r="D19" t="n">
         <v>1.21126e-07</v>
@@ -3304,7 +3304,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-282.302</v>
+        <v>105.208</v>
       </c>
       <c r="D20" t="n">
         <v>1.21159e-07</v>
@@ -3354,7 +3354,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-275.712</v>
+        <v>102.46</v>
       </c>
       <c r="D21" t="n">
         <v>1.21189e-07</v>
@@ -3404,7 +3404,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-282.243</v>
+        <v>99.137</v>
       </c>
       <c r="D22" t="n">
         <v>1.21212e-07</v>
@@ -3600,7 +3600,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-986.109</v>
+        <v>154.168</v>
       </c>
       <c r="D2" t="n">
         <v>1.32747e-07</v>
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-722.866</v>
+        <v>121.446</v>
       </c>
       <c r="D3" t="n">
         <v>1.30919e-07</v>
@@ -3700,7 +3700,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-600.921</v>
+        <v>111.069</v>
       </c>
       <c r="D4" t="n">
         <v>1.29034e-07</v>
@@ -3750,7 +3750,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-524.385</v>
+        <v>107.997</v>
       </c>
       <c r="D5" t="n">
         <v>1.27686e-07</v>
@@ -3800,7 +3800,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-476.685</v>
+        <v>101.894</v>
       </c>
       <c r="D6" t="n">
         <v>1.26802e-07</v>
@@ -3850,7 +3850,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-440.562</v>
+        <v>100.205</v>
       </c>
       <c r="D7" t="n">
         <v>1.26186e-07</v>
@@ -3900,7 +3900,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-413.5529999999999</v>
+        <v>98.029</v>
       </c>
       <c r="D8" t="n">
         <v>1.25762e-07</v>
@@ -3950,7 +3950,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-394.6850000000001</v>
+        <v>91.62099999999998</v>
       </c>
       <c r="D9" t="n">
         <v>1.25455e-07</v>
@@ -4000,7 +4000,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-375.1689999999999</v>
+        <v>92.24700000000001</v>
       </c>
       <c r="D10" t="n">
         <v>1.25236e-07</v>
@@ -4050,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-359.9040000000001</v>
+        <v>89.62699999999995</v>
       </c>
       <c r="D11" t="n">
         <v>1.2505e-07</v>
@@ -4246,7 +4246,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-635.5000000000001</v>
+        <v>169.186</v>
       </c>
       <c r="D2" t="n">
         <v>1.30706e-07</v>
@@ -4296,7 +4296,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-490.831</v>
+        <v>144.4109999999999</v>
       </c>
       <c r="D3" t="n">
         <v>1.28327e-07</v>
@@ -4346,7 +4346,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-425.772</v>
+        <v>140.296</v>
       </c>
       <c r="D4" t="n">
         <v>1.27039e-07</v>
@@ -4396,7 +4396,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-387.563</v>
+        <v>133.29</v>
       </c>
       <c r="D5" t="n">
         <v>1.26238e-07</v>
@@ -4446,7 +4446,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-360.293</v>
+        <v>130.823</v>
       </c>
       <c r="D6" t="n">
         <v>1.25732e-07</v>
@@ -4496,7 +4496,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-344.453</v>
+        <v>126.859</v>
       </c>
       <c r="D7" t="n">
         <v>1.25378e-07</v>
@@ -4546,7 +4546,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-332.53</v>
+        <v>124.0930000000001</v>
       </c>
       <c r="D8" t="n">
         <v>1.25107e-07</v>
@@ -4596,7 +4596,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-319.693</v>
+        <v>122.473</v>
       </c>
       <c r="D9" t="n">
         <v>1.2493e-07</v>
@@ -4646,7 +4646,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-313.4730000000001</v>
+        <v>119.389</v>
       </c>
       <c r="D10" t="n">
         <v>1.2475e-07</v>
@@ -4696,7 +4696,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-308.6129999999999</v>
+        <v>115.222</v>
       </c>
       <c r="D11" t="n">
         <v>1.24627e-07</v>
@@ -4746,7 +4746,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-297.4870000000001</v>
+        <v>114.9059999999999</v>
       </c>
       <c r="D12" t="n">
         <v>1.24514e-07</v>
@@ -4796,7 +4796,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-295.8099999999999</v>
+        <v>111.524</v>
       </c>
       <c r="D13" t="n">
         <v>1.24428e-07</v>
@@ -4846,7 +4846,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-294.326</v>
+        <v>107.45</v>
       </c>
       <c r="D14" t="n">
         <v>1.24404e-07</v>
@@ -4896,7 +4896,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-284.7909999999999</v>
+        <v>109.852</v>
       </c>
       <c r="D15" t="n">
         <v>1.24345e-07</v>
@@ -4946,7 +4946,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-281.174</v>
+        <v>107.895</v>
       </c>
       <c r="D16" t="n">
         <v>1.24315e-07</v>
@@ -4996,7 +4996,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-277.816</v>
+        <v>107.553</v>
       </c>
       <c r="D17" t="n">
         <v>1.2423e-07</v>
@@ -5046,7 +5046,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-274.038</v>
+        <v>105.43</v>
       </c>
       <c r="D18" t="n">
         <v>1.24185e-07</v>
@@ -5096,7 +5096,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-268.314</v>
+        <v>104.552</v>
       </c>
       <c r="D19" t="n">
         <v>1.24146e-07</v>
@@ -5146,7 +5146,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-266.547</v>
+        <v>102.219</v>
       </c>
       <c r="D20" t="n">
         <v>1.24131e-07</v>
@@ -5196,7 +5196,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-265.449</v>
+        <v>101.271</v>
       </c>
       <c r="D21" t="n">
         <v>1.24162e-07</v>
@@ -5246,7 +5246,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-260.703</v>
+        <v>99.02199999999999</v>
       </c>
       <c r="D22" t="n">
         <v>1.24093e-07</v>
@@ -5442,7 +5442,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-1056.626</v>
+        <v>170.454</v>
       </c>
       <c r="D2" t="n">
         <v>1.35515e-07</v>
@@ -5492,7 +5492,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-811.0740000000001</v>
+        <v>113.733</v>
       </c>
       <c r="D3" t="n">
         <v>1.3576e-07</v>
@@ -5542,7 +5542,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-670.4369999999999</v>
+        <v>104.842</v>
       </c>
       <c r="D4" t="n">
         <v>1.33892e-07</v>
@@ -5592,7 +5592,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-587.011</v>
+        <v>97.59699999999998</v>
       </c>
       <c r="D5" t="n">
         <v>1.32242e-07</v>
@@ -5642,7 +5642,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-529.675</v>
+        <v>92.56700000000001</v>
       </c>
       <c r="D6" t="n">
         <v>1.31062e-07</v>
@@ -5692,7 +5692,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-481.646</v>
+        <v>95.73299999999995</v>
       </c>
       <c r="D7" t="n">
         <v>1.3019e-07</v>
@@ -5742,7 +5742,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-449.7590000000001</v>
+        <v>90.78199999999998</v>
       </c>
       <c r="D8" t="n">
         <v>1.29518e-07</v>
@@ -5792,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-428.611</v>
+        <v>87.36899999999997</v>
       </c>
       <c r="D9" t="n">
         <v>1.28996e-07</v>
@@ -5842,7 +5842,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-406.5040000000001</v>
+        <v>84.72799999999995</v>
       </c>
       <c r="D10" t="n">
         <v>1.28643e-07</v>
@@ -5892,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-390.01</v>
+        <v>82.678</v>
       </c>
       <c r="D11" t="n">
         <v>1.28332e-07</v>
@@ -6088,7 +6088,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-605.5409999999999</v>
+        <v>165.807</v>
       </c>
       <c r="D2" t="n">
         <v>1.3174e-07</v>
@@ -6138,7 +6138,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-477.905</v>
+        <v>142.9909999999999</v>
       </c>
       <c r="D3" t="n">
         <v>1.29904e-07</v>
@@ -6188,7 +6188,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-418.8009999999999</v>
+        <v>134.7570000000001</v>
       </c>
       <c r="D4" t="n">
         <v>1.28818e-07</v>
@@ -6238,7 +6238,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-379.134</v>
+        <v>136.796</v>
       </c>
       <c r="D5" t="n">
         <v>1.28102e-07</v>
@@ -6288,7 +6288,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-358.9870000000001</v>
+        <v>130.842</v>
       </c>
       <c r="D6" t="n">
         <v>1.27721e-07</v>
@@ -6338,7 +6338,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-343.6850000000001</v>
+        <v>128.361</v>
       </c>
       <c r="D7" t="n">
         <v>1.27421e-07</v>
@@ -6388,7 +6388,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-334.998</v>
+        <v>123.628</v>
       </c>
       <c r="D8" t="n">
         <v>1.27209e-07</v>
@@ -6438,7 +6438,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-323.74</v>
+        <v>122.629</v>
       </c>
       <c r="D9" t="n">
         <v>1.27064e-07</v>
@@ -6488,7 +6488,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-316.516</v>
+        <v>118.23</v>
       </c>
       <c r="D10" t="n">
         <v>1.26921e-07</v>
@@ -6538,7 +6538,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-307.014</v>
+        <v>118.027</v>
       </c>
       <c r="D11" t="n">
         <v>1.26801e-07</v>
@@ -6588,7 +6588,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-299.1220000000001</v>
+        <v>117.991</v>
       </c>
       <c r="D12" t="n">
         <v>1.26742e-07</v>
@@ -6638,7 +6638,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-294.813</v>
+        <v>115.196</v>
       </c>
       <c r="D13" t="n">
         <v>1.26635e-07</v>
@@ -6688,7 +6688,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-290.412</v>
+        <v>113.675</v>
       </c>
       <c r="D14" t="n">
         <v>1.26562e-07</v>
@@ -6738,7 +6738,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-288.622</v>
+        <v>109.821</v>
       </c>
       <c r="D15" t="n">
         <v>1.26515e-07</v>
@@ -6788,7 +6788,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-284.066</v>
+        <v>109.083</v>
       </c>
       <c r="D16" t="n">
         <v>1.2646e-07</v>
@@ -6838,7 +6838,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-279.795</v>
+        <v>108.769</v>
       </c>
       <c r="D17" t="n">
         <v>1.26394e-07</v>
@@ -6888,7 +6888,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-275.567</v>
+        <v>107.908</v>
       </c>
       <c r="D18" t="n">
         <v>1.26374e-07</v>
@@ -6938,7 +6938,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-270.004</v>
+        <v>105.775</v>
       </c>
       <c r="D19" t="n">
         <v>1.2638e-07</v>
@@ -6988,7 +6988,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-266.783</v>
+        <v>105.679</v>
       </c>
       <c r="D20" t="n">
         <v>1.26328e-07</v>
@@ -7038,7 +7038,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-262.7550000000001</v>
+        <v>104.663</v>
       </c>
       <c r="D21" t="n">
         <v>1.2629e-07</v>
@@ -7088,7 +7088,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-262.084</v>
+        <v>100.023</v>
       </c>
       <c r="D22" t="n">
         <v>1.26279e-07</v>
@@ -7284,7 +7284,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-1116.007</v>
+        <v>166.581</v>
       </c>
       <c r="D2" t="n">
         <v>1.3844e-07</v>
@@ -7334,7 +7334,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-844.4739999999999</v>
+        <v>117.392</v>
       </c>
       <c r="D3" t="n">
         <v>1.37784e-07</v>
@@ -7384,7 +7384,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-691.444</v>
+        <v>107.657</v>
       </c>
       <c r="D4" t="n">
         <v>1.35504e-07</v>
@@ -7434,7 +7434,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-596.24</v>
+        <v>97.62200000000001</v>
       </c>
       <c r="D5" t="n">
         <v>1.33706e-07</v>
@@ -7484,7 +7484,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-527.187</v>
+        <v>96.35000000000002</v>
       </c>
       <c r="D6" t="n">
         <v>1.32416e-07</v>
@@ -7534,7 +7534,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-479.942</v>
+        <v>93.50099999999998</v>
       </c>
       <c r="D7" t="n">
         <v>1.31483e-07</v>
@@ -7584,7 +7584,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-435.574</v>
+        <v>92.28800000000001</v>
       </c>
       <c r="D8" t="n">
         <v>1.30793e-07</v>
@@ -7634,7 +7634,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-411.447</v>
+        <v>87.86500000000001</v>
       </c>
       <c r="D9" t="n">
         <v>1.30247e-07</v>
@@ -7684,7 +7684,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-388.778</v>
+        <v>85.19400000000002</v>
       </c>
       <c r="D10" t="n">
         <v>1.29801e-07</v>
@@ -7734,7 +7734,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-368.522</v>
+        <v>83.67599999999999</v>
       </c>
       <c r="D11" t="n">
         <v>1.29497e-07</v>
@@ -7930,7 +7930,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-589.119</v>
+        <v>166.4859999999999</v>
       </c>
       <c r="D2" t="n">
         <v>1.33147e-07</v>
@@ -7980,7 +7980,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-449.7940000000001</v>
+        <v>146.001</v>
       </c>
       <c r="D3" t="n">
         <v>1.30999e-07</v>
@@ -8030,7 +8030,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-392.052</v>
+        <v>136.545</v>
       </c>
       <c r="D4" t="n">
         <v>1.29836e-07</v>
@@ -8080,7 +8080,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-350.797</v>
+        <v>135.524</v>
       </c>
       <c r="D5" t="n">
         <v>1.29139e-07</v>
@@ -8130,7 +8130,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-331.1610000000001</v>
+        <v>129.4109999999999</v>
       </c>
       <c r="D6" t="n">
         <v>1.28691e-07</v>
@@ -8180,7 +8180,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-313.47</v>
+        <v>129.4039999999999</v>
       </c>
       <c r="D7" t="n">
         <v>1.2844e-07</v>
@@ -8230,7 +8230,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-306.149</v>
+        <v>126.652</v>
       </c>
       <c r="D8" t="n">
         <v>1.28249e-07</v>
@@ -8280,7 +8280,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-298.102</v>
+        <v>120.405</v>
       </c>
       <c r="D9" t="n">
         <v>1.28111e-07</v>
@@ -8330,7 +8330,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-288.6429999999999</v>
+        <v>118.8390000000001</v>
       </c>
       <c r="D10" t="n">
         <v>1.2803e-07</v>
@@ -8380,7 +8380,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-278.92</v>
+        <v>115.681</v>
       </c>
       <c r="D11" t="n">
         <v>1.27948e-07</v>
@@ -8430,7 +8430,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-276.6859999999999</v>
+        <v>112.958</v>
       </c>
       <c r="D12" t="n">
         <v>1.27892e-07</v>
@@ -8480,7 +8480,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-270.665</v>
+        <v>111.177</v>
       </c>
       <c r="D13" t="n">
         <v>1.27846e-07</v>
@@ -8530,7 +8530,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-266.7959999999999</v>
+        <v>108.74</v>
       </c>
       <c r="D14" t="n">
         <v>1.27794e-07</v>
@@ -8580,7 +8580,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-261.222</v>
+        <v>108.625</v>
       </c>
       <c r="D15" t="n">
         <v>1.27743e-07</v>
@@ -8630,7 +8630,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-254.509</v>
+        <v>109.842</v>
       </c>
       <c r="D16" t="n">
         <v>1.27717e-07</v>
@@ -8680,7 +8680,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-251.8969999999999</v>
+        <v>108.27</v>
       </c>
       <c r="D17" t="n">
         <v>1.27683e-07</v>
@@ -8730,7 +8730,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-248.052</v>
+        <v>105.467</v>
       </c>
       <c r="D18" t="n">
         <v>1.27651e-07</v>
@@ -8780,7 +8780,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-247.234</v>
+        <v>104.166</v>
       </c>
       <c r="D19" t="n">
         <v>1.27623e-07</v>
@@ -8830,7 +8830,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-247.227</v>
+        <v>100.913</v>
       </c>
       <c r="D20" t="n">
         <v>1.27607e-07</v>
@@ -8880,7 +8880,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-242.819</v>
+        <v>99.524</v>
       </c>
       <c r="D21" t="n">
         <v>1.27591e-07</v>
@@ -8930,7 +8930,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-240.8340000000001</v>
+        <v>97.82099999999997</v>
       </c>
       <c r="D22" t="n">
         <v>1.27573e-07</v>
@@ -9126,7 +9126,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-985.4110000000001</v>
+        <v>140.1929999999999</v>
       </c>
       <c r="D2" t="n">
         <v>1.40223e-07</v>
@@ -9176,7 +9176,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-656.3070000000001</v>
+        <v>96.63299999999998</v>
       </c>
       <c r="D3" t="n">
         <v>1.37618e-07</v>
@@ -9226,7 +9226,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-510.7180000000001</v>
+        <v>87.56</v>
       </c>
       <c r="D4" t="n">
         <v>1.35242e-07</v>
@@ -9276,7 +9276,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-430.376</v>
+        <v>82.64600000000002</v>
       </c>
       <c r="D5" t="n">
         <v>1.33778e-07</v>
@@ -9326,7 +9326,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-379.626</v>
+        <v>81.23000000000002</v>
       </c>
       <c r="D6" t="n">
         <v>1.32853e-07</v>
@@ -9376,7 +9376,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-351.289</v>
+        <v>76.25400000000002</v>
       </c>
       <c r="D7" t="n">
         <v>1.32323e-07</v>
@@ -9426,7 +9426,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-326.248</v>
+        <v>75.06899999999996</v>
       </c>
       <c r="D8" t="n">
         <v>1.31977e-07</v>
@@ -9476,7 +9476,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-310.277</v>
+        <v>73.928</v>
       </c>
       <c r="D9" t="n">
         <v>1.31771e-07</v>
@@ -9526,7 +9526,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-296.297</v>
+        <v>69.96699999999998</v>
       </c>
       <c r="D10" t="n">
         <v>1.31646e-07</v>
@@ -9576,7 +9576,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-284.457</v>
+        <v>69.30700000000002</v>
       </c>
       <c r="D11" t="n">
         <v>1.31534e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 44.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 44.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -564,6 +564,9 @@
       <c r="B2" t="n">
         <v>165.3560000000001</v>
       </c>
+      <c r="C2" t="n">
+        <v>1045.111006662003</v>
+      </c>
       <c r="D2" t="n">
         <v>1.20671e-07</v>
       </c>
@@ -614,6 +617,9 @@
       <c r="B3" t="n">
         <v>159.085</v>
       </c>
+      <c r="C3" t="n">
+        <v>1040.249048681838</v>
+      </c>
       <c r="D3" t="n">
         <v>1.19954e-07</v>
       </c>
@@ -664,6 +670,9 @@
       <c r="B4" t="n">
         <v>153.983</v>
       </c>
+      <c r="C4" t="n">
+        <v>1101.979719337023</v>
+      </c>
       <c r="D4" t="n">
         <v>1.19583e-07</v>
       </c>
@@ -714,6 +723,9 @@
       <c r="B5" t="n">
         <v>151.135</v>
       </c>
+      <c r="C5" t="n">
+        <v>1180.214540733193</v>
+      </c>
       <c r="D5" t="n">
         <v>1.19433e-07</v>
       </c>
@@ -764,6 +776,9 @@
       <c r="B6" t="n">
         <v>139.909</v>
       </c>
+      <c r="C6" t="n">
+        <v>992.5331859503139</v>
+      </c>
       <c r="D6" t="n">
         <v>1.19324e-07</v>
       </c>
@@ -814,6 +829,9 @@
       <c r="B7" t="n">
         <v>139.419</v>
       </c>
+      <c r="C7" t="n">
+        <v>1108.075420319863</v>
+      </c>
       <c r="D7" t="n">
         <v>1.19321e-07</v>
       </c>
@@ -864,6 +882,9 @@
       <c r="B8" t="n">
         <v>133.6900000000001</v>
       </c>
+      <c r="C8" t="n">
+        <v>1050.060894352629</v>
+      </c>
       <c r="D8" t="n">
         <v>1.19347e-07</v>
       </c>
@@ -914,6 +935,9 @@
       <c r="B9" t="n">
         <v>123.512</v>
       </c>
+      <c r="C9" t="n">
+        <v>916.482295631263</v>
+      </c>
       <c r="D9" t="n">
         <v>1.19379e-07</v>
       </c>
@@ -964,6 +988,9 @@
       <c r="B10" t="n">
         <v>128.252</v>
       </c>
+      <c r="C10" t="n">
+        <v>1087.431315153416</v>
+      </c>
       <c r="D10" t="n">
         <v>1.19423e-07</v>
       </c>
@@ -1013,6 +1040,9 @@
       </c>
       <c r="B11" t="n">
         <v>124.595</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1121.911138989311</v>
       </c>
       <c r="D11" t="n">
         <v>1.19487e-07</v>
@@ -1084,7 +1114,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1210,6 +1240,9 @@
       <c r="B2" t="n">
         <v>156.985</v>
       </c>
+      <c r="C2" t="n">
+        <v>1621.145838315899</v>
+      </c>
       <c r="D2" t="n">
         <v>1.31074e-07</v>
       </c>
@@ -1260,6 +1293,9 @@
       <c r="B3" t="n">
         <v>133.288</v>
       </c>
+      <c r="C3" t="n">
+        <v>1088.883548491037</v>
+      </c>
       <c r="D3" t="n">
         <v>1.31092e-07</v>
       </c>
@@ -1310,6 +1346,9 @@
       <c r="B4" t="n">
         <v>128.7099999999999</v>
       </c>
+      <c r="C4" t="n">
+        <v>1129.907670087515</v>
+      </c>
       <c r="D4" t="n">
         <v>1.30923e-07</v>
       </c>
@@ -1360,6 +1399,9 @@
       <c r="B5" t="n">
         <v>124.245</v>
       </c>
+      <c r="C5" t="n">
+        <v>1122.869499827731</v>
+      </c>
       <c r="D5" t="n">
         <v>1.30831e-07</v>
       </c>
@@ -1410,6 +1452,9 @@
       <c r="B6" t="n">
         <v>120.6560000000001</v>
       </c>
+      <c r="C6" t="n">
+        <v>1072.989310994566</v>
+      </c>
       <c r="D6" t="n">
         <v>1.30732e-07</v>
       </c>
@@ -1460,6 +1505,9 @@
       <c r="B7" t="n">
         <v>116.7300000000001</v>
       </c>
+      <c r="C7" t="n">
+        <v>1050.93581877685</v>
+      </c>
       <c r="D7" t="n">
         <v>1.30672e-07</v>
       </c>
@@ -1510,6 +1558,9 @@
       <c r="B8" t="n">
         <v>113.102</v>
       </c>
+      <c r="C8" t="n">
+        <v>1014.53888431003</v>
+      </c>
       <c r="D8" t="n">
         <v>1.30625e-07</v>
       </c>
@@ -1560,6 +1611,9 @@
       <c r="B9" t="n">
         <v>113.992</v>
       </c>
+      <c r="C9" t="n">
+        <v>1167.174437524019</v>
+      </c>
       <c r="D9" t="n">
         <v>1.30557e-07</v>
       </c>
@@ -1610,6 +1664,9 @@
       <c r="B10" t="n">
         <v>109.841</v>
       </c>
+      <c r="C10" t="n">
+        <v>1108.699081505459</v>
+      </c>
       <c r="D10" t="n">
         <v>1.30502e-07</v>
       </c>
@@ -1660,6 +1717,9 @@
       <c r="B11" t="n">
         <v>107.521</v>
       </c>
+      <c r="C11" t="n">
+        <v>1065.560926374041</v>
+      </c>
       <c r="D11" t="n">
         <v>1.30461e-07</v>
       </c>
@@ -1710,6 +1770,9 @@
       <c r="B12" t="n">
         <v>107.365</v>
       </c>
+      <c r="C12" t="n">
+        <v>1139.364016819648</v>
+      </c>
       <c r="D12" t="n">
         <v>1.30396e-07</v>
       </c>
@@ -1760,6 +1823,9 @@
       <c r="B13" t="n">
         <v>102.9</v>
       </c>
+      <c r="C13" t="n">
+        <v>1037.51082687527</v>
+      </c>
       <c r="D13" t="n">
         <v>1.30336e-07</v>
       </c>
@@ -1810,6 +1876,9 @@
       <c r="B14" t="n">
         <v>103.528</v>
       </c>
+      <c r="C14" t="n">
+        <v>1140.111296746734</v>
+      </c>
       <c r="D14" t="n">
         <v>1.30318e-07</v>
       </c>
@@ -1860,6 +1929,9 @@
       <c r="B15" t="n">
         <v>99.56200000000001</v>
       </c>
+      <c r="C15" t="n">
+        <v>1011.914910845446</v>
+      </c>
       <c r="D15" t="n">
         <v>1.30283e-07</v>
       </c>
@@ -1910,6 +1982,9 @@
       <c r="B16" t="n">
         <v>99.94499999999999</v>
       </c>
+      <c r="C16" t="n">
+        <v>1112.406871469197</v>
+      </c>
       <c r="D16" t="n">
         <v>1.3024e-07</v>
       </c>
@@ -1960,6 +2035,9 @@
       <c r="B17" t="n">
         <v>97.38499999999999</v>
       </c>
+      <c r="C17" t="n">
+        <v>1088.759056821231</v>
+      </c>
       <c r="D17" t="n">
         <v>1.30212e-07</v>
       </c>
@@ -2010,6 +2088,9 @@
       <c r="B18" t="n">
         <v>94.57000000000005</v>
       </c>
+      <c r="C18" t="n">
+        <v>1038.376503327636</v>
+      </c>
       <c r="D18" t="n">
         <v>1.302e-07</v>
       </c>
@@ -2060,6 +2141,9 @@
       <c r="B19" t="n">
         <v>97.08100000000002</v>
       </c>
+      <c r="C19" t="n">
+        <v>1297.413535790615</v>
+      </c>
       <c r="D19" t="n">
         <v>1.30153e-07</v>
       </c>
@@ -2110,6 +2194,9 @@
       <c r="B20" t="n">
         <v>96.137</v>
       </c>
+      <c r="C20" t="n">
+        <v>1321.871374120467</v>
+      </c>
       <c r="D20" t="n">
         <v>1.30162e-07</v>
       </c>
@@ -2160,6 +2247,9 @@
       <c r="B21" t="n">
         <v>94.35799999999995</v>
       </c>
+      <c r="C21" t="n">
+        <v>1331.630482137158</v>
+      </c>
       <c r="D21" t="n">
         <v>1.30124e-07</v>
       </c>
@@ -2209,6 +2299,9 @@
       </c>
       <c r="B22" t="n">
         <v>90.22499999999997</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1095.474097431361</v>
       </c>
       <c r="D22" t="n">
         <v>1.30106e-07</v>
@@ -2280,7 +2373,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2406,6 +2499,9 @@
       <c r="B2" t="n">
         <v>173.051</v>
       </c>
+      <c r="C2" t="n">
+        <v>1555.069771673009</v>
+      </c>
       <c r="D2" t="n">
         <v>1.25063e-07</v>
       </c>
@@ -2456,6 +2552,9 @@
       <c r="B3" t="n">
         <v>149.7909999999999</v>
       </c>
+      <c r="C3" t="n">
+        <v>1176.259471695698</v>
+      </c>
       <c r="D3" t="n">
         <v>1.23272e-07</v>
       </c>
@@ -2506,6 +2605,9 @@
       <c r="B4" t="n">
         <v>144.8030000000001</v>
       </c>
+      <c r="C4" t="n">
+        <v>1153.104331664492</v>
+      </c>
       <c r="D4" t="n">
         <v>1.22369e-07</v>
       </c>
@@ -2556,6 +2658,9 @@
       <c r="B5" t="n">
         <v>141.254</v>
       </c>
+      <c r="C5" t="n">
+        <v>1169.425887537154</v>
+      </c>
       <c r="D5" t="n">
         <v>1.21862e-07</v>
       </c>
@@ -2606,6 +2711,9 @@
       <c r="B6" t="n">
         <v>134.606</v>
       </c>
+      <c r="C6" t="n">
+        <v>1059.996194455794</v>
+      </c>
       <c r="D6" t="n">
         <v>1.21539e-07</v>
       </c>
@@ -2656,6 +2764,9 @@
       <c r="B7" t="n">
         <v>132.833</v>
       </c>
+      <c r="C7" t="n">
+        <v>1115.056361684947</v>
+      </c>
       <c r="D7" t="n">
         <v>1.21327e-07</v>
       </c>
@@ -2706,6 +2817,9 @@
       <c r="B8" t="n">
         <v>129.3650000000001</v>
       </c>
+      <c r="C8" t="n">
+        <v>963.9668523082921</v>
+      </c>
       <c r="D8" t="n">
         <v>1.21216e-07</v>
       </c>
@@ -2756,6 +2870,9 @@
       <c r="B9" t="n">
         <v>126.149</v>
       </c>
+      <c r="C9" t="n">
+        <v>1110.828324142022</v>
+      </c>
       <c r="D9" t="n">
         <v>1.21129e-07</v>
       </c>
@@ -2806,6 +2923,9 @@
       <c r="B10" t="n">
         <v>121.513</v>
       </c>
+      <c r="C10" t="n">
+        <v>1020.634328306055</v>
+      </c>
       <c r="D10" t="n">
         <v>1.21079e-07</v>
       </c>
@@ -2856,6 +2976,9 @@
       <c r="B11" t="n">
         <v>118.6129999999999</v>
       </c>
+      <c r="C11" t="n">
+        <v>1038.272022536314</v>
+      </c>
       <c r="D11" t="n">
         <v>1.21056e-07</v>
       </c>
@@ -2906,6 +3029,9 @@
       <c r="B12" t="n">
         <v>113.862</v>
       </c>
+      <c r="C12" t="n">
+        <v>954.9553177311874</v>
+      </c>
       <c r="D12" t="n">
         <v>1.21028e-07</v>
       </c>
@@ -2956,6 +3082,9 @@
       <c r="B13" t="n">
         <v>115.446</v>
       </c>
+      <c r="C13" t="n">
+        <v>1106.386500418628</v>
+      </c>
       <c r="D13" t="n">
         <v>1.21043e-07</v>
       </c>
@@ -3006,6 +3135,9 @@
       <c r="B14" t="n">
         <v>113.891</v>
       </c>
+      <c r="C14" t="n">
+        <v>1099.756131420056</v>
+      </c>
       <c r="D14" t="n">
         <v>1.21058e-07</v>
       </c>
@@ -3056,6 +3188,9 @@
       <c r="B15" t="n">
         <v>111.984</v>
       </c>
+      <c r="C15" t="n">
+        <v>1093.741340530384</v>
+      </c>
       <c r="D15" t="n">
         <v>1.21044e-07</v>
       </c>
@@ -3106,6 +3241,9 @@
       <c r="B16" t="n">
         <v>110.748</v>
       </c>
+      <c r="C16" t="n">
+        <v>1102.586185916655</v>
+      </c>
       <c r="D16" t="n">
         <v>1.21072e-07</v>
       </c>
@@ -3156,6 +3294,9 @@
       <c r="B17" t="n">
         <v>109.53</v>
       </c>
+      <c r="C17" t="n">
+        <v>1168.481360065424</v>
+      </c>
       <c r="D17" t="n">
         <v>1.21078e-07</v>
       </c>
@@ -3206,6 +3347,9 @@
       <c r="B18" t="n">
         <v>104.501</v>
       </c>
+      <c r="C18" t="n">
+        <v>998.4482839851482</v>
+      </c>
       <c r="D18" t="n">
         <v>1.21099e-07</v>
       </c>
@@ -3256,6 +3400,9 @@
       <c r="B19" t="n">
         <v>106.825</v>
       </c>
+      <c r="C19" t="n">
+        <v>1203.790747942653</v>
+      </c>
       <c r="D19" t="n">
         <v>1.21126e-07</v>
       </c>
@@ -3306,6 +3453,9 @@
       <c r="B20" t="n">
         <v>105.208</v>
       </c>
+      <c r="C20" t="n">
+        <v>1229.262998533652</v>
+      </c>
       <c r="D20" t="n">
         <v>1.21159e-07</v>
       </c>
@@ -3356,6 +3506,9 @@
       <c r="B21" t="n">
         <v>102.46</v>
       </c>
+      <c r="C21" t="n">
+        <v>1168.457692517914</v>
+      </c>
       <c r="D21" t="n">
         <v>1.21189e-07</v>
       </c>
@@ -3405,6 +3558,9 @@
       </c>
       <c r="B22" t="n">
         <v>99.137</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1046.640540163132</v>
       </c>
       <c r="D22" t="n">
         <v>1.21212e-07</v>
@@ -3476,7 +3632,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -3602,6 +3758,9 @@
       <c r="B2" t="n">
         <v>154.168</v>
       </c>
+      <c r="C2" t="n">
+        <v>5330.556493779118</v>
+      </c>
       <c r="D2" t="n">
         <v>1.32747e-07</v>
       </c>
@@ -3652,6 +3811,9 @@
       <c r="B3" t="n">
         <v>121.446</v>
       </c>
+      <c r="C3" t="n">
+        <v>1498.552779923557</v>
+      </c>
       <c r="D3" t="n">
         <v>1.30919e-07</v>
       </c>
@@ -3702,6 +3864,9 @@
       <c r="B4" t="n">
         <v>111.069</v>
       </c>
+      <c r="C4" t="n">
+        <v>1160.353541950791</v>
+      </c>
       <c r="D4" t="n">
         <v>1.29034e-07</v>
       </c>
@@ -3752,6 +3917,9 @@
       <c r="B5" t="n">
         <v>107.997</v>
       </c>
+      <c r="C5" t="n">
+        <v>1256.964312007618</v>
+      </c>
       <c r="D5" t="n">
         <v>1.27686e-07</v>
       </c>
@@ -3802,6 +3970,9 @@
       <c r="B6" t="n">
         <v>101.894</v>
       </c>
+      <c r="C6" t="n">
+        <v>1071.972502659168</v>
+      </c>
       <c r="D6" t="n">
         <v>1.26802e-07</v>
       </c>
@@ -3852,6 +4023,9 @@
       <c r="B7" t="n">
         <v>100.205</v>
       </c>
+      <c r="C7" t="n">
+        <v>1242.171366951171</v>
+      </c>
       <c r="D7" t="n">
         <v>1.26186e-07</v>
       </c>
@@ -3902,6 +4076,9 @@
       <c r="B8" t="n">
         <v>98.029</v>
       </c>
+      <c r="C8" t="n">
+        <v>1301.24016477401</v>
+      </c>
       <c r="D8" t="n">
         <v>1.25762e-07</v>
       </c>
@@ -3952,6 +4129,9 @@
       <c r="B9" t="n">
         <v>91.62099999999998</v>
       </c>
+      <c r="C9" t="n">
+        <v>1134.636503173657</v>
+      </c>
       <c r="D9" t="n">
         <v>1.25455e-07</v>
       </c>
@@ -4002,6 +4182,9 @@
       <c r="B10" t="n">
         <v>92.24700000000001</v>
       </c>
+      <c r="C10" t="n">
+        <v>1440.236742323683</v>
+      </c>
       <c r="D10" t="n">
         <v>1.25236e-07</v>
       </c>
@@ -4051,6 +4234,9 @@
       </c>
       <c r="B11" t="n">
         <v>89.62699999999995</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1586.386127993006</v>
       </c>
       <c r="D11" t="n">
         <v>1.2505e-07</v>
@@ -4122,7 +4308,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -4248,6 +4434,9 @@
       <c r="B2" t="n">
         <v>169.186</v>
       </c>
+      <c r="C2" t="n">
+        <v>1745.564564847555</v>
+      </c>
       <c r="D2" t="n">
         <v>1.30706e-07</v>
       </c>
@@ -4298,6 +4487,9 @@
       <c r="B3" t="n">
         <v>144.4109999999999</v>
       </c>
+      <c r="C3" t="n">
+        <v>1164.938609371968</v>
+      </c>
       <c r="D3" t="n">
         <v>1.28327e-07</v>
       </c>
@@ -4348,6 +4540,9 @@
       <c r="B4" t="n">
         <v>140.296</v>
       </c>
+      <c r="C4" t="n">
+        <v>1207.643241694592</v>
+      </c>
       <c r="D4" t="n">
         <v>1.27039e-07</v>
       </c>
@@ -4398,6 +4593,9 @@
       <c r="B5" t="n">
         <v>133.29</v>
       </c>
+      <c r="C5" t="n">
+        <v>1057.181993871552</v>
+      </c>
       <c r="D5" t="n">
         <v>1.26238e-07</v>
       </c>
@@ -4448,6 +4646,9 @@
       <c r="B6" t="n">
         <v>130.823</v>
       </c>
+      <c r="C6" t="n">
+        <v>1093.190886603918</v>
+      </c>
       <c r="D6" t="n">
         <v>1.25732e-07</v>
       </c>
@@ -4498,6 +4699,9 @@
       <c r="B7" t="n">
         <v>126.859</v>
       </c>
+      <c r="C7" t="n">
+        <v>1111.881149329189</v>
+      </c>
       <c r="D7" t="n">
         <v>1.25378e-07</v>
       </c>
@@ -4548,6 +4752,9 @@
       <c r="B8" t="n">
         <v>124.0930000000001</v>
       </c>
+      <c r="C8" t="n">
+        <v>1089.080056307583</v>
+      </c>
       <c r="D8" t="n">
         <v>1.25107e-07</v>
       </c>
@@ -4598,6 +4805,9 @@
       <c r="B9" t="n">
         <v>122.473</v>
       </c>
+      <c r="C9" t="n">
+        <v>1163.274178250816</v>
+      </c>
       <c r="D9" t="n">
         <v>1.2493e-07</v>
       </c>
@@ -4648,6 +4858,9 @@
       <c r="B10" t="n">
         <v>119.389</v>
       </c>
+      <c r="C10" t="n">
+        <v>1159.544464835631</v>
+      </c>
       <c r="D10" t="n">
         <v>1.2475e-07</v>
       </c>
@@ -4698,6 +4911,9 @@
       <c r="B11" t="n">
         <v>115.222</v>
       </c>
+      <c r="C11" t="n">
+        <v>1069.048009432805</v>
+      </c>
       <c r="D11" t="n">
         <v>1.24627e-07</v>
       </c>
@@ -4748,6 +4964,9 @@
       <c r="B12" t="n">
         <v>114.9059999999999</v>
       </c>
+      <c r="C12" t="n">
+        <v>1065.515368129375</v>
+      </c>
       <c r="D12" t="n">
         <v>1.24514e-07</v>
       </c>
@@ -4798,6 +5017,9 @@
       <c r="B13" t="n">
         <v>111.524</v>
       </c>
+      <c r="C13" t="n">
+        <v>1052.07552166449</v>
+      </c>
       <c r="D13" t="n">
         <v>1.24428e-07</v>
       </c>
@@ -4848,6 +5070,9 @@
       <c r="B14" t="n">
         <v>107.45</v>
       </c>
+      <c r="C14" t="n">
+        <v>960.5947486525413</v>
+      </c>
       <c r="D14" t="n">
         <v>1.24404e-07</v>
       </c>
@@ -4898,6 +5123,9 @@
       <c r="B15" t="n">
         <v>109.852</v>
       </c>
+      <c r="C15" t="n">
+        <v>1089.873759546387</v>
+      </c>
       <c r="D15" t="n">
         <v>1.24345e-07</v>
       </c>
@@ -4948,6 +5176,9 @@
       <c r="B16" t="n">
         <v>107.895</v>
       </c>
+      <c r="C16" t="n">
+        <v>1090.26844756299</v>
+      </c>
       <c r="D16" t="n">
         <v>1.24315e-07</v>
       </c>
@@ -4998,6 +5229,9 @@
       <c r="B17" t="n">
         <v>107.553</v>
       </c>
+      <c r="C17" t="n">
+        <v>1179.548300252117</v>
+      </c>
       <c r="D17" t="n">
         <v>1.2423e-07</v>
       </c>
@@ -5048,6 +5282,9 @@
       <c r="B18" t="n">
         <v>105.43</v>
       </c>
+      <c r="C18" t="n">
+        <v>1115.21442617366</v>
+      </c>
       <c r="D18" t="n">
         <v>1.24185e-07</v>
       </c>
@@ -5098,6 +5335,9 @@
       <c r="B19" t="n">
         <v>104.552</v>
       </c>
+      <c r="C19" t="n">
+        <v>1026.851877709759</v>
+      </c>
       <c r="D19" t="n">
         <v>1.24146e-07</v>
       </c>
@@ -5148,6 +5388,9 @@
       <c r="B20" t="n">
         <v>102.219</v>
       </c>
+      <c r="C20" t="n">
+        <v>1120.904675579753</v>
+      </c>
       <c r="D20" t="n">
         <v>1.24131e-07</v>
       </c>
@@ -5198,6 +5441,9 @@
       <c r="B21" t="n">
         <v>101.271</v>
       </c>
+      <c r="C21" t="n">
+        <v>1156.863287332887</v>
+      </c>
       <c r="D21" t="n">
         <v>1.24162e-07</v>
       </c>
@@ -5247,6 +5493,9 @@
       </c>
       <c r="B22" t="n">
         <v>99.02199999999999</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1113.970627693973</v>
       </c>
       <c r="D22" t="n">
         <v>1.24093e-07</v>
@@ -5318,7 +5567,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5444,6 +5693,9 @@
       <c r="B2" t="n">
         <v>170.454</v>
       </c>
+      <c r="C2" t="n">
+        <v>9036.674710320864</v>
+      </c>
       <c r="D2" t="n">
         <v>1.35515e-07</v>
       </c>
@@ -5494,6 +5746,9 @@
       <c r="B3" t="n">
         <v>113.733</v>
       </c>
+      <c r="C3" t="n">
+        <v>1782.587010514477</v>
+      </c>
       <c r="D3" t="n">
         <v>1.3576e-07</v>
       </c>
@@ -5544,6 +5799,9 @@
       <c r="B4" t="n">
         <v>104.842</v>
       </c>
+      <c r="C4" t="n">
+        <v>1552.539263166526</v>
+      </c>
       <c r="D4" t="n">
         <v>1.33892e-07</v>
       </c>
@@ -5594,6 +5852,9 @@
       <c r="B5" t="n">
         <v>97.59699999999998</v>
       </c>
+      <c r="C5" t="n">
+        <v>1318.217171735767</v>
+      </c>
       <c r="D5" t="n">
         <v>1.32242e-07</v>
       </c>
@@ -5644,6 +5905,9 @@
       <c r="B6" t="n">
         <v>92.56700000000001</v>
       </c>
+      <c r="C6" t="n">
+        <v>1219.415924086236</v>
+      </c>
       <c r="D6" t="n">
         <v>1.31062e-07</v>
       </c>
@@ -5694,6 +5958,9 @@
       <c r="B7" t="n">
         <v>95.73299999999995</v>
       </c>
+      <c r="C7" t="n">
+        <v>1346.96442917031</v>
+      </c>
       <c r="D7" t="n">
         <v>1.3019e-07</v>
       </c>
@@ -5744,6 +6011,9 @@
       <c r="B8" t="n">
         <v>90.78199999999998</v>
       </c>
+      <c r="C8" t="n">
+        <v>1334.87523017367</v>
+      </c>
       <c r="D8" t="n">
         <v>1.29518e-07</v>
       </c>
@@ -5794,6 +6064,9 @@
       <c r="B9" t="n">
         <v>87.36899999999997</v>
       </c>
+      <c r="C9" t="n">
+        <v>1378.20294676874</v>
+      </c>
       <c r="D9" t="n">
         <v>1.28996e-07</v>
       </c>
@@ -5844,6 +6117,9 @@
       <c r="B10" t="n">
         <v>84.72799999999995</v>
       </c>
+      <c r="C10" t="n">
+        <v>1428.180560721705</v>
+      </c>
       <c r="D10" t="n">
         <v>1.28643e-07</v>
       </c>
@@ -5893,6 +6169,9 @@
       </c>
       <c r="B11" t="n">
         <v>82.678</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1491.367187133959</v>
       </c>
       <c r="D11" t="n">
         <v>1.28332e-07</v>
@@ -5964,7 +6243,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -6090,6 +6369,9 @@
       <c r="B2" t="n">
         <v>165.807</v>
       </c>
+      <c r="C2" t="n">
+        <v>1546.078846593912</v>
+      </c>
       <c r="D2" t="n">
         <v>1.3174e-07</v>
       </c>
@@ -6140,6 +6422,9 @@
       <c r="B3" t="n">
         <v>142.9909999999999</v>
       </c>
+      <c r="C3" t="n">
+        <v>1094.586417785975</v>
+      </c>
       <c r="D3" t="n">
         <v>1.29904e-07</v>
       </c>
@@ -6190,6 +6475,9 @@
       <c r="B4" t="n">
         <v>134.7570000000001</v>
       </c>
+      <c r="C4" t="n">
+        <v>1000.32956085773</v>
+      </c>
       <c r="D4" t="n">
         <v>1.28818e-07</v>
       </c>
@@ -6240,6 +6528,9 @@
       <c r="B5" t="n">
         <v>136.796</v>
       </c>
+      <c r="C5" t="n">
+        <v>1259.231589310878</v>
+      </c>
       <c r="D5" t="n">
         <v>1.28102e-07</v>
       </c>
@@ -6290,6 +6581,9 @@
       <c r="B6" t="n">
         <v>130.842</v>
       </c>
+      <c r="C6" t="n">
+        <v>1076.533872308063</v>
+      </c>
       <c r="D6" t="n">
         <v>1.27721e-07</v>
       </c>
@@ -6340,6 +6634,9 @@
       <c r="B7" t="n">
         <v>128.361</v>
       </c>
+      <c r="C7" t="n">
+        <v>1138.747379521363</v>
+      </c>
       <c r="D7" t="n">
         <v>1.27421e-07</v>
       </c>
@@ -6390,6 +6687,9 @@
       <c r="B8" t="n">
         <v>123.628</v>
       </c>
+      <c r="C8" t="n">
+        <v>1032.655572425195</v>
+      </c>
       <c r="D8" t="n">
         <v>1.27209e-07</v>
       </c>
@@ -6440,6 +6740,9 @@
       <c r="B9" t="n">
         <v>122.629</v>
       </c>
+      <c r="C9" t="n">
+        <v>1043.888046370101</v>
+      </c>
       <c r="D9" t="n">
         <v>1.27064e-07</v>
       </c>
@@ -6490,6 +6793,9 @@
       <c r="B10" t="n">
         <v>118.23</v>
       </c>
+      <c r="C10" t="n">
+        <v>980.5106241748045</v>
+      </c>
       <c r="D10" t="n">
         <v>1.26921e-07</v>
       </c>
@@ -6540,6 +6846,9 @@
       <c r="B11" t="n">
         <v>118.027</v>
       </c>
+      <c r="C11" t="n">
+        <v>1043.281906227671</v>
+      </c>
       <c r="D11" t="n">
         <v>1.26801e-07</v>
       </c>
@@ -6590,6 +6899,9 @@
       <c r="B12" t="n">
         <v>117.991</v>
       </c>
+      <c r="C12" t="n">
+        <v>1138.491985032787</v>
+      </c>
       <c r="D12" t="n">
         <v>1.26742e-07</v>
       </c>
@@ -6640,6 +6952,9 @@
       <c r="B13" t="n">
         <v>115.196</v>
       </c>
+      <c r="C13" t="n">
+        <v>1121.357103549543</v>
+      </c>
       <c r="D13" t="n">
         <v>1.26635e-07</v>
       </c>
@@ -6690,6 +7005,9 @@
       <c r="B14" t="n">
         <v>113.675</v>
       </c>
+      <c r="C14" t="n">
+        <v>1101.110789966278</v>
+      </c>
       <c r="D14" t="n">
         <v>1.26562e-07</v>
       </c>
@@ -6740,6 +7058,9 @@
       <c r="B15" t="n">
         <v>109.821</v>
       </c>
+      <c r="C15" t="n">
+        <v>1027.688534551363</v>
+      </c>
       <c r="D15" t="n">
         <v>1.26515e-07</v>
       </c>
@@ -6790,6 +7111,9 @@
       <c r="B16" t="n">
         <v>109.083</v>
       </c>
+      <c r="C16" t="n">
+        <v>1014.111405102926</v>
+      </c>
       <c r="D16" t="n">
         <v>1.2646e-07</v>
       </c>
@@ -6840,6 +7164,9 @@
       <c r="B17" t="n">
         <v>108.769</v>
       </c>
+      <c r="C17" t="n">
+        <v>1130.221529607981</v>
+      </c>
       <c r="D17" t="n">
         <v>1.26394e-07</v>
       </c>
@@ -6890,6 +7217,9 @@
       <c r="B18" t="n">
         <v>107.908</v>
       </c>
+      <c r="C18" t="n">
+        <v>1121.895619824897</v>
+      </c>
       <c r="D18" t="n">
         <v>1.26374e-07</v>
       </c>
@@ -6940,6 +7270,9 @@
       <c r="B19" t="n">
         <v>105.775</v>
       </c>
+      <c r="C19" t="n">
+        <v>1093.808320524864</v>
+      </c>
       <c r="D19" t="n">
         <v>1.2638e-07</v>
       </c>
@@ -6990,6 +7323,9 @@
       <c r="B20" t="n">
         <v>105.679</v>
       </c>
+      <c r="C20" t="n">
+        <v>1202.807344717327</v>
+      </c>
       <c r="D20" t="n">
         <v>1.26328e-07</v>
       </c>
@@ -7040,6 +7376,9 @@
       <c r="B21" t="n">
         <v>104.663</v>
       </c>
+      <c r="C21" t="n">
+        <v>1189.827864981361</v>
+      </c>
       <c r="D21" t="n">
         <v>1.2629e-07</v>
       </c>
@@ -7089,6 +7428,9 @@
       </c>
       <c r="B22" t="n">
         <v>100.023</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1016.117291330994</v>
       </c>
       <c r="D22" t="n">
         <v>1.26279e-07</v>
@@ -7160,7 +7502,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7286,6 +7628,9 @@
       <c r="B2" t="n">
         <v>166.581</v>
       </c>
+      <c r="C2" t="n">
+        <v>20523.11205665578</v>
+      </c>
       <c r="D2" t="n">
         <v>1.3844e-07</v>
       </c>
@@ -7336,6 +7681,9 @@
       <c r="B3" t="n">
         <v>117.392</v>
       </c>
+      <c r="C3" t="n">
+        <v>1618.414981714367</v>
+      </c>
       <c r="D3" t="n">
         <v>1.37784e-07</v>
       </c>
@@ -7386,6 +7734,9 @@
       <c r="B4" t="n">
         <v>107.657</v>
       </c>
+      <c r="C4" t="n">
+        <v>1536.523249331721</v>
+      </c>
       <c r="D4" t="n">
         <v>1.35504e-07</v>
       </c>
@@ -7436,6 +7787,9 @@
       <c r="B5" t="n">
         <v>97.62200000000001</v>
       </c>
+      <c r="C5" t="n">
+        <v>1100.368101932839</v>
+      </c>
       <c r="D5" t="n">
         <v>1.33706e-07</v>
       </c>
@@ -7486,6 +7840,9 @@
       <c r="B6" t="n">
         <v>96.35000000000002</v>
       </c>
+      <c r="C6" t="n">
+        <v>1185.781549949033</v>
+      </c>
       <c r="D6" t="n">
         <v>1.32416e-07</v>
       </c>
@@ -7536,6 +7893,9 @@
       <c r="B7" t="n">
         <v>93.50099999999998</v>
       </c>
+      <c r="C7" t="n">
+        <v>1379.447824372992</v>
+      </c>
       <c r="D7" t="n">
         <v>1.31483e-07</v>
       </c>
@@ -7586,6 +7946,9 @@
       <c r="B8" t="n">
         <v>92.28800000000001</v>
       </c>
+      <c r="C8" t="n">
+        <v>1530.204816276668</v>
+      </c>
       <c r="D8" t="n">
         <v>1.30793e-07</v>
       </c>
@@ -7636,6 +7999,9 @@
       <c r="B9" t="n">
         <v>87.86500000000001</v>
       </c>
+      <c r="C9" t="n">
+        <v>1480.021665568028</v>
+      </c>
       <c r="D9" t="n">
         <v>1.30247e-07</v>
       </c>
@@ -7686,6 +8052,9 @@
       <c r="B10" t="n">
         <v>85.19400000000002</v>
       </c>
+      <c r="C10" t="n">
+        <v>1524.900817121409</v>
+      </c>
       <c r="D10" t="n">
         <v>1.29801e-07</v>
       </c>
@@ -7735,6 +8104,9 @@
       </c>
       <c r="B11" t="n">
         <v>83.67599999999999</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1836.017318540059</v>
       </c>
       <c r="D11" t="n">
         <v>1.29497e-07</v>
@@ -7806,7 +8178,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7932,6 +8304,9 @@
       <c r="B2" t="n">
         <v>166.4859999999999</v>
       </c>
+      <c r="C2" t="n">
+        <v>1502.224546260377</v>
+      </c>
       <c r="D2" t="n">
         <v>1.33147e-07</v>
       </c>
@@ -7982,6 +8357,9 @@
       <c r="B3" t="n">
         <v>146.001</v>
       </c>
+      <c r="C3" t="n">
+        <v>1141.339672971119</v>
+      </c>
       <c r="D3" t="n">
         <v>1.30999e-07</v>
       </c>
@@ -8032,6 +8410,9 @@
       <c r="B4" t="n">
         <v>136.545</v>
       </c>
+      <c r="C4" t="n">
+        <v>1003.756172955758</v>
+      </c>
       <c r="D4" t="n">
         <v>1.29836e-07</v>
       </c>
@@ -8082,6 +8463,9 @@
       <c r="B5" t="n">
         <v>135.524</v>
       </c>
+      <c r="C5" t="n">
+        <v>1097.818199350853</v>
+      </c>
       <c r="D5" t="n">
         <v>1.29139e-07</v>
       </c>
@@ -8132,6 +8516,9 @@
       <c r="B6" t="n">
         <v>129.4109999999999</v>
       </c>
+      <c r="C6" t="n">
+        <v>1025.034437731215</v>
+      </c>
       <c r="D6" t="n">
         <v>1.28691e-07</v>
       </c>
@@ -8182,6 +8569,9 @@
       <c r="B7" t="n">
         <v>129.4039999999999</v>
       </c>
+      <c r="C7" t="n">
+        <v>1157.648427677055</v>
+      </c>
       <c r="D7" t="n">
         <v>1.2844e-07</v>
       </c>
@@ -8232,6 +8622,9 @@
       <c r="B8" t="n">
         <v>126.652</v>
       </c>
+      <c r="C8" t="n">
+        <v>1153.88184002567</v>
+      </c>
       <c r="D8" t="n">
         <v>1.28249e-07</v>
       </c>
@@ -8282,6 +8675,9 @@
       <c r="B9" t="n">
         <v>120.405</v>
       </c>
+      <c r="C9" t="n">
+        <v>1039.125462561509</v>
+      </c>
       <c r="D9" t="n">
         <v>1.28111e-07</v>
       </c>
@@ -8332,6 +8728,9 @@
       <c r="B10" t="n">
         <v>118.8390000000001</v>
       </c>
+      <c r="C10" t="n">
+        <v>1054.447249510497</v>
+      </c>
       <c r="D10" t="n">
         <v>1.2803e-07</v>
       </c>
@@ -8382,6 +8781,9 @@
       <c r="B11" t="n">
         <v>115.681</v>
       </c>
+      <c r="C11" t="n">
+        <v>1068.611405053406</v>
+      </c>
       <c r="D11" t="n">
         <v>1.27948e-07</v>
       </c>
@@ -8432,6 +8834,9 @@
       <c r="B12" t="n">
         <v>112.958</v>
       </c>
+      <c r="C12" t="n">
+        <v>1046.259808181741</v>
+      </c>
       <c r="D12" t="n">
         <v>1.27892e-07</v>
       </c>
@@ -8482,6 +8887,9 @@
       <c r="B13" t="n">
         <v>111.177</v>
       </c>
+      <c r="C13" t="n">
+        <v>1057.000624936652</v>
+      </c>
       <c r="D13" t="n">
         <v>1.27846e-07</v>
       </c>
@@ -8532,6 +8940,9 @@
       <c r="B14" t="n">
         <v>108.74</v>
       </c>
+      <c r="C14" t="n">
+        <v>1025.05735737923</v>
+      </c>
       <c r="D14" t="n">
         <v>1.27794e-07</v>
       </c>
@@ -8582,6 +8993,9 @@
       <c r="B15" t="n">
         <v>108.625</v>
       </c>
+      <c r="C15" t="n">
+        <v>1077.583574399752</v>
+      </c>
       <c r="D15" t="n">
         <v>1.27743e-07</v>
       </c>
@@ -8632,6 +9046,9 @@
       <c r="B16" t="n">
         <v>109.842</v>
       </c>
+      <c r="C16" t="n">
+        <v>1282.38186636424</v>
+      </c>
       <c r="D16" t="n">
         <v>1.27717e-07</v>
       </c>
@@ -8682,6 +9099,9 @@
       <c r="B17" t="n">
         <v>108.27</v>
       </c>
+      <c r="C17" t="n">
+        <v>1255.363641731249</v>
+      </c>
       <c r="D17" t="n">
         <v>1.27683e-07</v>
       </c>
@@ -8732,6 +9152,9 @@
       <c r="B18" t="n">
         <v>105.467</v>
       </c>
+      <c r="C18" t="n">
+        <v>1225.681663840188</v>
+      </c>
       <c r="D18" t="n">
         <v>1.27651e-07</v>
       </c>
@@ -8782,6 +9205,9 @@
       <c r="B19" t="n">
         <v>104.166</v>
       </c>
+      <c r="C19" t="n">
+        <v>1169.112866239651</v>
+      </c>
       <c r="D19" t="n">
         <v>1.27623e-07</v>
       </c>
@@ -8832,6 +9258,9 @@
       <c r="B20" t="n">
         <v>100.913</v>
       </c>
+      <c r="C20" t="n">
+        <v>1126.220667121904</v>
+      </c>
       <c r="D20" t="n">
         <v>1.27607e-07</v>
       </c>
@@ -8882,6 +9311,9 @@
       <c r="B21" t="n">
         <v>99.524</v>
       </c>
+      <c r="C21" t="n">
+        <v>1164.202268827835</v>
+      </c>
       <c r="D21" t="n">
         <v>1.27591e-07</v>
       </c>
@@ -8931,6 +9363,9 @@
       </c>
       <c r="B22" t="n">
         <v>97.82099999999997</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1100.653267622819</v>
       </c>
       <c r="D22" t="n">
         <v>1.27573e-07</v>
@@ -9002,7 +9437,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -9128,6 +9563,9 @@
       <c r="B2" t="n">
         <v>140.1929999999999</v>
       </c>
+      <c r="C2" t="n">
+        <v>3500.671789095855</v>
+      </c>
       <c r="D2" t="n">
         <v>1.40223e-07</v>
       </c>
@@ -9178,6 +9616,9 @@
       <c r="B3" t="n">
         <v>96.63299999999998</v>
       </c>
+      <c r="C3" t="n">
+        <v>2479.083981626369</v>
+      </c>
       <c r="D3" t="n">
         <v>1.37618e-07</v>
       </c>
@@ -9228,6 +9669,9 @@
       <c r="B4" t="n">
         <v>87.56</v>
       </c>
+      <c r="C4" t="n">
+        <v>1840.307954126344</v>
+      </c>
       <c r="D4" t="n">
         <v>1.35242e-07</v>
       </c>
@@ -9278,6 +9722,9 @@
       <c r="B5" t="n">
         <v>82.64600000000002</v>
       </c>
+      <c r="C5" t="n">
+        <v>1614.324517107863</v>
+      </c>
       <c r="D5" t="n">
         <v>1.33778e-07</v>
       </c>
@@ -9328,6 +9775,9 @@
       <c r="B6" t="n">
         <v>81.23000000000002</v>
       </c>
+      <c r="C6" t="n">
+        <v>1828.495890847339</v>
+      </c>
       <c r="D6" t="n">
         <v>1.32853e-07</v>
       </c>
@@ -9378,6 +9828,9 @@
       <c r="B7" t="n">
         <v>76.25400000000002</v>
       </c>
+      <c r="C7" t="n">
+        <v>1849.582751138911</v>
+      </c>
       <c r="D7" t="n">
         <v>1.32323e-07</v>
       </c>
@@ -9428,6 +9881,9 @@
       <c r="B8" t="n">
         <v>75.06899999999996</v>
       </c>
+      <c r="C8" t="n">
+        <v>2300.024547323758</v>
+      </c>
       <c r="D8" t="n">
         <v>1.31977e-07</v>
       </c>
@@ -9478,6 +9934,9 @@
       <c r="B9" t="n">
         <v>73.928</v>
       </c>
+      <c r="C9" t="n">
+        <v>3080.419288637509</v>
+      </c>
       <c r="D9" t="n">
         <v>1.31771e-07</v>
       </c>
@@ -9528,6 +9987,9 @@
       <c r="B10" t="n">
         <v>69.96699999999998</v>
       </c>
+      <c r="C10" t="n">
+        <v>3288.979123830104</v>
+      </c>
       <c r="D10" t="n">
         <v>1.31646e-07</v>
       </c>
@@ -9577,6 +10039,9 @@
       </c>
       <c r="B11" t="n">
         <v>69.30700000000002</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4738.958569700412</v>
       </c>
       <c r="D11" t="n">
         <v>1.31534e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 44.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 44.xlsx
@@ -565,7 +565,7 @@
         <v>165.3560000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>1045.111006662003</v>
+        <v>165.3560000000001</v>
       </c>
       <c r="D2" t="n">
         <v>1.20671e-07</v>
@@ -597,11 +597,10 @@
       <c r="X2" t="n">
         <v>-13482.98883291923</v>
       </c>
-      <c r="Y2" t="n">
-        <v>411.7593169325443</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>12996.38220382945</v>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA2" t="n">
         <v>2.126325610808854e-07</v>
@@ -618,7 +617,7 @@
         <v>159.085</v>
       </c>
       <c r="C3" t="n">
-        <v>1040.249048681838</v>
+        <v>400.1117601489224</v>
       </c>
       <c r="D3" t="n">
         <v>1.19954e-07</v>
@@ -651,16 +650,13 @@
         <v>-14754.47805260957</v>
       </c>
       <c r="Y3" t="n">
-        <v>408.4420714575168</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>12831.97957776769</v>
+        <v>183.0250836196455</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.70928386553016e-07</v>
+        <v>1.81705851755891e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9531955260823682</v>
+        <v>0.9884541363061929</v>
       </c>
     </row>
     <row r="4">
@@ -671,7 +667,7 @@
         <v>153.983</v>
       </c>
       <c r="C4" t="n">
-        <v>1101.979719337023</v>
+        <v>387.5375635320746</v>
       </c>
       <c r="D4" t="n">
         <v>1.19583e-07</v>
@@ -704,16 +700,13 @@
         <v>-15805.6122655137</v>
       </c>
       <c r="Y4" t="n">
-        <v>508.2532943336094</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>417896320.6781315</v>
+        <v>192.1183460086119</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.587258504028678e-07</v>
+        <v>1.665587233513952e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9562218307784481</v>
+        <v>0.999831456383186</v>
       </c>
     </row>
     <row r="5">
@@ -724,7 +717,7 @@
         <v>151.135</v>
       </c>
       <c r="C5" t="n">
-        <v>1180.214540733193</v>
+        <v>151.135</v>
       </c>
       <c r="D5" t="n">
         <v>1.19433e-07</v>
@@ -756,11 +749,10 @@
       <c r="X5" t="n">
         <v>-16662.24750039758</v>
       </c>
-      <c r="Y5" t="n">
-        <v>502.7470326817317</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>275812126.4245548</v>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA5" t="n">
         <v>1.564040085131281e-07</v>
@@ -777,7 +769,7 @@
         <v>139.909</v>
       </c>
       <c r="C6" t="n">
-        <v>992.5331859503139</v>
+        <v>139.909</v>
       </c>
       <c r="D6" t="n">
         <v>1.19324e-07</v>
@@ -809,11 +801,10 @@
       <c r="X6" t="n">
         <v>-16250.75718620393</v>
       </c>
-      <c r="Y6" t="n">
-        <v>497.3203805432613</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>440524805.7179161</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>1.546538643246325e-07</v>
@@ -830,7 +821,7 @@
         <v>139.419</v>
       </c>
       <c r="C7" t="n">
-        <v>1108.075420319863</v>
+        <v>370.3454917511363</v>
       </c>
       <c r="D7" t="n">
         <v>1.19321e-07</v>
@@ -863,16 +854,13 @@
         <v>-17312.65688873198</v>
       </c>
       <c r="Y7" t="n">
-        <v>492.1355905401169</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>268873143.2274749</v>
+        <v>190.9958570874498</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.531511706728881e-07</v>
+        <v>1.737326555492724e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9613525716706356</v>
+        <v>0.9999358462048032</v>
       </c>
     </row>
     <row r="8">
@@ -883,7 +871,7 @@
         <v>133.6900000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>1050.060894352629</v>
+        <v>133.6900000000001</v>
       </c>
       <c r="D8" t="n">
         <v>1.19347e-07</v>
@@ -915,11 +903,10 @@
       <c r="X8" t="n">
         <v>-17370.87342789974</v>
       </c>
-      <c r="Y8" t="n">
-        <v>487.1860973437121</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>136545608.480812</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA8" t="n">
         <v>1.519242541262174e-07</v>
@@ -936,7 +923,7 @@
         <v>123.512</v>
       </c>
       <c r="C9" t="n">
-        <v>916.482295631263</v>
+        <v>362.0964040365431</v>
       </c>
       <c r="D9" t="n">
         <v>1.19379e-07</v>
@@ -969,16 +956,13 @@
         <v>-16398.22928104388</v>
       </c>
       <c r="Y9" t="n">
-        <v>482.430855581866</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>31925202.95289881</v>
+        <v>182.9901054516226</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.506891132876705e-07</v>
+        <v>1.686506126870111e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9639062228131657</v>
+        <v>0.9996179400194639</v>
       </c>
     </row>
     <row r="10">
@@ -989,7 +973,7 @@
         <v>128.252</v>
       </c>
       <c r="C10" t="n">
-        <v>1087.431315153416</v>
+        <v>271.8104170474262</v>
       </c>
       <c r="D10" t="n">
         <v>1.19423e-07</v>
@@ -1022,10 +1006,7 @@
         <v>-18104.56078389052</v>
       </c>
       <c r="Y10" t="n">
-        <v>455.381417439908</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>19846.0964544713</v>
+        <v>615.0800901428261</v>
       </c>
       <c r="AA10" t="n">
         <v>1.520922072394433e-07</v>
@@ -1042,7 +1023,7 @@
         <v>124.595</v>
       </c>
       <c r="C11" t="n">
-        <v>1121.911138989311</v>
+        <v>354.8623024914639</v>
       </c>
       <c r="D11" t="n">
         <v>1.19487e-07</v>
@@ -1075,16 +1056,13 @@
         <v>-18220.44189905057</v>
       </c>
       <c r="Y11" t="n">
-        <v>450.053664539966</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>19670.14489609735</v>
+        <v>181.349910469209</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.562523329086697e-07</v>
+        <v>1.76136837552478e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9997907550928897</v>
+        <v>0.9995779623255583</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1219,7 @@
         <v>156.985</v>
       </c>
       <c r="C2" t="n">
-        <v>1621.145838315899</v>
+        <v>372.509562498546</v>
       </c>
       <c r="D2" t="n">
         <v>1.31074e-07</v>
@@ -1274,16 +1252,13 @@
         <v>-17353.57524213114</v>
       </c>
       <c r="Y2" t="n">
-        <v>410.1391862482902</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>12630.45900436312</v>
+        <v>194.8392034727747</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.093273558950987e-07</v>
+        <v>1.632428405261561e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9999116059118714</v>
+        <v>0.9972348170603681</v>
       </c>
     </row>
     <row r="3">
@@ -1294,7 +1269,7 @@
         <v>133.288</v>
       </c>
       <c r="C3" t="n">
-        <v>1088.883548491037</v>
+        <v>656.752559189013</v>
       </c>
       <c r="D3" t="n">
         <v>1.31092e-07</v>
@@ -1327,16 +1302,13 @@
         <v>-18131.16864417374</v>
       </c>
       <c r="Y3" t="n">
-        <v>493.9139008458086</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>273699440.7054271</v>
+        <v>1.325754793522079</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.666724291889467e-07</v>
+        <v>1.182411890749819e-07</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9628264413360366</v>
+        <v>0.6460112160597945</v>
       </c>
     </row>
     <row r="4">
@@ -1347,7 +1319,7 @@
         <v>128.7099999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>1129.907670087515</v>
+        <v>332.8564851213093</v>
       </c>
       <c r="D4" t="n">
         <v>1.30923e-07</v>
@@ -1380,16 +1352,13 @@
         <v>-19324.75488081173</v>
       </c>
       <c r="Y4" t="n">
-        <v>487.9730295432886</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>565722063.336921</v>
+        <v>228.1100755848424</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.645372564140362e-07</v>
+        <v>3.122622505737328e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9646060326260341</v>
+        <v>0.9702660801886869</v>
       </c>
     </row>
     <row r="5">
@@ -1400,7 +1369,7 @@
         <v>124.245</v>
       </c>
       <c r="C5" t="n">
-        <v>1122.869499827731</v>
+        <v>329.5088824589109</v>
       </c>
       <c r="D5" t="n">
         <v>1.30831e-07</v>
@@ -1433,16 +1402,13 @@
         <v>-19669.0640710365</v>
       </c>
       <c r="Y5" t="n">
-        <v>483.5685848812222</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>34807032.39252497</v>
+        <v>216.8059916639323</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.629435086995487e-07</v>
+        <v>2.013639817783223e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.965989828461488</v>
+        <v>0.999679119833617</v>
       </c>
     </row>
     <row r="6">
@@ -1453,7 +1419,7 @@
         <v>120.6560000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>1072.989310994566</v>
+        <v>327.8547979811365</v>
       </c>
       <c r="D6" t="n">
         <v>1.30732e-07</v>
@@ -1486,16 +1452,13 @@
         <v>-19500.70018840255</v>
       </c>
       <c r="Y6" t="n">
-        <v>479.2088034241564</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>131330757.6997159</v>
+        <v>213.8034042653467</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.620041392643991e-07</v>
+        <v>2.000462006330202e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9667632488015196</v>
+        <v>0.9998026957579937</v>
       </c>
     </row>
     <row r="7">
@@ -1506,7 +1469,7 @@
         <v>116.7300000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>1050.93581877685</v>
+        <v>324.38032762529</v>
       </c>
       <c r="D7" t="n">
         <v>1.30672e-07</v>
@@ -1539,16 +1502,13 @@
         <v>-19445.72062952601</v>
       </c>
       <c r="Y7" t="n">
-        <v>474.9458182087178</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>531346021.4324536</v>
+        <v>212.051808546952</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.611908377862559e-07</v>
+        <v>2.000436941129308e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9674692400662943</v>
+        <v>0.9999832521757775</v>
       </c>
     </row>
     <row r="8">
@@ -1559,7 +1519,7 @@
         <v>113.102</v>
       </c>
       <c r="C8" t="n">
-        <v>1014.53888431003</v>
+        <v>320.0799584869671</v>
       </c>
       <c r="D8" t="n">
         <v>1.30625e-07</v>
@@ -1592,16 +1552,13 @@
         <v>-19403.55810838039</v>
       </c>
       <c r="Y8" t="n">
-        <v>452.6693174013192</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>19540.95346841798</v>
+        <v>208.0074639823007</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.651426516536248e-07</v>
+        <v>2.018656534481645e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9999407474072944</v>
+        <v>0.9985444964104068</v>
       </c>
     </row>
     <row r="9">
@@ -1612,7 +1569,7 @@
         <v>113.992</v>
       </c>
       <c r="C9" t="n">
-        <v>1167.174437524019</v>
+        <v>335.8495273111578</v>
       </c>
       <c r="D9" t="n">
         <v>1.30557e-07</v>
@@ -1645,16 +1602,13 @@
         <v>-20583.00029529128</v>
       </c>
       <c r="Y9" t="n">
-        <v>444.4654801102821</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>19373.55504270451</v>
+        <v>188.1219784763243</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.619434150107878e-07</v>
+        <v>1.847661292696819e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9999971707143199</v>
+        <v>0.9994312949802087</v>
       </c>
     </row>
     <row r="10">
@@ -1665,7 +1619,7 @@
         <v>109.841</v>
       </c>
       <c r="C10" t="n">
-        <v>1108.699081505459</v>
+        <v>314.4535308700859</v>
       </c>
       <c r="D10" t="n">
         <v>1.30502e-07</v>
@@ -1698,16 +1652,13 @@
         <v>-19986.55733397512</v>
       </c>
       <c r="Y10" t="n">
-        <v>463.3826782451251</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>505037849.5341532</v>
+        <v>207.4322664007058</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.590784952882569e-07</v>
+        <v>2.09485235488373e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9692961082749496</v>
+        <v>0.9977818574704189</v>
       </c>
     </row>
     <row r="11">
@@ -1718,7 +1669,7 @@
         <v>107.521</v>
       </c>
       <c r="C11" t="n">
-        <v>1065.560926374041</v>
+        <v>314.5717674952584</v>
       </c>
       <c r="D11" t="n">
         <v>1.30461e-07</v>
@@ -1751,16 +1702,13 @@
         <v>-19865.0899368243</v>
       </c>
       <c r="Y11" t="n">
-        <v>459.8460698803496</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>125205771.326377</v>
+        <v>202.102111506277</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.585200962990779e-07</v>
+        <v>2.050165530558116e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9697854849437182</v>
+        <v>0.9984955149947142</v>
       </c>
     </row>
     <row r="12">
@@ -1771,7 +1719,7 @@
         <v>107.365</v>
       </c>
       <c r="C12" t="n">
-        <v>1139.364016819648</v>
+        <v>321.3848316597167</v>
       </c>
       <c r="D12" t="n">
         <v>1.30396e-07</v>
@@ -1804,16 +1752,13 @@
         <v>-20438.61023290347</v>
       </c>
       <c r="Y12" t="n">
-        <v>456.535593862355</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>30261567.83792722</v>
+        <v>193.7946186520622</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.578304503495486e-07</v>
+        <v>2.075764012250078e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.9703828459429824</v>
+        <v>0.9971455772267578</v>
       </c>
     </row>
     <row r="13">
@@ -1824,7 +1769,7 @@
         <v>102.9</v>
       </c>
       <c r="C13" t="n">
-        <v>1037.51082687527</v>
+        <v>308.2731038694725</v>
       </c>
       <c r="D13" t="n">
         <v>1.30336e-07</v>
@@ -1857,16 +1802,13 @@
         <v>-19658.85723440928</v>
       </c>
       <c r="Y13" t="n">
-        <v>453.3252433312804</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>24406528.33733271</v>
+        <v>213.1614113459096</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.571142709843805e-07</v>
+        <v>3.017638076126673e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.9710070636950802</v>
+        <v>0.9786987001819787</v>
       </c>
     </row>
     <row r="14">
@@ -1877,7 +1819,7 @@
         <v>103.528</v>
       </c>
       <c r="C14" t="n">
-        <v>1140.111296746734</v>
+        <v>304.4269452985353</v>
       </c>
       <c r="D14" t="n">
         <v>1.30318e-07</v>
@@ -1910,16 +1852,13 @@
         <v>-20518.7504317746</v>
       </c>
       <c r="Y14" t="n">
-        <v>450.1756658591516</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>368403734.9110797</v>
+        <v>200.470652447151</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.570387008638566e-07</v>
+        <v>2.070655342531419e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.9710668020018245</v>
+        <v>0.9993434536846061</v>
       </c>
     </row>
     <row r="15">
@@ -1930,7 +1869,7 @@
         <v>99.56200000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>1011.914910845446</v>
+        <v>99.56200000000001</v>
       </c>
       <c r="D15" t="n">
         <v>1.30283e-07</v>
@@ -1962,11 +1901,10 @@
       <c r="X15" t="n">
         <v>-19610.25467803122</v>
       </c>
-      <c r="Y15" t="n">
-        <v>390.4033625687773</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>14812.44420648461</v>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA15" t="n">
         <v>1.810943691312676e-07</v>
@@ -1983,7 +1921,7 @@
         <v>99.94499999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>1112.406871469197</v>
+        <v>301.5498715661653</v>
       </c>
       <c r="D16" t="n">
         <v>1.3024e-07</v>
@@ -2016,16 +1954,13 @@
         <v>-20467.66969357239</v>
       </c>
       <c r="Y16" t="n">
-        <v>389.6324228856581</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>14696.0377982667</v>
+        <v>202.2355643762466</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.92395061491683e-07</v>
+        <v>2.168020423936196e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9999099209967212</v>
+        <v>0.999990910934249</v>
       </c>
     </row>
     <row r="17">
@@ -2036,7 +1971,7 @@
         <v>97.38499999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>1088.759056821231</v>
+        <v>299.8596576298117</v>
       </c>
       <c r="D17" t="n">
         <v>1.30212e-07</v>
@@ -2069,16 +2004,13 @@
         <v>-19765.59665077637</v>
       </c>
       <c r="Y17" t="n">
-        <v>391.6664340667907</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>14606.99948540395</v>
+        <v>198.4380844126443</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.821039805761228e-07</v>
+        <v>2.179875050291306e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9999809804529132</v>
+        <v>0.9984473884286449</v>
       </c>
     </row>
     <row r="18">
@@ -2089,7 +2021,7 @@
         <v>94.57000000000005</v>
       </c>
       <c r="C18" t="n">
-        <v>1038.376503327636</v>
+        <v>295.8772145212901</v>
       </c>
       <c r="D18" t="n">
         <v>1.302e-07</v>
@@ -2122,16 +2054,13 @@
         <v>-19426.78853111032</v>
       </c>
       <c r="Y18" t="n">
-        <v>437.7563510322282</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>238340325.8260486</v>
+        <v>193.7764217326319</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.553730672204273e-07</v>
+        <v>2.049428766410002e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9725661161631419</v>
+        <v>0.9997545998221142</v>
       </c>
     </row>
     <row r="19">
@@ -2142,7 +2071,7 @@
         <v>97.08100000000002</v>
       </c>
       <c r="C19" t="n">
-        <v>1297.413535790615</v>
+        <v>295.7887100523882</v>
       </c>
       <c r="D19" t="n">
         <v>1.30153e-07</v>
@@ -2175,16 +2104,13 @@
         <v>-21074.70458151443</v>
       </c>
       <c r="Y19" t="n">
-        <v>434.6282572127394</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>43203306.43225927</v>
+        <v>192.9903732792495</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.548358501799225e-07</v>
+        <v>2.092119517697357e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.9730434320345782</v>
+        <v>0.9994168217353023</v>
       </c>
     </row>
     <row r="20">
@@ -2195,7 +2121,7 @@
         <v>96.137</v>
       </c>
       <c r="C20" t="n">
-        <v>1321.871374120467</v>
+        <v>294.2730518025084</v>
       </c>
       <c r="D20" t="n">
         <v>1.30162e-07</v>
@@ -2228,16 +2154,13 @@
         <v>-21298.44450886489</v>
       </c>
       <c r="Y20" t="n">
-        <v>431.5496335866495</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>240533985.6582939</v>
+        <v>188.4630927141799</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.547163012132256e-07</v>
+        <v>2.222997265952816e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9731733912713522</v>
+        <v>0.996604458815566</v>
       </c>
     </row>
     <row r="21">
@@ -2248,7 +2171,7 @@
         <v>94.35799999999995</v>
       </c>
       <c r="C21" t="n">
-        <v>1331.630482137158</v>
+        <v>289.5711579822464</v>
       </c>
       <c r="D21" t="n">
         <v>1.30124e-07</v>
@@ -2281,16 +2204,13 @@
         <v>-21457.98938338228</v>
       </c>
       <c r="Y21" t="n">
-        <v>428.4961588415422</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>118815944.0394076</v>
+        <v>196.4313722729031</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.542253843597307e-07</v>
+        <v>2.354955806952794e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9736206015581541</v>
+        <v>0.9985817293485175</v>
       </c>
     </row>
     <row r="22">
@@ -2301,7 +2221,7 @@
         <v>90.22499999999997</v>
       </c>
       <c r="C22" t="n">
-        <v>1095.474097431361</v>
+        <v>284.1483193072186</v>
       </c>
       <c r="D22" t="n">
         <v>1.30106e-07</v>
@@ -2334,16 +2254,13 @@
         <v>-19936.89837474209</v>
       </c>
       <c r="Y22" t="n">
-        <v>425.4542816572644</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>347583200.8772737</v>
+        <v>199.2264003885679</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.540041125874781e-07</v>
+        <v>2.361492632500844e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9738210209580928</v>
+        <v>0.9985991965947012</v>
       </c>
     </row>
   </sheetData>
@@ -2500,7 +2417,7 @@
         <v>173.051</v>
       </c>
       <c r="C2" t="n">
-        <v>1555.069771673009</v>
+        <v>444.7884772957032</v>
       </c>
       <c r="D2" t="n">
         <v>1.25063e-07</v>
@@ -2533,16 +2450,13 @@
         <v>-12416.24824919289</v>
       </c>
       <c r="Y2" t="n">
-        <v>416.7629595657864</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>13043.37358641603</v>
+        <v>139.892800437904</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.027534594319083e-07</v>
+        <v>1.203049561110753e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9998456956762208</v>
+        <v>0.9995461588573076</v>
       </c>
     </row>
     <row r="3">
@@ -2553,7 +2467,7 @@
         <v>149.7909999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>1176.259471695698</v>
+        <v>149.7909999999999</v>
       </c>
       <c r="D3" t="n">
         <v>1.23272e-07</v>
@@ -2585,11 +2499,10 @@
       <c r="X3" t="n">
         <v>-15186.3575794681</v>
       </c>
-      <c r="Y3" t="n">
-        <v>511.2152587891023</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1153050632.107476</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA3" t="n">
         <v>1.65047606081878e-07</v>
@@ -2606,7 +2519,7 @@
         <v>144.8030000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>1153.104331664492</v>
+        <v>382.3673002596863</v>
       </c>
       <c r="D4" t="n">
         <v>1.22369e-07</v>
@@ -2639,16 +2552,13 @@
         <v>-16863.78495476274</v>
       </c>
       <c r="Y4" t="n">
-        <v>505.9367732007904</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>276973980.2023099</v>
+        <v>184.8338997922385</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.5975165127509e-07</v>
+        <v>1.575428170740311e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9587661132799178</v>
+        <v>0.9988028191376429</v>
       </c>
     </row>
     <row r="5">
@@ -2659,7 +2569,7 @@
         <v>141.254</v>
       </c>
       <c r="C5" t="n">
-        <v>1169.425887537154</v>
+        <v>382.4025178043914</v>
       </c>
       <c r="D5" t="n">
         <v>1.21862e-07</v>
@@ -2692,16 +2602,13 @@
         <v>-17961.24743845963</v>
       </c>
       <c r="Y5" t="n">
-        <v>501.6073645736557</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>274198527.786215</v>
+        <v>178.8075481234039</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.567713072065792e-07</v>
+        <v>1.598918258485465e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9609994784080305</v>
+        <v>0.9978000013571195</v>
       </c>
     </row>
     <row r="6">
@@ -2712,7 +2619,7 @@
         <v>134.606</v>
       </c>
       <c r="C6" t="n">
-        <v>1059.996194455794</v>
+        <v>380.3370567929444</v>
       </c>
       <c r="D6" t="n">
         <v>1.21539e-07</v>
@@ -2745,16 +2652,13 @@
         <v>-17997.61842269876</v>
       </c>
       <c r="Y6" t="n">
-        <v>497.2754351093973</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>339643224.7489861</v>
+        <v>182.2146363645353</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.547601861903376e-07</v>
+        <v>1.625840746883724e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9625708344887036</v>
+        <v>0.9999850894244195</v>
       </c>
     </row>
     <row r="7">
@@ -2765,7 +2669,7 @@
         <v>132.833</v>
       </c>
       <c r="C7" t="n">
-        <v>1115.056361684947</v>
+        <v>558.7323243069739</v>
       </c>
       <c r="D7" t="n">
         <v>1.21327e-07</v>
@@ -2798,16 +2702,13 @@
         <v>-18713.21818627753</v>
       </c>
       <c r="Y7" t="n">
-        <v>492.8619727179022</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>48122411.69188027</v>
+        <v>3.593552210654685</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.530852102112056e-07</v>
+        <v>1.402466681286796e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9639646642554476</v>
+        <v>0.9656649941082681</v>
       </c>
     </row>
     <row r="8">
@@ -2818,7 +2719,7 @@
         <v>129.3650000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>963.9668523082921</v>
+        <v>627.0408761239223</v>
       </c>
       <c r="D8" t="n">
         <v>1.21216e-07</v>
@@ -2851,16 +2752,13 @@
         <v>-18898.64523204229</v>
       </c>
       <c r="Y8" t="n">
-        <v>488.3942272544898</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>139167288.1738239</v>
+        <v>22.87328665904335</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.521024047703086e-07</v>
+        <v>2.714998837892551e-08</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.964807304604266</v>
+        <v>0.7589626585682619</v>
       </c>
     </row>
     <row r="9">
@@ -2871,7 +2769,7 @@
         <v>126.149</v>
       </c>
       <c r="C9" t="n">
-        <v>1110.828324142022</v>
+        <v>620.8428707088781</v>
       </c>
       <c r="D9" t="n">
         <v>1.21129e-07</v>
@@ -2904,16 +2802,13 @@
         <v>-19225.25622158501</v>
       </c>
       <c r="Y9" t="n">
-        <v>484.120822323998</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>132677314.3519183</v>
+        <v>22.40994578688241</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.511903614561794e-07</v>
+        <v>2.730774502367257e-08</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9656207271375492</v>
+        <v>0.7590075750107679</v>
       </c>
     </row>
     <row r="10">
@@ -2924,7 +2819,7 @@
         <v>121.513</v>
       </c>
       <c r="C10" t="n">
-        <v>1020.634328306055</v>
+        <v>121.513</v>
       </c>
       <c r="D10" t="n">
         <v>1.21079e-07</v>
@@ -2956,11 +2851,10 @@
       <c r="X10" t="n">
         <v>-18659.02516410564</v>
       </c>
-      <c r="Y10" t="n">
-        <v>463.1183379140412</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>19931.75710437477</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>1.514960415288417e-07</v>
@@ -2977,7 +2871,7 @@
         <v>118.6129999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>1038.272022536314</v>
+        <v>357.5270703348632</v>
       </c>
       <c r="D11" t="n">
         <v>1.21056e-07</v>
@@ -3010,16 +2904,13 @@
         <v>-18979.19883645495</v>
       </c>
       <c r="Y11" t="n">
-        <v>447.4710340674641</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>19780.44097911213</v>
+        <v>175.9089617374916</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.544921834051245e-07</v>
+        <v>1.678757179471214e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9998720592015995</v>
+        <v>0.9984536816798879</v>
       </c>
     </row>
     <row r="12">
@@ -3030,7 +2921,7 @@
         <v>113.862</v>
       </c>
       <c r="C12" t="n">
-        <v>954.9553177311874</v>
+        <v>355.0079273603395</v>
       </c>
       <c r="D12" t="n">
         <v>1.21028e-07</v>
@@ -3063,16 +2954,13 @@
         <v>-18468.81200397372</v>
       </c>
       <c r="Y12" t="n">
-        <v>450.809896135095</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>19636.48241462802</v>
+        <v>177.7557527474399</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.53486678242163e-07</v>
+        <v>1.799463191473608e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.9999784495102679</v>
+        <v>0.9981007465527786</v>
       </c>
     </row>
     <row r="13">
@@ -3083,7 +2971,7 @@
         <v>115.446</v>
       </c>
       <c r="C13" t="n">
-        <v>1106.386500418628</v>
+        <v>530.6027059886111</v>
       </c>
       <c r="D13" t="n">
         <v>1.21043e-07</v>
@@ -3116,16 +3004,13 @@
         <v>-19566.44751812772</v>
       </c>
       <c r="Y13" t="n">
-        <v>469.4180430424947</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>195687052.8469674</v>
+        <v>1.670455266752515</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.486442747547208e-07</v>
+        <v>1.236188957410127e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.9681241025185824</v>
+        <v>0.9795691034232376</v>
       </c>
     </row>
     <row r="14">
@@ -3136,7 +3021,7 @@
         <v>113.891</v>
       </c>
       <c r="C14" t="n">
-        <v>1099.756131420056</v>
+        <v>533.9556268212297</v>
       </c>
       <c r="D14" t="n">
         <v>1.21058e-07</v>
@@ -3169,16 +3054,13 @@
         <v>-19723.2558422374</v>
       </c>
       <c r="Y14" t="n">
-        <v>466.1555757796788</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>33889271.05198988</v>
+        <v>0.8283793683879426</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.481236604844619e-07</v>
+        <v>1.491172551382819e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.9686812738645403</v>
+        <v>0.9656667555855388</v>
       </c>
     </row>
     <row r="15">
@@ -3189,7 +3071,7 @@
         <v>111.984</v>
       </c>
       <c r="C15" t="n">
-        <v>1093.741340530384</v>
+        <v>111.984</v>
       </c>
       <c r="D15" t="n">
         <v>1.21044e-07</v>
@@ -3221,11 +3103,10 @@
       <c r="X15" t="n">
         <v>-19826.4224640925</v>
       </c>
-      <c r="Y15" t="n">
-        <v>463.0021897313908</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>30610608.87774355</v>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA15" t="n">
         <v>1.47557375829487e-07</v>
@@ -3242,7 +3123,7 @@
         <v>110.748</v>
       </c>
       <c r="C16" t="n">
-        <v>1102.586185916655</v>
+        <v>354.9389193226639</v>
       </c>
       <c r="D16" t="n">
         <v>1.21072e-07</v>
@@ -3275,16 +3156,13 @@
         <v>-19831.29149342823</v>
       </c>
       <c r="Y16" t="n">
-        <v>459.8739648972207</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1017990087.164893</v>
+        <v>171.5507361794584</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.475107914481014e-07</v>
+        <v>1.887708891937781e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9693403502596317</v>
+        <v>0.9973824890073947</v>
       </c>
     </row>
     <row r="17">
@@ -3295,7 +3173,7 @@
         <v>109.53</v>
       </c>
       <c r="C17" t="n">
-        <v>1168.481360065424</v>
+        <v>109.53</v>
       </c>
       <c r="D17" t="n">
         <v>1.21078e-07</v>
@@ -3327,11 +3205,10 @@
       <c r="X17" t="n">
         <v>-20320.00828788663</v>
       </c>
-      <c r="Y17" t="n">
-        <v>456.860752762009</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>501709512.345993</v>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA17" t="n">
         <v>1.469994822494576e-07</v>
@@ -3348,7 +3225,7 @@
         <v>104.501</v>
       </c>
       <c r="C18" t="n">
-        <v>998.4482839851482</v>
+        <v>351.0468026344484</v>
       </c>
       <c r="D18" t="n">
         <v>1.21099e-07</v>
@@ -3381,16 +3258,13 @@
         <v>-19124.79737006264</v>
       </c>
       <c r="Y18" t="n">
-        <v>453.9074739756753</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>32599065.49987507</v>
+        <v>161.7801282491701</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.465458601378154e-07</v>
+        <v>1.72675433836841e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.970382403861018</v>
+        <v>0.9982996938656616</v>
       </c>
     </row>
     <row r="19">
@@ -3401,7 +3275,7 @@
         <v>106.825</v>
       </c>
       <c r="C19" t="n">
-        <v>1203.790747942653</v>
+        <v>210.9403337012228</v>
       </c>
       <c r="D19" t="n">
         <v>1.21126e-07</v>
@@ -3434,10 +3308,7 @@
         <v>-20487.72512551313</v>
       </c>
       <c r="Y19" t="n">
-        <v>450.9131413153963</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>371115134.107501</v>
+        <v>562.7454064895539</v>
       </c>
       <c r="AA19" t="n">
         <v>1.463834274094101e-07</v>
@@ -3454,7 +3325,7 @@
         <v>105.208</v>
       </c>
       <c r="C20" t="n">
-        <v>1229.262998533652</v>
+        <v>345.1146658947244</v>
       </c>
       <c r="D20" t="n">
         <v>1.21159e-07</v>
@@ -3487,16 +3358,13 @@
         <v>-20400.88055875661</v>
       </c>
       <c r="Y20" t="n">
-        <v>447.9520199798416</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>488609989.4587379</v>
+        <v>160.0973020866855</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.461839679337601e-07</v>
+        <v>1.749809757452327e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9708403020313032</v>
+        <v>0.9995223133727702</v>
       </c>
     </row>
     <row r="21">
@@ -3507,7 +3375,7 @@
         <v>102.46</v>
       </c>
       <c r="C21" t="n">
-        <v>1168.457692517914</v>
+        <v>204.6117640380447</v>
       </c>
       <c r="D21" t="n">
         <v>1.21189e-07</v>
@@ -3540,10 +3408,7 @@
         <v>-20450.9722368486</v>
       </c>
       <c r="Y21" t="n">
-        <v>445.0454203031626</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>24252836.08707369</v>
+        <v>553.4695627151405</v>
       </c>
       <c r="AA21" t="n">
         <v>1.454227153458093e-07</v>
@@ -3560,7 +3425,7 @@
         <v>99.137</v>
       </c>
       <c r="C22" t="n">
-        <v>1046.640540163132</v>
+        <v>99.137</v>
       </c>
       <c r="D22" t="n">
         <v>1.21212e-07</v>
@@ -3592,11 +3457,10 @@
       <c r="X22" t="n">
         <v>-19296.228715192</v>
       </c>
-      <c r="Y22" t="n">
-        <v>442.0774439788123</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>254351094.1608738</v>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA22" t="n">
         <v>1.45726388151133e-07</v>
@@ -3759,7 +3623,7 @@
         <v>154.168</v>
       </c>
       <c r="C2" t="n">
-        <v>5330.556493779118</v>
+        <v>154.168</v>
       </c>
       <c r="D2" t="n">
         <v>1.32747e-07</v>
@@ -3791,11 +3655,10 @@
       <c r="X2" t="n">
         <v>-6573.881938216876</v>
       </c>
-      <c r="Y2" t="n">
-        <v>384.3381527024216</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>11775.32105460459</v>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA2" t="n">
         <v>2.374093315062157e-07</v>
@@ -3812,7 +3675,7 @@
         <v>121.446</v>
       </c>
       <c r="C3" t="n">
-        <v>1498.552779923557</v>
+        <v>121.446</v>
       </c>
       <c r="D3" t="n">
         <v>1.30919e-07</v>
@@ -3844,11 +3707,10 @@
       <c r="X3" t="n">
         <v>-8455.454687471025</v>
       </c>
-      <c r="Y3" t="n">
-        <v>453.5502752916325</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>744707921.196215</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA3" t="n">
         <v>1.905968989159095e-07</v>
@@ -3865,7 +3727,7 @@
         <v>111.069</v>
       </c>
       <c r="C4" t="n">
-        <v>1160.353541950791</v>
+        <v>111.069</v>
       </c>
       <c r="D4" t="n">
         <v>1.29034e-07</v>
@@ -3897,11 +3759,10 @@
       <c r="X4" t="n">
         <v>-9966.589926908709</v>
       </c>
-      <c r="Y4" t="n">
-        <v>446.9128653674636</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>122348596.6650685</v>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA4" t="n">
         <v>1.773423667132198e-07</v>
@@ -3918,7 +3779,7 @@
         <v>107.997</v>
       </c>
       <c r="C5" t="n">
-        <v>1256.964312007618</v>
+        <v>363.5760180369984</v>
       </c>
       <c r="D5" t="n">
         <v>1.27686e-07</v>
@@ -3951,16 +3812,13 @@
         <v>-11379.84288682476</v>
       </c>
       <c r="Y5" t="n">
-        <v>442.1150697035575</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>483107236.94912</v>
+        <v>136.2515746037265</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.696845536368017e-07</v>
+        <v>1.682013128452782e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9562245000466196</v>
+        <v>0.9965571308534045</v>
       </c>
     </row>
     <row r="6">
@@ -3971,7 +3829,7 @@
         <v>101.894</v>
       </c>
       <c r="C6" t="n">
-        <v>1071.972502659168</v>
+        <v>295.0471967439368</v>
       </c>
       <c r="D6" t="n">
         <v>1.26802e-07</v>
@@ -4004,16 +3862,13 @@
         <v>-12212.47173573682</v>
       </c>
       <c r="Y6" t="n">
-        <v>437.4918011690357</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>716242726.0374465</v>
+        <v>202.7985626825797</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.646980008581899e-07</v>
+        <v>2.343727445419775e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9596925259217173</v>
+        <v>0.9975582084073989</v>
       </c>
     </row>
     <row r="7">
@@ -4024,7 +3879,7 @@
         <v>100.205</v>
       </c>
       <c r="C7" t="n">
-        <v>1242.171366951171</v>
+        <v>595.4633156346957</v>
       </c>
       <c r="D7" t="n">
         <v>1.26186e-07</v>
@@ -4057,16 +3912,13 @@
         <v>-13152.68204207807</v>
       </c>
       <c r="Y7" t="n">
-        <v>375.2179786613265</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>14362.51599599425</v>
+        <v>0.5740854435417805</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.011577568869954e-07</v>
+        <v>1.95146761387755e-07</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9991934526489029</v>
+        <v>0.6215940068269361</v>
       </c>
     </row>
     <row r="8">
@@ -4077,7 +3929,7 @@
         <v>98.029</v>
       </c>
       <c r="C8" t="n">
-        <v>1301.24016477401</v>
+        <v>335.7239728801575</v>
       </c>
       <c r="D8" t="n">
         <v>1.25762e-07</v>
@@ -4110,16 +3962,13 @@
         <v>-13825.47071609503</v>
       </c>
       <c r="Y8" t="n">
-        <v>376.1330110265083</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>14197.74840955629</v>
+        <v>147.6753050315465</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.860080093500697e-07</v>
+        <v>1.810050764156763e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9997302702765594</v>
+        <v>0.998522369708451</v>
       </c>
     </row>
     <row r="9">
@@ -4130,7 +3979,7 @@
         <v>91.62099999999998</v>
       </c>
       <c r="C9" t="n">
-        <v>1134.636503173657</v>
+        <v>91.62099999999998</v>
       </c>
       <c r="D9" t="n">
         <v>1.25455e-07</v>
@@ -4162,11 +4011,10 @@
       <c r="X9" t="n">
         <v>-13944.87180468092</v>
       </c>
-      <c r="Y9" t="n">
-        <v>423.2257346382985</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>232460446.9736118</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>1.565866153131764e-07</v>
@@ -4183,7 +4031,7 @@
         <v>92.24700000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>1440.236742323683</v>
+        <v>243.603206235788</v>
       </c>
       <c r="D10" t="n">
         <v>1.25236e-07</v>
@@ -4216,16 +4064,13 @@
         <v>-14845.97249191081</v>
       </c>
       <c r="Y10" t="n">
-        <v>418.5699821633839</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>114807163.3957939</v>
+        <v>262.0811860270032</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.549818680972762e-07</v>
+        <v>9.193444650639813e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9670550345576974</v>
+        <v>0.9320508607612904</v>
       </c>
     </row>
     <row r="11">
@@ -4236,7 +4081,7 @@
         <v>89.62699999999995</v>
       </c>
       <c r="C11" t="n">
-        <v>1586.386127993006</v>
+        <v>285.5480759578967</v>
       </c>
       <c r="D11" t="n">
         <v>1.2505e-07</v>
@@ -4269,10 +4114,7 @@
         <v>-15346.09664441817</v>
       </c>
       <c r="Y11" t="n">
-        <v>414.1299460976634</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>451825689.7642848</v>
+        <v>521.6363754433793</v>
       </c>
       <c r="AA11" t="n">
         <v>1.536131569002642e-07</v>
@@ -4435,7 +4277,7 @@
         <v>169.186</v>
       </c>
       <c r="C2" t="n">
-        <v>1745.564564847555</v>
+        <v>169.186</v>
       </c>
       <c r="D2" t="n">
         <v>1.30706e-07</v>
@@ -4467,11 +4309,10 @@
       <c r="X2" t="n">
         <v>-11143.10422310316</v>
       </c>
-      <c r="Y2" t="n">
-        <v>417.5068185752541</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>12977.65313528089</v>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA2" t="n">
         <v>2.038867498814914e-07</v>
@@ -4488,7 +4329,7 @@
         <v>144.4109999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>1164.938609371968</v>
+        <v>380.5296603977646</v>
       </c>
       <c r="D3" t="n">
         <v>1.28327e-07</v>
@@ -4521,16 +4362,13 @@
         <v>-13751.00150610183</v>
       </c>
       <c r="Y3" t="n">
-        <v>508.0667941279152</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>451461944.1884012</v>
+        <v>187.8069389898081</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.750376676224168e-07</v>
+        <v>1.570638312892047e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.952159472204091</v>
+        <v>0.9997911920692778</v>
       </c>
     </row>
     <row r="4">
@@ -4541,7 +4379,7 @@
         <v>140.296</v>
       </c>
       <c r="C4" t="n">
-        <v>1207.643241694592</v>
+        <v>376.0119431107408</v>
       </c>
       <c r="D4" t="n">
         <v>1.27039e-07</v>
@@ -4574,16 +4412,13 @@
         <v>-15747.41414918185</v>
       </c>
       <c r="Y4" t="n">
-        <v>502.6456510843087</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>206166154.7535846</v>
+        <v>186.2315684273312</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.678223889175268e-07</v>
+        <v>1.658820708122115e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9570167642475148</v>
+        <v>0.9965600487384333</v>
       </c>
     </row>
     <row r="5">
@@ -4594,7 +4429,7 @@
         <v>133.29</v>
       </c>
       <c r="C5" t="n">
-        <v>1057.181993871552</v>
+        <v>374.7533239974774</v>
       </c>
       <c r="D5" t="n">
         <v>1.26238e-07</v>
@@ -4627,16 +4462,13 @@
         <v>-16627.16855542043</v>
       </c>
       <c r="Y5" t="n">
-        <v>498.4396734279157</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>204393482.0758557</v>
+        <v>186.1921206545465</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.634445930390748e-07</v>
+        <v>1.83360858441949e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.960071266487176</v>
+        <v>0.9915259559174473</v>
       </c>
     </row>
     <row r="6">
@@ -4647,7 +4479,7 @@
         <v>130.823</v>
       </c>
       <c r="C6" t="n">
-        <v>1093.190886603918</v>
+        <v>554.150877168374</v>
       </c>
       <c r="D6" t="n">
         <v>1.25732e-07</v>
@@ -4680,16 +4512,13 @@
         <v>-17551.88878711573</v>
       </c>
       <c r="Y6" t="n">
-        <v>494.0234310620984</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>438625635.8532071</v>
+        <v>3.525404679349104</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.606462367255953e-07</v>
+        <v>1.252559817357728e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9620840071446448</v>
+        <v>0.9737385358150706</v>
       </c>
     </row>
     <row r="7">
@@ -4700,7 +4529,7 @@
         <v>126.859</v>
       </c>
       <c r="C7" t="n">
-        <v>1111.881149329189</v>
+        <v>361.6214158506603</v>
       </c>
       <c r="D7" t="n">
         <v>1.25378e-07</v>
@@ -4733,16 +4562,13 @@
         <v>-18173.35050536688</v>
       </c>
       <c r="Y7" t="n">
-        <v>489.4728570395134</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>32380417.54701016</v>
+        <v>183.4074887254987</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.584815734986672e-07</v>
+        <v>1.68963149530145e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9637287600108656</v>
+        <v>0.9970466854421181</v>
       </c>
     </row>
     <row r="8">
@@ -4753,7 +4579,7 @@
         <v>124.0930000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>1089.080056307583</v>
+        <v>360.7407993754404</v>
       </c>
       <c r="D8" t="n">
         <v>1.25107e-07</v>
@@ -4786,16 +4612,13 @@
         <v>-18510.38553921237</v>
       </c>
       <c r="Y8" t="n">
-        <v>485.0689837616429</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>531345991.4080034</v>
+        <v>177.6952175653396</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.571962671235971e-07</v>
+        <v>1.583236977678895e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9646456513848748</v>
+        <v>0.9996451126551226</v>
       </c>
     </row>
     <row r="9">
@@ -4806,7 +4629,7 @@
         <v>122.473</v>
       </c>
       <c r="C9" t="n">
-        <v>1163.274178250816</v>
+        <v>357.7249100770655</v>
       </c>
       <c r="D9" t="n">
         <v>1.2493e-07</v>
@@ -4839,16 +4662,13 @@
         <v>-19274.90352499807</v>
       </c>
       <c r="Y9" t="n">
-        <v>461.6395463025264</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>19981.87027291454</v>
+        <v>182.2379065076975</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.561293990758285e-07</v>
+        <v>1.73229268593407e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9999662812709396</v>
+        <v>0.9979258091841393</v>
       </c>
     </row>
     <row r="10">
@@ -4859,7 +4679,7 @@
         <v>119.389</v>
       </c>
       <c r="C10" t="n">
-        <v>1159.544464835631</v>
+        <v>119.389</v>
       </c>
       <c r="D10" t="n">
         <v>1.2475e-07</v>
@@ -4891,11 +4711,10 @@
       <c r="X10" t="n">
         <v>-19354.11255195818</v>
       </c>
-      <c r="Y10" t="n">
-        <v>456.4975233873164</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>19821.06600705465</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>1.608007004954683e-07</v>
@@ -4912,7 +4731,7 @@
         <v>115.222</v>
       </c>
       <c r="C11" t="n">
-        <v>1069.048009432805</v>
+        <v>231.4420411401244</v>
       </c>
       <c r="D11" t="n">
         <v>1.24627e-07</v>
@@ -4945,10 +4764,7 @@
         <v>-19036.10569833713</v>
       </c>
       <c r="Y11" t="n">
-        <v>454.1545828518642</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>19700.56225115172</v>
+        <v>593.5153368456678</v>
       </c>
       <c r="AA11" t="n">
         <v>1.618344503575198e-07</v>
@@ -4965,7 +4781,7 @@
         <v>114.9059999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>1065.515368129375</v>
+        <v>114.9059999999999</v>
       </c>
       <c r="D12" t="n">
         <v>1.24514e-07</v>
@@ -4997,11 +4813,10 @@
       <c r="X12" t="n">
         <v>-19497.40703510112</v>
       </c>
-      <c r="Y12" t="n">
-        <v>471.1205816293415</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>257051752.1430815</v>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA12" t="n">
         <v>1.531553734385983e-07</v>
@@ -5018,7 +4833,7 @@
         <v>111.524</v>
       </c>
       <c r="C13" t="n">
-        <v>1052.07552166449</v>
+        <v>354.2713017492295</v>
       </c>
       <c r="D13" t="n">
         <v>1.24428e-07</v>
@@ -5051,16 +4866,13 @@
         <v>-19293.01124821303</v>
       </c>
       <c r="Y13" t="n">
-        <v>468.0741620206001</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>196796592.6595076</v>
+        <v>170.6525106867111</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.526117669715226e-07</v>
+        <v>1.70344781742188e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.9683422125716753</v>
+        <v>0.9988720380543018</v>
       </c>
     </row>
     <row r="14">
@@ -5071,7 +4883,7 @@
         <v>107.45</v>
       </c>
       <c r="C14" t="n">
-        <v>960.5947486525413</v>
+        <v>351.9995363554009</v>
       </c>
       <c r="D14" t="n">
         <v>1.24404e-07</v>
@@ -5104,16 +4916,13 @@
         <v>-18633.70275949086</v>
       </c>
       <c r="Y14" t="n">
-        <v>465.1827305649302</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>24933884.25577632</v>
+        <v>170.1520618673792</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.518962477579243e-07</v>
+        <v>1.721940679840552e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.9690302537693788</v>
+        <v>0.9988105812639083</v>
       </c>
     </row>
     <row r="15">
@@ -5124,7 +4933,7 @@
         <v>109.852</v>
       </c>
       <c r="C15" t="n">
-        <v>1089.873759546387</v>
+        <v>350.5152140666699</v>
       </c>
       <c r="D15" t="n">
         <v>1.24345e-07</v>
@@ -5157,16 +4966,13 @@
         <v>-19901.54851131805</v>
       </c>
       <c r="Y15" t="n">
-        <v>462.256513666429</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>508127762.911929</v>
+        <v>172.454232267292</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.515884585214217e-07</v>
+        <v>1.809578552083691e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9692657220254105</v>
+        <v>0.9971671428552108</v>
       </c>
     </row>
     <row r="16">
@@ -5177,7 +4983,7 @@
         <v>107.895</v>
       </c>
       <c r="C16" t="n">
-        <v>1090.26844756299</v>
+        <v>107.895</v>
       </c>
       <c r="D16" t="n">
         <v>1.24315e-07</v>
@@ -5209,11 +5015,10 @@
       <c r="X16" t="n">
         <v>-20000.50700315995</v>
       </c>
-      <c r="Y16" t="n">
-        <v>459.4788567106507</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>29889948.63197297</v>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA16" t="n">
         <v>1.509417738307164e-07</v>
@@ -5230,7 +5035,7 @@
         <v>107.553</v>
       </c>
       <c r="C17" t="n">
-        <v>1179.548300252117</v>
+        <v>346.3844681947523</v>
       </c>
       <c r="D17" t="n">
         <v>1.2423e-07</v>
@@ -5263,16 +5068,13 @@
         <v>-20360.78126008563</v>
       </c>
       <c r="Y17" t="n">
-        <v>456.5584869726523</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>24405148.00093558</v>
+        <v>168.1998557789877</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.504166853825801e-07</v>
+        <v>1.781865339032481e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9703192114877017</v>
+        <v>0.998484590903389</v>
       </c>
     </row>
     <row r="18">
@@ -5283,7 +5085,7 @@
         <v>105.43</v>
       </c>
       <c r="C18" t="n">
-        <v>1115.21442617366</v>
+        <v>105.43</v>
       </c>
       <c r="D18" t="n">
         <v>1.24185e-07</v>
@@ -5315,11 +5117,10 @@
       <c r="X18" t="n">
         <v>-20263.0610343937</v>
       </c>
-      <c r="Y18" t="n">
-        <v>453.6618683443547</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>372428787.2463068</v>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA18" t="n">
         <v>1.501992025221879e-07</v>
@@ -5336,7 +5137,7 @@
         <v>104.552</v>
       </c>
       <c r="C19" t="n">
-        <v>1026.851877709759</v>
+        <v>363.5192082549586</v>
       </c>
       <c r="D19" t="n">
         <v>1.24146e-07</v>
@@ -5369,16 +5170,13 @@
         <v>-20591.79155524877</v>
       </c>
       <c r="Y19" t="n">
-        <v>450.8250450737046</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>123559401.376678</v>
+        <v>146.6633284199095</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.49664764293655e-07</v>
+        <v>1.625747724555426e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.9709854369999015</v>
+        <v>0.9998514103001476</v>
       </c>
     </row>
     <row r="20">
@@ -5389,7 +5187,7 @@
         <v>102.219</v>
       </c>
       <c r="C20" t="n">
-        <v>1120.904675579753</v>
+        <v>340.7232741805845</v>
       </c>
       <c r="D20" t="n">
         <v>1.24131e-07</v>
@@ -5422,16 +5220,13 @@
         <v>-20371.84324781778</v>
       </c>
       <c r="Y20" t="n">
-        <v>447.9321946077594</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>39584486.3827277</v>
+        <v>162.7485321764183</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.491831414766263e-07</v>
+        <v>1.753199407349242e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.971460780650405</v>
+        <v>0.9993972780672632</v>
       </c>
     </row>
     <row r="21">
@@ -5442,7 +5237,7 @@
         <v>101.271</v>
       </c>
       <c r="C21" t="n">
-        <v>1156.863287332887</v>
+        <v>101.271</v>
       </c>
       <c r="D21" t="n">
         <v>1.24162e-07</v>
@@ -5474,11 +5269,10 @@
       <c r="X21" t="n">
         <v>-20458.4021150452</v>
       </c>
-      <c r="Y21" t="n">
-        <v>444.9643080183889</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>486018027.4957576</v>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA21" t="n">
         <v>1.491712496362159e-07</v>
@@ -5495,7 +5289,7 @@
         <v>99.02199999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>1113.970627693973</v>
+        <v>336.1547939860418</v>
       </c>
       <c r="D22" t="n">
         <v>1.24093e-07</v>
@@ -5528,16 +5322,13 @@
         <v>-20509.68482550468</v>
       </c>
       <c r="Y22" t="n">
-        <v>387.491590786557</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>14647.29090377409</v>
+        <v>172.2488533172049</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.931470320474982e-07</v>
+        <v>1.956997781804142e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9994536368452093</v>
+        <v>0.9973187183922376</v>
       </c>
     </row>
   </sheetData>
@@ -5694,7 +5485,7 @@
         <v>170.454</v>
       </c>
       <c r="C2" t="n">
-        <v>9036.674710320864</v>
+        <v>344.3813496519741</v>
       </c>
       <c r="D2" t="n">
         <v>1.35515e-07</v>
@@ -5727,16 +5518,13 @@
         <v>-6318.601230315276</v>
       </c>
       <c r="Y2" t="n">
-        <v>401.3409320117067</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>12266.62804113551</v>
+        <v>213.3807149805746</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.885917557203309e-07</v>
+        <v>1.730176872934462e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9998607934151046</v>
+        <v>0.9973804398598546</v>
       </c>
     </row>
     <row r="3">
@@ -5747,7 +5535,7 @@
         <v>113.733</v>
       </c>
       <c r="C3" t="n">
-        <v>1782.587010514477</v>
+        <v>113.733</v>
       </c>
       <c r="D3" t="n">
         <v>1.3576e-07</v>
@@ -5779,11 +5567,10 @@
       <c r="X3" t="n">
         <v>-7267.108957893212</v>
       </c>
-      <c r="Y3" t="n">
-        <v>461.9684892189916</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>189176154.32179</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA3" t="n">
         <v>2.071882196427054e-07</v>
@@ -5800,7 +5587,7 @@
         <v>104.842</v>
       </c>
       <c r="C4" t="n">
-        <v>1552.539263166526</v>
+        <v>366.9779471844934</v>
       </c>
       <c r="D4" t="n">
         <v>1.33892e-07</v>
@@ -5833,16 +5620,13 @@
         <v>-8697.313979497821</v>
       </c>
       <c r="Y4" t="n">
-        <v>452.8946722373672</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>247333581.1174081</v>
+        <v>137.9879853590958</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.910211725883793e-07</v>
+        <v>1.482933739320654e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9455506425615341</v>
+        <v>0.9995164367187145</v>
       </c>
     </row>
     <row r="5">
@@ -5853,7 +5637,7 @@
         <v>97.59699999999998</v>
       </c>
       <c r="C5" t="n">
-        <v>1318.217171735767</v>
+        <v>299.4458685213738</v>
       </c>
       <c r="D5" t="n">
         <v>1.32242e-07</v>
@@ -5886,16 +5670,13 @@
         <v>-9727.399628183486</v>
       </c>
       <c r="Y5" t="n">
-        <v>448.0721764289243</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>489651655.3091006</v>
+        <v>214.2714592013445</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.811749780587644e-07</v>
+        <v>2.358890836599947e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9516550946126729</v>
+        <v>0.9994620390055986</v>
       </c>
     </row>
     <row r="6">
@@ -5906,7 +5687,7 @@
         <v>92.56700000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>1219.415924086236</v>
+        <v>349.9742726318105</v>
       </c>
       <c r="D6" t="n">
         <v>1.31062e-07</v>
@@ -5939,16 +5720,13 @@
         <v>-10613.00555506835</v>
       </c>
       <c r="Y6" t="n">
-        <v>387.8907264242617</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>14722.57483900916</v>
+        <v>148.0640079026161</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.78467925192736e-07</v>
+        <v>1.621714205336754e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.999954871514722</v>
+        <v>0.9997177718639118</v>
       </c>
     </row>
     <row r="7">
@@ -5959,7 +5737,7 @@
         <v>95.73299999999995</v>
       </c>
       <c r="C7" t="n">
-        <v>1346.96442917031</v>
+        <v>95.73299999999995</v>
       </c>
       <c r="D7" t="n">
         <v>1.3019e-07</v>
@@ -5991,11 +5769,10 @@
       <c r="X7" t="n">
         <v>-11939.00536769757</v>
       </c>
-      <c r="Y7" t="n">
-        <v>387.4882096521496</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>14565.33249140431</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA7" t="n">
         <v>1.858273155035598e-07</v>
@@ -6012,7 +5789,7 @@
         <v>90.78199999999998</v>
       </c>
       <c r="C8" t="n">
-        <v>1334.87523017367</v>
+        <v>345.1937630416481</v>
       </c>
       <c r="D8" t="n">
         <v>1.29518e-07</v>
@@ -6045,16 +5822,13 @@
         <v>-12399.00526128336</v>
       </c>
       <c r="Y8" t="n">
-        <v>435.3280852846409</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1067083309.103381</v>
+        <v>144.6993992335626</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.66515963430215e-07</v>
+        <v>1.691241151809523e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9612697947300535</v>
+        <v>0.9991647457712878</v>
       </c>
     </row>
     <row r="9">
@@ -6065,7 +5839,7 @@
         <v>87.36899999999997</v>
       </c>
       <c r="C9" t="n">
-        <v>1378.20294676874</v>
+        <v>87.36899999999997</v>
       </c>
       <c r="D9" t="n">
         <v>1.28996e-07</v>
@@ -6097,11 +5871,10 @@
       <c r="X9" t="n">
         <v>-12770.77070569713</v>
       </c>
-      <c r="Y9" t="n">
-        <v>431.080079089411</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>236711912.7382494</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>1.639521466366806e-07</v>
@@ -6118,7 +5891,7 @@
         <v>84.72799999999995</v>
       </c>
       <c r="C10" t="n">
-        <v>1428.180560721705</v>
+        <v>328.1234509401165</v>
       </c>
       <c r="D10" t="n">
         <v>1.28643e-07</v>
@@ -6151,16 +5924,13 @@
         <v>-13239.06867644153</v>
       </c>
       <c r="Y10" t="n">
-        <v>426.9455822466085</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>232797051.4751672</v>
+        <v>156.9466611754991</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.617918238474145e-07</v>
+        <v>1.950766456238779e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9646142846243742</v>
+        <v>0.9964690674560508</v>
       </c>
     </row>
     <row r="11">
@@ -6171,7 +5941,7 @@
         <v>82.678</v>
       </c>
       <c r="C11" t="n">
-        <v>1491.367187133959</v>
+        <v>338.8579435611051</v>
       </c>
       <c r="D11" t="n">
         <v>1.28332e-07</v>
@@ -6204,16 +5974,13 @@
         <v>-13642.32268949657</v>
       </c>
       <c r="Y11" t="n">
-        <v>422.9713898025815</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>460142131.6411566</v>
+        <v>140.195159535321</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.600997412236512e-07</v>
+        <v>1.730829596592261e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9658481183341294</v>
+        <v>0.9996435806054071</v>
       </c>
     </row>
   </sheetData>
@@ -6370,7 +6137,7 @@
         <v>165.807</v>
       </c>
       <c r="C2" t="n">
-        <v>1546.078846593912</v>
+        <v>165.807</v>
       </c>
       <c r="D2" t="n">
         <v>1.3174e-07</v>
@@ -6402,11 +6169,10 @@
       <c r="X2" t="n">
         <v>-11267.54250541104</v>
       </c>
-      <c r="Y2" t="n">
-        <v>413.6397995909341</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>12855.27665633393</v>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA2" t="n">
         <v>2.063059043963831e-07</v>
@@ -6423,7 +6189,7 @@
         <v>142.9909999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>1094.586417785975</v>
+        <v>376.581917165246</v>
       </c>
       <c r="D3" t="n">
         <v>1.29904e-07</v>
@@ -6456,16 +6222,13 @@
         <v>-13623.49116949148</v>
       </c>
       <c r="Y3" t="n">
-        <v>504.1080482705274</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>212004258.9676698</v>
+        <v>193.0802789905085</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.76960210774205e-07</v>
+        <v>1.890578334638012e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.952351491373408</v>
+        <v>0.989076893304015</v>
       </c>
     </row>
     <row r="4">
@@ -6476,7 +6239,7 @@
         <v>134.7570000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>1000.32956085773</v>
+        <v>374.6957292848591</v>
       </c>
       <c r="D4" t="n">
         <v>1.28818e-07</v>
@@ -6509,16 +6272,13 @@
         <v>-14977.867423515</v>
       </c>
       <c r="Y4" t="n">
-        <v>498.9625108066003</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>205971976.4805169</v>
+        <v>180.8463253870782</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.701795515197108e-07</v>
+        <v>1.554018502889128e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9570047195353525</v>
+        <v>0.9997702710024874</v>
       </c>
     </row>
     <row r="5">
@@ -6529,7 +6289,7 @@
         <v>136.796</v>
       </c>
       <c r="C5" t="n">
-        <v>1259.231589310878</v>
+        <v>136.796</v>
       </c>
       <c r="D5" t="n">
         <v>1.28102e-07</v>
@@ -6561,11 +6321,10 @@
       <c r="X5" t="n">
         <v>-16860.74281362224</v>
       </c>
-      <c r="Y5" t="n">
-        <v>494.8279817347797</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>204276944.4449124</v>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA5" t="n">
         <v>1.662980667773361e-07</v>
@@ -6582,7 +6341,7 @@
         <v>130.842</v>
       </c>
       <c r="C6" t="n">
-        <v>1076.533872308063</v>
+        <v>364.3542089306175</v>
       </c>
       <c r="D6" t="n">
         <v>1.27721e-07</v>
@@ -6615,16 +6374,13 @@
         <v>-17204.99234994837</v>
       </c>
       <c r="Y6" t="n">
-        <v>491.1009426238819</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>268276508.0949699</v>
+        <v>186.2301917329795</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.638297250791552e-07</v>
+        <v>1.77985753477124e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9614932281963975</v>
+        <v>0.9951400002934712</v>
       </c>
     </row>
     <row r="7">
@@ -6635,7 +6391,7 @@
         <v>128.361</v>
       </c>
       <c r="C7" t="n">
-        <v>1138.747379521363</v>
+        <v>260.5779538968749</v>
       </c>
       <c r="D7" t="n">
         <v>1.27421e-07</v>
@@ -6668,10 +6424,7 @@
         <v>-17826.12717549497</v>
       </c>
       <c r="Y7" t="n">
-        <v>487.5097976123487</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>266696322.562239</v>
+        <v>619.7448984132324</v>
       </c>
       <c r="AA7" t="n">
         <v>1.620722230722741e-07</v>
@@ -6688,7 +6441,7 @@
         <v>123.628</v>
       </c>
       <c r="C8" t="n">
-        <v>1032.655572425195</v>
+        <v>360.3055560539425</v>
       </c>
       <c r="D8" t="n">
         <v>1.27209e-07</v>
@@ -6721,16 +6474,13 @@
         <v>-17662.87811060166</v>
       </c>
       <c r="Y8" t="n">
-        <v>483.9257299017522</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>32436991.70759945</v>
+        <v>179.708627663903</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.605428083959634e-07</v>
+        <v>1.658177559920032e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9639753032259454</v>
+        <v>0.998557778743852</v>
       </c>
     </row>
     <row r="9">
@@ -6741,7 +6491,7 @@
         <v>122.629</v>
       </c>
       <c r="C9" t="n">
-        <v>1043.888046370101</v>
+        <v>359.4847179813507</v>
       </c>
       <c r="D9" t="n">
         <v>1.27064e-07</v>
@@ -6774,16 +6524,13 @@
         <v>-18142.0077608619</v>
       </c>
       <c r="Y9" t="n">
-        <v>480.5746890858928</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>265881309.4744598</v>
+        <v>175.4761608350891</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.595987671116799e-07</v>
+        <v>1.621789286448239e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.964701457858171</v>
+        <v>0.9992237386601405</v>
       </c>
     </row>
     <row r="10">
@@ -6794,7 +6541,7 @@
         <v>118.23</v>
       </c>
       <c r="C10" t="n">
-        <v>980.5106241748045</v>
+        <v>360.5954560556953</v>
       </c>
       <c r="D10" t="n">
         <v>1.26921e-07</v>
@@ -6827,16 +6574,13 @@
         <v>-18028.23479334352</v>
       </c>
       <c r="Y10" t="n">
-        <v>477.3957378957134</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>39976177.00676858</v>
+        <v>169.1649976113479</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.584275984886347e-07</v>
+        <v>1.574113944588705e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9656534236131127</v>
+        <v>0.9997629101886834</v>
       </c>
     </row>
     <row r="11">
@@ -6847,7 +6591,7 @@
         <v>118.027</v>
       </c>
       <c r="C11" t="n">
-        <v>1043.281906227671</v>
+        <v>229.4026776436762</v>
       </c>
       <c r="D11" t="n">
         <v>1.26801e-07</v>
@@ -6880,10 +6624,7 @@
         <v>-18594.15966303758</v>
       </c>
       <c r="Y11" t="n">
-        <v>474.2632636704056</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>277771317.5458045</v>
+        <v>595.5428623834688</v>
       </c>
       <c r="AA11" t="n">
         <v>1.57690799887126e-07</v>
@@ -6900,7 +6641,7 @@
         <v>117.991</v>
       </c>
       <c r="C12" t="n">
-        <v>1138.491985032787</v>
+        <v>117.991</v>
       </c>
       <c r="D12" t="n">
         <v>1.26742e-07</v>
@@ -6932,11 +6673,10 @@
       <c r="X12" t="n">
         <v>-19294.28177003079</v>
       </c>
-      <c r="Y12" t="n">
-        <v>452.1065659361487</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>19558.83710782218</v>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA12" t="n">
         <v>1.616303913931211e-07</v>
@@ -6953,7 +6693,7 @@
         <v>115.196</v>
       </c>
       <c r="C13" t="n">
-        <v>1121.357103549543</v>
+        <v>364.2902465569415</v>
       </c>
       <c r="D13" t="n">
         <v>1.26635e-07</v>
@@ -6986,16 +6726,13 @@
         <v>-19260.95894229419</v>
       </c>
       <c r="Y13" t="n">
-        <v>449.1944204792102</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>19425.52933163869</v>
+        <v>155.4021135301599</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.639577318564796e-07</v>
+        <v>1.598008428672112e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.999619091970365</v>
+        <v>0.9972625943331045</v>
       </c>
     </row>
     <row r="14">
@@ -7006,7 +6743,7 @@
         <v>113.675</v>
       </c>
       <c r="C14" t="n">
-        <v>1101.110789966278</v>
+        <v>360.9394217507477</v>
       </c>
       <c r="D14" t="n">
         <v>1.26562e-07</v>
@@ -7039,16 +6776,13 @@
         <v>-19448.23039167188</v>
       </c>
       <c r="Y14" t="n">
-        <v>460.2325273481125</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>38683.00340727783</v>
+        <v>159.8609034772183</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.351863288882294e-07</v>
+        <v>1.620884818143401e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.9999853736984827</v>
+        <v>0.999657152049834</v>
       </c>
     </row>
     <row r="15">
@@ -7059,7 +6793,7 @@
         <v>109.821</v>
       </c>
       <c r="C15" t="n">
-        <v>1027.688534551363</v>
+        <v>574.7629633345304</v>
       </c>
       <c r="D15" t="n">
         <v>1.26515e-07</v>
@@ -7092,16 +6826,13 @@
         <v>-18725.89809953444</v>
       </c>
       <c r="Y15" t="n">
-        <v>462.4229830846041</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>144479826.0997836</v>
+        <v>0.5400324439906118</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.552128336099687e-07</v>
+        <v>1.476623165449608e-08</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9683037781995539</v>
+        <v>0.7959028889451695</v>
       </c>
     </row>
     <row r="16">
@@ -7112,7 +6843,7 @@
         <v>109.083</v>
       </c>
       <c r="C16" t="n">
-        <v>1014.111405102926</v>
+        <v>109.083</v>
       </c>
       <c r="D16" t="n">
         <v>1.2646e-07</v>
@@ -7144,11 +6875,10 @@
       <c r="X16" t="n">
         <v>-18886.9408467312</v>
       </c>
-      <c r="Y16" t="n">
-        <v>459.5585606628492</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>41238169.75850678</v>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA16" t="n">
         <v>1.545466003043468e-07</v>
@@ -7165,7 +6895,7 @@
         <v>108.769</v>
       </c>
       <c r="C17" t="n">
-        <v>1130.221529607981</v>
+        <v>108.769</v>
       </c>
       <c r="D17" t="n">
         <v>1.26394e-07</v>
@@ -7197,11 +6927,10 @@
       <c r="X17" t="n">
         <v>-19615.42122235966</v>
       </c>
-      <c r="Y17" t="n">
-        <v>456.6859799976505</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>43460215.46930999</v>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA17" t="n">
         <v>1.540925058369769e-07</v>
@@ -7218,7 +6947,7 @@
         <v>107.908</v>
       </c>
       <c r="C18" t="n">
-        <v>1121.895619824897</v>
+        <v>359.6806356247288</v>
       </c>
       <c r="D18" t="n">
         <v>1.26374e-07</v>
@@ -7251,16 +6980,13 @@
         <v>-19647.01006491083</v>
       </c>
       <c r="Y18" t="n">
-        <v>453.8411188632443</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>38460242.22836501</v>
+        <v>147.7487558954327</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.536211345540183e-07</v>
+        <v>1.585822963342831e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9697153380012947</v>
+        <v>0.999762124523032</v>
       </c>
     </row>
     <row r="19">
@@ -7271,7 +6997,7 @@
         <v>105.775</v>
       </c>
       <c r="C19" t="n">
-        <v>1093.808320524864</v>
+        <v>414.4256517422324</v>
       </c>
       <c r="D19" t="n">
         <v>1.2638e-07</v>
@@ -7304,16 +7030,13 @@
         <v>-19761.71601802037</v>
       </c>
       <c r="Y19" t="n">
-        <v>451.0108621774502</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>21259478.69612383</v>
+        <v>87.4178716251028</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.529559385986428e-07</v>
+        <v>1.244172958466301e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.9703830507537771</v>
+        <v>0.9998959769898075</v>
       </c>
     </row>
     <row r="20">
@@ -7324,7 +7047,7 @@
         <v>105.679</v>
       </c>
       <c r="C20" t="n">
-        <v>1202.807344717327</v>
+        <v>105.679</v>
       </c>
       <c r="D20" t="n">
         <v>1.26328e-07</v>
@@ -7356,11 +7079,10 @@
       <c r="X20" t="n">
         <v>-20289.56991448857</v>
       </c>
-      <c r="Y20" t="n">
-        <v>448.1262092295214</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>490198934.9228548</v>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA20" t="n">
         <v>1.52920920227185e-07</v>
@@ -7377,7 +7099,7 @@
         <v>104.663</v>
       </c>
       <c r="C21" t="n">
-        <v>1189.827864981361</v>
+        <v>357.9719608736819</v>
       </c>
       <c r="D21" t="n">
         <v>1.2629e-07</v>
@@ -7410,16 +7132,13 @@
         <v>-20282.43814255865</v>
       </c>
       <c r="Y21" t="n">
-        <v>445.2077970737978</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>32351444.4834045</v>
+        <v>142.9114691891614</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.522644306313298e-07</v>
+        <v>1.641513227281714e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9709733423175045</v>
+        <v>0.9992051954558074</v>
       </c>
     </row>
     <row r="22">
@@ -7430,7 +7149,7 @@
         <v>100.023</v>
       </c>
       <c r="C22" t="n">
-        <v>1016.117291330994</v>
+        <v>356.2116523972225</v>
       </c>
       <c r="D22" t="n">
         <v>1.26279e-07</v>
@@ -7463,16 +7182,13 @@
         <v>-19417.87201350284</v>
       </c>
       <c r="Y22" t="n">
-        <v>387.6326706436827</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>14650.15744522106</v>
+        <v>137.7090245811963</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.770970618415128e-07</v>
+        <v>1.561534021057335e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9999999992224516</v>
+        <v>0.9998951926981049</v>
       </c>
     </row>
   </sheetData>
@@ -7629,7 +7345,7 @@
         <v>166.581</v>
       </c>
       <c r="C2" t="n">
-        <v>20523.11205665578</v>
+        <v>404.3320718098353</v>
       </c>
       <c r="D2" t="n">
         <v>1.3844e-07</v>
@@ -7662,16 +7378,13 @@
         <v>-5797.629448077008</v>
       </c>
       <c r="Y2" t="n">
-        <v>401.2684479302368</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>12277.19927807831</v>
+        <v>148.4292158319404</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.936443436839519e-07</v>
+        <v>1.252037515929684e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9999570629799829</v>
+        <v>0.9992855523359402</v>
       </c>
     </row>
     <row r="3">
@@ -7682,7 +7395,7 @@
         <v>117.392</v>
       </c>
       <c r="C3" t="n">
-        <v>1618.414981714367</v>
+        <v>294.5764904548918</v>
       </c>
       <c r="D3" t="n">
         <v>1.37784e-07</v>
@@ -7715,16 +7428,13 @@
         <v>-6922.350553473259</v>
       </c>
       <c r="Y3" t="n">
-        <v>462.997499506849</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>127063480.6720969</v>
+        <v>238.2144132704892</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.152318743749638e-07</v>
+        <v>2.532878154468126e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9319402511427759</v>
+        <v>0.9957915875042469</v>
       </c>
     </row>
     <row r="4">
@@ -7735,7 +7445,7 @@
         <v>107.657</v>
       </c>
       <c r="C4" t="n">
-        <v>1536.523249331721</v>
+        <v>302.4745540300998</v>
       </c>
       <c r="D4" t="n">
         <v>1.35504e-07</v>
@@ -7768,16 +7478,13 @@
         <v>-8366.976392895383</v>
       </c>
       <c r="Y4" t="n">
-        <v>453.5408611539115</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>866894126.9619812</v>
+        <v>210.4866539793753</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.963171007952433e-07</v>
+        <v>2.109995681099472e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9432320972927444</v>
+        <v>0.9995508895713295</v>
       </c>
     </row>
     <row r="5">
@@ -7788,7 +7495,7 @@
         <v>97.62200000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>1100.368101932839</v>
+        <v>298.5956499805025</v>
       </c>
       <c r="D5" t="n">
         <v>1.33706e-07</v>
@@ -7821,16 +7528,13 @@
         <v>-9391.427589237817</v>
       </c>
       <c r="Y5" t="n">
-        <v>447.951195547946</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>244803525.546838</v>
+        <v>214.3842709554947</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.84725242443577e-07</v>
+        <v>2.272773849791348e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.950380062239808</v>
+        <v>0.9997248935604036</v>
       </c>
     </row>
     <row r="6">
@@ -7841,7 +7545,7 @@
         <v>96.35000000000002</v>
       </c>
       <c r="C6" t="n">
-        <v>1185.781549949033</v>
+        <v>345.7051231260724</v>
       </c>
       <c r="D6" t="n">
         <v>1.32416e-07</v>
@@ -7874,16 +7578,13 @@
         <v>-10553.16174262014</v>
       </c>
       <c r="Y6" t="n">
-        <v>442.9257617222612</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>856282864.8633318</v>
+        <v>151.9046922913789</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.772644914782185e-07</v>
+        <v>1.662832061621077e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9551420399356122</v>
+        <v>0.9995497282560616</v>
       </c>
     </row>
     <row r="7">
@@ -7894,7 +7595,7 @@
         <v>93.50099999999998</v>
       </c>
       <c r="C7" t="n">
-        <v>1379.447824372992</v>
+        <v>93.50099999999998</v>
       </c>
       <c r="D7" t="n">
         <v>1.31483e-07</v>
@@ -7926,11 +7627,10 @@
       <c r="X7" t="n">
         <v>-11536.42873129448</v>
       </c>
-      <c r="Y7" t="n">
-        <v>437.7637461364064</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>268724466.0924232</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA7" t="n">
         <v>1.720905355363748e-07</v>
@@ -7947,7 +7647,7 @@
         <v>92.28800000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>1530.204816276668</v>
+        <v>346.5359663012102</v>
       </c>
       <c r="D8" t="n">
         <v>1.30793e-07</v>
@@ -7980,16 +7680,13 @@
         <v>-12587.04489751725</v>
       </c>
       <c r="Y8" t="n">
-        <v>432.8112250283656</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>480685736.6744587</v>
+        <v>134.1021042588505</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.678937175833626e-07</v>
+        <v>1.535031157389176e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9615026410472478</v>
+        <v>0.9996746292223634</v>
       </c>
     </row>
     <row r="9">
@@ -8000,7 +7697,7 @@
         <v>87.86500000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>1480.021665568028</v>
+        <v>362.695621646991</v>
       </c>
       <c r="D9" t="n">
         <v>1.30247e-07</v>
@@ -8033,16 +7730,13 @@
         <v>-12987.06484830528</v>
       </c>
       <c r="Y9" t="n">
-        <v>427.7116423138801</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>466906241.2131789</v>
+        <v>119.791012806693</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.650264029140633e-07</v>
+        <v>1.591583344770426e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9634826176562891</v>
+        <v>0.998834397329377</v>
       </c>
     </row>
     <row r="10">
@@ -8053,7 +7747,7 @@
         <v>85.19400000000002</v>
       </c>
       <c r="C10" t="n">
-        <v>1524.900817121409</v>
+        <v>345.2910818316124</v>
       </c>
       <c r="D10" t="n">
         <v>1.29801e-07</v>
@@ -8086,16 +7780,13 @@
         <v>-13563.95959294808</v>
       </c>
       <c r="Y10" t="n">
-        <v>422.8134724267125</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>115514300.6546874</v>
+        <v>136.1326477951614</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.624899104186133e-07</v>
+        <v>1.71731802437612e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9653207405812123</v>
+        <v>0.9997618026992423</v>
       </c>
     </row>
     <row r="11">
@@ -8106,7 +7797,7 @@
         <v>83.67599999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>1836.017318540059</v>
+        <v>234.972352216596</v>
       </c>
       <c r="D11" t="n">
         <v>1.29497e-07</v>
@@ -8139,16 +7830,13 @@
         <v>-14140.52357055255</v>
       </c>
       <c r="Y11" t="n">
-        <v>418.1694107433777</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>228006258.8307897</v>
+        <v>264.5787946923299</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.606098128282009e-07</v>
+        <v>6.490921521726114e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9667348603860002</v>
+        <v>0.9602576625502314</v>
       </c>
     </row>
   </sheetData>
@@ -8305,7 +7993,7 @@
         <v>166.4859999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>1502.224546260377</v>
+        <v>429.5452704607691</v>
       </c>
       <c r="D2" t="n">
         <v>1.33147e-07</v>
@@ -8338,16 +8026,13 @@
         <v>-11445.01442247303</v>
       </c>
       <c r="Y2" t="n">
-        <v>411.4847566371973</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>12805.52047976563</v>
+        <v>136.7667967255225</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.019861976126505e-07</v>
+        <v>1.179866855636604e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9992221911964151</v>
+        <v>0.9996750922670959</v>
       </c>
     </row>
     <row r="3">
@@ -8358,7 +8043,7 @@
         <v>146.001</v>
       </c>
       <c r="C3" t="n">
-        <v>1141.339672971119</v>
+        <v>372.2191323889165</v>
       </c>
       <c r="D3" t="n">
         <v>1.30999e-07</v>
@@ -8391,16 +8076,13 @@
         <v>-14334.55366853595</v>
       </c>
       <c r="Y3" t="n">
-        <v>406.6230085257923</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>12499.71566678819</v>
+        <v>191.8593949029238</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.958769300755683e-07</v>
+        <v>1.842915347592702e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9998564064757421</v>
+        <v>0.9905010629301984</v>
       </c>
     </row>
     <row r="4">
@@ -8411,7 +8093,7 @@
         <v>136.545</v>
       </c>
       <c r="C4" t="n">
-        <v>1003.756172955758</v>
+        <v>370.540690514722</v>
       </c>
       <c r="D4" t="n">
         <v>1.29836e-07</v>
@@ -8444,16 +8126,13 @@
         <v>-15655.2204556749</v>
       </c>
       <c r="Y4" t="n">
-        <v>496.8019119526533</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>38329289.77467448</v>
+        <v>194.1108524838753</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.702237719215283e-07</v>
+        <v>2.231884977613195e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9581560383515961</v>
+        <v>0.9807284666597523</v>
       </c>
     </row>
     <row r="5">
@@ -8464,7 +8143,7 @@
         <v>135.524</v>
       </c>
       <c r="C5" t="n">
-        <v>1097.818199350853</v>
+        <v>367.4169961429868</v>
       </c>
       <c r="D5" t="n">
         <v>1.29139e-07</v>
@@ -8497,16 +8176,13 @@
         <v>-17552.9021772235</v>
       </c>
       <c r="Y5" t="n">
-        <v>492.5871603537111</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>206150332.7870738</v>
+        <v>184.2528367725377</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.66218556101196e-07</v>
+        <v>1.632251977675167e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.96095755194495</v>
+        <v>0.9998436033564717</v>
       </c>
     </row>
     <row r="6">
@@ -8517,7 +8193,7 @@
         <v>129.4109999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>1025.034437731215</v>
+        <v>129.4109999999999</v>
       </c>
       <c r="D6" t="n">
         <v>1.28691e-07</v>
@@ -8549,11 +8225,10 @@
       <c r="X6" t="n">
         <v>-17665.17301877854</v>
       </c>
-      <c r="Y6" t="n">
-        <v>488.1433242255991</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>533020840.2533325</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>1.636272364173152e-07</v>
@@ -8570,7 +8245,7 @@
         <v>129.4039999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>1157.648427677055</v>
+        <v>594.5652092781086</v>
       </c>
       <c r="D7" t="n">
         <v>1.2844e-07</v>
@@ -8603,16 +8278,13 @@
         <v>-19045.01738430858</v>
       </c>
       <c r="Y7" t="n">
-        <v>483.708953156379</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>528397900.0558928</v>
+        <v>0.2571159343816903</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.619029547129035e-07</v>
+        <v>6.641213540798994e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9641508311391753</v>
+        <v>0.8519416848297341</v>
       </c>
     </row>
     <row r="8">
@@ -8623,7 +8295,7 @@
         <v>126.652</v>
       </c>
       <c r="C8" t="n">
-        <v>1153.88184002567</v>
+        <v>550.2742942820371</v>
       </c>
       <c r="D8" t="n">
         <v>1.28249e-07</v>
@@ -8656,16 +8328,13 @@
         <v>-19086.18945467061</v>
       </c>
       <c r="Y8" t="n">
-        <v>479.120900958271</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>27815257.0629561</v>
+        <v>0.4077057123426893</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.604447601736841e-07</v>
+        <v>1.759147354261444e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9653078051009671</v>
+        <v>0.9507903998134069</v>
       </c>
     </row>
     <row r="9">
@@ -8676,7 +8345,7 @@
         <v>120.405</v>
       </c>
       <c r="C9" t="n">
-        <v>1039.125462561509</v>
+        <v>398.8744070248752</v>
       </c>
       <c r="D9" t="n">
         <v>1.28111e-07</v>
@@ -8709,16 +8378,13 @@
         <v>-18740.19042748851</v>
       </c>
       <c r="Y9" t="n">
-        <v>474.6818010733176</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>209061758.1705164</v>
+        <v>129.5817820809572</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.594313289769467e-07</v>
+        <v>1.472023397813351e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9661143745270701</v>
+        <v>0.9958554328797904</v>
       </c>
     </row>
     <row r="10">
@@ -8729,7 +8395,7 @@
         <v>118.8390000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>1054.447249510497</v>
+        <v>393.116402330824</v>
       </c>
       <c r="D10" t="n">
         <v>1.2803e-07</v>
@@ -8762,16 +8428,13 @@
         <v>-19162.2325878878</v>
       </c>
       <c r="Y10" t="n">
-        <v>470.4776566608213</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>376317361.8949968</v>
+        <v>128.673380255507</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.584780816567173e-07</v>
+        <v>1.372333451546971e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9669291287786758</v>
+        <v>0.9997212604565566</v>
       </c>
     </row>
     <row r="11">
@@ -8782,7 +8445,7 @@
         <v>115.681</v>
       </c>
       <c r="C11" t="n">
-        <v>1068.611405053406</v>
+        <v>620.6916234897556</v>
       </c>
       <c r="D11" t="n">
         <v>1.27948e-07</v>
@@ -8815,16 +8478,13 @@
         <v>-19537.47587190667</v>
       </c>
       <c r="Y11" t="n">
-        <v>466.3157580589374</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>184502702.3353789</v>
+        <v>1.59935571906165</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.574328816867003e-07</v>
+        <v>1.111021994886208e-07</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9678495856498377</v>
+        <v>0.6554324845435642</v>
       </c>
     </row>
     <row r="12">
@@ -8835,7 +8495,7 @@
         <v>112.958</v>
       </c>
       <c r="C12" t="n">
-        <v>1046.259808181741</v>
+        <v>112.958</v>
       </c>
       <c r="D12" t="n">
         <v>1.27892e-07</v>
@@ -8867,11 +8527,10 @@
       <c r="X12" t="n">
         <v>-19293.52170483638</v>
       </c>
-      <c r="Y12" t="n">
-        <v>462.4596568639181</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>252268722.3131012</v>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA12" t="n">
         <v>1.568592973788237e-07</v>
@@ -8888,7 +8547,7 @@
         <v>111.177</v>
       </c>
       <c r="C13" t="n">
-        <v>1057.000624936652</v>
+        <v>367.3423829029809</v>
       </c>
       <c r="D13" t="n">
         <v>1.27846e-07</v>
@@ -8921,16 +8580,13 @@
         <v>-19418.17589975747</v>
       </c>
       <c r="Y13" t="n">
-        <v>459.0536672754662</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>500444557.5419207</v>
+        <v>151.7880940752743</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.56204689521897e-07</v>
+        <v>1.687818891438429e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.9689315162202172</v>
+        <v>0.9979133880889888</v>
       </c>
     </row>
     <row r="14">
@@ -8941,7 +8597,7 @@
         <v>108.74</v>
       </c>
       <c r="C14" t="n">
-        <v>1025.05735737923</v>
+        <v>309.5668579508043</v>
       </c>
       <c r="D14" t="n">
         <v>1.27794e-07</v>
@@ -8974,16 +8630,13 @@
         <v>-19580.67726198515</v>
       </c>
       <c r="Y14" t="n">
-        <v>455.9005693837224</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>20455725.14820769</v>
+        <v>207.0516635665244</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.552862953913366e-07</v>
+        <v>2.215911411159566e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.9697708494781503</v>
+        <v>0.9948460541378944</v>
       </c>
     </row>
     <row r="15">
@@ -8994,7 +8647,7 @@
         <v>108.625</v>
       </c>
       <c r="C15" t="n">
-        <v>1077.583574399752</v>
+        <v>307.3757665849507</v>
       </c>
       <c r="D15" t="n">
         <v>1.27743e-07</v>
@@ -9027,16 +8680,13 @@
         <v>-20255.00593051117</v>
       </c>
       <c r="Y15" t="n">
-        <v>452.9030260230035</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>31005403.79109703</v>
+        <v>212.0688987468131</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.548692116930682e-07</v>
+        <v>2.615966517767903e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9701243141686168</v>
+        <v>0.9888421305492039</v>
       </c>
     </row>
     <row r="16">
@@ -9047,7 +8697,7 @@
         <v>109.842</v>
       </c>
       <c r="C16" t="n">
-        <v>1282.38186636424</v>
+        <v>305.2206543385009</v>
       </c>
       <c r="D16" t="n">
         <v>1.27717e-07</v>
@@ -9080,16 +8730,13 @@
         <v>-21207.89974175621</v>
       </c>
       <c r="Y16" t="n">
-        <v>449.9864692495883</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>63631055.82727703</v>
+        <v>210.339643834722</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.545176062880895e-07</v>
+        <v>2.584248806067236e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9704422031000955</v>
+        <v>0.9900960216006117</v>
       </c>
     </row>
     <row r="17">
@@ -9100,7 +8747,7 @@
         <v>108.27</v>
       </c>
       <c r="C17" t="n">
-        <v>1255.363641731249</v>
+        <v>108.27</v>
       </c>
       <c r="D17" t="n">
         <v>1.27683e-07</v>
@@ -9132,11 +8779,10 @@
       <c r="X17" t="n">
         <v>-21310.61041361716</v>
       </c>
-      <c r="Y17" t="n">
-        <v>447.16368423153</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>29137634.58581872</v>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA17" t="n">
         <v>1.53973230184615e-07</v>
@@ -9153,7 +8799,7 @@
         <v>105.467</v>
       </c>
       <c r="C18" t="n">
-        <v>1225.681663840188</v>
+        <v>105.467</v>
       </c>
       <c r="D18" t="n">
         <v>1.27651e-07</v>
@@ -9185,11 +8831,10 @@
       <c r="X18" t="n">
         <v>-21027.09218341374</v>
       </c>
-      <c r="Y18" t="n">
-        <v>444.3426586010088</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>243619641.034614</v>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA18" t="n">
         <v>1.53662878373613e-07</v>
@@ -9206,7 +8851,7 @@
         <v>104.166</v>
       </c>
       <c r="C19" t="n">
-        <v>1169.112866239651</v>
+        <v>298.7474149943026</v>
       </c>
       <c r="D19" t="n">
         <v>1.27623e-07</v>
@@ -9239,16 +8884,13 @@
         <v>-20863.32448287797</v>
       </c>
       <c r="Y19" t="n">
-        <v>382.5665925025276</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>14640.61363609664</v>
+        <v>200.3007105594325</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.840020828968935e-07</v>
+        <v>2.20694937584854e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.9999916004944329</v>
+        <v>0.9976526790682875</v>
       </c>
     </row>
     <row r="20">
@@ -9259,7 +8901,7 @@
         <v>100.913</v>
       </c>
       <c r="C20" t="n">
-        <v>1126.220667121904</v>
+        <v>353.5165311931254</v>
       </c>
       <c r="D20" t="n">
         <v>1.27607e-07</v>
@@ -9292,16 +8934,13 @@
         <v>-20423.78777180623</v>
       </c>
       <c r="Y20" t="n">
-        <v>384.0746943260944</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>14528.86542580894</v>
+        <v>144.1287471073647</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.807623170057344e-07</v>
+        <v>1.778777094515884e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9999939742079252</v>
+        <v>0.9970484771061782</v>
       </c>
     </row>
     <row r="21">
@@ -9312,7 +8951,7 @@
         <v>99.524</v>
       </c>
       <c r="C21" t="n">
-        <v>1164.202268827835</v>
+        <v>294.6259200071722</v>
       </c>
       <c r="D21" t="n">
         <v>1.27591e-07</v>
@@ -9345,16 +8984,13 @@
         <v>-20697.07563756706</v>
       </c>
       <c r="Y21" t="n">
-        <v>383.3399647353281</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>14444.32641952303</v>
+        <v>197.6632720569948</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.830018224121077e-07</v>
+        <v>2.207572491645847e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9999761710090245</v>
+        <v>0.998294977253638</v>
       </c>
     </row>
     <row r="22">
@@ -9365,7 +9001,7 @@
         <v>97.82099999999997</v>
       </c>
       <c r="C22" t="n">
-        <v>1100.653267622819</v>
+        <v>97.82099999999997</v>
       </c>
       <c r="D22" t="n">
         <v>1.27573e-07</v>
@@ -9397,11 +9033,10 @@
       <c r="X22" t="n">
         <v>-20228.36187724904</v>
       </c>
-      <c r="Y22" t="n">
-        <v>384.3909374771277</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>14340.04024074499</v>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA22" t="n">
         <v>1.828160608103209e-07</v>
@@ -9564,7 +9199,7 @@
         <v>140.1929999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>3500.671789095855</v>
+        <v>290.7104328277486</v>
       </c>
       <c r="D2" t="n">
         <v>1.40223e-07</v>
@@ -9597,16 +9232,13 @@
         <v>-6003.296112035475</v>
       </c>
       <c r="Y2" t="n">
-        <v>464.9724588880945</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>220306949.1122401</v>
+        <v>241.2914604789362</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.374492149744388e-07</v>
+        <v>2.351000553219934e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.9199419207352918</v>
+        <v>0.99809717431954</v>
       </c>
     </row>
     <row r="3">
@@ -9617,7 +9249,7 @@
         <v>96.63299999999998</v>
       </c>
       <c r="C3" t="n">
-        <v>2479.083981626369</v>
+        <v>273.1628915765251</v>
       </c>
       <c r="D3" t="n">
         <v>1.37618e-07</v>
@@ -9650,16 +9282,13 @@
         <v>-8212.592004588181</v>
       </c>
       <c r="Y3" t="n">
-        <v>434.490743922799</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>237105640.0677775</v>
+        <v>217.6869903485797</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.954888243984967e-07</v>
+        <v>2.363706679182493e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.9462547863971524</v>
+        <v>0.9984376972006724</v>
       </c>
     </row>
     <row r="4">
@@ -9670,7 +9299,7 @@
         <v>87.56</v>
       </c>
       <c r="C4" t="n">
-        <v>1840.307954126344</v>
+        <v>359.4195212867166</v>
       </c>
       <c r="D4" t="n">
         <v>1.35242e-07</v>
@@ -9703,16 +9332,13 @@
         <v>-10330.03164878563</v>
       </c>
       <c r="Y4" t="n">
-        <v>425.7608775569464</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>348104184.3594183</v>
+        <v>125.1752651378661</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.794161866603849e-07</v>
+        <v>1.891637176522678e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9565540520001856</v>
+        <v>0.9870288683449935</v>
       </c>
     </row>
     <row r="5">
@@ -9723,7 +9349,7 @@
         <v>82.64600000000002</v>
       </c>
       <c r="C5" t="n">
-        <v>1614.324517107863</v>
+        <v>266.2244502090098</v>
       </c>
       <c r="D5" t="n">
         <v>1.33778e-07</v>
@@ -9756,16 +9382,13 @@
         <v>-11897.86760157973</v>
       </c>
       <c r="Y5" t="n">
-        <v>420.4304966360089</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>458055224.3765739</v>
+        <v>210.8079988923757</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.710629628121894e-07</v>
+        <v>2.71065622785568e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9621202160241172</v>
+        <v>0.9944119982537603</v>
       </c>
     </row>
     <row r="6">
@@ -9776,7 +9399,7 @@
         <v>81.23000000000002</v>
       </c>
       <c r="C6" t="n">
-        <v>1828.495890847339</v>
+        <v>445.7358690001405</v>
       </c>
       <c r="D6" t="n">
         <v>1.32853e-07</v>
@@ -9809,16 +9432,13 @@
         <v>-13355.92669654902</v>
       </c>
       <c r="Y6" t="n">
-        <v>397.8913973704734</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3397.831774943771</v>
+        <v>17.29584377290938</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.571162943572849e-06</v>
+        <v>1.052174146632629e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.6752791414455797</v>
+        <v>0.9999966444284676</v>
       </c>
     </row>
     <row r="7">
@@ -9829,7 +9449,7 @@
         <v>76.25400000000002</v>
       </c>
       <c r="C7" t="n">
-        <v>1849.582751138911</v>
+        <v>271.8650139462728</v>
       </c>
       <c r="D7" t="n">
         <v>1.32323e-07</v>
@@ -9862,16 +9482,13 @@
         <v>-13800.84145847396</v>
       </c>
       <c r="Y7" t="n">
-        <v>410.1174022247833</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>334276082.5770438</v>
+        <v>200.0360906456226</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.630213256622675e-07</v>
+        <v>2.572314866208271e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9677724451568417</v>
+        <v>0.9981223894639772</v>
       </c>
     </row>
     <row r="8">
@@ -9882,7 +9499,7 @@
         <v>75.06899999999996</v>
       </c>
       <c r="C8" t="n">
-        <v>2300.024547323758</v>
+        <v>251.8794163242707</v>
       </c>
       <c r="D8" t="n">
         <v>1.31977e-07</v>
@@ -9915,10 +9532,7 @@
         <v>-14793.3004948806</v>
       </c>
       <c r="Y8" t="n">
-        <v>396.2959188826026</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>6346.574506333167</v>
+        <v>505.9722960364498</v>
       </c>
       <c r="AA8" t="n">
         <v>1.356028611338022e-06</v>
@@ -9935,7 +9549,7 @@
         <v>73.928</v>
       </c>
       <c r="C9" t="n">
-        <v>3080.419288637509</v>
+        <v>216.7721207317109</v>
       </c>
       <c r="D9" t="n">
         <v>1.31771e-07</v>
@@ -9968,16 +9582,13 @@
         <v>-15514.39383203477</v>
       </c>
       <c r="Y9" t="n">
-        <v>392.3626232627054</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>5996.277670237979</v>
+        <v>261.968425104891</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.64233392790516e-07</v>
+        <v>6.599944264409463e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.8106817111585489</v>
+        <v>0.9670229222973675</v>
       </c>
     </row>
     <row r="10">
@@ -9988,7 +9599,7 @@
         <v>69.96699999999998</v>
       </c>
       <c r="C10" t="n">
-        <v>3288.979123830104</v>
+        <v>216.7103555970839</v>
       </c>
       <c r="D10" t="n">
         <v>1.31646e-07</v>
@@ -10021,16 +9632,13 @@
         <v>-15488.91399378103</v>
       </c>
       <c r="Y10" t="n">
-        <v>395.169689835852</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>858168112.426217</v>
+        <v>245.8683265861594</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.578396045130931e-07</v>
+        <v>3.933825862081696e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9719144384489259</v>
+        <v>0.997281391106552</v>
       </c>
     </row>
     <row r="11">
@@ -10041,7 +9649,7 @@
         <v>69.30700000000002</v>
       </c>
       <c r="C11" t="n">
-        <v>4738.958569700412</v>
+        <v>211.1580227323518</v>
       </c>
       <c r="D11" t="n">
         <v>1.31534e-07</v>
@@ -10074,16 +9682,13 @@
         <v>-16175.81827169919</v>
       </c>
       <c r="Y11" t="n">
-        <v>390.8990093260031</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>106492834.8877234</v>
+        <v>236.5059777795611</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.56732814570492e-07</v>
+        <v>3.359406107966151e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9728603115912168</v>
+        <v>0.9998693732407529</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 44.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 44.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1124,6 +1124,566 @@
         <v>1.76136837552478e-09</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.9995779623255583</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>165.3560000000001</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1058.371135265326</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.20671e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-85.027</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2592409025321324</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.9470958424594437</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.083809444969338</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.885659123435903</v>
+      </c>
+      <c r="L12" t="n">
+        <v>25.87851946020051</v>
+      </c>
+      <c r="M12" t="n">
+        <v>87.4424278048556</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>22.38752812102091</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-13482.98883291923</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-374.4647264797472</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.126325610808854e-07</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9935780019390091</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>159.085</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9620757638065748</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1166.849438320753</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1.102495523017294</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.19954e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-85.34</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2288959382093803</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.059651900100525</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.30958613787316</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.267012574421083</v>
+      </c>
+      <c r="L13" t="n">
+        <v>29.24786619718802</v>
+      </c>
+      <c r="M13" t="n">
+        <v>87.6983490486076</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>24.87994801800321</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-14754.47805260957</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-474.7153730341131</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.70928386553016e-07</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9531955260823682</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>153.983</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.9312211229105685</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1170.629375619097</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.106066989748005</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.19583e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-85.55200000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.2820303004677656</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.127764399325045</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.561763980526628</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.914912258458589</v>
+      </c>
+      <c r="L14" t="n">
+        <v>31.78288735280085</v>
+      </c>
+      <c r="M14" t="n">
+        <v>87.8781563271466</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>26.9904823777094</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-15805.6122655137</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-487.188179879557</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.587258504028678e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9562218307784481</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>151.135</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.9139976777377296</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1125.777346719982</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1.06368863360749</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.19433e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-85.705</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.617726263216971</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.466357826862079</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.43325503512701</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.723863567195568</v>
+      </c>
+      <c r="L15" t="n">
+        <v>34.05395567057716</v>
+      </c>
+      <c r="M15" t="n">
+        <v>88.01088500171414</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>28.7930860066893</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-16662.24750039758</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-457.976286216449</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.564040085131281e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9582697792751641</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>139.909</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.8461077916737219</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1112.890782667933</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.051512787514693</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.19324e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-85.821</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.08341713720714644</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.6927304569214585</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.719033824937099</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.390682883751945</v>
+      </c>
+      <c r="L16" t="n">
+        <v>35.25600591313493</v>
+      </c>
+      <c r="M16" t="n">
+        <v>88.00346802386724</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>28.68603553470534</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-16250.75718620393</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-455.4864840233376</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.546538643246325e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9598706068651358</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>139.419</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.843144488255642</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1142.611134585273</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.079594006783669</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.19321e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-85.932</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.4477101144131692</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.21157984861598</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.488766060222591</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.528723460939269</v>
+      </c>
+      <c r="L17" t="n">
+        <v>37.47266828665983</v>
+      </c>
+      <c r="M17" t="n">
+        <v>88.14003333900527</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>30.79391307633621</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-17312.65688873198</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-487.9439690862148</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.531511706728881e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9613525716706356</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>133.6900000000001</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.8084980284960933</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1146.848292243133</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.083597477321249</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.19347e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-86.023</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2192703842532396</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8899690075623548</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.33330608949918</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.352120064226918</v>
+      </c>
+      <c r="L18" t="n">
+        <v>38.91708004599719</v>
+      </c>
+      <c r="M18" t="n">
+        <v>88.17364051126479</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>31.36095214640958</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-17370.87342789974</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-498.4593100759382</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.519242541262174e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9626157026254559</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>123.512</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7469459832119788</v>
+      </c>
+      <c r="D19" t="n">
+        <v>362.0964040365431</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.3421261143386797</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.19379e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-86.107</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.293677663963487</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.295911837183952</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.970807334557848</v>
+      </c>
+      <c r="L19" t="n">
+        <v>39.61543225940728</v>
+      </c>
+      <c r="M19" t="n">
+        <v>88.10651301461166</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>30.24838303471771</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-16398.22928104388</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>182.9901054516226</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.686506126870111e-09</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9996179400194639</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>128.252</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7756114081134037</v>
+      </c>
+      <c r="D20" t="n">
+        <v>358.4448764585171</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.3386759752935416</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.19423e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-86.176</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.2999328747787245</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.175056750453406</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.238146360464952</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.557186703779543</v>
+      </c>
+      <c r="L20" t="n">
+        <v>41.70704608956122</v>
+      </c>
+      <c r="M20" t="n">
+        <v>88.28540654790196</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>33.40656362594859</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-18104.56078389052</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>182.8309996315077</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.753483177189518e-09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9994256455321877</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>124.595</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.7534954885217345</v>
+      </c>
+      <c r="D21" t="n">
+        <v>354.8623024914639</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.3352909869395697</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.19487e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-86.23</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.211663794161916</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.000507544959648</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.352497966147505</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.335805436043651</v>
+      </c>
+      <c r="L21" t="n">
+        <v>42.49744099667571</v>
+      </c>
+      <c r="M21" t="n">
+        <v>88.31519116606668</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>33.99748577623005</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-18220.44189905057</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>181.349910469209</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.76136837552478e-09</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.9995779623255583</v>
       </c>
     </row>
@@ -1138,7 +1698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2456,6 +3016,1182 @@
         <v>2.361492632500844e-09</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9985991965947012</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>156.985</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>372.509562498546</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.31074e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-85.693</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1891677672469068</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7369276951108555</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.646059691506951</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.274137981231705</v>
+      </c>
+      <c r="L23" t="n">
+        <v>43.23998836931862</v>
+      </c>
+      <c r="M23" t="n">
+        <v>88.04074021856752</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>29.2321853742016</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-17353.57524213114</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>194.8392034727747</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.632428405261561e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9972348170603681</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>133.288</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8490492722234608</v>
+      </c>
+      <c r="D24" t="n">
+        <v>656.752559189013</v>
+      </c>
+      <c r="E24" t="n">
+        <v>1.763048859159358</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.31092e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-85.965</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1238418258838945</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.8256399147447308</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.969801875323515</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.437909316127456</v>
+      </c>
+      <c r="L24" t="n">
+        <v>46.60818918490256</v>
+      </c>
+      <c r="M24" t="n">
+        <v>88.22567557649077</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>32.28127953372072</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-18131.16864417374</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.325754793522079</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.182411890749819e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.6460112160597945</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>128.7099999999999</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.819887250374239</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1170.142618186917</v>
+      </c>
+      <c r="E25" t="n">
+        <v>3.14124182568195</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.30923e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-86.087</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2144136583031686</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.124017338721299</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.182837451482748</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.65248513987442</v>
+      </c>
+      <c r="L25" t="n">
+        <v>49.20482039651593</v>
+      </c>
+      <c r="M25" t="n">
+        <v>88.35940401177758</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>34.91421424587239</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-19324.75488081173</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-528.1121140844598</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.645372564140362e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9646060326260341</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>124.245</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7914450425199859</v>
+      </c>
+      <c r="D26" t="n">
+        <v>329.5088824589109</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8845648961298733</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.30831e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-86.172</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.2476273661163117</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.154570546728067</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.053075183255546</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.636362038593727</v>
+      </c>
+      <c r="L26" t="n">
+        <v>51.18873802409495</v>
+      </c>
+      <c r="M26" t="n">
+        <v>88.40748480580964</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>35.96890284209613</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-19669.0640710365</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>216.8059916639323</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.013639817783223e-09</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.999679119833617</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>120.6560000000001</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7685829856355706</v>
+      </c>
+      <c r="D27" t="n">
+        <v>327.8547979811365</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8801245148771615</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.30732e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-86.23999999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1252804013569031</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.9704399411066609</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.061181387223711</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.636420322434469</v>
+      </c>
+      <c r="L27" t="n">
+        <v>52.94814378168517</v>
+      </c>
+      <c r="M27" t="n">
+        <v>88.4142134505725</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>36.12160081984797</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-19500.70018840255</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>213.8034042653467</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.000462006330202e-09</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9998026957579937</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>116.7300000000001</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7435742268369594</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1242.573000440917</v>
+      </c>
+      <c r="E28" t="n">
+        <v>3.335680813417419</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.30672e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-86.295</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.09404670860756448</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.7812088270480014</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.867572637364046</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.22129298974005</v>
+      </c>
+      <c r="L28" t="n">
+        <v>53.52551061649774</v>
+      </c>
+      <c r="M28" t="n">
+        <v>88.42772692480922</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>36.43221901709584</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-19445.72062952601</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-608.6944182227145</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.611908377862559e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9674692400662943</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>113.102</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7204637385737489</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1249.119737002362</v>
+      </c>
+      <c r="E29" t="n">
+        <v>3.353255493963964</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.30625e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-86.34</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1228003521305071</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.746298260802548</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.859051873793806</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.695443427447941</v>
+      </c>
+      <c r="L29" t="n">
+        <v>55.01521405872123</v>
+      </c>
+      <c r="M29" t="n">
+        <v>88.44136907204947</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>36.7512568353227</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-19403.55810838039</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-619.7385934488286</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.651426516536248e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9999407474072944</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>113.992</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7261330700385384</v>
+      </c>
+      <c r="D30" t="n">
+        <v>335.8495273111578</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.9015863245456113</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.30557e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-86.38800000000001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.3173440132565482</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.215377711469345</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.049935329264336</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.833846285352921</v>
+      </c>
+      <c r="L30" t="n">
+        <v>56.28781123008387</v>
+      </c>
+      <c r="M30" t="n">
+        <v>88.53736308504917</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>39.16442447517871</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-20583.00029529128</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>188.1219784763243</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.847661292696819e-09</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9994312949802087</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>109.841</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6996910532853458</v>
+      </c>
+      <c r="D31" t="n">
+        <v>314.4535308700859</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8441488824097322</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.30502e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-86.435</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1473610650084578</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.8975412581101935</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.994539157616666</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.334364118080773</v>
+      </c>
+      <c r="L31" t="n">
+        <v>56.98661826206741</v>
+      </c>
+      <c r="M31" t="n">
+        <v>88.51207522436367</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>38.49851807474564</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-19986.55733397512</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>207.4322664007058</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.09485235488373e-09</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9977818574704189</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>107.521</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6849125712647702</v>
+      </c>
+      <c r="D32" t="n">
+        <v>314.5717674952584</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8444662880204217</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.30461e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-86.471</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.2008111106454332</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.936753940896295</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.022717128860716</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.708103625232501</v>
+      </c>
+      <c r="L32" t="n">
+        <v>58.23754521918063</v>
+      </c>
+      <c r="M32" t="n">
+        <v>88.51733126350859</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>38.63505603306751</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-19865.0899368243</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>202.102111506277</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.050165530558116e-09</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9984955149947142</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>107.365</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6839188457495939</v>
+      </c>
+      <c r="D33" t="n">
+        <v>321.3848316597167</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8627559236441645</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.30396e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-86.502</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.2182071178662087</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.238854444106783</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.126442471263416</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.769790194419202</v>
+      </c>
+      <c r="L33" t="n">
+        <v>58.78268433913383</v>
+      </c>
+      <c r="M33" t="n">
+        <v>88.56720331537667</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>39.98043567866102</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-20438.61023290347</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>193.7946186520622</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.075764012250078e-09</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9971455772267578</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>102.9</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6554766378953405</v>
+      </c>
+      <c r="D34" t="n">
+        <v>308.2731038694725</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8275575579906778</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.30336e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-86.551</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.057203935471222</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.7423998963592601</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.825349951805483</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.749675994406678</v>
+      </c>
+      <c r="L34" t="n">
+        <v>60.55232095585726</v>
+      </c>
+      <c r="M34" t="n">
+        <v>88.52835104804589</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>38.92448607146015</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-19658.85723440928</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>213.1614113459096</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>3.017638076126673e-09</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9786987001819787</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>103.528</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6594770200974616</v>
+      </c>
+      <c r="D35" t="n">
+        <v>304.4269452985353</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8172325651364278</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.30318e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-86.578</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.3355118006090689</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.0546286162963</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.963915187534201</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.653681702395809</v>
+      </c>
+      <c r="L35" t="n">
+        <v>60.39003210395629</v>
+      </c>
+      <c r="M35" t="n">
+        <v>88.59559147359067</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>40.78891806168746</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-20518.7504317746</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>200.470652447151</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.070655342531419e-09</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9993434536846061</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99.56200000000001</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6342134598847023</v>
+      </c>
+      <c r="D36" t="n">
+        <v>302.3277267170711</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8115972236773148</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.30283e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-86.607</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.08381697072254403</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.6622663164524278</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.821702201168221</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.598462456042973</v>
+      </c>
+      <c r="L36" t="n">
+        <v>60.93329143749861</v>
+      </c>
+      <c r="M36" t="n">
+        <v>88.54799173466215</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>39.45123082301276</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-19610.25467803122</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>199.4600769182538</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.096113644261957e-09</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9992805009495781</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99.94499999999999</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6366531834251679</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1495.117490469509</v>
+      </c>
+      <c r="E37" t="n">
+        <v>4.013635194869244</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.3024e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-86.645</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.208993761671171</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.9838515005265427</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.276315517275626</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4.036776084535712</v>
+      </c>
+      <c r="L37" t="n">
+        <v>62.76000087932445</v>
+      </c>
+      <c r="M37" t="n">
+        <v>88.61491352476993</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>41.35815267015276</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-20467.66969357239</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-865.5959474832268</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.92395061491683e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9999099209967212</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>97.38499999999999</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6203458929197055</v>
+      </c>
+      <c r="D38" t="n">
+        <v>299.8596576298117</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8049717049370569</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.30212e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-86.661</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.05504091268241985</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.813299975779324</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.808545190727474</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.598157774250983</v>
+      </c>
+      <c r="L38" t="n">
+        <v>62.23119011215179</v>
+      </c>
+      <c r="M38" t="n">
+        <v>88.58032367455016</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>40.35008009489908</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-19765.59665077637</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>198.4380844126443</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.179875050291306e-09</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9984473884286449</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>94.57000000000005</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.6024142433990511</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1604.075951334955</v>
+      </c>
+      <c r="E39" t="n">
+        <v>4.306133621311308</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.302e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-86.70099999999999</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.01006198454032868</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.6724467444565766</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.913784081724455</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.619853803284911</v>
+      </c>
+      <c r="L39" t="n">
+        <v>63.74488861182004</v>
+      </c>
+      <c r="M39" t="n">
+        <v>88.56936219810409</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>40.04079270212811</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-19426.78853111032</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-966.9882677550171</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.553730672204273e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9725661161631419</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>97.08100000000002</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.6184094021721821</v>
+      </c>
+      <c r="D40" t="n">
+        <v>295.7887100523882</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.794043267153827</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.30153e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-86.73099999999999</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.3489491391578226</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.14543414556674</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.094766878576161</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.895603469208018</v>
+      </c>
+      <c r="L40" t="n">
+        <v>64.49380423097003</v>
+      </c>
+      <c r="M40" t="n">
+        <v>88.68260999075152</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>43.48422405642729</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-21074.70458151443</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>192.9903732792495</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2.092119517697357e-09</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9994168217353023</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>96.137</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.6123960887982928</v>
+      </c>
+      <c r="D41" t="n">
+        <v>294.2730518025084</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7899744903962217</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.30162e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-86.751</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.4592932571369939</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.262518948695205</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.138603999650732</v>
+      </c>
+      <c r="K41" t="n">
+        <v>4.093030726535285</v>
+      </c>
+      <c r="L41" t="n">
+        <v>64.75111926901496</v>
+      </c>
+      <c r="M41" t="n">
+        <v>88.70555660327932</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>44.25533876230251</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-21298.44450886489</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>188.4630927141799</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>2.222997265952816e-09</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.996604458815566</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>94.35799999999995</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.6010637959040669</v>
+      </c>
+      <c r="D42" t="n">
+        <v>289.5711579822464</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7773522806770273</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.30124e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-86.788</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.5784393798319761</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.199006056664344</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.584353767217681</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4.09893110001336</v>
+      </c>
+      <c r="L42" t="n">
+        <v>66.00820900158939</v>
+      </c>
+      <c r="M42" t="n">
+        <v>88.72506501427763</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>44.93274033895188</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-21457.98938338228</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>196.4313722729031</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>2.354955806952794e-09</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9985817293485175</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>90.22499999999997</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5747364397872405</v>
+      </c>
+      <c r="D43" t="n">
+        <v>284.1483193072186</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7627946982121505</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.30106e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-86.80500000000001</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1841589197346305</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.8254539618597847</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.79962785055217</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.64399304451693</v>
+      </c>
+      <c r="L43" t="n">
+        <v>65.09843453295856</v>
+      </c>
+      <c r="M43" t="n">
+        <v>88.64646175454304</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>42.32249866755602</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-19936.89837474209</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>199.2264003885679</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>2.361492632500844e-09</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9985991965947012</v>
       </c>
     </row>
@@ -2470,7 +4206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3788,6 +5524,1182 @@
         <v>1.818331000514512e-09</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9997605360604088</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>173.051</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>444.7884772957032</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.25063e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-84.61</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3000083943625262</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.9158886657891948</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.051297540249093</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.327041424851076</v>
+      </c>
+      <c r="L23" t="n">
+        <v>23.34614256899606</v>
+      </c>
+      <c r="M23" t="n">
+        <v>87.15764732125336</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>20.14133245779954</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-12416.24824919289</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>139.892800437904</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.203049561110753e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9995461588573076</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>149.7909999999999</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8655887570716144</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1160.594327957755</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.609317433342977</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.23272e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-85.401</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3718031353244102</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.150446463190796</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.105665931539575</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.666482707452562</v>
+      </c>
+      <c r="L24" t="n">
+        <v>30.72085962664737</v>
+      </c>
+      <c r="M24" t="n">
+        <v>87.78532861792188</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>25.85812158977623</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-15186.3575794681</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-481.6876295343397</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.65047606081878e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9549259975515666</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>144.8030000000001</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8367648843404549</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1134.927514187875</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.55161177080888</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.22369e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-85.697</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.5130646141852944</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.164007022900213</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.356902026301368</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.812946807856191</v>
+      </c>
+      <c r="L25" t="n">
+        <v>35.20072304081879</v>
+      </c>
+      <c r="M25" t="n">
+        <v>88.03366245045362</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>29.12688285461806</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-16863.78495476274</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-470.6227555048055</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.5975165127509e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9587661132799178</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>141.254</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8162564793037889</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1150.601392046659</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.586850718440978</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.21862e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-85.873</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.5440481711753026</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.300054607860941</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.442327180136729</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.373229128399669</v>
+      </c>
+      <c r="L26" t="n">
+        <v>38.52866075119788</v>
+      </c>
+      <c r="M26" t="n">
+        <v>88.17218214797073</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>31.33591318030961</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-17961.24743845963</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-490.3733843357707</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.567713072065792e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9609994784080305</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>134.606</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7778400587110158</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1138.407666299771</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.559436056485199</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.21539e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-85.994</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1618090581572138</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.036940590453794</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.273496132321186</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.30493880081522</v>
+      </c>
+      <c r="L27" t="n">
+        <v>40.92424233450262</v>
+      </c>
+      <c r="M27" t="n">
+        <v>88.20328996725124</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>31.87882102497744</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-17997.61842269876</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-485.8316987900907</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.547601861903376e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9625708344887036</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>132.833</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7675945241576182</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1192.663982421537</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.681418344451925</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.21327e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-86.095</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2322641009039744</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.186193344601766</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.310006168819295</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.900509452169649</v>
+      </c>
+      <c r="L28" t="n">
+        <v>42.73237899993157</v>
+      </c>
+      <c r="M28" t="n">
+        <v>88.28718814438813</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>33.44133250330943</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-18713.21818627753</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-537.457049138618</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.530852102112056e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9639646642554476</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>129.3650000000001</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7475541892274536</v>
+      </c>
+      <c r="D29" t="n">
+        <v>627.0408761239223</v>
+      </c>
+      <c r="E29" t="n">
+        <v>1.409750720019337</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.21216e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-86.167</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.3722272200796527</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.064072962050821</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.209219656306761</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.435566180927724</v>
+      </c>
+      <c r="L29" t="n">
+        <v>44.38599647293455</v>
+      </c>
+      <c r="M29" t="n">
+        <v>88.32363446272743</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>34.16881832590185</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-18898.64523204229</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>22.87328665904335</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.714998837892551e-08</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.7589626585682619</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>126.149</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7289700724064004</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1205.64681858012</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.71060713153004</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.21129e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-86.23</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.4087745846202038</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.055070454831164</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.195061888764573</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.911996225899578</v>
+      </c>
+      <c r="L30" t="n">
+        <v>45.1429322308387</v>
+      </c>
+      <c r="M30" t="n">
+        <v>88.36763392993825</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>35.09033763922436</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-19225.25622158501</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-560.5064945983686</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.511903614561794e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9656207271375492</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>121.513</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7021802821133654</v>
+      </c>
+      <c r="D31" t="n">
+        <v>545.6426754923696</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1.226746427447617</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.21079e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-86.28</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1400350886607939</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.7379697854399586</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.997536108911883</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.745755240794018</v>
+      </c>
+      <c r="L31" t="n">
+        <v>46.09280040956353</v>
+      </c>
+      <c r="M31" t="n">
+        <v>88.34160963739218</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>34.53938201459988</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-18659.02516410564</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.62335314010603</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.374723388034861e-09</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9697301635230764</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>118.6129999999999</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.685422216571993</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1272.435245384833</v>
+      </c>
+      <c r="E32" t="n">
+        <v>2.860764858660886</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.21056e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-86.343</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.7206889141056847</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.125091127095456</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.895131803872445</v>
+      </c>
+      <c r="L32" t="n">
+        <v>47.57521652007836</v>
+      </c>
+      <c r="M32" t="n">
+        <v>88.38430872173819</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>35.45268359604334</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-18979.19883645495</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-628.0098650157474</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.544921834051245e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9998720592015995</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>113.862</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6579678823005933</v>
+      </c>
+      <c r="D33" t="n">
+        <v>355.0079273603395</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.7981500094579203</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.21028e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-86.38800000000001</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.4152602782483014</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.639276292922631</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.319077867050486</v>
+      </c>
+      <c r="L33" t="n">
+        <v>47.9705969226253</v>
+      </c>
+      <c r="M33" t="n">
+        <v>88.35971792468607</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>34.9208996904884</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-18468.81200397372</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>177.7557527474399</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.799463191473608e-09</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9981007465527786</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>115.446</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.667121253272157</v>
+      </c>
+      <c r="D34" t="n">
+        <v>530.6027059886111</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1.192932670411462</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.21043e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-86.422</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.1987081434781723</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.8072135140727715</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.169363442069613</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.727183872848466</v>
+      </c>
+      <c r="L34" t="n">
+        <v>48.93086825827017</v>
+      </c>
+      <c r="M34" t="n">
+        <v>88.45574418417671</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>37.09353364939714</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-19566.44751812772</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1.670455266752515</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.236188957410127e-09</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9795691034232376</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>113.891</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.658135462956007</v>
+      </c>
+      <c r="D35" t="n">
+        <v>533.9556268212297</v>
+      </c>
+      <c r="E35" t="n">
+        <v>1.20047090713244</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.21058e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-86.45</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.4021529186021932</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.021582353028955</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.074545426710853</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4.092368856186695</v>
+      </c>
+      <c r="L35" t="n">
+        <v>49.48891371898634</v>
+      </c>
+      <c r="M35" t="n">
+        <v>88.4792489974719</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>37.6671290290443</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-19723.2558422374</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0.8283793683879426</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.491172551382819e-09</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9656667555855388</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>111.984</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6471155902017324</v>
+      </c>
+      <c r="D36" t="n">
+        <v>528.5125573603748</v>
+      </c>
+      <c r="E36" t="n">
+        <v>1.188233473523664</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.21044e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-86.494</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.2486247768178571</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.033305322371733</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.163700048807765</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.826135880936663</v>
+      </c>
+      <c r="L36" t="n">
+        <v>50.40206552789888</v>
+      </c>
+      <c r="M36" t="n">
+        <v>88.49929168139049</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>38.17042650371392</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-19826.4224640925</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1.156982517341205</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.412900409199524e-09</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9694785201792006</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>110.748</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6399731870951338</v>
+      </c>
+      <c r="D37" t="n">
+        <v>354.9389193226639</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7979948614691613</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.21072e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-86.518</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.3275684081618971</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.021644997469853</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.288826933864577</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.913387317242083</v>
+      </c>
+      <c r="L37" t="n">
+        <v>50.66712618557644</v>
+      </c>
+      <c r="M37" t="n">
+        <v>88.51103564188456</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>38.47162663800614</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-19831.29149342823</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>171.5507361794584</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.887708891937781e-09</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9973824890073947</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>109.53</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6329347995677573</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1401.737028953351</v>
+      </c>
+      <c r="E38" t="n">
+        <v>3.151468845316897</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.21078e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-86.562</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.2219867409237588</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.169840118159426</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.466983994616491</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.457823184390808</v>
+      </c>
+      <c r="L38" t="n">
+        <v>52.24965849362908</v>
+      </c>
+      <c r="M38" t="n">
+        <v>88.55553570648043</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>39.657359911227</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-20320.00828788663</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-764.1597074720906</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.469994822494576e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9698792964890748</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>104.501</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.603874002461702</v>
+      </c>
+      <c r="D39" t="n">
+        <v>351.0468026344484</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7892443724459757</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.21099e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-86.58199999999999</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.05189449339734914</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.5526090158011652</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.725850722246733</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.36217087547942</v>
+      </c>
+      <c r="L39" t="n">
+        <v>51.66254020830205</v>
+      </c>
+      <c r="M39" t="n">
+        <v>88.48590104804566</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>37.83269357607153</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-19124.79737006264</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>161.7801282491701</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.72675433836841e-09</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9982996938656616</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>106.825</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.6173035694679603</v>
+      </c>
+      <c r="D40" t="n">
+        <v>349.1366123555276</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7849497686591719</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.21126e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-86.619</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.345839797616567</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.263085181407936</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.348656458485426</v>
+      </c>
+      <c r="K40" t="n">
+        <v>4.501850808431209</v>
+      </c>
+      <c r="L40" t="n">
+        <v>53.38551896821182</v>
+      </c>
+      <c r="M40" t="n">
+        <v>88.58755038149658</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>40.5566129735538</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-20487.72512551313</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>167.0939719374874</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.889735000579048e-09</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.998169995835327</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>105.208</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.6079595032678227</v>
+      </c>
+      <c r="D41" t="n">
+        <v>345.1146658947244</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7759073885929065</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.21159e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-86.63800000000001</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.4923295745828308</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.26394536192847</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.536477595217099</v>
+      </c>
+      <c r="K41" t="n">
+        <v>4.177107884469164</v>
+      </c>
+      <c r="L41" t="n">
+        <v>53.31935458482945</v>
+      </c>
+      <c r="M41" t="n">
+        <v>88.59251266954739</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>40.69965867500078</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-20400.88055875661</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>160.0973020866855</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.749809757452327e-09</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9995223133727702</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>102.46</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5920797915065503</v>
+      </c>
+      <c r="D42" t="n">
+        <v>345.3951031948574</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7765378844677954</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.21189e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-86.685</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.2881277376624667</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.178764676032695</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.422534925743671</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4.68560362374344</v>
+      </c>
+      <c r="L42" t="n">
+        <v>55.24004642700121</v>
+      </c>
+      <c r="M42" t="n">
+        <v>88.60755895712755</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>41.13962263995629</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-20450.9722368486</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>161.2103304856029</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.924264236202264e-09</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.996284200593529</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99.137</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5728773598534537</v>
+      </c>
+      <c r="D43" t="n">
+        <v>336.8613495171095</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.7573517901480126</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.21212e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-86.68000000000001</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.08822780322679714</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.66186518467809</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.813005322637104</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.616948192704309</v>
+      </c>
+      <c r="L43" t="n">
+        <v>53.31111285670836</v>
+      </c>
+      <c r="M43" t="n">
+        <v>88.54159149224458</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>39.27802433211544</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-19296.228715192</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>163.8074185238285</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.818331000514512e-09</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9997605360604088</v>
       </c>
     </row>
@@ -3802,7 +6714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4504,6 +7416,566 @@
         <v>2.123505423887805e-09</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.9993517506851066</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>154.168</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>675.1685013796711</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.32747e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-82.62</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1361674486368757</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.6951387111463744</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.570732828739516</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.689883408787427</v>
+      </c>
+      <c r="L12" t="n">
+        <v>12.53857835234174</v>
+      </c>
+      <c r="M12" t="n">
+        <v>85.15893059983844</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>11.80717833307756</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-6573.881938216876</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.041466005733803</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.300970091161617e-07</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.5580203120111747</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>121.446</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.787751024856001</v>
+      </c>
+      <c r="D13" t="n">
+        <v>310.744325911879</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.4602470720670313</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.30919e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-84.18300000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.532150272004141</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.210418908681541</v>
+      </c>
+      <c r="J13" t="n">
+        <v>2.338021988684739</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.062052903139473</v>
+      </c>
+      <c r="L13" t="n">
+        <v>17.44851834549598</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.52053831888745</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>16.44660403800632</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-8455.454687471025</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>202.1394036365965</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.996187901909929e-09</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9998316571666811</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>111.069</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.720441336723574</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1458.6186985553</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.160377291853353</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.29034e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-84.90900000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.2469856326385768</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.055304848843566</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.101027334430435</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.120585401615591</v>
+      </c>
+      <c r="L14" t="n">
+        <v>21.6456801803703</v>
+      </c>
+      <c r="M14" t="n">
+        <v>87.11978400360309</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>19.87611670466828</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-9966.589926908709</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-810.2143512521097</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.773423667132198e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9511392247189556</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>107.997</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.7005150225727774</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1529.439443039894</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.265270728587849</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.27686e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-85.346</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.3863131525657775</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.179541527615291</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.289245961809367</v>
+      </c>
+      <c r="K15" t="n">
+        <v>4.288325019824794</v>
+      </c>
+      <c r="L15" t="n">
+        <v>25.26169656842603</v>
+      </c>
+      <c r="M15" t="n">
+        <v>87.50438817739025</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>22.94408966952435</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-11379.84288682476</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-879.3549720897217</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.696845536368017e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9562245000466196</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101.894</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.6609283379170775</v>
+      </c>
+      <c r="D16" t="n">
+        <v>295.0471967439368</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.4369978696296161</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.26802e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-85.64</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.179374713438361</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8884067456263414</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.078081249393724</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.161591249876211</v>
+      </c>
+      <c r="L16" t="n">
+        <v>28.37953158425153</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.71142443502828</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>25.02224796670136</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-12212.47173573682</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>202.7985626825797</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.343727445419775e-09</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9975582084073989</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>100.205</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.6499727569923718</v>
+      </c>
+      <c r="D17" t="n">
+        <v>595.4633156346957</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8819477129307691</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.26186e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-85.848</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.4169030028191914</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.175918185659689</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.310833883318672</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.230985236751725</v>
+      </c>
+      <c r="L17" t="n">
+        <v>30.95396112776657</v>
+      </c>
+      <c r="M17" t="n">
+        <v>87.89546152366736</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>27.21262190425853</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-13152.68204207807</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0.5740854435417805</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.95146761387755e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.6215940068269361</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98.029</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.635858284468891</v>
+      </c>
+      <c r="D18" t="n">
+        <v>335.7239728801575</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.4972447206795391</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.25762e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-86.011</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.32157645890788</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.14066606777911</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.150468722718487</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.337236574369384</v>
+      </c>
+      <c r="L18" t="n">
+        <v>33.18990029491716</v>
+      </c>
+      <c r="M18" t="n">
+        <v>88.02257435294243</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>28.96342985097152</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-13825.47071609503</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>147.6753050315465</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.810050764156763e-09</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.998522369708451</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>91.62099999999998</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5942932385449637</v>
+      </c>
+      <c r="D19" t="n">
+        <v>341.7482295535347</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.5061673180179322</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.25455e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-86.15000000000001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.02551731958397743</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.6761551914902059</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.880578455709672</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.8867058155056</v>
+      </c>
+      <c r="L19" t="n">
+        <v>35.21594600656827</v>
+      </c>
+      <c r="M19" t="n">
+        <v>88.07443435814942</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>29.74409468062561</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-13944.87180468092</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>141.5226898210372</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.7829878744755e-09</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9999612937281547</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92.24700000000001</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5983537439676198</v>
+      </c>
+      <c r="D20" t="n">
+        <v>243.603206235788</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.3608035708686021</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.25236e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-86.256</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.4566571384644836</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.223104794895522</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.439441831590814</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.561734848174533</v>
+      </c>
+      <c r="L20" t="n">
+        <v>37.00941068948779</v>
+      </c>
+      <c r="M20" t="n">
+        <v>88.2036612326601</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>31.88541402709111</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-14845.97249191081</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>262.0811860270032</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>9.193444650639813e-09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9320508607612904</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>89.62699999999995</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.5813592963520312</v>
+      </c>
+      <c r="D21" t="n">
+        <v>290.7563580463497</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.4306426580212265</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.2505e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-86.35599999999999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4441617951607826</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.303725084715581</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.47961051565611</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.853929146596404</v>
+      </c>
+      <c r="L21" t="n">
+        <v>38.77297714531522</v>
+      </c>
+      <c r="M21" t="n">
+        <v>88.28161213153919</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>33.33275362869809</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-15346.09664441817</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>179.6705565001796</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.123505423887805e-09</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.9993517506851066</v>
       </c>
     </row>
@@ -4518,7 +7990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5836,6 +9308,1182 @@
         <v>1.956997781804142e-09</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9973187183922376</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>169.186</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>414.0478335069021</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.30706e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-84.178</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.34997300561733</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.068307750939603</v>
+      </c>
+      <c r="J23" t="n">
+        <v>2.107521643482996</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.855595614588376</v>
+      </c>
+      <c r="L23" t="n">
+        <v>20.61445383534398</v>
+      </c>
+      <c r="M23" t="n">
+        <v>86.86144946380473</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>18.23722750448354</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-11143.10422310316</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>166.3006164582653</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.342441404671057e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9996382840895879</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>144.4109999999999</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8535635336257135</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1268.206842603698</v>
+      </c>
+      <c r="E24" t="n">
+        <v>3.062947659603095</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.28327e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-85.096</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3480201929434792</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.122418004165132</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.332426035980133</v>
+      </c>
+      <c r="K24" t="n">
+        <v>4.025322765063958</v>
+      </c>
+      <c r="L24" t="n">
+        <v>27.64414288353401</v>
+      </c>
+      <c r="M24" t="n">
+        <v>87.58003764361428</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>23.66222979266279</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-13751.00150610183</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-579.0399608056234</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.750376676224168e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.952159472204091</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>140.296</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8292411901693995</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1187.733170642985</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.868589265600361</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.27039e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-85.479</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.4797119460741948</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.393004009766325</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.665058076893076</v>
+      </c>
+      <c r="K25" t="n">
+        <v>4.374769836106637</v>
+      </c>
+      <c r="L25" t="n">
+        <v>32.46834711581667</v>
+      </c>
+      <c r="M25" t="n">
+        <v>87.91385601540614</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>27.4527831287973</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-15747.41414918185</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-523.5152592212467</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.678223889175268e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9570167642475148</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>133.29</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7878311444209334</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1137.588748963841</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.747481466884376</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.26238e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-85.726</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.1509853362372944</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.028815228672975</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.953242640510532</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.623318961829938</v>
+      </c>
+      <c r="L26" t="n">
+        <v>36.19187331902096</v>
+      </c>
+      <c r="M26" t="n">
+        <v>88.05373631179418</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>29.42753379693054</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-16627.16855542043</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-486.9652585233059</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.634445930390748e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.960071266487176</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>130.823</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7732495596562367</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1164.540425385895</v>
+      </c>
+      <c r="E27" t="n">
+        <v>2.81257461371666</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.25732e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-85.892</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.33539212366313</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.086720055367662</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.923474992936034</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.597600772268267</v>
+      </c>
+      <c r="L27" t="n">
+        <v>39.386628487237</v>
+      </c>
+      <c r="M27" t="n">
+        <v>88.17432383016353</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>31.37269795974946</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-17551.88878711573</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-515.9477914462159</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.606462367255953e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9620840071446448</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>126.859</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7498197250363509</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1212.318596612709</v>
+      </c>
+      <c r="E28" t="n">
+        <v>2.927967491931099</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.25378e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-86.005</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2050212053430038</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.098739483456608</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.995448201650674</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.628447982528026</v>
+      </c>
+      <c r="L28" t="n">
+        <v>41.5542873515418</v>
+      </c>
+      <c r="M28" t="n">
+        <v>88.25540629771258</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>32.8317540952881</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-18173.35050536688</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-562.74194379005</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.584815734986672e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9637287600108656</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>124.0930000000001</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7334708545624348</v>
+      </c>
+      <c r="D29" t="n">
+        <v>360.7407993754404</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8712539232968283</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.25107e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-86.09399999999999</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1863026194483362</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.198981194939213</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.28739097338252</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.37752713498274</v>
+      </c>
+      <c r="L29" t="n">
+        <v>43.72072980697462</v>
+      </c>
+      <c r="M29" t="n">
+        <v>88.30606317303224</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>33.81418008510435</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-18510.38553921237</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>177.6952175653396</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.583236977678895e-09</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9996451126551226</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>122.473</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7238955941981013</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1228.329549517527</v>
+      </c>
+      <c r="E30" t="n">
+        <v>2.966636823368502</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.2493e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-86.17700000000001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.3698680663038392</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.207732489257296</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.357290938704292</v>
+      </c>
+      <c r="K30" t="n">
+        <v>4.160520434592018</v>
+      </c>
+      <c r="L30" t="n">
+        <v>45.43859926446282</v>
+      </c>
+      <c r="M30" t="n">
+        <v>88.38564068815192</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>35.48195020107263</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-19274.90352499807</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-588.4328860451606</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.561293990758285e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9999662812709396</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>119.389</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7056671355785938</v>
+      </c>
+      <c r="D31" t="n">
+        <v>356.1024292553308</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8600514250713851</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.2475e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-86.23399999999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.3186650638850966</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.183238834098437</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.285978271572241</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.84111882406275</v>
+      </c>
+      <c r="L31" t="n">
+        <v>46.26871929486438</v>
+      </c>
+      <c r="M31" t="n">
+        <v>88.40788830141688</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>35.97802328936388</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-19354.11255195818</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>179.1751363031973</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.710597186752105e-09</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9984493520035852</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>115.222</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6810374380858939</v>
+      </c>
+      <c r="D32" t="n">
+        <v>354.4636788295074</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.8560935480021018</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.24627e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-86.288</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1000187332045756</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9334257235927691</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.178012065861433</v>
+      </c>
+      <c r="K32" t="n">
+        <v>4.403926230720264</v>
+      </c>
+      <c r="L32" t="n">
+        <v>47.7987471254273</v>
+      </c>
+      <c r="M32" t="n">
+        <v>88.39919616265577</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>35.78256683045963</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-19036.10569833713</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>176.993022402099</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.702993094457459e-09</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9987517212223116</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>114.9059999999999</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.679169671249394</v>
+      </c>
+      <c r="D33" t="n">
+        <v>356.6475504675168</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8613679908593738</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.24514e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-86.354</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1979704984502514</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.9459101128129158</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.069024636101454</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.745052116782441</v>
+      </c>
+      <c r="L33" t="n">
+        <v>49.15079237132448</v>
+      </c>
+      <c r="M33" t="n">
+        <v>88.4476791384474</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>36.90072148038194</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-19497.40703510112</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>171.0886449974462</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.682826317348739e-09</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9990691076587206</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>111.524</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6591798375752131</v>
+      </c>
+      <c r="D34" t="n">
+        <v>354.2713017492295</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.855628922746975</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.24428e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-86.38800000000001</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.1465717306350811</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.8235232392790938</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.91135430950407</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.788301351993532</v>
+      </c>
+      <c r="L34" t="n">
+        <v>49.90071484780559</v>
+      </c>
+      <c r="M34" t="n">
+        <v>88.44513591150732</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>36.84033492456643</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-19293.01124821303</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>170.6525106867111</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.70344781742188e-09</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9988720380543018</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>107.45</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6350998309552803</v>
+      </c>
+      <c r="D35" t="n">
+        <v>351.9995363554009</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8501422006584007</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.24404e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-86.423</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.4575688148383557</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.749847401600178</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.788845591553747</v>
+      </c>
+      <c r="L35" t="n">
+        <v>50.69654843323498</v>
+      </c>
+      <c r="M35" t="n">
+        <v>88.40789809003768</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>35.9782446047068</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-18633.70275949086</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>170.1520618673792</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.721940679840552e-09</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9988105812639083</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>109.852</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6492972231744946</v>
+      </c>
+      <c r="D36" t="n">
+        <v>350.5152140666699</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8465572953199062</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.24345e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-86.467</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.2989020923816637</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.9949061126661013</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.230222417198598</v>
+      </c>
+      <c r="K36" t="n">
+        <v>4.260751953319771</v>
+      </c>
+      <c r="L36" t="n">
+        <v>52.20507813638782</v>
+      </c>
+      <c r="M36" t="n">
+        <v>88.5112146069895</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>38.4762533487286</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-19901.54851131805</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>172.454232267292</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.809578552083691e-09</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9971671428552108</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>107.895</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6377300722281986</v>
+      </c>
+      <c r="D37" t="n">
+        <v>368.86098076119</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8908656220635462</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.24315e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-86.499</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.1717064825833105</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.078459478462247</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.222011098371834</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4.436703981218254</v>
+      </c>
+      <c r="L37" t="n">
+        <v>52.91428360131394</v>
+      </c>
+      <c r="M37" t="n">
+        <v>88.52840792470087</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>38.92599115469031</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-20000.50700315995</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>147.6871098019474</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.603962064851944e-09</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.998864348348363</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>107.553</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6357086283735062</v>
+      </c>
+      <c r="D38" t="n">
+        <v>346.3844681947523</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.8365808009691665</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.2423e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-86.52800000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.3425369347413282</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.109439532511245</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.321838790590484</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.13101221015685</v>
+      </c>
+      <c r="L38" t="n">
+        <v>53.06704557050637</v>
+      </c>
+      <c r="M38" t="n">
+        <v>88.56260943717959</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>39.85260544806466</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-20360.78126008563</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>168.1998557789877</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.781865339032481e-09</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.998484590903389</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>105.43</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.6231603087725935</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1374.522901070304</v>
+      </c>
+      <c r="E39" t="n">
+        <v>3.319720065743059</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.24185e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-86.566</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.3901634095448928</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.019409482490878</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.258237197299817</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4.486474963116302</v>
+      </c>
+      <c r="L39" t="n">
+        <v>54.36689369533922</v>
+      </c>
+      <c r="M39" t="n">
+        <v>88.56753740361231</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>39.98976406375478</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-20263.0610343937</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-748.2773772533258</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.501992025221879e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9704868570277222</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>104.552</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.6179707540813069</v>
+      </c>
+      <c r="D40" t="n">
+        <v>363.5192082549586</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.8779642805422354</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.24146e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-86.60599999999999</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.4607338224862711</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.061792391589784</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.31994462243097</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.943979187191733</v>
+      </c>
+      <c r="L40" t="n">
+        <v>55.10218724730932</v>
+      </c>
+      <c r="M40" t="n">
+        <v>88.59895201626152</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>40.88679319135042</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-20591.79155524877</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>146.6633284199095</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.625747724555426e-09</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9998514103001476</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>102.219</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.6041811970257587</v>
+      </c>
+      <c r="D41" t="n">
+        <v>340.7232741805845</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.8229079990462133</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.24131e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-86.634</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.2308113243613014</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.9916132066949297</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.134387622570785</v>
+      </c>
+      <c r="K41" t="n">
+        <v>4.107375136290581</v>
+      </c>
+      <c r="L41" t="n">
+        <v>55.86309720888527</v>
+      </c>
+      <c r="M41" t="n">
+        <v>88.59557787635029</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>40.78852299604019</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-20371.84324781778</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>162.7485321764183</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.753199407349242e-09</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9993972780672632</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>101.271</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5985778965162604</v>
+      </c>
+      <c r="D42" t="n">
+        <v>337.4330557852733</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.8149615297519686</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.24162e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-86.652</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.3199519294809126</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.008254574876492</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.266414422292578</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4.2604254969553</v>
+      </c>
+      <c r="L42" t="n">
+        <v>56.04949379710914</v>
+      </c>
+      <c r="M42" t="n">
+        <v>88.61092415293518</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>41.23932730799857</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-20458.4021150452</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>165.0401472854043</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.822742677252119e-09</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9991653033464765</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99.02199999999999</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5852848344425662</v>
+      </c>
+      <c r="D43" t="n">
+        <v>336.1547939860418</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.8118742975633469</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.24093e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-86.69499999999999</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1624381050349279</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.952099154792975</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.166182340570337</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.806378148365617</v>
+      </c>
+      <c r="L43" t="n">
+        <v>57.05982317227738</v>
+      </c>
+      <c r="M43" t="n">
+        <v>88.62558245532303</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>41.6793203925384</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-20509.68482550468</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>172.2488533172049</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.956997781804142e-09</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9973187183922376</v>
       </c>
     </row>
@@ -5850,7 +10498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6552,6 +11200,566 @@
         <v>1.730829596592261e-09</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.9996435806054071</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>170.454</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>344.3813496519741</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.35515e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-81.949</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1170783647342188</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.5059949187078068</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.244073675354597</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.505660756385728</v>
+      </c>
+      <c r="L12" t="n">
+        <v>11.58510910988858</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.62960094989177</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10.63755028327457</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-6318.601230315276</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>213.3807149805746</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.730176872934462e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9973804398598546</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>113.733</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6672357351543525</v>
+      </c>
+      <c r="D13" t="n">
+        <v>304.2518827313417</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8834737509415461</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.3576e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-83.504</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1770143049183889</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.7288909806375486</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.743827917031706</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.238376637589871</v>
+      </c>
+      <c r="L13" t="n">
+        <v>14.98251882609012</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.91547373847337</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>14.00375052746339</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-7267.108957893212</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>217.9344205253663</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.129985928047176e-09</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9960990254852253</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>104.842</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6150750349067783</v>
+      </c>
+      <c r="D14" t="n">
+        <v>366.9779471844934</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.065615044355204</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.33892e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-84.34999999999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3774864855725109</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.222253321778176</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.153717627897348</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.949111041390478</v>
+      </c>
+      <c r="L14" t="n">
+        <v>18.53797784322582</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.67284613602878</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>17.20129726343182</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-8697.313979497821</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>137.9879853590958</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.482933739320654e-09</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9995164367187145</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97.59699999999998</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.572570898893543</v>
+      </c>
+      <c r="D15" t="n">
+        <v>299.4458685213738</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.8695182501142663</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.32242e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-84.872</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2207267044645005</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.7850253600324124</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.927979268195397</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.594281116519263</v>
+      </c>
+      <c r="L15" t="n">
+        <v>21.70898147114228</v>
+      </c>
+      <c r="M15" t="n">
+        <v>87.07813236585309</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>19.59229849147633</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-9727.399628183486</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>214.2714592013445</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.358890836599947e-09</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9994620390055986</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92.56700000000001</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.543061471130041</v>
+      </c>
+      <c r="D16" t="n">
+        <v>349.9742726318105</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.016240493236607</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.31062e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-85.23</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.7682043116565506</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.856546614266416</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.507778122344825</v>
+      </c>
+      <c r="L16" t="n">
+        <v>24.55633013016182</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.35690331565235</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>21.66214025265463</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-10613.00555506835</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>148.0640079026161</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.621714205336754e-09</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9997177718639118</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>95.73299999999995</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5616353972332708</v>
+      </c>
+      <c r="D17" t="n">
+        <v>345.7450170683671</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1.003959759777268</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.3019e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-85.489</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6938688356963437</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.535191137175546</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2.373345303758873</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.187859866391999</v>
+      </c>
+      <c r="L17" t="n">
+        <v>27.15753613198025</v>
+      </c>
+      <c r="M17" t="n">
+        <v>87.6524006523772</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>24.39245563260854</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-11939.00536769757</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>149.7289023716054</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.691282056344018e-09</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9991218975543892</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90.78199999999998</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5325894376195336</v>
+      </c>
+      <c r="D18" t="n">
+        <v>345.1937630416481</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1.002359051645785</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.29518e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-85.70099999999999</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.4273147365462783</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.164794258278842</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.110231392073239</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.69012131262431</v>
+      </c>
+      <c r="L18" t="n">
+        <v>29.50944106745597</v>
+      </c>
+      <c r="M18" t="n">
+        <v>87.77488195674073</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>25.73659953235223</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-12399.00526128336</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>144.6993992335626</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.691241151809523e-09</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9991647457712878</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>87.36899999999997</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5125664402126084</v>
+      </c>
+      <c r="D19" t="n">
+        <v>367.3582656024856</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1.066719396894552</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.28996e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-85.848</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.0996481150750038</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.8816638290681411</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.159627993282163</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.81846214288689</v>
+      </c>
+      <c r="L19" t="n">
+        <v>31.32364688653896</v>
+      </c>
+      <c r="M19" t="n">
+        <v>87.86689840153443</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>26.84790333880436</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-12770.77070569713</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>120.281159039758</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.524275067585915e-09</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9999972461478975</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>84.72799999999995</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4970725239654097</v>
+      </c>
+      <c r="D20" t="n">
+        <v>328.1234509401165</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9527910012307937</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.28643e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-85.988</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.2098674807550704</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.8915616150853767</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.883437041723484</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.496889128610654</v>
+      </c>
+      <c r="L20" t="n">
+        <v>33.1771868432983</v>
+      </c>
+      <c r="M20" t="n">
+        <v>87.96552851428962</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>28.15065127886286</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-13239.06867644153</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>156.9466611754991</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.950766456238779e-09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9964690674560508</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>82.678</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4850458188132868</v>
+      </c>
+      <c r="D21" t="n">
+        <v>338.8579435611051</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.9839613669658626</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.28332e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-86.09699999999999</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.2707419140622818</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.8057784469185791</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.969836104905034</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.531162463444806</v>
+      </c>
+      <c r="L21" t="n">
+        <v>34.79719312026643</v>
+      </c>
+      <c r="M21" t="n">
+        <v>88.04529689164828</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>29.30038257793186</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-13642.32268949657</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>140.195159535321</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.730829596592261e-09</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.9996435806054071</v>
       </c>
     </row>
@@ -6566,7 +11774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7884,6 +13092,1182 @@
         <v>1.770970618415128e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9999999992224516</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>165.807</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>414.0040921693853</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.3174e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-84.312</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1466560106074055</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7909223270948768</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.834458300235291</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.378101104123332</v>
+      </c>
+      <c r="L23" t="n">
+        <v>21.64528522293118</v>
+      </c>
+      <c r="M23" t="n">
+        <v>86.93415724150684</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>18.67058754681381</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-11267.54250541104</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>158.8195658681473</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.294661882695531e-09</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9998299126115482</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>142.9909999999999</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8623942294354274</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1160.92068907055</v>
+      </c>
+      <c r="E24" t="n">
+        <v>2.804128536477296</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.29904e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-85.123</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.005538227187246246</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.8767578020637388</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.056940813997742</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.48077490730674</v>
+      </c>
+      <c r="L24" t="n">
+        <v>28.07064347318826</v>
+      </c>
+      <c r="M24" t="n">
+        <v>87.57886299883263</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>23.65073609951575</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-13623.49116949148</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-492.7044803178855</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.76960210774205e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.952351491373408</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>134.7570000000001</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8127340823970041</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1108.780302026609</v>
+      </c>
+      <c r="E25" t="n">
+        <v>2.678186817469823</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.28818e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-85.491</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1084492126329171</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.6216246200157268</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.787129843763723</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.417993202758161</v>
+      </c>
+      <c r="L25" t="n">
+        <v>32.79156716416851</v>
+      </c>
+      <c r="M25" t="n">
+        <v>87.83651041555267</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>26.47045134942096</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-14977.867423515</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-459.4804910563275</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.701795515197108e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9570047195353525</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>136.796</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8250315125416899</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1172.452782643009</v>
+      </c>
+      <c r="E26" t="n">
+        <v>2.831983559629437</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.28102e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-85.702</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.5128371948061642</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.270905694763022</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.320494709531284</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.145127283348575</v>
+      </c>
+      <c r="L26" t="n">
+        <v>36.66467659377618</v>
+      </c>
+      <c r="M26" t="n">
+        <v>88.08318252701439</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>29.8799458783788</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-16860.74281362224</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-520.3436286319436</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.662980667773361e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9596698304204523</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>130.842</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7891222927861909</v>
+      </c>
+      <c r="D27" t="n">
+        <v>364.3542089306175</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.880073931205361</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.27721e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-85.84699999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1422573560457784</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.072839873372846</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.155257463792059</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.689192494796274</v>
+      </c>
+      <c r="L27" t="n">
+        <v>39.15116107258653</v>
+      </c>
+      <c r="M27" t="n">
+        <v>88.146135370062</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>30.89534296018612</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-17204.99234994837</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>186.2301917329795</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.77985753477124e-09</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9951400002934712</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>128.361</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7741591127033236</v>
+      </c>
+      <c r="D28" t="n">
+        <v>361.725903551324</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.8737254302388098</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.27421e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-85.94799999999999</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.3380801083358004</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.101765365166823</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.186822727042977</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.972537064581535</v>
+      </c>
+      <c r="L28" t="n">
+        <v>41.36042981173465</v>
+      </c>
+      <c r="M28" t="n">
+        <v>88.22461016538058</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>32.26189514937747</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-17826.12717549497</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>182.1945800310474</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.659087494380763e-09</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9983705640396385</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>123.628</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7456138763743387</v>
+      </c>
+      <c r="D29" t="n">
+        <v>360.3055560539425</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.8702946730935389</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.27209e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-86.026</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.07073546241606062</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.7628891307913273</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.919110813184661</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.625164154394543</v>
+      </c>
+      <c r="L29" t="n">
+        <v>42.61115366685323</v>
+      </c>
+      <c r="M29" t="n">
+        <v>88.22980484370761</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>32.35662896061542</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-17662.87811060166</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>179.708627663903</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.658177559920032e-09</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.998557778743852</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>122.629</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7395887990253726</v>
+      </c>
+      <c r="D30" t="n">
+        <v>359.4847179813507</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8683119920328505</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.27064e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-86.09999999999999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.10520214565025</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.8956999781879786</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.053744069667137</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.642056169251668</v>
+      </c>
+      <c r="L30" t="n">
+        <v>44.38049495350964</v>
+      </c>
+      <c r="M30" t="n">
+        <v>88.28871311541049</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>33.4711506743183</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-18142.0077608619</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>175.4761608350891</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.621789286448239e-09</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9992237386601405</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>118.23</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7130579529211675</v>
+      </c>
+      <c r="D31" t="n">
+        <v>360.5954560556953</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.8709949077222203</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.26921e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-86.16500000000001</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.1293459264094534</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.6908941506051539</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.825486447114681</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.554737399297384</v>
+      </c>
+      <c r="L31" t="n">
+        <v>45.70796032381075</v>
+      </c>
+      <c r="M31" t="n">
+        <v>88.29553731921057</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>33.60523960628514</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-18028.23479334352</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>169.1649976113479</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.574113944588705e-09</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9997629101886834</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>118.027</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.7118336379043106</v>
+      </c>
+      <c r="D32" t="n">
+        <v>379.8842276356633</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.9175856828976409</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.26801e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-86.223</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1071733257497104</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.794890130587134</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.867954467227979</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.483286109589747</v>
+      </c>
+      <c r="L32" t="n">
+        <v>46.86128319522583</v>
+      </c>
+      <c r="M32" t="n">
+        <v>88.35670680541432</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>34.85687671376026</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-18594.15966303758</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>147.0602344502924</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.461394305989511e-09</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9997644115143904</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>117.991</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.711616517999843</v>
+      </c>
+      <c r="D33" t="n">
+        <v>365.6531741064249</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8832114972352058</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.26742e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-86.271</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.2706083490681295</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.091031177201525</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.234953854333868</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.763714525688878</v>
+      </c>
+      <c r="L33" t="n">
+        <v>48.18520150771418</v>
+      </c>
+      <c r="M33" t="n">
+        <v>88.42310230508649</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>36.32531931398978</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-19294.28177003079</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>162.119251806383</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.618963278208631e-09</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9993238787887065</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>115.196</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6947595698613449</v>
+      </c>
+      <c r="D34" t="n">
+        <v>364.2902465569415</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.879919434245341</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.26635e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-86.316</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.3267298175510797</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.014292689819402</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.134192927024096</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.937175823566062</v>
+      </c>
+      <c r="L34" t="n">
+        <v>49.60921218783606</v>
+      </c>
+      <c r="M34" t="n">
+        <v>88.4329419493239</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>36.55352286501222</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-19260.95894229419</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>155.4021135301599</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.598008428672112e-09</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9972625943331045</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>113.675</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6855862538976039</v>
+      </c>
+      <c r="D35" t="n">
+        <v>360.9394217507477</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.8718257345221438</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.26562e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-86.355</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.3094855945849919</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.068789551178543</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.338753151420487</v>
+      </c>
+      <c r="K35" t="n">
+        <v>4.243791745242246</v>
+      </c>
+      <c r="L35" t="n">
+        <v>50.42886630235844</v>
+      </c>
+      <c r="M35" t="n">
+        <v>88.45874035630399</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>37.16567749678064</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-19448.23039167188</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>159.8609034772183</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.620884818143401e-09</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.999657152049834</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>109.821</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6623423619026938</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1310.17164268119</v>
+      </c>
+      <c r="E36" t="n">
+        <v>3.164634522851884</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.26515e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-86.39</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.7983451849352146</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.740528127336466</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.255942271477679</v>
+      </c>
+      <c r="L36" t="n">
+        <v>50.34829654686414</v>
+      </c>
+      <c r="M36" t="n">
+        <v>88.41744094016497</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>36.19530523381967</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-18725.89809953444</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-680.0856257211083</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.552128336099687e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9683037781995539</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>109.083</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6578914038611154</v>
+      </c>
+      <c r="D37" t="n">
+        <v>357.455156919874</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.8634097190846729</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.2646e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-86.42700000000001</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.1279106318375822</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.5754525880817078</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.784440624225103</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.448260582828453</v>
+      </c>
+      <c r="L37" t="n">
+        <v>51.22309445809199</v>
+      </c>
+      <c r="M37" t="n">
+        <v>88.44132740436413</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>36.75027388639614</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-18886.9408467312</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>155.3060580298089</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>1.592429105673855e-09</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9998788060934622</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>108.769</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6559976358054846</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1686.799351860961</v>
+      </c>
+      <c r="E38" t="n">
+        <v>4.074354296891406</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.26394e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-86.45699999999999</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.253654714929808</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.022723335436528</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.224548951030416</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.765334561674507</v>
+      </c>
+      <c r="L38" t="n">
+        <v>52.19987647105145</v>
+      </c>
+      <c r="M38" t="n">
+        <v>88.50440518869166</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>38.30099254929406</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-19615.42122235966</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-1010.124692960563</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.540925058369769e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9692702804163457</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>107.908</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.6508048514236432</v>
+      </c>
+      <c r="D39" t="n">
+        <v>359.6806356247288</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.8687852183779124</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.26374e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-86.492</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.2159049786653465</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.9761446982641432</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.940968751994782</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.722405636825479</v>
+      </c>
+      <c r="L39" t="n">
+        <v>52.83708057919942</v>
+      </c>
+      <c r="M39" t="n">
+        <v>88.51765224689362</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>38.64342569425023</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-19647.01006491083</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>147.7487558954327</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.585822963342831e-09</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.999762124523032</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>105.775</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.6379404970839588</v>
+      </c>
+      <c r="D40" t="n">
+        <v>414.4256517422324</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1.001018249772939</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.2638e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-86.536</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.2534787236025289</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.9834675489087685</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.268755383824328</v>
+      </c>
+      <c r="K40" t="n">
+        <v>4.316719300911866</v>
+      </c>
+      <c r="L40" t="n">
+        <v>54.80611539971656</v>
+      </c>
+      <c r="M40" t="n">
+        <v>88.53705771774206</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>39.15624593465425</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-19761.71601802037</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>87.4178716251028</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.244172958466301e-09</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9998959769898075</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>105.679</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.6373615106720462</v>
+      </c>
+      <c r="D41" t="n">
+        <v>349.3781885964166</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.8439003266022606</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.26328e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-86.56100000000001</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.3066626449590391</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.18561329762216</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.338480945484351</v>
+      </c>
+      <c r="K41" t="n">
+        <v>4.341233181403069</v>
+      </c>
+      <c r="L41" t="n">
+        <v>55.10881030534473</v>
+      </c>
+      <c r="M41" t="n">
+        <v>88.58152449431284</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>40.38425269964616</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-20289.56991448857</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>153.0329735797137</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.663033947114978e-09</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9997921721343725</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>104.663</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.6312339044793039</v>
+      </c>
+      <c r="D42" t="n">
+        <v>357.9719608736819</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.8646580254748341</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.2629e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-86.595</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.3668393158147265</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.127873434860789</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.474121194570248</v>
+      </c>
+      <c r="K42" t="n">
+        <v>4.076683365692913</v>
+      </c>
+      <c r="L42" t="n">
+        <v>55.83818631662398</v>
+      </c>
+      <c r="M42" t="n">
+        <v>88.59181697158111</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>40.67954334462346</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-20282.43814255865</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>142.9114691891614</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.641513227281714e-09</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9992051954558074</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>100.023</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.6032495612368595</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1521.927201449653</v>
+      </c>
+      <c r="E43" t="n">
+        <v>3.676116324055494</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.26279e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-86.629</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1438473665939159</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.7442005041494888</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.933264284410188</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.81839016743388</v>
+      </c>
+      <c r="L43" t="n">
+        <v>56.5397844351407</v>
+      </c>
+      <c r="M43" t="n">
+        <v>88.54693039657742</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>39.42240286257832</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-19417.87201350284</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-886.091361108953</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.770970618415128e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9999999992224516</v>
       </c>
     </row>
@@ -7898,7 +14282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8600,6 +14984,566 @@
         <v>6.490921521726114e-09</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.9602576625502314</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>166.581</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>404.3320718098353</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.3844e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-81.483</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.3382322657692987</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.157843625984063</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.422606508382946</v>
+      </c>
+      <c r="L12" t="n">
+        <v>10.68008110400516</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.19640999586274</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.838684912765187</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-5797.629448077008</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>148.4292158319404</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1.252037515929684e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9992855523359402</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>117.392</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.7047142231106788</v>
+      </c>
+      <c r="D13" t="n">
+        <v>294.5764904548918</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.7285508892142408</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.37784e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-83.21899999999999</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2654812877297626</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.9215643634608963</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.669345070026846</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.068149414999698</v>
+      </c>
+      <c r="L13" t="n">
+        <v>14.11268588153117</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.68961848328014</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>13.26742145290707</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-6922.350553473259</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>238.2144132704892</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.532878154468126e-09</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9957915875042469</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>107.657</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6462741849310547</v>
+      </c>
+      <c r="D14" t="n">
+        <v>302.4745540300998</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.748084495687394</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.35504e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-84.16500000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4100689592596045</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.298320342097948</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.284799040593863</v>
+      </c>
+      <c r="K14" t="n">
+        <v>4.042781692325867</v>
+      </c>
+      <c r="L14" t="n">
+        <v>17.73830282654147</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.52767524266713</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>16.48049111772875</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-8366.976392895383</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>210.4866539793753</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.109995681099472e-09</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9995508895713295</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97.62200000000001</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5860332210756329</v>
+      </c>
+      <c r="D15" t="n">
+        <v>298.5956499805025</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.7384911333992259</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.33706e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-84.77800000000001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.4899967867846697</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.735179536800184</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.193156145591488</v>
+      </c>
+      <c r="L15" t="n">
+        <v>21.1798942205214</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.97704545282109</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>18.93597953363713</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-9391.427589237817</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>214.3842709554947</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.272773849791348e-09</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9997248935604036</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>96.35000000000002</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5783972962102522</v>
+      </c>
+      <c r="D16" t="n">
+        <v>345.7051231260724</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.855002972132925</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.32416e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-85.18600000000001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.141345512817076</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8190931707101601</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.756938166500427</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.386988568805672</v>
+      </c>
+      <c r="L16" t="n">
+        <v>24.36108710288901</v>
+      </c>
+      <c r="M16" t="n">
+        <v>87.33710315743693</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>21.50084027900747</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-10553.16174262014</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>151.9046922913789</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.662832061621077e-09</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9995497282560616</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>93.50099999999998</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.561294505375763</v>
+      </c>
+      <c r="D17" t="n">
+        <v>343.9501886324593</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8506626424485698</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.31483e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-85.47499999999999</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.3439401604466351</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8657656126410932</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.875856121602542</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.537895632568991</v>
+      </c>
+      <c r="L17" t="n">
+        <v>27.13202657744137</v>
+      </c>
+      <c r="M17" t="n">
+        <v>87.59032332998324</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>23.76335180213213</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-11536.42873129448</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>149.2830536445382</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.69931760819661e-09</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.999081174276963</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92.28800000000001</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5540127625599558</v>
+      </c>
+      <c r="D18" t="n">
+        <v>346.5359663012102</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.8570578256384083</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.30793e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-85.732</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.4604850833243131</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.109914848374851</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.308342263894427</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.920045801734132</v>
+      </c>
+      <c r="L18" t="n">
+        <v>30.35279066342608</v>
+      </c>
+      <c r="M18" t="n">
+        <v>87.8143050160608</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>26.2012697335072</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-12587.04489751725</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>134.1021042588505</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1.535031157389176e-09</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9996746292223634</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>87.86500000000001</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5274611150131168</v>
+      </c>
+      <c r="D19" t="n">
+        <v>362.695621646991</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.8970241218400634</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.30247e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-85.902</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2999307877428217</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9800893598861788</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.119079371528126</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.908558183588118</v>
+      </c>
+      <c r="L19" t="n">
+        <v>32.53982992533621</v>
+      </c>
+      <c r="M19" t="n">
+        <v>87.9145297638772</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>27.46166008361796</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-12987.06484830528</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>119.791012806693</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1.591583344770426e-09</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.998834397329377</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>85.19400000000002</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.5114268734129342</v>
+      </c>
+      <c r="D20" t="n">
+        <v>345.2910818316124</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8539789591413097</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.29801e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-86.053</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.411238113829507</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9952827532781753</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.028326472117302</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.894566949310097</v>
+      </c>
+      <c r="L20" t="n">
+        <v>34.76397741326362</v>
+      </c>
+      <c r="M20" t="n">
+        <v>88.02824320657038</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>29.04676655345619</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-13563.95959294808</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>136.1326477951614</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.71731802437612e-09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9997618026992423</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>83.67599999999999</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.5023141894933995</v>
+      </c>
+      <c r="D21" t="n">
+        <v>234.972352216596</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.5811370618334422</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.29497e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-86.179</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.5134694490528923</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.109108059572474</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.039385633766229</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.713173305765208</v>
+      </c>
+      <c r="L21" t="n">
+        <v>36.67342717835749</v>
+      </c>
+      <c r="M21" t="n">
+        <v>88.1294758376914</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>30.61998538944753</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-14140.52357055255</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>264.5787946923299</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>6.490921521726114e-09</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.9602576625502314</v>
       </c>
     </row>
@@ -8614,7 +15558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9932,6 +16876,1182 @@
         <v>2.03410439754182e-09</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9997936615059234</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>166.4859999999999</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>1472.50235988201</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.33147e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-84.33799999999999</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3258577084993483</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.9520017987766776</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.855944644003308</v>
+      </c>
+      <c r="K23" t="n">
+        <v>3.316435731796127</v>
+      </c>
+      <c r="L23" t="n">
+        <v>21.96761367783734</v>
+      </c>
+      <c r="M23" t="n">
+        <v>86.99143406142086</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>19.02670963092257</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-11445.01442247303</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-714.0202079607252</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.019861976126505e-07</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.9992221911964151</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>146.001</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8769566209771394</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1141.33967297112</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.7751021010673114</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.30999e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-85.217</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3293039216451865</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.033546965194124</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.002769489833849</v>
+      </c>
+      <c r="K24" t="n">
+        <v>3.413611935319827</v>
+      </c>
+      <c r="L24" t="n">
+        <v>29.733003271023</v>
+      </c>
+      <c r="M24" t="n">
+        <v>87.69798119081817</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>24.87596797356468</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-14334.55366853595</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-476.4763834765448</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.958769300755683e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9998564064757421</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>136.545</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8201590524128156</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1085.690279108806</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.7373097040033275</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.29836e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-85.58499999999999</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.04455474984218243</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.7565947237361847</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.866204306430255</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.614826827480504</v>
+      </c>
+      <c r="L25" t="n">
+        <v>35.2788430528721</v>
+      </c>
+      <c r="M25" t="n">
+        <v>87.93297297251844</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>27.70690446285733</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-15655.2204556749</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-440.3596826788238</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.702237719215283e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9581560383515961</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>135.524</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8140264046226112</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1097.818199350854</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.7455459694059986</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1.29139e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-85.819</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.4013141461522192</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.107291610322234</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.302745424725117</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.608208940133158</v>
+      </c>
+      <c r="L26" t="n">
+        <v>39.78538437699773</v>
+      </c>
+      <c r="M26" t="n">
+        <v>88.1673149802655</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>31.2526360170059</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-17552.9021772235</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-456.6087542331966</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.66218556101196e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.96095755194495</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>129.4109999999999</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7773086025251372</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1116.020011588132</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.7579071124052782</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.28691e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-85.967</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.03479645903504334</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8812153160969424</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.872818297105591</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.67302559839973</v>
+      </c>
+      <c r="L27" t="n">
+        <v>42.98167512642116</v>
+      </c>
+      <c r="M27" t="n">
+        <v>88.20694045728443</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>31.94376564284343</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-17665.17301877854</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-478.1485188471826</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.636272364173152e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9628296080854974</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>129.4039999999999</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7772665569477313</v>
+      </c>
+      <c r="D28" t="n">
+        <v>594.5652092781086</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.4037787819407981</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1.2844e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-86.069</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.3528049734544864</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.165020149584014</v>
+      </c>
+      <c r="J28" t="n">
+        <v>2.21839936886128</v>
+      </c>
+      <c r="K28" t="n">
+        <v>3.66548990642041</v>
+      </c>
+      <c r="L28" t="n">
+        <v>45.31578484970868</v>
+      </c>
+      <c r="M28" t="n">
+        <v>88.34535717654239</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>34.61765263849517</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-19045.01738430858</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0.2571159343816903</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>6.641213540798994e-09</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8519416848297341</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>126.652</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7607366385161517</v>
+      </c>
+      <c r="D29" t="n">
+        <v>550.2742942820371</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.3737001102844617</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1.28249e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-86.137</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.272422507264124</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.309936203944573</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.236105257702661</v>
+      </c>
+      <c r="K29" t="n">
+        <v>4.210769440082148</v>
+      </c>
+      <c r="L29" t="n">
+        <v>46.91691415303764</v>
+      </c>
+      <c r="M29" t="n">
+        <v>88.36962109374078</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>35.13313012917322</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-19086.18945467061</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0.4077057123426893</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1.759147354261444e-09</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9507903998134069</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>120.405</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7232139639369081</v>
+      </c>
+      <c r="D30" t="n">
+        <v>398.8744070248752</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.2708820154670833</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.28111e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-86.21899999999999</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.1506620635191318</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.8463571645583284</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.967692609759312</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.596630110209516</v>
+      </c>
+      <c r="L30" t="n">
+        <v>48.36515225953097</v>
+      </c>
+      <c r="M30" t="n">
+        <v>88.36376478389015</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>35.00731581978029</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-18740.19042748851</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>129.5817820809572</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1.472023397813351e-09</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9958554328797904</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>118.8390000000001</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7138077676201008</v>
+      </c>
+      <c r="D31" t="n">
+        <v>393.116402330824</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.2669716620096446</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1.2803e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-86.28700000000001</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.2225815255348992</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.9682392106775048</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.990809095765928</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.619191134727895</v>
+      </c>
+      <c r="L31" t="n">
+        <v>50.35375143179193</v>
+      </c>
+      <c r="M31" t="n">
+        <v>88.41430249651171</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>36.12363028953727</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-19162.2325878878</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>128.673380255507</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1.372333451546971e-09</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9997212604565566</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>115.681</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6948392056989778</v>
+      </c>
+      <c r="D32" t="n">
+        <v>620.6916234897556</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.4215216494046848</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1.27948e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-86.35899999999999</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.2162050347754862</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.165015622510612</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.012037859329955</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.825982988594146</v>
+      </c>
+      <c r="L32" t="n">
+        <v>52.35326364388573</v>
+      </c>
+      <c r="M32" t="n">
+        <v>88.46027909897302</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>37.20283747653777</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-19537.47587190667</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.59935571906165</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.111021994886208e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.6554324845435642</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>112.958</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6784834760880799</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1245.978575039738</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.8461640598929685</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1.27892e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-86.398</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.2130842364610746</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.9223338840492973</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.020537080491285</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.87030527589662</v>
+      </c>
+      <c r="L33" t="n">
+        <v>53.17769611302881</v>
+      </c>
+      <c r="M33" t="n">
+        <v>88.45790751371491</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>37.14559562717868</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-19293.52170483638</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-622.7664653043203</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>1.568592973788237e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9683443735731847</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>111.177</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6677858798938052</v>
+      </c>
+      <c r="D34" t="n">
+        <v>367.3423829029809</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.2494681115026639</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1.27846e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-86.446</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.8189507774767394</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.082851587733845</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.859974788990074</v>
+      </c>
+      <c r="L34" t="n">
+        <v>54.20515290736561</v>
+      </c>
+      <c r="M34" t="n">
+        <v>88.48120916935508</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>37.71576555712016</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-19418.17589975747</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>151.7880940752743</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>1.687818891438429e-09</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9979133880889888</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>108.74</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6531480124454913</v>
+      </c>
+      <c r="D35" t="n">
+        <v>309.5668579508043</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.2102318246713096</v>
+      </c>
+      <c r="F35" t="n">
+        <v>1.27794e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-86.485</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.1562899414167817</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.9193115289736362</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.038768073066207</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.858321619859296</v>
+      </c>
+      <c r="L35" t="n">
+        <v>55.19783926016496</v>
+      </c>
+      <c r="M35" t="n">
+        <v>88.50555168438382</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>38.33038926246649</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-19580.67726198515</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>207.0516635665244</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>2.215911411159566e-09</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9948460541378944</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>108.625</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6524572636738227</v>
+      </c>
+      <c r="D36" t="n">
+        <v>307.3757665849507</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.208743819337295</v>
+      </c>
+      <c r="F36" t="n">
+        <v>1.27743e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-86.523</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3537218889199849</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.9495326202037344</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.085128330697852</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.908830738010967</v>
+      </c>
+      <c r="L36" t="n">
+        <v>56.12994823689989</v>
+      </c>
+      <c r="M36" t="n">
+        <v>88.56203744312006</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>39.83674618757358</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-20255.00593051117</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>212.0688987468131</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.615966517767903e-09</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9888421305492039</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>109.842</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6597671876313926</v>
+      </c>
+      <c r="D37" t="n">
+        <v>305.2206543385009</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.2072802480010681</v>
+      </c>
+      <c r="F37" t="n">
+        <v>1.27717e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-86.559</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.7574180232765471</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.407892515069325</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.52556589879231</v>
+      </c>
+      <c r="K37" t="n">
+        <v>4.475928413108665</v>
+      </c>
+      <c r="L37" t="n">
+        <v>57.49036305754034</v>
+      </c>
+      <c r="M37" t="n">
+        <v>88.63150128014676</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>41.85965454286513</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-21207.89974175621</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>210.339643834722</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.584248806067236e-09</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9900960216006117</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>108.27</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6503249522482373</v>
+      </c>
+      <c r="D38" t="n">
+        <v>303.1286136865223</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.2058595095975342</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1.27683e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-86.58799999999999</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.5542309681581681</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.422936979236153</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.525252422402946</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.539571968238964</v>
+      </c>
+      <c r="L38" t="n">
+        <v>58.07758416564766</v>
+      </c>
+      <c r="M38" t="n">
+        <v>88.64734493622599</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>42.35014234586185</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-21310.61041361716</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>209.7022868340541</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.605477537594034e-09</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9902372347211755</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>105.467</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.6334887017527001</v>
+      </c>
+      <c r="D39" t="n">
+        <v>301.4235780149083</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.2047015924912073</v>
+      </c>
+      <c r="F39" t="n">
+        <v>1.27651e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-86.629</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.5209003317724171</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.283280774650653</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.399450948407695</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4.314842577668829</v>
+      </c>
+      <c r="L39" t="n">
+        <v>59.44820497917339</v>
+      </c>
+      <c r="M39" t="n">
+        <v>88.64176660387149</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>42.17614341893815</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-21027.09218341374</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>202.4852962395396</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2.183936192804692e-09</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9997051182009625</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>104.166</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.6256742308662593</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1426.613731653973</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.9688362956296287</v>
+      </c>
+      <c r="F40" t="n">
+        <v>1.27623e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-86.649</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.4068267615120338</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.237068690615623</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.266937673015637</v>
+      </c>
+      <c r="K40" t="n">
+        <v>4.345863648322625</v>
+      </c>
+      <c r="L40" t="n">
+        <v>59.41282454077522</v>
+      </c>
+      <c r="M40" t="n">
+        <v>88.6415447618203</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>42.16925327755298</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-20863.32448287797</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-803.5893940639592</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1.840020828968935e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9999916004944329</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>100.913</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.6061350503946281</v>
+      </c>
+      <c r="D41" t="n">
+        <v>353.5165311931254</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.2400787535725596</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.27607e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-86.673</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.3695311121514252</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.038505783191453</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.271131201469705</v>
+      </c>
+      <c r="K41" t="n">
+        <v>4.40071741080645</v>
+      </c>
+      <c r="L41" t="n">
+        <v>59.78483602410884</v>
+      </c>
+      <c r="M41" t="n">
+        <v>88.62503337343971</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>41.66266970249227</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-20423.78777180623</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>144.1287471073647</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.778777094515884e-09</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9970484771061782</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99.524</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5977920065350842</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1514.948745984391</v>
+      </c>
+      <c r="E42" t="n">
+        <v>1.02882602246273</v>
+      </c>
+      <c r="F42" t="n">
+        <v>1.27591e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-86.708</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.2545535526063741</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.120415397779185</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.193693232619549</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.778796737428401</v>
+      </c>
+      <c r="L42" t="n">
+        <v>60.36278398469429</v>
+      </c>
+      <c r="M42" t="n">
+        <v>88.65168799164165</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>42.48660724714126</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-20697.07563756706</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-886.3615875207115</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.830018224121077e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9999761710090245</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>97.82099999999997</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5875629182033325</v>
+      </c>
+      <c r="D43" t="n">
+        <v>295.4112886054764</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.200618550199911</v>
+      </c>
+      <c r="F43" t="n">
+        <v>1.27573e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-86.736</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.1190667162621253</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.8753615421750344</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.953911778508747</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.734256223231199</v>
+      </c>
+      <c r="L43" t="n">
+        <v>61.13808275216898</v>
+      </c>
+      <c r="M43" t="n">
+        <v>88.63309405342189</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>41.90844962525627</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-20228.36187724904</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>188.6350441371038</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>2.03410439754182e-09</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9997936615059234</v>
       </c>
     </row>
@@ -9946,7 +18066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10651,6 +18771,566 @@
         <v>0.9998693732407529</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>140.1929999999999</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>290.7104328277486</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.40223e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-82.286</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.06162012762814157</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.439228780333837</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.195203042418833</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.32066092744001</v>
+      </c>
+      <c r="L12" t="n">
+        <v>12.01798818002055</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.8139623061827</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>11.01789625690584</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-6003.296112035475</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>241.2914604789362</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.351000553219934e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.99809717431954</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>96.63299999999998</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6892854850099508</v>
+      </c>
+      <c r="D13" t="n">
+        <v>273.1628915765251</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9396391072706333</v>
+      </c>
+      <c r="F13" t="n">
+        <v>1.37618e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-84.377</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.1849950104960643</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.8423112625826841</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.833908928148588</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.162219921272718</v>
+      </c>
+      <c r="L13" t="n">
+        <v>18.50798644541923</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.62458325486665</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>16.9547893359629</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-8212.592004588181</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>217.6869903485797</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.363706679182493e-09</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.9984376972006724</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>87.56</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6245675604345442</v>
+      </c>
+      <c r="D14" t="n">
+        <v>359.4195212867166</v>
+      </c>
+      <c r="E14" t="n">
+        <v>1.23634889119951</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1.35242e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-85.26000000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3405918299855741</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.073089468789402</v>
+      </c>
+      <c r="J14" t="n">
+        <v>2.042218242309757</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.574660683794903</v>
+      </c>
+      <c r="L14" t="n">
+        <v>24.60534947919054</v>
+      </c>
+      <c r="M14" t="n">
+        <v>87.3890273612713</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>21.92903611373315</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-10330.03164878563</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>125.1752651378661</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.891637176522678e-09</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9870288683449935</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>82.64600000000002</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5895158816774023</v>
+      </c>
+      <c r="D15" t="n">
+        <v>266.2244502090098</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9157719164717862</v>
+      </c>
+      <c r="F15" t="n">
+        <v>1.33778e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-85.744</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2967348996549194</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.851350060147066</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.893777366735887</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.419631047145218</v>
+      </c>
+      <c r="L15" t="n">
+        <v>30.0053737842962</v>
+      </c>
+      <c r="M15" t="n">
+        <v>87.77139012119497</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>25.6962342498526</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-11897.86760157973</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>210.8079988923757</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.71065622785568e-09</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9944119982537603</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>81.23000000000002</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5794155200330977</v>
+      </c>
+      <c r="D16" t="n">
+        <v>445.7358690001405</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.533264096043802</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.32853e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-86.042</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.6226230013620048</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.121965273119605</v>
+      </c>
+      <c r="J16" t="n">
+        <v>2.254890971691287</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.926950469623697</v>
+      </c>
+      <c r="L16" t="n">
+        <v>34.62174111700075</v>
+      </c>
+      <c r="M16" t="n">
+        <v>88.03533260284908</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>29.15166289375034</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-13355.92669654902</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>17.29584377290938</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.052174146632629e-09</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9999966444284676</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>76.25400000000002</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5439215938028293</v>
+      </c>
+      <c r="D17" t="n">
+        <v>271.8650139462728</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9351746041648182</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1.32323e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-86.236</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1877202104371021</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.818183521928777</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.940188897509272</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.589569572338323</v>
+      </c>
+      <c r="L17" t="n">
+        <v>38.06080787104456</v>
+      </c>
+      <c r="M17" t="n">
+        <v>88.13283198947201</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>30.67506254791456</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-13800.84145847396</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>200.0360906456226</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.572314866208271e-09</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9981223894639772</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>75.06899999999996</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5354689606471079</v>
+      </c>
+      <c r="D18" t="n">
+        <v>220.5640514843933</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7587070382681508</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.31977e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-86.39</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.4209796303226168</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.192217601717408</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.251904411361157</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.924028481412031</v>
+      </c>
+      <c r="L18" t="n">
+        <v>41.41661017260304</v>
+      </c>
+      <c r="M18" t="n">
+        <v>88.27693489298296</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>33.24221793349674</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-14793.3004948806</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>262.9673839965514</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>5.897920943673502e-09</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9725499111517852</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>73.928</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5273301805368317</v>
+      </c>
+      <c r="D19" t="n">
+        <v>216.7721207317109</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7456633689515796</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.31771e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-86.495</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.6791812691234488</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.466788809007914</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.400432718480625</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.196222456706882</v>
+      </c>
+      <c r="L19" t="n">
+        <v>43.57931849112421</v>
+      </c>
+      <c r="M19" t="n">
+        <v>88.37610270270885</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>35.2734357622226</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-15514.39383203477</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>261.968425104891</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>6.599944264409463e-09</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9670229222973675</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>69.96699999999998</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4990762734230669</v>
+      </c>
+      <c r="D20" t="n">
+        <v>216.7103555970839</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7454509062132243</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.31646e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-86.59999999999999</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.4905549652338899</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9134199675749795</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.298762745894673</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.896246123998786</v>
+      </c>
+      <c r="L20" t="n">
+        <v>46.25133121667332</v>
+      </c>
+      <c r="M20" t="n">
+        <v>88.40072588932526</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>35.81681113464622</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-15488.91399378103</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>245.8683265861594</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.933825862081696e-09</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.997281391106552</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>69.30700000000002</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4943684777413997</v>
+      </c>
+      <c r="D21" t="n">
+        <v>211.1580227323518</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.7263517194013703</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.31534e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-86.676</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.6496682845579123</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.380142625163894</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.323237249056527</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.385269091674787</v>
+      </c>
+      <c r="L21" t="n">
+        <v>48.12029825382421</v>
+      </c>
+      <c r="M21" t="n">
+        <v>88.48310651177644</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>37.76296282865111</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-16175.81827169919</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>236.5059777795611</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.359406107966151e-09</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.9998693732407529</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
